--- a/generated/committee_recommendations.xlsx
+++ b/generated/committee_recommendations.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,65 +473,901 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>佐藤健</t>
+          <t>但木 陸</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>都市交通需要予測に対する時系列深層学習の適用</t>
+          <t>大学入試業務の人員配置最適化における数理モデルの改良</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>鈴木花子</t>
+          <t>高野祐一</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>山田太郎</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t>繁野麻衣子</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>吉瀬章子</t>
+        </is>
+      </c>
       <c r="F2" t="n">
-        <v>0.442595083489533</v>
+        <v>0.7990804751472282</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2112356007377654</v>
+        <v>0.7457407141319889</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>0.7436180316601839</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>田中葵</t>
+          <t>吉田 響</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>災害時避難行動データを用いた最適配置モデルの研究</t>
+          <t>社会工学・サービス工学学位プログラムにおける修士論文審査員の割り当て問題</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>鈴木花子</t>
+          <t>原田信行</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>山田太郎</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
+          <t>繁野麻衣子</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>秋山英三</t>
+        </is>
+      </c>
       <c r="F3" t="n">
-        <v>0.579686085202809</v>
+        <v>0.7645546623853985</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2974948991787114</v>
+        <v>0.7560855235494532</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>0.7519666255181408</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>金原 壮汰</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LiDARデータに基づく視線および姿勢情報統合による危険行動の動的検出システム〜荷役作業ケース</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>黒瀬雄大</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>木下陽平</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>岡田幸彦</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0.7730844708148208</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7492663532653359</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.7377681360832717</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>宍戸 唯輝</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>3階層サプライチェーンにおける協調的納期決定アルゴリズム</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>LiuTianxiang</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Phung-DucTuan</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>高野祐一</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0.7807969700848041</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.7802955162809034</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.7629236394713367</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>堤 敬信</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>閉鎖型待ち行列ネットワークモデルを用いたシェアサイクルの運用分析</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>秋山英三</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TranLamAnhDuong</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>佐野幸恵</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0.777475428793001</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.7589512752102814</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.7599317009143467</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>寺田 海渡</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>中小企業デフォルト予測における月次流動性預金残高特徴量の有効性検証</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>大久保正勝</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TranLamAnhDuong</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>原田信行</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0.793365402119634</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.7704139251473998</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.7705694203287918</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>益子 颯太</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>仕訳データの異常検知モデルの高度化：Data Collaboration解析と摘要欄の活用</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>黒瀬雄大</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>岡田幸彦</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>吉瀬章子</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>0.7940385736544479</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.7610796693064201</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.75741082965535</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>平井 佑樹</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>仕訳データを用いた利速測定の研究</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>大西正輝</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>黒瀬雄大</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>小西葉子</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0.7926388773523594</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.7877466609819869</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.7493271465883786</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>飯田 真実</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>HPVワクチン接種に対する意見の変遷とその要因</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>大西正輝</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LiuTianxiang</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>佐野幸恵</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>0.7691184801505473</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.7682644978240212</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.7133311424561222</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>川井 貫太朗</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SNSを用いた労働者の集団感情分析</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>佐野幸恵</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TranLamAnhDuong</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>秋山英三</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>0.7986562750682954</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.7927969203779757</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.7810778899836618</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>冨樫 歩大</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>テキスト情報と財務情報の統合による中小企業の将来性予測</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>原田信行</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TranLamAnhDuong</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>岡田幸彦</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0.7900498149708934</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.7786515345644294</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.725379641877675</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>出口 達也</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>地域要因を用いた慢性腎臓病患者の悪化予測の研究</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>TranLamAnhDuong</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>大久保正勝</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>岡田幸彦</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0.8140611779324148</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.7479848455984035</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.7371903975067992</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>長谷川 弘貴</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>生体情報とテンソルデータ解析によるコンサート満足度の研究</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>岡本直久</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>黒瀬雄大</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>讃井知</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0.7821082462268162</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.7676686179623895</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.7572288631246638</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>中山 友琉</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>特異値分解を用いた効率的な分散データファインチューニング手法の提案</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>黒瀬雄大</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>繁野麻衣子</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>高野祐一</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0.7824792788319687</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.7662843099258541</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.7643935545360966</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>齋藤 彩</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>地域愛着の規定因に関する実証分析：つながりの影響の検討</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>讃井知</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>岡本直久</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>小西葉子</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0.7914804368112953</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.7809460412806564</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.7260086165237314</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>李 宗晟</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>エラスティック光ネットワークにおける通信要求の保持時間を考慮した予約種別リソース割り当て戦略の提案</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Phung-DucTuan</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LiuTianxiang</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>張勇兵</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0.7838991994343767</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.7700758577991739</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.7349688599838846</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>澤口 瑛都</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>列生成法を軸とした電気バスの仕業編成最適化</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>高野祐一</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>繁野麻衣子</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>吉瀬章子</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>0.8087958270757369</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.7325343050318592</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.7298264185003422</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>中本 武志</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>大規模言語モデルを活用した非専門家による継続運用可能な勤務表作成手法の検討</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Phung-DucTuan</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>黒瀬雄大</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>有馬澄佳</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>0.8145593294894845</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.6931889628284444</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.6843139670630791</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>髙橋 優介</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>重量・近接規制を考慮した異種ドローン経路問題：規制による配送時間・コストへの影響分析</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>高野祐一</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>秋山英三</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>髙橋裕紀</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>0.7922602110802039</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.7447926232143768</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.7327941651160159</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>鈴木 颯斗</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>最適多分木を用いた解釈可能なクラスタリング</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>高野祐一</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>吉瀬章子</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>八森正泰</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>0.8031707666476058</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.7521326585034569</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.7488486792745004</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>佐川 翼</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>社会工学・サービス工学学位プログラムにおける修士論文発表会スケジューリングシステムの開発</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>佐野幸恵</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>秋山英三</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>繁野麻衣子</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>0.7747239808897584</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.7675358273173142</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.750361214367077</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>加田 昌杜</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>学年暦の自動生成 〜曜日変更最小化モデルとその修正の自動化〜</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>高野祐一</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>繁野麻衣子</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>吉瀬章子</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>0.7861770081289896</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.7544270065638702</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.7540988778190654</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>八角 朋樹</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>機械学習モデルと特徴量選択によるファミリーレストラン店舗別売上予測方法の検討</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>高野祐一</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>繁野麻衣子</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>小西葉子</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>0.783767485062085</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.7504054209416953</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.7363430054106848</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>山下 穂乃花</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Continual Learning by Null Space of Weight Matrix of Previous Task for Deep Neural Network</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>繁野麻衣子</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>張勇兵</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>八森正泰</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>0.8210970053065357</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.7549542035323578</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.75543937381531</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>崔 涵喬</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>観光客のセグメンテーションとマーケティングへの応用可能性に関する研究</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>岡本直久</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>秋山英三</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>小西葉子</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>0.814169194661074</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.7201431580307053</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.7087410383921012</v>
       </c>
     </row>
   </sheetData>

--- a/generated/committee_recommendations.xlsx
+++ b/generated/committee_recommendations.xlsx
@@ -497,13 +497,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.7990804751472282</v>
+        <v>0.7990804274635125</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7457407141319889</v>
+        <v>0.7457402581648052</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7436180316601839</v>
+        <v>0.7436177763005982</v>
       </c>
     </row>
     <row r="3">
@@ -533,13 +533,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.7645546623853985</v>
+        <v>0.7645543882040327</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7560855235494532</v>
+        <v>0.7560853040622968</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7519666255181408</v>
+        <v>0.7519664923645055</v>
       </c>
     </row>
     <row r="4">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.7730844708148208</v>
+        <v>0.7730841042462554</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7492663532653359</v>
+        <v>0.7492674908878771</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7377681360832717</v>
+        <v>0.7377690010942336</v>
       </c>
     </row>
     <row r="5">
@@ -605,13 +605,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.7807969700848041</v>
+        <v>0.7807967912708698</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7802955162809034</v>
+        <v>0.7802953974873792</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7629236394713367</v>
+        <v>0.7629234126410744</v>
       </c>
     </row>
     <row r="6">
@@ -641,13 +641,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.777475428793001</v>
+        <v>0.777475255939531</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7589512752102814</v>
+        <v>0.7589518741093517</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7599317009143467</v>
+        <v>0.7599318540748284</v>
       </c>
     </row>
     <row r="7">
@@ -677,13 +677,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.793365402119634</v>
+        <v>0.7933650683336233</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7704139251473998</v>
+        <v>0.7704144901022719</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7705694203287918</v>
+        <v>0.7705693880514656</v>
       </c>
     </row>
     <row r="8">
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.7940385736544479</v>
+        <v>0.7940382994730818</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7610796693064201</v>
+        <v>0.7610796382356125</v>
       </c>
       <c r="H8" t="n">
-        <v>0.75741082965535</v>
+        <v>0.7574106571633021</v>
       </c>
     </row>
     <row r="9">
@@ -749,13 +749,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.7926388773523594</v>
+        <v>0.7926386627756383</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7877466609819869</v>
+        <v>0.7877462265913011</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7493271465883786</v>
+        <v>0.7493271225600245</v>
       </c>
     </row>
     <row r="10">
@@ -785,13 +785,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.7691184801505473</v>
+        <v>0.7691182834552195</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7682644978240212</v>
+        <v>0.7682641227123544</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7133311424561222</v>
+        <v>0.7133301731439236</v>
       </c>
     </row>
     <row r="11">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.7986562750682954</v>
+        <v>0.7986562214241151</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7927969203779757</v>
+        <v>0.7927967786996586</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7810778899836618</v>
+        <v>0.7810777642715331</v>
       </c>
     </row>
     <row r="12">
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.7900498149708934</v>
+        <v>0.7900495735720822</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7786515345644294</v>
+        <v>0.7786514969208398</v>
       </c>
       <c r="H12" t="n">
-        <v>0.725379641877675</v>
+        <v>0.7253796473706519</v>
       </c>
     </row>
     <row r="13">
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.8140611779324148</v>
+        <v>0.8140611481300924</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7479848455984035</v>
+        <v>0.7479844665463535</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7371903975067992</v>
+        <v>0.7371900102257737</v>
       </c>
     </row>
     <row r="14">
@@ -929,13 +929,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.7821082462268162</v>
+        <v>0.782108156819849</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7676686179623895</v>
+        <v>0.7676688665050833</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7572288631246638</v>
+        <v>0.7572289475039931</v>
       </c>
     </row>
     <row r="15">
@@ -965,13 +965,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.7824792788319687</v>
+        <v>0.7824789212041</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7662843099258541</v>
+        <v>0.76628436598381</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7643935545360966</v>
+        <v>0.7643934909274448</v>
       </c>
     </row>
     <row r="16">
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.7914804368112953</v>
+        <v>0.7914803682659539</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7809460412806564</v>
+        <v>0.7809458850818162</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7260086165237314</v>
+        <v>0.7260085511688839</v>
       </c>
     </row>
     <row r="17">
@@ -1037,13 +1037,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0.7838991994343767</v>
+        <v>0.7838990802250871</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7700758577991739</v>
+        <v>0.7700759127212329</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7349688599838846</v>
+        <v>0.7349685150032662</v>
       </c>
     </row>
     <row r="18">
@@ -1073,13 +1073,13 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0.8087958270757369</v>
+        <v>0.8087957674710922</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7325343050318592</v>
+        <v>0.7325339222958936</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7298264185003422</v>
+        <v>0.7298260897893794</v>
       </c>
     </row>
     <row r="19">
@@ -1109,13 +1109,13 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0.8145593294894845</v>
+        <v>0.814559100011602</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6931889628284444</v>
+        <v>0.6931882855272998</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6843139670630791</v>
+        <v>0.6843139228665569</v>
       </c>
     </row>
     <row r="20">
@@ -1145,13 +1145,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0.7922602110802039</v>
+        <v>0.7922601157127722</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7447926232143768</v>
+        <v>0.7447926398263299</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7327941651160159</v>
+        <v>0.7327940278041978</v>
       </c>
     </row>
     <row r="21">
@@ -1181,13 +1181,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0.8031707666476058</v>
+        <v>0.803170656379013</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7521326585034569</v>
+        <v>0.7521329343305779</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7488486792745004</v>
+        <v>0.748848610248332</v>
       </c>
     </row>
     <row r="22">
@@ -1217,13 +1217,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0.7747239808897584</v>
+        <v>0.7747237871746628</v>
       </c>
       <c r="G22" t="n">
-        <v>0.7675358273173142</v>
+        <v>0.7675355400107383</v>
       </c>
       <c r="H22" t="n">
-        <v>0.750361214367077</v>
+        <v>0.7503609303117418</v>
       </c>
     </row>
     <row r="23">
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0.7861770081289896</v>
+        <v>0.7861768024929651</v>
       </c>
       <c r="G23" t="n">
-        <v>0.7544270065638702</v>
+        <v>0.7544270183052249</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7540988778190654</v>
+        <v>0.7540984845610337</v>
       </c>
     </row>
     <row r="24">
@@ -1289,13 +1289,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0.783767485062085</v>
+        <v>0.7837673479714021</v>
       </c>
       <c r="G24" t="n">
-        <v>0.7504054209416953</v>
+        <v>0.750405486413361</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7363430054106848</v>
+        <v>0.7363429784589886</v>
       </c>
     </row>
     <row r="25">
@@ -1325,13 +1325,13 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0.8210970053065357</v>
+        <v>0.8210967430460986</v>
       </c>
       <c r="G25" t="n">
-        <v>0.7549542035323578</v>
+        <v>0.7549537327645731</v>
       </c>
       <c r="H25" t="n">
-        <v>0.75543937381531</v>
+        <v>0.7554390257603816</v>
       </c>
     </row>
     <row r="26">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0.814169194661074</v>
+        <v>0.8141689771041204</v>
       </c>
       <c r="G26" t="n">
-        <v>0.7201431580307053</v>
+        <v>0.7201433013654972</v>
       </c>
       <c r="H26" t="n">
-        <v>0.7087410383921012</v>
+        <v>0.7087411805502536</v>
       </c>
     </row>
   </sheetData>

--- a/generated/committee_recommendations.xlsx
+++ b/generated/committee_recommendations.xlsx
@@ -497,13 +497,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.7990804274635125</v>
+        <v>0.7980324189169082</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7457402581648052</v>
+        <v>0.7476459495927925</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7436177763005982</v>
+        <v>0.745967923074087</v>
       </c>
     </row>
     <row r="3">
@@ -533,13 +533,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.7645543882040327</v>
+        <v>0.7646012657634985</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7560853040622968</v>
+        <v>0.7542134458195275</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7519664923645055</v>
+        <v>0.7485639766309413</v>
       </c>
     </row>
     <row r="4">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.7730841042462554</v>
+        <v>0.7730491480516837</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7492674908878771</v>
+        <v>0.749730500747122</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7377690010942336</v>
+        <v>0.7382624589564942</v>
       </c>
     </row>
     <row r="5">
@@ -591,27 +591,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LiuTianxiang</t>
+          <t>Phung DucTuan</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Phung-DucTuan</t>
+          <t>高野祐一</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>高野祐一</t>
+          <t>有馬澄佳</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.7807967912708698</v>
+        <v>0.7948736779933087</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7802953974873792</v>
+        <v>0.7307908669503085</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7629234126410744</v>
+        <v>0.7273656892848034</v>
       </c>
     </row>
     <row r="6">
@@ -627,27 +627,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>Phung DucTuan</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>秋山英三</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>TranLamAnhDuong</t>
-        </is>
-      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>佐野幸恵</t>
+          <t>Tran Lam Anh Duong</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.777475255939531</v>
+        <v>0.7806034182445172</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7589518741093517</v>
+        <v>0.7666447199205355</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7599318540748284</v>
+        <v>0.7472143551988655</v>
       </c>
     </row>
     <row r="7">
@@ -668,22 +668,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>TranLamAnhDuong</t>
+          <t>原田信行</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>原田信行</t>
+          <t>黒瀬雄大</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.7933650683336233</v>
+        <v>0.7934823490723095</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7704144901022719</v>
+        <v>0.7708026639766218</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7705693880514656</v>
+        <v>0.747030667028405</v>
       </c>
     </row>
     <row r="8">
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.7940382994730818</v>
+        <v>0.7937366282266973</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7610796382356125</v>
+        <v>0.7604838642054538</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7574106571633021</v>
+        <v>0.7573704867578485</v>
       </c>
     </row>
     <row r="9">
@@ -749,13 +749,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.7926386627756383</v>
+        <v>0.7916116180778753</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7877462265913011</v>
+        <v>0.7898925298906265</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7493271225600245</v>
+        <v>0.7455020044017525</v>
       </c>
     </row>
     <row r="10">
@@ -776,7 +776,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LiuTianxiang</t>
+          <t>Phung DucTuan</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -785,13 +785,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.7691182834552195</v>
+        <v>0.7715006839331053</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7682641227123544</v>
+        <v>0.7343256014576269</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7133301731439236</v>
+        <v>0.7080079314742604</v>
       </c>
     </row>
     <row r="11">
@@ -812,22 +812,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>TranLamAnhDuong</t>
+          <t>秋山英三</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>秋山英三</t>
+          <t>作道真理</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.7986562214241151</v>
+        <v>0.7987352560391006</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7927967786996586</v>
+        <v>0.780725968062059</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7810777642715331</v>
+        <v>0.7535015021715852</v>
       </c>
     </row>
     <row r="12">
@@ -848,7 +848,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>TranLamAnhDuong</t>
+          <t>Phung DucTuan</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.7900495735720822</v>
+        <v>0.790145127807668</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7786514969208398</v>
+        <v>0.7164647088437599</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7253796473706519</v>
+        <v>0.7259820112678075</v>
       </c>
     </row>
     <row r="13">
@@ -879,7 +879,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TranLamAnhDuong</t>
+          <t>Phung DucTuan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.8140611481300924</v>
+        <v>0.8039493044152165</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7479844665463535</v>
+        <v>0.7679389095274342</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7371900102257737</v>
+        <v>0.7559164131217846</v>
       </c>
     </row>
     <row r="14">
@@ -929,13 +929,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.782108156819849</v>
+        <v>0.7820176892100249</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7676688665050833</v>
+        <v>0.766323994656363</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7572289475039931</v>
+        <v>0.7547788508099192</v>
       </c>
     </row>
     <row r="15">
@@ -965,13 +965,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.7824789212041</v>
+        <v>0.7822583937871146</v>
       </c>
       <c r="G15" t="n">
-        <v>0.76628436598381</v>
+        <v>0.7670135299720341</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7643934909274448</v>
+        <v>0.7624678544637103</v>
       </c>
     </row>
     <row r="16">
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.7914803682659539</v>
+        <v>0.7913745143188848</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7809458850818162</v>
+        <v>0.7797478985608814</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7260085511688839</v>
+        <v>0.721518415283814</v>
       </c>
     </row>
     <row r="17">
@@ -1023,27 +1023,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Phung-DucTuan</t>
+          <t>Phung DucTuan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LiuTianxiang</t>
+          <t>張勇兵</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>張勇兵</t>
+          <t>高野祐一</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0.7838990802250871</v>
+        <v>0.8022595901834515</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7700759127212329</v>
+        <v>0.7080182967337185</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7349685150032662</v>
+        <v>0.6946508938559388</v>
       </c>
     </row>
     <row r="18">
@@ -1069,17 +1069,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>吉瀬章子</t>
+          <t>Phung DucTuan</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0.8087957674710922</v>
+        <v>0.8074081286133804</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7325339222958936</v>
+        <v>0.7342494314362839</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7298260897893794</v>
+        <v>0.7239668004375618</v>
       </c>
     </row>
     <row r="19">
@@ -1095,27 +1095,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Phung-DucTuan</t>
+          <t>黒瀬雄大</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>黒瀬雄大</t>
+          <t>有馬澄佳</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>有馬澄佳</t>
+          <t>大久保正勝</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0.814559100011602</v>
+        <v>0.7710509269969877</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6931882855272998</v>
+        <v>0.7593669993368094</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6843139228665569</v>
+        <v>0.743980413093444</v>
       </c>
     </row>
     <row r="20">
@@ -1136,22 +1136,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>Tran Lam Anh Duong</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>秋山英三</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>髙橋裕紀</t>
-        </is>
-      </c>
       <c r="F20" t="n">
-        <v>0.7922601157127722</v>
+        <v>0.7917937472707031</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7447926398263299</v>
+        <v>0.7576218148018588</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7327940278041978</v>
+        <v>0.7455660530617956</v>
       </c>
     </row>
     <row r="21">
@@ -1172,22 +1172,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>Liu Tianxiang</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>吉瀬章子</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>八森正泰</t>
-        </is>
-      </c>
       <c r="F21" t="n">
-        <v>0.803170656379013</v>
+        <v>0.8020794856104024</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7521329343305779</v>
+        <v>0.7792631197856266</v>
       </c>
       <c r="H21" t="n">
-        <v>0.748848610248332</v>
+        <v>0.7548336135955751</v>
       </c>
     </row>
     <row r="22">
@@ -1213,17 +1213,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>繁野麻衣子</t>
+          <t>Phung DucTuan</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0.7747237871746628</v>
+        <v>0.7748048081702387</v>
       </c>
       <c r="G22" t="n">
-        <v>0.7675355400107383</v>
+        <v>0.7662738286239533</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7503609303117418</v>
+        <v>0.7395404025384898</v>
       </c>
     </row>
     <row r="23">
@@ -1244,22 +1244,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>Liu Tianxiang</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>繁野麻衣子</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>吉瀬章子</t>
-        </is>
-      </c>
       <c r="F23" t="n">
-        <v>0.7861768024929651</v>
+        <v>0.7852747180597276</v>
       </c>
       <c r="G23" t="n">
-        <v>0.7544270183052249</v>
+        <v>0.76053871506522</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7540984845610337</v>
+        <v>0.7564891461325435</v>
       </c>
     </row>
     <row r="24">
@@ -1280,22 +1280,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>Phung DucTuan</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>繁野麻衣子</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>小西葉子</t>
-        </is>
-      </c>
       <c r="F24" t="n">
-        <v>0.7837673479714021</v>
+        <v>0.7832724380676721</v>
       </c>
       <c r="G24" t="n">
-        <v>0.750405486413361</v>
+        <v>0.751198502802636</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7363429784589886</v>
+        <v>0.7517470788490264</v>
       </c>
     </row>
     <row r="25">
@@ -1316,22 +1316,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>Liu Tianxiang</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>張勇兵</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>八森正泰</t>
-        </is>
-      </c>
       <c r="F25" t="n">
-        <v>0.8210967430460986</v>
+        <v>0.8202514556630865</v>
       </c>
       <c r="G25" t="n">
-        <v>0.7549537327645731</v>
+        <v>0.7815374074296739</v>
       </c>
       <c r="H25" t="n">
-        <v>0.7554390257603816</v>
+        <v>0.7536571363979294</v>
       </c>
     </row>
     <row r="26">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0.8141689771041204</v>
+        <v>0.814105680937531</v>
       </c>
       <c r="G26" t="n">
-        <v>0.7201433013654972</v>
+        <v>0.7197502719371935</v>
       </c>
       <c r="H26" t="n">
-        <v>0.7087411805502536</v>
+        <v>0.7064874531815901</v>
       </c>
     </row>
   </sheetData>

--- a/generated/committee_recommendations.xlsx
+++ b/generated/committee_recommendations.xlsx
@@ -497,13 +497,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.7980324189169082</v>
+        <v>0.7990804751472282</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7476459495927925</v>
+        <v>0.7457407141319889</v>
       </c>
       <c r="H2" t="n">
-        <v>0.745967923074087</v>
+        <v>0.7436180316601839</v>
       </c>
     </row>
     <row r="3">
@@ -533,13 +533,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.7646012657634985</v>
+        <v>0.7645546623853985</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7542134458195275</v>
+        <v>0.7560855235494532</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7485639766309413</v>
+        <v>0.7519666255181408</v>
       </c>
     </row>
     <row r="4">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.7730491480516837</v>
+        <v>0.7730844708148208</v>
       </c>
       <c r="G4" t="n">
-        <v>0.749730500747122</v>
+        <v>0.7492663532653359</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7382624589564942</v>
+        <v>0.7377681360832717</v>
       </c>
     </row>
     <row r="5">
@@ -591,27 +591,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Phung DucTuan</t>
+          <t>LiuTianxiang</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>Phung-DucTuan</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>高野祐一</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>有馬澄佳</t>
-        </is>
-      </c>
       <c r="F5" t="n">
-        <v>0.7948736779933087</v>
+        <v>0.7807969700848041</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7307908669503085</v>
+        <v>0.7802955162809034</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7273656892848034</v>
+        <v>0.7629236394713367</v>
       </c>
     </row>
     <row r="6">
@@ -627,27 +627,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Phung DucTuan</t>
+          <t>秋山英三</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>秋山英三</t>
+          <t>TranLamAnhDuong</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Tran Lam Anh Duong</t>
+          <t>佐野幸恵</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.7806034182445172</v>
+        <v>0.777475428793001</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7666447199205355</v>
+        <v>0.7589512752102814</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7472143551988655</v>
+        <v>0.7599317009143467</v>
       </c>
     </row>
     <row r="7">
@@ -668,22 +668,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>TranLamAnhDuong</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>原田信行</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>黒瀬雄大</t>
-        </is>
-      </c>
       <c r="F7" t="n">
-        <v>0.7934823490723095</v>
+        <v>0.793365402119634</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7708026639766218</v>
+        <v>0.7704139251473998</v>
       </c>
       <c r="H7" t="n">
-        <v>0.747030667028405</v>
+        <v>0.7705694203287918</v>
       </c>
     </row>
     <row r="8">
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.7937366282266973</v>
+        <v>0.7940385736544479</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7604838642054538</v>
+        <v>0.7610796693064201</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7573704867578485</v>
+        <v>0.75741082965535</v>
       </c>
     </row>
     <row r="9">
@@ -749,13 +749,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.7916116180778753</v>
+        <v>0.7926388773523594</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7898925298906265</v>
+        <v>0.7877466609819869</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7455020044017525</v>
+        <v>0.7493271465883786</v>
       </c>
     </row>
     <row r="10">
@@ -776,7 +776,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Phung DucTuan</t>
+          <t>LiuTianxiang</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -785,13 +785,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.7715006839331053</v>
+        <v>0.7691184801505473</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7343256014576269</v>
+        <v>0.7682644978240212</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7080079314742604</v>
+        <v>0.7133311424561222</v>
       </c>
     </row>
     <row r="11">
@@ -812,22 +812,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>TranLamAnhDuong</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>秋山英三</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>作道真理</t>
-        </is>
-      </c>
       <c r="F11" t="n">
-        <v>0.7987352560391006</v>
+        <v>0.7986562750682954</v>
       </c>
       <c r="G11" t="n">
-        <v>0.780725968062059</v>
+        <v>0.7927969203779757</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7535015021715852</v>
+        <v>0.7810778899836618</v>
       </c>
     </row>
     <row r="12">
@@ -848,7 +848,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Phung DucTuan</t>
+          <t>TranLamAnhDuong</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.790145127807668</v>
+        <v>0.7900498149708934</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7164647088437599</v>
+        <v>0.7786515345644294</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7259820112678075</v>
+        <v>0.725379641877675</v>
       </c>
     </row>
     <row r="13">
@@ -879,7 +879,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Phung DucTuan</t>
+          <t>TranLamAnhDuong</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.8039493044152165</v>
+        <v>0.8140611779324148</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7679389095274342</v>
+        <v>0.7479848455984035</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7559164131217846</v>
+        <v>0.7371903975067992</v>
       </c>
     </row>
     <row r="14">
@@ -929,13 +929,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.7820176892100249</v>
+        <v>0.7821082462268162</v>
       </c>
       <c r="G14" t="n">
-        <v>0.766323994656363</v>
+        <v>0.7676686179623895</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7547788508099192</v>
+        <v>0.7572288631246638</v>
       </c>
     </row>
     <row r="15">
@@ -965,13 +965,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.7822583937871146</v>
+        <v>0.7824792788319687</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7670135299720341</v>
+        <v>0.7662843099258541</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7624678544637103</v>
+        <v>0.7643935545360966</v>
       </c>
     </row>
     <row r="16">
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.7913745143188848</v>
+        <v>0.7914804368112953</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7797478985608814</v>
+        <v>0.7809460412806564</v>
       </c>
       <c r="H16" t="n">
-        <v>0.721518415283814</v>
+        <v>0.7260086165237314</v>
       </c>
     </row>
     <row r="17">
@@ -1023,27 +1023,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Phung DucTuan</t>
+          <t>Phung-DucTuan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>LiuTianxiang</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>張勇兵</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>高野祐一</t>
-        </is>
-      </c>
       <c r="F17" t="n">
-        <v>0.8022595901834515</v>
+        <v>0.7838991994343767</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7080182967337185</v>
+        <v>0.7700758577991739</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6946508938559388</v>
+        <v>0.7349688599838846</v>
       </c>
     </row>
     <row r="18">
@@ -1069,17 +1069,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Phung DucTuan</t>
+          <t>吉瀬章子</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0.8074081286133804</v>
+        <v>0.8087958270757369</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7342494314362839</v>
+        <v>0.7325343050318592</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7239668004375618</v>
+        <v>0.7298264185003422</v>
       </c>
     </row>
     <row r="19">
@@ -1095,27 +1095,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>Phung-DucTuan</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>黒瀬雄大</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>有馬澄佳</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>大久保正勝</t>
-        </is>
-      </c>
       <c r="F19" t="n">
-        <v>0.7710509269969877</v>
+        <v>0.8145593294894845</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7593669993368094</v>
+        <v>0.6931889628284444</v>
       </c>
       <c r="H19" t="n">
-        <v>0.743980413093444</v>
+        <v>0.6843139670630791</v>
       </c>
     </row>
     <row r="20">
@@ -1136,22 +1136,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Tran Lam Anh Duong</t>
+          <t>秋山英三</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>秋山英三</t>
+          <t>髙橋裕紀</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0.7917937472707031</v>
+        <v>0.7922602110802039</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7576218148018588</v>
+        <v>0.7447926232143768</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7455660530617956</v>
+        <v>0.7327941651160159</v>
       </c>
     </row>
     <row r="21">
@@ -1172,22 +1172,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Liu Tianxiang</t>
+          <t>吉瀬章子</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>吉瀬章子</t>
+          <t>八森正泰</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0.8020794856104024</v>
+        <v>0.8031707666476058</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7792631197856266</v>
+        <v>0.7521326585034569</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7548336135955751</v>
+        <v>0.7488486792745004</v>
       </c>
     </row>
     <row r="22">
@@ -1213,17 +1213,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Phung DucTuan</t>
+          <t>繁野麻衣子</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0.7748048081702387</v>
+        <v>0.7747239808897584</v>
       </c>
       <c r="G22" t="n">
-        <v>0.7662738286239533</v>
+        <v>0.7675358273173142</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7395404025384898</v>
+        <v>0.750361214367077</v>
       </c>
     </row>
     <row r="23">
@@ -1244,22 +1244,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Liu Tianxiang</t>
+          <t>繁野麻衣子</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>繁野麻衣子</t>
+          <t>吉瀬章子</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0.7852747180597276</v>
+        <v>0.7861770081289896</v>
       </c>
       <c r="G23" t="n">
-        <v>0.76053871506522</v>
+        <v>0.7544270065638702</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7564891461325435</v>
+        <v>0.7540988778190654</v>
       </c>
     </row>
     <row r="24">
@@ -1280,22 +1280,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Phung DucTuan</t>
+          <t>繁野麻衣子</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>繁野麻衣子</t>
+          <t>小西葉子</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0.7832724380676721</v>
+        <v>0.783767485062085</v>
       </c>
       <c r="G24" t="n">
-        <v>0.751198502802636</v>
+        <v>0.7504054209416953</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7517470788490264</v>
+        <v>0.7363430054106848</v>
       </c>
     </row>
     <row r="25">
@@ -1316,22 +1316,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Liu Tianxiang</t>
+          <t>張勇兵</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>張勇兵</t>
+          <t>八森正泰</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0.8202514556630865</v>
+        <v>0.8210970053065357</v>
       </c>
       <c r="G25" t="n">
-        <v>0.7815374074296739</v>
+        <v>0.7549542035323578</v>
       </c>
       <c r="H25" t="n">
-        <v>0.7536571363979294</v>
+        <v>0.75543937381531</v>
       </c>
     </row>
     <row r="26">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0.814105680937531</v>
+        <v>0.814169194661074</v>
       </c>
       <c r="G26" t="n">
-        <v>0.7197502719371935</v>
+        <v>0.7201431580307053</v>
       </c>
       <c r="H26" t="n">
-        <v>0.7064874531815901</v>
+        <v>0.7087410383921012</v>
       </c>
     </row>
   </sheetData>

--- a/generated/committee_recommendations.xlsx
+++ b/generated/committee_recommendations.xlsx
@@ -483,27 +483,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>Liu Tianxiang</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>高野祐一</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>繁野麻衣子</t>
-        </is>
-      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>吉瀬章子</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.7990804751472282</v>
+        <v>0.6942373478412628</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7457407141319889</v>
+        <v>0.6933760726451873</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7436180316601839</v>
+        <v>0.6656171238422395</v>
       </c>
     </row>
     <row r="3">
@@ -533,13 +533,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.7645546623853985</v>
+        <v>0.661869711279869</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7560855235494532</v>
+        <v>0.6321662741899491</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7519666255181408</v>
+        <v>0.6299933689832689</v>
       </c>
     </row>
     <row r="4">
@@ -555,27 +555,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>木下陽平</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>黒瀬雄大</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>木下陽平</t>
-        </is>
-      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>岡田幸彦</t>
+          <t>志田洋平</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.7730844708148208</v>
+        <v>0.6376265454292298</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7492663532653359</v>
+        <v>0.6320436316728593</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7377681360832717</v>
+        <v>0.6292038726806641</v>
       </c>
     </row>
     <row r="5">
@@ -591,27 +591,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LiuTianxiang</t>
+          <t>Phung Duc Tuan</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Phung-DucTuan</t>
+          <t>高野祐一</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>高野祐一</t>
+          <t>有馬澄佳</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.7807969700848041</v>
+        <v>0.6306278753280641</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7802955162809034</v>
+        <v>0.626043536067009</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7629236394713367</v>
+        <v>0.6272811847925186</v>
       </c>
     </row>
     <row r="6">
@@ -627,12 +627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>秋山英三</t>
+          <t>張勇兵</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>TranLamAnhDuong</t>
+          <t>Phung Duc Tuan</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -641,13 +641,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.777475428793001</v>
+        <v>0.6579499936103821</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7589512752102814</v>
+        <v>0.6420861113071442</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7599317009143467</v>
+        <v>0.6316490072011949</v>
       </c>
     </row>
     <row r="7">
@@ -668,22 +668,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>TranLamAnhDuong</t>
+          <t>原田信行</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>原田信行</t>
+          <t>岡田幸彦</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.793365402119634</v>
+        <v>0.6723432636260986</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7704139251473998</v>
+        <v>0.6693654781579972</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7705694203287918</v>
+        <v>0.6650735533237457</v>
       </c>
     </row>
     <row r="8">
@@ -709,17 +709,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>吉瀬章子</t>
+          <t>木下陽平</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.7940385736544479</v>
+        <v>0.6603522902727128</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7610796693064201</v>
+        <v>0.6283706593513489</v>
       </c>
       <c r="H8" t="n">
-        <v>0.75741082965535</v>
+        <v>0.6232489931583405</v>
       </c>
     </row>
     <row r="9">
@@ -735,27 +735,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>大西正輝</t>
+          <t>黒瀬雄大</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>黒瀬雄大</t>
+          <t>大久保正勝</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>小西葉子</t>
+          <t>岡田幸彦</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.7926388773523594</v>
+        <v>0.7029805594682693</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7877466609819869</v>
+        <v>0.6661788946390153</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7493271465883786</v>
+        <v>0.6654861068725586</v>
       </c>
     </row>
     <row r="10">
@@ -771,27 +771,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>讃井知</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>佐野幸恵</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>大西正輝</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>LiuTianxiang</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>佐野幸恵</t>
-        </is>
-      </c>
       <c r="F10" t="n">
-        <v>0.7691184801505473</v>
+        <v>0.5899906814098359</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7682644978240212</v>
+        <v>0.5892313271760941</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7133311424561222</v>
+        <v>0.5791996479034425</v>
       </c>
     </row>
     <row r="11">
@@ -807,27 +807,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>佐野幸恵</t>
+          <t>岡田幸彦</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>TranLamAnhDuong</t>
+          <t>作道真理</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>秋山英三</t>
+          <t>大久保正勝</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.7986562750682954</v>
+        <v>0.7013333642482757</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7927969203779757</v>
+        <v>0.6997858339548111</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7810778899836618</v>
+        <v>0.6942957365512848</v>
       </c>
     </row>
     <row r="12">
@@ -843,27 +843,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>岡田幸彦</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>大久保正勝</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>原田信行</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>TranLamAnhDuong</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>岡田幸彦</t>
-        </is>
-      </c>
       <c r="F12" t="n">
-        <v>0.7900498149708934</v>
+        <v>0.6649727618694306</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7786515345644294</v>
+        <v>0.6620100116729737</v>
       </c>
       <c r="H12" t="n">
-        <v>0.725379641877675</v>
+        <v>0.6624937987327577</v>
       </c>
     </row>
     <row r="13">
@@ -879,7 +879,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TranLamAnhDuong</t>
+          <t>岡田幸彦</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -889,17 +889,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>岡田幸彦</t>
+          <t>原田信行</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.8140611779324148</v>
+        <v>0.7049451702833175</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7479848455984035</v>
+        <v>0.704819198846817</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7371903975067992</v>
+        <v>0.6991705858707428</v>
       </c>
     </row>
     <row r="14">
@@ -915,27 +915,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>黒瀬雄大</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>岡本直久</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>黒瀬雄大</t>
-        </is>
-      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>讃井知</t>
+          <t>木下陽平</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.7821082462268162</v>
+        <v>0.6614419287443161</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7676686179623895</v>
+        <v>0.6603341853618623</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7572288631246638</v>
+        <v>0.6249271798133851</v>
       </c>
     </row>
     <row r="15">
@@ -951,27 +951,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>黒瀬雄大</t>
+          <t>繁野麻衣子</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>繁野麻衣子</t>
+          <t>高野祐一</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>高野祐一</t>
+          <t>吉瀬章子</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.7824792788319687</v>
+        <v>0.6310107427835465</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7662843099258541</v>
+        <v>0.6247260349988938</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7643935545360966</v>
+        <v>0.6299715566635132</v>
       </c>
     </row>
     <row r="16">
@@ -997,17 +997,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>小西葉子</t>
+          <t>大久保正勝</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.7914804368112953</v>
+        <v>0.6762837952375413</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7809460412806564</v>
+        <v>0.6680268353223802</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7260086165237314</v>
+        <v>0.6645299291610718</v>
       </c>
     </row>
     <row r="17">
@@ -1023,27 +1023,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Phung-DucTuan</t>
+          <t>張勇兵</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LiuTianxiang</t>
+          <t>髙橋裕紀</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>張勇兵</t>
+          <t>原田信行</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0.7838991994343767</v>
+        <v>0.6308579701185226</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7700758577991739</v>
+        <v>0.6239504534006119</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7349688599838846</v>
+        <v>0.6244541603326799</v>
       </c>
     </row>
     <row r="18">
@@ -1059,27 +1059,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>Liu Tianxiang</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>高野祐一</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>繁野麻衣子</t>
-        </is>
-      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>吉瀬章子</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0.8087958270757369</v>
+        <v>0.6960857892036437</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7325343050318592</v>
+        <v>0.6943575197458267</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7298264185003422</v>
+        <v>0.6700493580102922</v>
       </c>
     </row>
     <row r="19">
@@ -1095,27 +1095,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Phung-DucTuan</t>
+          <t>黒瀬雄大</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>黒瀬雄大</t>
+          <t>大久保正勝</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>有馬澄佳</t>
+          <t>岡田幸彦</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0.8145593294894845</v>
+        <v>0.6643847322463989</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6931889628284444</v>
+        <v>0.6618160730600358</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6843139670630791</v>
+        <v>0.6606702184677125</v>
       </c>
     </row>
     <row r="20">
@@ -1136,22 +1136,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>秋山英三</t>
+          <t>志田洋平</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>髙橋裕紀</t>
+          <t>Tran Lam Anh Duong</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0.7922602110802039</v>
+        <v>0.672881174683571</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7447926232143768</v>
+        <v>0.6654806292057038</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7327941651160159</v>
+        <v>0.6635458892583848</v>
       </c>
     </row>
     <row r="21">
@@ -1167,27 +1167,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>Liu Tianxiang</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>高野祐一</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>吉瀬章子</t>
-        </is>
-      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>八森正泰</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0.8031707666476058</v>
+        <v>0.7063434445858002</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7521326585034569</v>
+        <v>0.6976198369264602</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7488486792745004</v>
+        <v>0.6699643528461456</v>
       </c>
     </row>
     <row r="22">
@@ -1208,22 +1208,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>作道真理</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>秋山英三</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>繁野麻衣子</t>
-        </is>
-      </c>
       <c r="F22" t="n">
-        <v>0.7747239808897584</v>
+        <v>0.6717876440286636</v>
       </c>
       <c r="G22" t="n">
-        <v>0.7675358273173142</v>
+        <v>0.6643758332729339</v>
       </c>
       <c r="H22" t="n">
-        <v>0.750361214367077</v>
+        <v>0.6644772207736969</v>
       </c>
     </row>
     <row r="23">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>高野祐一</t>
+          <t>Liu Tianxiang</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>繁野麻衣子</t>
+          <t>黒瀬雄大</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0.7861770081289896</v>
+        <v>0.6957991892099381</v>
       </c>
       <c r="G23" t="n">
-        <v>0.7544270065638702</v>
+        <v>0.6662005817890169</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7540988778190654</v>
+        <v>0.6679016059637071</v>
       </c>
     </row>
     <row r="24">
@@ -1275,27 +1275,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>高野祐一</t>
+          <t>髙橋裕紀</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>繁野麻衣子</t>
+          <t>小西葉子</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>小西葉子</t>
+          <t>秋山英三</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0.783767485062085</v>
+        <v>0.6684142744541168</v>
       </c>
       <c r="G24" t="n">
-        <v>0.7504054209416953</v>
+        <v>0.6655541515350343</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7363430054106848</v>
+        <v>0.6632857269048691</v>
       </c>
     </row>
     <row r="25">
@@ -1311,27 +1311,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>Liu Tianxiang</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
           <t>繁野麻衣子</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>張勇兵</t>
-        </is>
-      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>八森正泰</t>
+          <t>木下陽平</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0.8210970053065357</v>
+        <v>0.6349575239419938</v>
       </c>
       <c r="G25" t="n">
-        <v>0.7549542035323578</v>
+        <v>0.6348465549945832</v>
       </c>
       <c r="H25" t="n">
-        <v>0.75543937381531</v>
+        <v>0.630517550110817</v>
       </c>
     </row>
     <row r="26">
@@ -1352,22 +1352,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>髙橋裕紀</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>秋山英三</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>小西葉子</t>
-        </is>
-      </c>
       <c r="F26" t="n">
-        <v>0.814169194661074</v>
+        <v>0.6688809162378311</v>
       </c>
       <c r="G26" t="n">
-        <v>0.7201431580307053</v>
+        <v>0.6247280704975129</v>
       </c>
       <c r="H26" t="n">
-        <v>0.7087410383921012</v>
+        <v>0.6255099284648895</v>
       </c>
     </row>
   </sheetData>

--- a/generated/committee_recommendations.xlsx
+++ b/generated/committee_recommendations.xlsx
@@ -494,27 +494,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>原田 信行</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>澤 亮治</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>岡田 幸彦</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>堤 盛人</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.4166747704148293</v>
+        <v>0.8848052024841309</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3506117314100266</v>
+        <v>0.8768253028392792</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3256209790706635</v>
+        <v>0.8756940066814423</v>
       </c>
     </row>
     <row r="3">
@@ -535,27 +535,27 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>高野 祐一</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>岡田 幸彦</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>上市 秀雄</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>高野 祐一</t>
+          <t>原田 信行</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.4109171628952026</v>
+        <v>0.8693127036094666</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3983999341726303</v>
+        <v>0.8668391108512878</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3738963529467583</v>
+        <v>0.8660216927528381</v>
       </c>
     </row>
     <row r="4">
@@ -581,22 +581,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>岡田 幸彦</t>
+          <t>上市 秀雄</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>上市 秀雄</t>
+          <t>原田 信行</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.4043055549263954</v>
+        <v>0.8791826665401459</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3439278230071068</v>
+        <v>0.8787448704242706</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3088571578264236</v>
+        <v>0.8747391700744629</v>
       </c>
     </row>
     <row r="5">
@@ -622,22 +622,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>原田 信行</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>有馬 澄佳</t>
+          <t>高野 祐一</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.3892151936888695</v>
+        <v>0.8856546580791473</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3543544039130211</v>
+        <v>0.8759098052978516</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3251767382025719</v>
+        <v>0.87310791015625</v>
       </c>
     </row>
     <row r="6">
@@ -663,22 +663,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>太田 充</t>
+          <t>原田 信行</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>秋山 英三</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.3042872324585915</v>
+        <v>0.8744120597839355</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2901603765785694</v>
+        <v>0.8719078898429871</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2736799046397209</v>
+        <v>0.8683663904666901</v>
       </c>
     </row>
     <row r="7">
@@ -699,27 +699,27 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>甲斐田 直子</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>上市 秀雄</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>秋山 英三</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>岡田 幸彦</t>
-        </is>
-      </c>
       <c r="G7" t="n">
-        <v>0.4714049026370049</v>
+        <v>0.8821147382259369</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4255065023899078</v>
+        <v>0.8790072798728943</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4112908914685249</v>
+        <v>0.8756900429725647</v>
       </c>
     </row>
     <row r="8">
@@ -750,17 +750,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>堤 盛人</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.3920368030667305</v>
+        <v>0.876313328742981</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3326244056224823</v>
+        <v>0.8706642985343933</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2532849088311195</v>
+        <v>0.8669158816337585</v>
       </c>
     </row>
     <row r="9">
@@ -781,27 +781,27 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>澤 亮治</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Phung-Duc Tuan</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>繁野 麻衣子</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>繆 瑩</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>澤 亮治</t>
-        </is>
-      </c>
       <c r="G9" t="n">
-        <v>0.4257870763540268</v>
+        <v>0.8768597841262817</v>
       </c>
       <c r="H9" t="n">
-        <v>0.353876993060112</v>
+        <v>0.8675379455089569</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3519550785422325</v>
+        <v>0.8638555705547333</v>
       </c>
     </row>
     <row r="10">
@@ -822,27 +822,27 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>松原 康介</t>
+          <t>堤 盛人</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>村上 暁信</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>甲斐田 直子</t>
+          <t>雨宮 護</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.4792971834540367</v>
+        <v>0.8745534121990204</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4617466926574707</v>
+        <v>0.8721719980239868</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4469739198684692</v>
+        <v>0.8710920810699463</v>
       </c>
     </row>
     <row r="11">
@@ -863,27 +863,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>有馬 澄佳</t>
+          <t>八森 正泰</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>渡邉 俊</t>
+          <t>浦田淳司</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>繆 瑩</t>
+          <t>繁野 麻衣子</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.3776281848549843</v>
+        <v>0.8750033974647522</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3693093433976173</v>
+        <v>0.8726652562618256</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3605907782912254</v>
+        <v>0.8723176121711731</v>
       </c>
     </row>
     <row r="12">
@@ -904,27 +904,27 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>澤 亮治</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>繁野 麻衣子</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>岡田 幸彦</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>吉瀬 章子</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>繁野 麻衣子</t>
-        </is>
-      </c>
       <c r="G12" t="n">
-        <v>0.3296805396676064</v>
+        <v>0.8597085773944855</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3108825087547302</v>
+        <v>0.8590877652168274</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3062139898538589</v>
+        <v>0.8567173480987549</v>
       </c>
     </row>
     <row r="13">
@@ -950,22 +950,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>大西 正輝</t>
+          <t>繁野 麻衣子</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>岡本 直久</t>
+          <t>作道 真理</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.3932128697633743</v>
+        <v>0.8433670103549957</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3610677607357502</v>
+        <v>0.8428361415863037</v>
       </c>
       <c r="I13" t="n">
-        <v>0.349505752325058</v>
+        <v>0.8402458429336548</v>
       </c>
     </row>
     <row r="14">
@@ -986,27 +986,27 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>大西 正輝</t>
+          <t>作道 真理</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>鈴木 勉</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>岡本 直久</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>雨宮 護</t>
-        </is>
-      </c>
       <c r="G14" t="n">
-        <v>0.5125848725438118</v>
+        <v>0.8757067024707794</v>
       </c>
       <c r="H14" t="n">
-        <v>0.44338508695364</v>
+        <v>0.875690758228302</v>
       </c>
       <c r="I14" t="n">
-        <v>0.440148264169693</v>
+        <v>0.8736236691474915</v>
       </c>
     </row>
     <row r="15">
@@ -1027,27 +1027,27 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>Phung-Duc Tuan</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>大西 正輝</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>有馬 澄佳</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>渡邉 俊</t>
+          <t>浦田淳司</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.4157977551221848</v>
+        <v>0.8783397376537323</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3905382007360458</v>
+        <v>0.8763073980808258</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3541748523712158</v>
+        <v>0.8728134036064148</v>
       </c>
     </row>
     <row r="16">
@@ -1068,27 +1068,27 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>繆 瑩</t>
+          <t>有馬 澄佳</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>有馬 澄佳</t>
+          <t>繁野 麻衣子</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>吉瀬 章子</t>
+          <t>髙橋裕紀</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.4866152331233025</v>
+        <v>0.8736388683319092</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4357407093048096</v>
+        <v>0.8663072884082794</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3751474320888519</v>
+        <v>0.8623422682285309</v>
       </c>
     </row>
     <row r="17">
@@ -1109,27 +1109,27 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>上市 秀雄</t>
+          <t>澤 亮治</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>澤 亮治</t>
+          <t>秋山 英三</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>岡田 幸彦</t>
+          <t>甲斐田 直子</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0.3500119596719742</v>
+        <v>0.8675330877304077</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3252760618925095</v>
+        <v>0.8611766695976257</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3127514272928238</v>
+        <v>0.8608874678611755</v>
       </c>
     </row>
     <row r="18">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>有馬 澄佳</t>
+          <t>繆 瑩</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>繆 瑩</t>
+          <t>黒瀬 雄大</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1164,13 +1164,13 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0.4115282148122787</v>
+        <v>0.8702408373355865</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4100497215986252</v>
+        <v>0.8691293001174927</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3690649345517159</v>
+        <v>0.8680429458618164</v>
       </c>
     </row>
     <row r="19">
@@ -1196,22 +1196,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>有馬 澄佳</t>
+          <t>繁野 麻衣子</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>甲斐田 直子</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0.3506056442856789</v>
+        <v>0.8696708679199219</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3500727117061615</v>
+        <v>0.868317723274231</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3256340175867081</v>
+        <v>0.8637782335281372</v>
       </c>
     </row>
     <row r="20">
@@ -1232,27 +1232,27 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>澤 亮治</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>秋山 英三</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Phung-Duc Tuan</t>
+          <t>谷口 綾子</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0.4192173779010773</v>
+        <v>0.8816474974155426</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3575773537158966</v>
+        <v>0.8761932849884033</v>
       </c>
       <c r="I20" t="n">
-        <v>0.324680894613266</v>
+        <v>0.8759990930557251</v>
       </c>
     </row>
     <row r="21">
@@ -1273,27 +1273,27 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>繆 瑩</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>有馬 澄佳</t>
+          <t>繁野 麻衣子</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>高野 祐一</t>
+          <t>髙橋裕紀</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0.432977706193924</v>
+        <v>0.8575855791568756</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3221636563539505</v>
+        <v>0.8572642803192139</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3163709565997124</v>
+        <v>0.8561837077140808</v>
       </c>
     </row>
     <row r="22">
@@ -1314,27 +1314,27 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>藤川 昌樹</t>
+          <t>浦田淳司</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>八森 正泰</t>
+          <t>渡邉 俊</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>和田 健太郎</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.4549147188663483</v>
+        <v>0.8822779059410095</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4442000836133957</v>
+        <v>0.8764758110046387</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4329839646816254</v>
+        <v>0.8735903799533844</v>
       </c>
     </row>
     <row r="23">
@@ -1360,22 +1360,22 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>有馬 澄佳</t>
+          <t>繁野 麻衣子</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>甲斐田 直子</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0.3262973129749298</v>
+        <v>0.8626037240028381</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3210520222783089</v>
+        <v>0.8603973388671875</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3127037659287453</v>
+        <v>0.8597329556941986</v>
       </c>
     </row>
     <row r="24">
@@ -1401,22 +1401,22 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>作道 真理</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t>澤 亮治</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>堤 盛人</t>
-        </is>
-      </c>
       <c r="G24" t="n">
-        <v>0.4540447294712067</v>
+        <v>0.8749946355819702</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4360441192984581</v>
+        <v>0.8652920126914978</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3972113430500031</v>
+        <v>0.8621540665626526</v>
       </c>
     </row>
     <row r="25">
@@ -1437,27 +1437,27 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>奥島 真一郎</t>
+          <t>原田 信行</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>有馬 澄佳</t>
+          <t>作道 真理</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>岡田 幸彦</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0.2865549400448799</v>
+        <v>0.8712714612483978</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2849324941635132</v>
+        <v>0.8705659508705139</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2822191566228867</v>
+        <v>0.8689519762992859</v>
       </c>
     </row>
     <row r="26">
@@ -1478,27 +1478,27 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>岡田 幸彦</t>
+          <t>原田 信行</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>上市 秀雄</t>
+          <t>秋山 英三</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>澤 亮治</t>
+          <t>作道 真理</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0.3304425254464149</v>
+        <v>0.878558874130249</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2968719452619553</v>
+        <v>0.8698205053806305</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2821801975369453</v>
+        <v>0.8683366775512695</v>
       </c>
     </row>
     <row r="27">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>太田 充</t>
+          <t>上市 秀雄</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1529,17 +1529,17 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>上市 秀雄</t>
+          <t>作道 真理</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0.4401953369379044</v>
+        <v>0.8689084053039551</v>
       </c>
       <c r="H27" t="n">
-        <v>0.4047196172177792</v>
+        <v>0.866457462310791</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4004700854420662</v>
+        <v>0.8636112809181213</v>
       </c>
     </row>
     <row r="28">
@@ -1560,27 +1560,27 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>繆 瑩</t>
+          <t>有馬 澄佳</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>有馬 澄佳</t>
+          <t>繁野 麻衣子</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>高野 祐一</t>
+          <t>大西 正輝</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0.4854395166039467</v>
+        <v>0.8729794323444366</v>
       </c>
       <c r="H28" t="n">
-        <v>0.4064581245183945</v>
+        <v>0.8698991537094116</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3575337454676628</v>
+        <v>0.8678604066371918</v>
       </c>
     </row>
     <row r="29">
@@ -1606,22 +1606,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
+          <t>繁野 麻衣子</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t>岡田 幸彦</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>繁野 麻衣子</t>
-        </is>
-      </c>
       <c r="G29" t="n">
-        <v>0.3564027398824692</v>
+        <v>0.8743135333061218</v>
       </c>
       <c r="H29" t="n">
-        <v>0.344151645898819</v>
+        <v>0.8710212707519531</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3318030461668968</v>
+        <v>0.8706225752830505</v>
       </c>
     </row>
     <row r="30">
@@ -1647,22 +1647,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
+          <t>繁野 麻衣子</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t>岡田 幸彦</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>繁野 麻衣子</t>
-        </is>
-      </c>
       <c r="G30" t="n">
-        <v>0.4018908143043518</v>
+        <v>0.8728483319282532</v>
       </c>
       <c r="H30" t="n">
-        <v>0.2116046100854874</v>
+        <v>0.8566639721393585</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1945343464612961</v>
+        <v>0.8563459515571594</v>
       </c>
     </row>
     <row r="31">
@@ -1683,27 +1683,27 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>有田 智一</t>
+          <t>原田 信行</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>山本 幸子</t>
+          <t>秋山 英三</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>堤 盛人</t>
+          <t>甲斐田 直子</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0.4743466153740883</v>
+        <v>0.8736870586872101</v>
       </c>
       <c r="H31" t="n">
-        <v>0.4609044045209885</v>
+        <v>0.8708910942077637</v>
       </c>
       <c r="I31" t="n">
-        <v>0.4581665769219398</v>
+        <v>0.8651430904865265</v>
       </c>
     </row>
     <row r="32">
@@ -1724,27 +1724,27 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t>甲斐田 直子</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>雨宮 護</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t>佐野 幸恵</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>吉瀬 章子</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>松原 康介</t>
-        </is>
-      </c>
       <c r="G32" t="n">
-        <v>0.329257607460022</v>
+        <v>0.8561131954193115</v>
       </c>
       <c r="H32" t="n">
-        <v>0.301259383559227</v>
+        <v>0.8527567386627197</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2979333400726318</v>
+        <v>0.8503190577030182</v>
       </c>
     </row>
     <row r="33">
@@ -1770,22 +1770,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>上市 秀雄</t>
+          <t>藤井 さやか</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>甲斐田 直子</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0.4008801877498627</v>
+        <v>0.8680321872234344</v>
       </c>
       <c r="H33" t="n">
-        <v>0.3822698593139648</v>
+        <v>0.8663512766361237</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3795605376362801</v>
+        <v>0.8609660863876343</v>
       </c>
     </row>
     <row r="34">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>上市 秀雄</t>
+          <t>雨宮 護</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>山本 幸子</t>
+          <t>渡邉 俊</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0.407227098941803</v>
+        <v>0.8717754483222961</v>
       </c>
       <c r="H34" t="n">
-        <v>0.3791009485721588</v>
+        <v>0.8688279688358307</v>
       </c>
       <c r="I34" t="n">
-        <v>0.3674851655960083</v>
+        <v>0.8672304451465607</v>
       </c>
     </row>
     <row r="35">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>藤井 さやか</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>藤井 さやか</t>
+          <t>渡邉 俊</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1861,13 +1861,13 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0.5182433873414993</v>
+        <v>0.8760980069637299</v>
       </c>
       <c r="H35" t="n">
-        <v>0.5133289843797684</v>
+        <v>0.8746935427188873</v>
       </c>
       <c r="I35" t="n">
-        <v>0.4933153390884399</v>
+        <v>0.873765230178833</v>
       </c>
     </row>
     <row r="36">
@@ -1888,27 +1888,27 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>有田 智一</t>
+          <t>村上 暁信</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>太田 充</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>岡本 直久</t>
+          <t>甲斐田 直子</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0.5204322934150696</v>
+        <v>0.8773117661476135</v>
       </c>
       <c r="H36" t="n">
-        <v>0.4853076934814453</v>
+        <v>0.875573992729187</v>
       </c>
       <c r="I36" t="n">
-        <v>0.4728722274303436</v>
+        <v>0.8741279244422913</v>
       </c>
     </row>
     <row r="37">
@@ -1934,22 +1934,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>有田 智一</t>
+          <t>岡田 幸彦</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>山本 幸子</t>
+          <t>甲斐田 直子</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0.5066809505224228</v>
+        <v>0.8822030425071716</v>
       </c>
       <c r="H37" t="n">
-        <v>0.504463329911232</v>
+        <v>0.877425342798233</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4833681285381317</v>
+        <v>0.8771246671676636</v>
       </c>
     </row>
     <row r="38">
@@ -1975,22 +1975,22 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
+          <t>藤井 さやか</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t>川島 宏一</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>藤井 さやか</t>
-        </is>
-      </c>
       <c r="G38" t="n">
-        <v>0.4380344897508621</v>
+        <v>0.8677642643451691</v>
       </c>
       <c r="H38" t="n">
-        <v>0.4270626306533813</v>
+        <v>0.8663949072360992</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4145728200674057</v>
+        <v>0.8658533990383148</v>
       </c>
     </row>
     <row r="39">
@@ -2011,27 +2011,27 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>村上 暁信</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>松原 康介</t>
+          <t>雨宮 護</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>藤川 昌樹</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0.4656005352735519</v>
+        <v>0.8803601562976837</v>
       </c>
       <c r="H39" t="n">
-        <v>0.462663397192955</v>
+        <v>0.8787698745727539</v>
       </c>
       <c r="I39" t="n">
-        <v>0.4341594129800797</v>
+        <v>0.8784969449043274</v>
       </c>
     </row>
     <row r="40">
@@ -2057,22 +2057,22 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>藤川 昌樹</t>
+          <t>堤 盛人</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>和田 健太郎</t>
+          <t>甲斐田 直子</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0.4960251897573471</v>
+        <v>0.884984940290451</v>
       </c>
       <c r="H40" t="n">
-        <v>0.4903744608163834</v>
+        <v>0.8826780319213867</v>
       </c>
       <c r="I40" t="n">
-        <v>0.4786133170127869</v>
+        <v>0.8774478733539581</v>
       </c>
     </row>
     <row r="41">
@@ -2093,27 +2093,27 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t>堤 盛人</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>川島 宏一</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t>松原 康介</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>甲斐田 直子</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>太田 充</t>
-        </is>
-      </c>
       <c r="G41" t="n">
-        <v>0.518221452832222</v>
+        <v>0.8720704913139343</v>
       </c>
       <c r="H41" t="n">
-        <v>0.4704625084996223</v>
+        <v>0.8697050213813782</v>
       </c>
       <c r="I41" t="n">
-        <v>0.4653588831424713</v>
+        <v>0.8684079647064209</v>
       </c>
     </row>
     <row r="42">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>太田 充</t>
+          <t>秋山 英三</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2148,13 +2148,13 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0.2098722755908966</v>
+        <v>0.8570056855678558</v>
       </c>
       <c r="H42" t="n">
-        <v>0.2028913870453835</v>
+        <v>0.8475772440433502</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2025479972362518</v>
+        <v>0.8470962643623352</v>
       </c>
     </row>
     <row r="43">
@@ -2175,27 +2175,27 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>八森 正泰</t>
+          <t>渡邉 俊</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>松原 康介</t>
+          <t>藤井 さやか</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>藤川 昌樹</t>
+          <t>雨宮 護</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0.4171333275735378</v>
+        <v>0.8702762126922607</v>
       </c>
       <c r="H43" t="n">
-        <v>0.3982899934053421</v>
+        <v>0.8699823319911957</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3789577186107635</v>
+        <v>0.8686732649803162</v>
       </c>
     </row>
     <row r="44">
@@ -2216,27 +2216,27 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t>雨宮 護</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
           <t>太田 充</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>藤川 昌樹</t>
-        </is>
-      </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>岡田 幸彦</t>
+          <t>繁野 麻衣子</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0.2048846483230591</v>
+        <v>0.8487688601016998</v>
       </c>
       <c r="H44" t="n">
-        <v>0.1998257488012314</v>
+        <v>0.8464263081550598</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1929562017321587</v>
+        <v>0.8433281183242798</v>
       </c>
     </row>
     <row r="45">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>村上 暁信</t>
+          <t>松原 康介</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>松原 康介</t>
+          <t>渡邉 俊</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2271,13 +2271,13 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0.5336017161607742</v>
+        <v>0.8856144547462463</v>
       </c>
       <c r="H45" t="n">
-        <v>0.509978212416172</v>
+        <v>0.8848127126693726</v>
       </c>
       <c r="I45" t="n">
-        <v>0.4846635609865189</v>
+        <v>0.8812952637672424</v>
       </c>
     </row>
     <row r="46">
@@ -2303,22 +2303,22 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>秋山 英三</t>
+          <t>渡邉 俊</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>雨宮 護</t>
+          <t>繁野 麻衣子</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0.4817467480897903</v>
+        <v>0.87106853723526</v>
       </c>
       <c r="H46" t="n">
-        <v>0.4256856888532639</v>
+        <v>0.8708507418632507</v>
       </c>
       <c r="I46" t="n">
-        <v>0.4147410541772842</v>
+        <v>0.8703113496303558</v>
       </c>
     </row>
     <row r="47">
@@ -2339,27 +2339,27 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>甲斐田 直子</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>有田 智一</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>松原 康介</t>
+          <t>太田 充</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>0.476320669054985</v>
+        <v>0.8803860545158386</v>
       </c>
       <c r="H47" t="n">
-        <v>0.4699381589889526</v>
+        <v>0.8798553049564362</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4695268720388412</v>
+        <v>0.8788651823997498</v>
       </c>
     </row>
     <row r="48">
@@ -2385,22 +2385,22 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>松原 康介</t>
+          <t>岡本 直久</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>有田 智一</t>
+          <t>雨宮 護</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>0.4666003882884979</v>
+        <v>0.8730646371841431</v>
       </c>
       <c r="H48" t="n">
-        <v>0.4576002359390259</v>
+        <v>0.8723333775997162</v>
       </c>
       <c r="I48" t="n">
-        <v>0.4332947209477425</v>
+        <v>0.868208110332489</v>
       </c>
     </row>
     <row r="49">
@@ -2421,27 +2421,27 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>渡邉 俊</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>村上 暁信</t>
+          <t>太田 充</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>藤井 さやか</t>
+          <t>藤川 昌樹</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>0.4254945367574692</v>
+        <v>0.8705888986587524</v>
       </c>
       <c r="H49" t="n">
-        <v>0.4196152240037918</v>
+        <v>0.8669873476028442</v>
       </c>
       <c r="I49" t="n">
-        <v>0.4078935533761978</v>
+        <v>0.8661882281303406</v>
       </c>
     </row>
     <row r="50">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>渡邉 俊</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2476,13 +2476,13 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>0.5202682912349701</v>
+        <v>0.8833150863647461</v>
       </c>
       <c r="H50" t="n">
-        <v>0.4804174304008484</v>
+        <v>0.8816799223423004</v>
       </c>
       <c r="I50" t="n">
-        <v>0.4105108007788658</v>
+        <v>0.8803482055664062</v>
       </c>
     </row>
     <row r="51">
@@ -2503,27 +2503,27 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>澤 亮治</t>
+          <t>雨宮 護</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
+          <t>秋山 英三</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
           <t>岡田 幸彦</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>佐野 幸恵</t>
-        </is>
-      </c>
       <c r="G51" t="n">
-        <v>0.1838598996400833</v>
+        <v>0.8630247712135315</v>
       </c>
       <c r="H51" t="n">
-        <v>0.182458259165287</v>
+        <v>0.8506519198417664</v>
       </c>
       <c r="I51" t="n">
-        <v>0.1817226260900497</v>
+        <v>0.8482785820960999</v>
       </c>
     </row>
     <row r="52">
@@ -2549,22 +2549,22 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>有馬 澄佳</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>雨宮 護</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>0.2888300269842148</v>
+        <v>0.8618446588516235</v>
       </c>
       <c r="H52" t="n">
-        <v>0.2809312790632248</v>
+        <v>0.8603324294090271</v>
       </c>
       <c r="I52" t="n">
-        <v>0.270343966782093</v>
+        <v>0.8595001697540283</v>
       </c>
     </row>
     <row r="53">
@@ -2585,27 +2585,27 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>有田 智一</t>
+          <t>藤井 さやか</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>和田 健太郎</t>
+          <t>雨宮 護</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>雨宮 護</t>
+          <t>渡邉 俊</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>0.4229609146714211</v>
+        <v>0.880888044834137</v>
       </c>
       <c r="H53" t="n">
-        <v>0.386085256934166</v>
+        <v>0.8738102912902832</v>
       </c>
       <c r="I53" t="n">
-        <v>0.383851483464241</v>
+        <v>0.8714291453361511</v>
       </c>
     </row>
     <row r="54">
@@ -2626,27 +2626,27 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>甲斐田 直子</t>
+          <t>堤 盛人</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>松原 康介</t>
+          <t>雨宮 護</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>雨宮 護</t>
+          <t>村上 暁信</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>0.3664065301418304</v>
+        <v>0.8651339709758759</v>
       </c>
       <c r="H54" t="n">
-        <v>0.3533423990011215</v>
+        <v>0.859698623418808</v>
       </c>
       <c r="I54" t="n">
-        <v>0.3393831178545952</v>
+        <v>0.8588502407073975</v>
       </c>
     </row>
     <row r="55">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>岡田 幸彦</t>
+          <t>雨宮 護</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2677,17 +2677,17 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>澤 亮治</t>
+          <t>甲斐田 直子</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>0.1733894124627113</v>
+        <v>0.8542676866054535</v>
       </c>
       <c r="H55" t="n">
-        <v>0.166567899286747</v>
+        <v>0.8511963486671448</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1657562106847763</v>
+        <v>0.849749356508255</v>
       </c>
     </row>
     <row r="56">
@@ -2708,27 +2708,27 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>藤川 昌樹</t>
+          <t>山本 幸子</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>太田 充</t>
+          <t>藤井 さやか</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>和田 健太郎</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>0.2309069633483887</v>
+        <v>0.859814316034317</v>
       </c>
       <c r="H56" t="n">
-        <v>0.2289677411317825</v>
+        <v>0.859036386013031</v>
       </c>
       <c r="I56" t="n">
-        <v>0.2279248759150505</v>
+        <v>0.8581754565238953</v>
       </c>
     </row>
     <row r="57">
@@ -2754,22 +2754,22 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>村上 暁信</t>
+          <t>岡田 幸彦</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>太田 充</t>
+          <t>繁野 麻衣子</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>0.2832713425159454</v>
+        <v>0.8475391864776611</v>
       </c>
       <c r="H57" t="n">
-        <v>0.2549052760004997</v>
+        <v>0.8461900353431702</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2406051084399223</v>
+        <v>0.8431481719017029</v>
       </c>
     </row>
     <row r="58">
@@ -2790,27 +2790,27 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
+          <t>繁野 麻衣子</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>作道 真理</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
           <t>岡田 幸彦</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>渡邉 俊</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>太田 充</t>
-        </is>
-      </c>
       <c r="G58" t="n">
-        <v>0.2077242583036423</v>
+        <v>0.8584452867507935</v>
       </c>
       <c r="H58" t="n">
-        <v>0.1970057263970375</v>
+        <v>0.8539338707923889</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1969832181930542</v>
+        <v>0.8530483841896057</v>
       </c>
     </row>
     <row r="59">
@@ -2836,22 +2836,22 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>岡本 直久</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>渡邉 俊</t>
+          <t>浦田淳司</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>0.4434704482555389</v>
+        <v>0.8807176947593689</v>
       </c>
       <c r="H59" t="n">
-        <v>0.4385496228933334</v>
+        <v>0.8800468444824219</v>
       </c>
       <c r="I59" t="n">
-        <v>0.4192341864109039</v>
+        <v>0.8795809149742126</v>
       </c>
     </row>
     <row r="60">
@@ -2872,27 +2872,27 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>有馬 澄佳</t>
+          <t>飛田 幹男</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>黒瀬 雄大</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>八森 正泰</t>
+          <t>浦田淳司</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>0.393385037779808</v>
+        <v>0.8769747614860535</v>
       </c>
       <c r="H60" t="n">
-        <v>0.3817732930183411</v>
+        <v>0.87520432472229</v>
       </c>
       <c r="I60" t="n">
-        <v>0.374508835375309</v>
+        <v>0.8735997974872589</v>
       </c>
     </row>
     <row r="61">
@@ -2913,27 +2913,27 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>松原 康介</t>
+          <t>甲斐田 直子</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>甲斐田 直子</t>
+          <t>村上 暁信</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>有田 智一</t>
+          <t>渡邉 俊</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>0.4017220139503479</v>
+        <v>0.8747804462909698</v>
       </c>
       <c r="H61" t="n">
-        <v>0.3824743330478668</v>
+        <v>0.8732750713825226</v>
       </c>
       <c r="I61" t="n">
-        <v>0.3779747933149338</v>
+        <v>0.8700069189071655</v>
       </c>
     </row>
     <row r="62">
@@ -2954,27 +2954,27 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
+          <t>藤川 昌樹</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>太田 充</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
           <t>繁野 麻衣子</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>藤川 昌樹</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>太田 充</t>
-        </is>
-      </c>
       <c r="G62" t="n">
-        <v>0.2094625160098076</v>
+        <v>0.8412084877490997</v>
       </c>
       <c r="H62" t="n">
-        <v>0.2094019651412964</v>
+        <v>0.8337130546569824</v>
       </c>
       <c r="I62" t="n">
-        <v>0.2065354883670807</v>
+        <v>0.8296669721603394</v>
       </c>
     </row>
     <row r="63">
@@ -2995,27 +2995,27 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
+          <t>甲斐田 直子</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
           <t>岡田 幸彦</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>藤川 昌樹</t>
-        </is>
-      </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>太田 充</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>0.2012085765600204</v>
+        <v>0.8578905463218689</v>
       </c>
       <c r="H63" t="n">
-        <v>0.1913343966007233</v>
+        <v>0.8514300584793091</v>
       </c>
       <c r="I63" t="n">
-        <v>0.1904072314500809</v>
+        <v>0.8506066501140594</v>
       </c>
     </row>
     <row r="64">
@@ -3036,27 +3036,27 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
+          <t>甲斐田 直子</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>秋山 英三</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
           <t>岡田 幸彦</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>澤 亮治</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>甲斐田 直子</t>
-        </is>
-      </c>
       <c r="G64" t="n">
-        <v>0.1643966883420944</v>
+        <v>0.8607906699180603</v>
       </c>
       <c r="H64" t="n">
-        <v>0.1569813787937164</v>
+        <v>0.8573346734046936</v>
       </c>
       <c r="I64" t="n">
-        <v>0.152058020234108</v>
+        <v>0.8567694127559662</v>
       </c>
     </row>
     <row r="65">
@@ -3077,27 +3077,27 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
+          <t>渡邉 俊</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
           <t>有田 智一</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>藤井 さやか</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>川島 宏一</t>
-        </is>
-      </c>
       <c r="G65" t="n">
-        <v>0.4439074844121933</v>
+        <v>0.8773432672023773</v>
       </c>
       <c r="H65" t="n">
-        <v>0.4201424121856689</v>
+        <v>0.8766514658927917</v>
       </c>
       <c r="I65" t="n">
-        <v>0.4130714237689972</v>
+        <v>0.8733845949172974</v>
       </c>
     </row>
     <row r="66">
@@ -3118,27 +3118,27 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>山本 幸子</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>甲斐田 直子</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>有田 智一</t>
+          <t>渡邉 俊</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>0.4298336058855057</v>
+        <v>0.8660189807415009</v>
       </c>
       <c r="H66" t="n">
-        <v>0.4216112941503525</v>
+        <v>0.8657122552394867</v>
       </c>
       <c r="I66" t="n">
-        <v>0.4011538326740265</v>
+        <v>0.8648081421852112</v>
       </c>
     </row>
     <row r="67">
@@ -3159,27 +3159,27 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
+          <t>雨宮 護</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>渡邉 俊</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
           <t>岡田 幸彦</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>村上 暁信</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>太田 充</t>
-        </is>
-      </c>
       <c r="G67" t="n">
-        <v>0.2511622905731201</v>
+        <v>0.8575069308280945</v>
       </c>
       <c r="H67" t="n">
-        <v>0.2418305054306984</v>
+        <v>0.8562852144241333</v>
       </c>
       <c r="I67" t="n">
-        <v>0.2410106509923935</v>
+        <v>0.8543129563331604</v>
       </c>
     </row>
     <row r="68">
@@ -3200,7 +3200,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>上市 秀雄</t>
+          <t>澤 亮治</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3210,17 +3210,17 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>澤 亮治</t>
+          <t>原田 信行</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>0.3584244772791862</v>
+        <v>0.8587094247341156</v>
       </c>
       <c r="H68" t="n">
-        <v>0.3151032403111458</v>
+        <v>0.8550151884555817</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3104838728904724</v>
+        <v>0.8549315929412842</v>
       </c>
     </row>
     <row r="69">
@@ -3241,27 +3241,27 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
+          <t>秋山 英三</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>上市 秀雄</t>
+          <t>雨宮 護</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>藤川 昌樹</t>
+          <t>甲斐田 直子</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>0.3907737582921982</v>
+        <v>0.8701651096343994</v>
       </c>
       <c r="H69" t="n">
-        <v>0.3789228275418282</v>
+        <v>0.8668938279151917</v>
       </c>
       <c r="I69" t="n">
-        <v>0.3584048673510551</v>
+        <v>0.8668799698352814</v>
       </c>
     </row>
     <row r="70">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
+          <t>堤 盛人</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>上市 秀雄</t>
+          <t>原田 信行</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3296,13 +3296,13 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>0.3896287977695465</v>
+        <v>0.8791024386882782</v>
       </c>
       <c r="H70" t="n">
-        <v>0.3704666271805763</v>
+        <v>0.8728480637073517</v>
       </c>
       <c r="I70" t="n">
-        <v>0.3410095050930977</v>
+        <v>0.8702419698238373</v>
       </c>
     </row>
     <row r="71">
@@ -3323,27 +3323,27 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>太田 充</t>
+          <t>甲斐田 直子</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
+          <t>原田 信行</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>上市 秀雄</t>
+          <t>堤 盛人</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>0.3861951231956482</v>
+        <v>0.8686790764331818</v>
       </c>
       <c r="H71" t="n">
-        <v>0.3834148570895195</v>
+        <v>0.8682980537414551</v>
       </c>
       <c r="I71" t="n">
-        <v>0.3830224275588989</v>
+        <v>0.8650796711444855</v>
       </c>
     </row>
     <row r="72">
@@ -3364,27 +3364,27 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>太田 充</t>
+          <t>八森 正泰</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>八森 正泰</t>
+          <t>飛田 幹男</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>藤川 昌樹</t>
+          <t>浦田淳司</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>0.2903497666120529</v>
+        <v>0.8655970394611359</v>
       </c>
       <c r="H72" t="n">
-        <v>0.2871075384318829</v>
+        <v>0.8654685616493225</v>
       </c>
       <c r="I72" t="n">
-        <v>0.2862713262438774</v>
+        <v>0.8631964921951294</v>
       </c>
     </row>
     <row r="73">
@@ -3405,27 +3405,27 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
+          <t>Phung-Duc Tuan</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
           <t>大西 正輝</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>繆 瑩</t>
-        </is>
-      </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>有馬 澄佳</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>0.4246783778071404</v>
+        <v>0.8710783421993256</v>
       </c>
       <c r="H73" t="n">
-        <v>0.3745965585112572</v>
+        <v>0.8704829216003418</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3669904321432114</v>
+        <v>0.8681328892707825</v>
       </c>
     </row>
     <row r="74">
@@ -3446,27 +3446,27 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
+          <t>甲斐田 直子</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>浦田淳司</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
           <t>繁野 麻衣子</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>岡田 幸彦</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>和田 健太郎</t>
-        </is>
-      </c>
       <c r="G74" t="n">
-        <v>0.3353070840239525</v>
+        <v>0.877896249294281</v>
       </c>
       <c r="H74" t="n">
-        <v>0.3291667848825455</v>
+        <v>0.8770155608654022</v>
       </c>
       <c r="I74" t="n">
-        <v>0.3246199414134026</v>
+        <v>0.875188946723938</v>
       </c>
     </row>
     <row r="75">
@@ -3492,22 +3492,22 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
+          <t>Phung-Duc Tuan</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
           <t>繁野 麻衣子</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>有馬 澄佳</t>
-        </is>
-      </c>
       <c r="G75" t="n">
-        <v>0.450570359826088</v>
+        <v>0.8937357366085052</v>
       </c>
       <c r="H75" t="n">
-        <v>0.3969211876392365</v>
+        <v>0.882947713136673</v>
       </c>
       <c r="I75" t="n">
-        <v>0.3961055129766464</v>
+        <v>0.8791115880012512</v>
       </c>
     </row>
     <row r="76">
@@ -3533,22 +3533,22 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>繆 瑩</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Phung-Duc Tuan</t>
+          <t>作道 真理</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>0.4383934810757637</v>
+        <v>0.8748579323291779</v>
       </c>
       <c r="H76" t="n">
-        <v>0.4043017849326134</v>
+        <v>0.8651790022850037</v>
       </c>
       <c r="I76" t="n">
-        <v>0.3702045828104019</v>
+        <v>0.8583352863788605</v>
       </c>
     </row>
     <row r="77">
@@ -3579,17 +3579,17 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>有馬 澄佳</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>0.5287798643112183</v>
+        <v>0.8886218667030334</v>
       </c>
       <c r="H77" t="n">
-        <v>0.4284575283527374</v>
+        <v>0.8746299743652344</v>
       </c>
       <c r="I77" t="n">
-        <v>0.4224733039736748</v>
+        <v>0.8740542829036713</v>
       </c>
     </row>
     <row r="78">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>太田 充</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3624,13 +3624,13 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>0.456459254026413</v>
+        <v>0.880220502614975</v>
       </c>
       <c r="H78" t="n">
-        <v>0.4544224888086319</v>
+        <v>0.8740869164466858</v>
       </c>
       <c r="I78" t="n">
-        <v>0.4507510289549828</v>
+        <v>0.8736548125743866</v>
       </c>
     </row>
     <row r="79">
@@ -3651,27 +3651,27 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>甲斐田 直子</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>岡田 幸彦</t>
+          <t>渡邉 俊</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>渡邉 俊</t>
+          <t>雨宮 護</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>0.3246788121759892</v>
+        <v>0.8804406523704529</v>
       </c>
       <c r="H79" t="n">
-        <v>0.3242762088775635</v>
+        <v>0.8778083324432373</v>
       </c>
       <c r="I79" t="n">
-        <v>0.3006051108241081</v>
+        <v>0.8772007524967194</v>
       </c>
     </row>
     <row r="80">
@@ -3697,22 +3697,22 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>秋山 英三</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>岡田 幸彦</t>
+          <t>甲斐田 直子</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>0.4478202313184738</v>
+        <v>0.865395188331604</v>
       </c>
       <c r="H80" t="n">
-        <v>0.4457578659057617</v>
+        <v>0.8596368134021759</v>
       </c>
       <c r="I80" t="n">
-        <v>0.4033527970314026</v>
+        <v>0.8592325747013092</v>
       </c>
     </row>
     <row r="81">
@@ -3733,27 +3733,27 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>岡田 幸彦</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>上市 秀雄</t>
+          <t>雨宮 護</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>有馬 澄佳</t>
+          <t>堤 盛人</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>0.1961449086666107</v>
+        <v>0.8603357672691345</v>
       </c>
       <c r="H81" t="n">
-        <v>0.1940049156546593</v>
+        <v>0.8560177385807037</v>
       </c>
       <c r="I81" t="n">
-        <v>0.1939944177865982</v>
+        <v>0.8558715879917145</v>
       </c>
     </row>
     <row r="82">
@@ -3774,27 +3774,27 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
+          <t>原田 信行</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>甲斐田 直子</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
           <t>佐野 幸恵</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>上市 秀雄</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>甲斐田 直子</t>
-        </is>
-      </c>
       <c r="G82" t="n">
-        <v>0.3843019232153893</v>
+        <v>0.8518300950527191</v>
       </c>
       <c r="H82" t="n">
-        <v>0.3630199730396271</v>
+        <v>0.8514336049556732</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3488073945045471</v>
+        <v>0.8513353765010834</v>
       </c>
     </row>
     <row r="83">
@@ -3815,27 +3815,27 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>秋山 英三</t>
+          <t>原田 信行</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>太田 充</t>
+          <t>甲斐田 直子</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>上市 秀雄</t>
+          <t>作道 真理</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>0.4055556207895279</v>
+        <v>0.8639160990715027</v>
       </c>
       <c r="H83" t="n">
-        <v>0.3846563845872879</v>
+        <v>0.8579046726226807</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3839711621403694</v>
+        <v>0.8572237193584442</v>
       </c>
     </row>
     <row r="84">
@@ -3856,27 +3856,27 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
+          <t>甲斐田 直子</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
           <t>岡田 幸彦</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>村上 暁信</t>
-        </is>
-      </c>
       <c r="F84" t="inlineStr">
         <is>
           <t>繁野 麻衣子</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>0.3009283989667892</v>
+        <v>0.8577942550182343</v>
       </c>
       <c r="H84" t="n">
-        <v>0.2860175520181656</v>
+        <v>0.8510209619998932</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2770201861858368</v>
+        <v>0.8502745926380157</v>
       </c>
     </row>
   </sheetData>
@@ -3958,27 +3958,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>岡田 幸彦</t>
+          <t>繁野 麻衣子</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>高野 祐一</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>有馬 澄佳</t>
+          <t>吉瀬 章子</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.2748250067234039</v>
+        <v>0.862188994884491</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2631377428770065</v>
+        <v>0.858819305896759</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2612879052758217</v>
+        <v>0.8546646237373352</v>
       </c>
     </row>
     <row r="3">
@@ -3999,27 +3999,27 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>雨宮 護</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>浦田淳司</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>繆 瑩</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>高野 祐一</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>大西 正輝</t>
-        </is>
-      </c>
       <c r="G3" t="n">
-        <v>0.4564302563667297</v>
+        <v>0.8571438193321228</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3267651721835136</v>
+        <v>0.8564046025276184</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3092896118760109</v>
+        <v>0.855046272277832</v>
       </c>
     </row>
     <row r="4">
@@ -4040,27 +4040,27 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>繆 瑩</t>
+          <t>大西 正輝</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>繁野 麻衣子</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>吉瀬 章子</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>高野 祐一</t>
-        </is>
-      </c>
       <c r="G4" t="n">
-        <v>0.463890515267849</v>
+        <v>0.8557466268539429</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3707488477230072</v>
+        <v>0.853240042924881</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3511120900511742</v>
+        <v>0.8521353006362915</v>
       </c>
     </row>
     <row r="5">
@@ -4081,27 +4081,27 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>繆 瑩</t>
+          <t>大西 正輝</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>繁野 麻衣子</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>有馬 澄佳</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>吉瀬 章子</t>
-        </is>
-      </c>
       <c r="G5" t="n">
-        <v>0.4633695483207703</v>
+        <v>0.875066727399826</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4356444180011749</v>
+        <v>0.8710565567016602</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3982209712266922</v>
+        <v>0.8685732483863831</v>
       </c>
     </row>
     <row r="6">
@@ -4122,27 +4122,27 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>松原 康介</t>
+          <t>上市 秀雄</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>有田 智一</t>
+          <t>雨宮 護</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.4497134685516357</v>
+        <v>0.871045708656311</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4412962198257446</v>
+        <v>0.8696443438529968</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4383320212364197</v>
+        <v>0.8690361082553864</v>
       </c>
     </row>
     <row r="7">
@@ -4163,27 +4163,27 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>大西 正輝</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>繁野 麻衣子</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>秋山 英三</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>岡本 直久</t>
-        </is>
-      </c>
       <c r="G7" t="n">
-        <v>0.3910352289676666</v>
+        <v>0.8687897622585297</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3663668632507324</v>
+        <v>0.860876590013504</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3651508465409279</v>
+        <v>0.8586911857128143</v>
       </c>
     </row>
     <row r="8">
@@ -4204,27 +4204,27 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>大西 正輝</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>繆 瑩</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>有馬 澄佳</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>繁野 麻衣子</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.4170525930821896</v>
+        <v>0.8762173652648926</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3866965025663376</v>
+        <v>0.8738330900669098</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3755729645490646</v>
+        <v>0.8689559698104858</v>
       </c>
     </row>
     <row r="9">
@@ -4245,27 +4245,27 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>高野 祐一</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>岡田 幸彦</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>有馬 澄佳</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>繁野 麻衣子</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.2015916928648949</v>
+        <v>0.8533464968204498</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1840513050556183</v>
+        <v>0.8533048927783966</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1782828867435455</v>
+        <v>0.850794792175293</v>
       </c>
     </row>
     <row r="10">
@@ -4296,17 +4296,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>有馬 澄佳</t>
+          <t>澤 亮治</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.4206091910600662</v>
+        <v>0.8619266152381897</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4143236428499222</v>
+        <v>0.8615545630455017</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4112304002046585</v>
+        <v>0.8611488342285156</v>
       </c>
     </row>
     <row r="11">
@@ -4332,22 +4332,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>有馬 澄佳</t>
+          <t>繁野 麻衣子</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>高野 祐一</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.181618794798851</v>
+        <v>0.8465540111064911</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1752120852470398</v>
+        <v>0.8464995324611664</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1644988730549812</v>
+        <v>0.8445603251457214</v>
       </c>
     </row>
     <row r="12">
@@ -4373,22 +4373,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>繁野 麻衣子</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>岡田 幸彦</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>有馬 澄佳</t>
-        </is>
-      </c>
       <c r="G12" t="n">
-        <v>0.3730254918336868</v>
+        <v>0.8796535432338715</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2587501555681229</v>
+        <v>0.8640227913856506</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2458886578679085</v>
+        <v>0.8568365573883057</v>
       </c>
     </row>
     <row r="13">
@@ -4409,27 +4409,27 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>佐野 幸恵</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>岡田 幸彦</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>繁野 麻衣子</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>雨宮 護</t>
+          <t>上市 秀雄</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.1883506327867508</v>
+        <v>0.8531846702098846</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1852785721421242</v>
+        <v>0.843764066696167</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1832002848386765</v>
+        <v>0.842092365026474</v>
       </c>
     </row>
     <row r="14">
@@ -4450,27 +4450,27 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>奥島 真一郎</t>
+          <t>岡田 幸彦</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>太田 充</t>
+          <t>黒瀬 雄大</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>堤 盛人</t>
+          <t>高野 祐一</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.2905746102333069</v>
+        <v>0.8570942282676697</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2816853374242783</v>
+        <v>0.8538691699504852</v>
       </c>
       <c r="I14" t="n">
-        <v>0.277130126953125</v>
+        <v>0.8538650572299957</v>
       </c>
     </row>
     <row r="15">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>太田 充</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>有馬 澄佳</t>
+          <t>黒瀬 雄大</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.1771631836891174</v>
+        <v>0.8393575847148895</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1649222671985626</v>
+        <v>0.8330047726631165</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1631815358996391</v>
+        <v>0.8324172794818878</v>
       </c>
     </row>
     <row r="16">
@@ -4542,17 +4542,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>有馬 澄佳</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.487185537815094</v>
+        <v>0.8683789074420929</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4218198657035828</v>
+        <v>0.8614305257797241</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4043929651379585</v>
+        <v>0.85704305768013</v>
       </c>
     </row>
     <row r="17">
@@ -4578,22 +4578,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>岡田 幸彦</t>
+          <t>高野 祐一</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>有馬 澄佳</t>
+          <t>吉瀬 章子</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0.2768545597791672</v>
+        <v>0.8672901391983032</v>
       </c>
       <c r="H17" t="n">
-        <v>0.255385585129261</v>
+        <v>0.8645013272762299</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2494091615080833</v>
+        <v>0.8597360551357269</v>
       </c>
     </row>
     <row r="18">
@@ -4624,17 +4624,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>渡邉 俊</t>
+          <t>岡本 直久</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0.2090619057416916</v>
+        <v>0.8459638953208923</v>
       </c>
       <c r="H18" t="n">
-        <v>0.205047395080328</v>
+        <v>0.8379291594028473</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2041157111525536</v>
+        <v>0.8348133265972137</v>
       </c>
     </row>
     <row r="19">
@@ -4655,27 +4655,27 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>繆 瑩</t>
+          <t>吉瀬 章子</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>高野 祐一</t>
+          <t>大西 正輝</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>有馬 澄佳</t>
+          <t>繁野 麻衣子</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0.4665180593729019</v>
+        <v>0.8622571527957916</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3540980964899063</v>
+        <v>0.8603937029838562</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3519240468740463</v>
+        <v>0.8602149486541748</v>
       </c>
     </row>
     <row r="20">
@@ -4696,27 +4696,27 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>上市 秀雄</t>
+          <t>岡田 幸彦</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>岡田 幸彦</t>
+          <t>澤 亮治</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>澤 亮治</t>
+          <t>秋山 英三</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0.4405992329120636</v>
+        <v>0.8785312175750732</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4024849757552147</v>
+        <v>0.8755816221237183</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3827997595071793</v>
+        <v>0.8698488175868988</v>
       </c>
     </row>
     <row r="21">
@@ -4737,27 +4737,27 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>吉瀬 章子</t>
+          <t>大西 正輝</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>繆 瑩</t>
+          <t>雨宮 護</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>高野 祐一</t>
+          <t>浦田淳司</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0.4228997677564621</v>
+        <v>0.8697235882282257</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4059822373092175</v>
+        <v>0.8666972517967224</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3880046159029007</v>
+        <v>0.8661553859710693</v>
       </c>
     </row>
     <row r="22">
@@ -4778,27 +4778,27 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>有田 智一</t>
+          <t>原田 信行</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>藤川 昌樹</t>
+          <t>岡田 幸彦</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>堤 盛人</t>
+          <t>黒瀬 雄大</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.4134034663438797</v>
+        <v>0.8749107420444489</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3978354260325432</v>
+        <v>0.8701186776161194</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3928539976477623</v>
+        <v>0.868733823299408</v>
       </c>
     </row>
   </sheetData>

--- a/generated/committee_recommendations.xlsx
+++ b/generated/committee_recommendations.xlsx
@@ -494,27 +494,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>原田 信行</t>
+          <t>上市 秀雄</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>澤 亮治</t>
+          <t>髙橋裕紀</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>堤 盛人</t>
+          <t>秋山 英三</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.8848052024841309</v>
+        <v>0.8622280657291412</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8768253028392792</v>
+        <v>0.860817015171051</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8756940066814423</v>
+        <v>0.856243759393692</v>
       </c>
     </row>
     <row r="3">
@@ -535,27 +535,27 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>高野 祐一</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>岡田 幸彦</t>
+          <t>秋山 英三</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>原田 信行</t>
+          <t>太田 充</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.8693127036094666</v>
+        <v>0.867502748966217</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8668391108512878</v>
+        <v>0.8587009906768799</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8660216927528381</v>
+        <v>0.8585590720176697</v>
       </c>
     </row>
     <row r="4">
@@ -576,27 +576,27 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>澤 亮治</t>
+          <t>上市 秀雄</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>上市 秀雄</t>
+          <t>髙橋裕紀</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>原田 信行</t>
+          <t>秋山 英三</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.8791826665401459</v>
+        <v>0.8694976568222046</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8787448704242706</v>
+        <v>0.8618543148040771</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8747391700744629</v>
+        <v>0.8569416403770447</v>
       </c>
     </row>
     <row r="5">
@@ -617,27 +617,27 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>澤 亮治</t>
+          <t>高野 祐一</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>原田 信行</t>
+          <t>吉瀬 章子</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>高野 祐一</t>
+          <t>髙橋裕紀</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.8856546580791473</v>
+        <v>0.8732118904590607</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8759098052978516</v>
+        <v>0.8708003759384155</v>
       </c>
       <c r="I5" t="n">
-        <v>0.87310791015625</v>
+        <v>0.8691686987876892</v>
       </c>
     </row>
     <row r="6">
@@ -658,27 +658,27 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>作道 真理</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>岡田 幸彦</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>原田 信行</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>秋山 英三</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.8744120597839355</v>
+        <v>0.8707860708236694</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8719078898429871</v>
+        <v>0.8629058003425598</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8683663904666901</v>
+        <v>0.8617391288280487</v>
       </c>
     </row>
     <row r="7">
@@ -699,27 +699,27 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>上市 秀雄</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>秋山 英三</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>甲斐田 直子</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>上市 秀雄</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>秋山 英三</t>
-        </is>
-      </c>
       <c r="G7" t="n">
-        <v>0.8821147382259369</v>
+        <v>0.8775012493133545</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8790072798728943</v>
+        <v>0.873183935880661</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8756900429725647</v>
+        <v>0.8704139590263367</v>
       </c>
     </row>
     <row r="8">
@@ -745,22 +745,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>八森 正泰</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Phung-Duc Tuan</t>
+          <t>繆 瑩</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.876313328742981</v>
+        <v>0.8788286447525024</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8706642985343933</v>
+        <v>0.8646557033061981</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8669158816337585</v>
+        <v>0.8591321110725403</v>
       </c>
     </row>
     <row r="9">
@@ -786,22 +786,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Phung-Duc Tuan</t>
+          <t>高野 祐一</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>黒瀬 雄大</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.8768597841262817</v>
+        <v>0.868406355381012</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8675379455089569</v>
+        <v>0.8616978526115417</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8638555705547333</v>
+        <v>0.8596908450126648</v>
       </c>
     </row>
     <row r="10">
@@ -822,27 +822,27 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>鈴木 勉</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>太田 充</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>堤 盛人</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>鈴木 勉</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>雨宮 護</t>
-        </is>
-      </c>
       <c r="G10" t="n">
-        <v>0.8745534121990204</v>
+        <v>0.8736737668514252</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8721719980239868</v>
+        <v>0.8708745837211609</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8710920810699463</v>
+        <v>0.8708597719669342</v>
       </c>
     </row>
     <row r="11">
@@ -863,27 +863,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>八森 正泰</t>
+          <t>吉瀬 章子</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>繁野 麻衣子</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>浦田淳司</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>繁野 麻衣子</t>
-        </is>
-      </c>
       <c r="G11" t="n">
-        <v>0.8750033974647522</v>
+        <v>0.871646523475647</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8726652562618256</v>
+        <v>0.8702176809310913</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8723176121711731</v>
+        <v>0.8686382174491882</v>
       </c>
     </row>
     <row r="12">
@@ -904,27 +904,27 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>佐野 幸恵</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>澤 亮治</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>繁野 麻衣子</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>岡田 幸彦</t>
+          <t>上市 秀雄</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.8597085773944855</v>
+        <v>0.8563922941684723</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8590877652168274</v>
+        <v>0.853992760181427</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8567173480987549</v>
+        <v>0.8530559241771698</v>
       </c>
     </row>
     <row r="13">
@@ -955,17 +955,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>作道 真理</t>
+          <t>繆 瑩</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.8433670103549957</v>
+        <v>0.8606098890304565</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8428361415863037</v>
+        <v>0.8565657436847687</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8402458429336548</v>
+        <v>0.8463118970394135</v>
       </c>
     </row>
     <row r="14">
@@ -986,27 +986,27 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>作道 真理</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>八森 正泰</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>岡本 直久</t>
+          <t>繁野 麻衣子</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.8757067024707794</v>
+        <v>0.8741859197616577</v>
       </c>
       <c r="H14" t="n">
-        <v>0.875690758228302</v>
+        <v>0.8717276751995087</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8736236691474915</v>
+        <v>0.8688391745090485</v>
       </c>
     </row>
     <row r="15">
@@ -1032,22 +1032,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>大西 正輝</t>
+          <t>和田 健太郎</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>浦田淳司</t>
+          <t>吉瀬 章子</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.8783397376537323</v>
+        <v>0.8765020668506622</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8763073980808258</v>
+        <v>0.8727556467056274</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8728134036064148</v>
+        <v>0.871123731136322</v>
       </c>
     </row>
     <row r="16">
@@ -1078,17 +1078,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>髙橋裕紀</t>
+          <t>吉瀬 章子</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.8736388683319092</v>
+        <v>0.880088746547699</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8663072884082794</v>
+        <v>0.8798215389251709</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8623422682285309</v>
+        <v>0.8703469336032867</v>
       </c>
     </row>
     <row r="17">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>澤 亮治</t>
+          <t>髙橋裕紀</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1119,17 +1119,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>甲斐田 直子</t>
+          <t>上市 秀雄</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0.8675330877304077</v>
+        <v>0.860830545425415</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8611766695976257</v>
+        <v>0.860471248626709</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8608874678611755</v>
+        <v>0.8592727482318878</v>
       </c>
     </row>
     <row r="18">
@@ -1150,27 +1150,27 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>繆 瑩</t>
+          <t>高野 祐一</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>有馬 澄佳</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>黒瀬 雄大</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>繁野 麻衣子</t>
-        </is>
-      </c>
       <c r="G18" t="n">
-        <v>0.8702408373355865</v>
+        <v>0.8734438419342041</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8691293001174927</v>
+        <v>0.8697305023670197</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8680429458618164</v>
+        <v>0.8687523305416107</v>
       </c>
     </row>
     <row r="19">
@@ -1191,27 +1191,27 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>イリチュ 美佳</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>岡田 幸彦</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>繁野 麻衣子</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>甲斐田 直子</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0.8696708679199219</v>
+        <v>0.8666941523551941</v>
       </c>
       <c r="H19" t="n">
-        <v>0.868317723274231</v>
+        <v>0.8642557859420776</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8637782335281372</v>
+        <v>0.8628633618354797</v>
       </c>
     </row>
     <row r="20">
@@ -1232,27 +1232,27 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Phung-Duc Tuan</t>
+          <t>澤 亮治</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>和田 健太郎</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>秋山 英三</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>谷口 綾子</t>
-        </is>
-      </c>
       <c r="G20" t="n">
-        <v>0.8816474974155426</v>
+        <v>0.8812617063522339</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8761932849884033</v>
+        <v>0.8769907653331757</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8759990930557251</v>
+        <v>0.8655136823654175</v>
       </c>
     </row>
     <row r="21">
@@ -1283,17 +1283,17 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>髙橋裕紀</t>
+          <t>吉瀬 章子</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0.8575855791568756</v>
+        <v>0.8566152155399323</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8572642803192139</v>
+        <v>0.8559147119522095</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8561837077140808</v>
+        <v>0.8549613058567047</v>
       </c>
     </row>
     <row r="22">
@@ -1319,22 +1319,22 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>鈴木 勉</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>渡邉 俊</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>鈴木 勉</t>
-        </is>
-      </c>
       <c r="G22" t="n">
-        <v>0.8822779059410095</v>
+        <v>0.8830437958240509</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8764758110046387</v>
+        <v>0.8812804818153381</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8735903799533844</v>
+        <v>0.8750165104866028</v>
       </c>
     </row>
     <row r="23">
@@ -1355,27 +1355,27 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>岡田 幸彦</t>
+          <t>黒瀬 雄大</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>甲斐田 直子</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0.8626037240028381</v>
+        <v>0.8554224669933319</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8603973388671875</v>
+        <v>0.8533744513988495</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8597329556941986</v>
+        <v>0.8531850874423981</v>
       </c>
     </row>
     <row r="24">
@@ -1396,27 +1396,27 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>イリチュ 美佳</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>原田 信行</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>作道 真理</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>澤 亮治</t>
-        </is>
-      </c>
       <c r="G24" t="n">
-        <v>0.8749946355819702</v>
+        <v>0.8565972447395325</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8652920126914978</v>
+        <v>0.8563653528690338</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8621540665626526</v>
+        <v>0.8553677499294281</v>
       </c>
     </row>
     <row r="25">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>原田 信行</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
+          <t>上市 秀雄</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0.8712714612483978</v>
+        <v>0.8749534487724304</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8705659508705139</v>
+        <v>0.8748263418674469</v>
       </c>
       <c r="I25" t="n">
-        <v>0.8689519762992859</v>
+        <v>0.8660167157649994</v>
       </c>
     </row>
     <row r="26">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>原田 信行</t>
+          <t>作道 真理</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1488,17 +1488,17 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>作道 真理</t>
+          <t>黒瀬 雄大</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0.878558874130249</v>
+        <v>0.8669944107532501</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8698205053806305</v>
+        <v>0.8630058169364929</v>
       </c>
       <c r="I26" t="n">
-        <v>0.8683366775512695</v>
+        <v>0.8572041392326355</v>
       </c>
     </row>
     <row r="27">
@@ -1524,22 +1524,22 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>原田 信行</t>
+          <t>岡田 幸彦</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>作道 真理</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0.8689084053039551</v>
+        <v>0.861872673034668</v>
       </c>
       <c r="H27" t="n">
-        <v>0.866457462310791</v>
+        <v>0.8589910268783569</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8636112809181213</v>
+        <v>0.8534484505653381</v>
       </c>
     </row>
     <row r="28">
@@ -1560,27 +1560,27 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>繁野 麻衣子</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>有馬 澄佳</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>繁野 麻衣子</t>
-        </is>
-      </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>大西 正輝</t>
+          <t>吉瀬 章子</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0.8729794323444366</v>
+        <v>0.8814447820186615</v>
       </c>
       <c r="H28" t="n">
-        <v>0.8698991537094116</v>
+        <v>0.8795143067836761</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8678604066371918</v>
+        <v>0.8726982176303864</v>
       </c>
     </row>
     <row r="29">
@@ -1606,22 +1606,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>岡田 幸彦</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>岡田 幸彦</t>
+          <t>高野 祐一</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0.8743135333061218</v>
+        <v>0.8719902336597443</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8710212707519531</v>
+        <v>0.8634964525699615</v>
       </c>
       <c r="I29" t="n">
-        <v>0.8706225752830505</v>
+        <v>0.8624171614646912</v>
       </c>
     </row>
     <row r="30">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>髙橋裕紀</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1656,13 +1656,13 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0.8728483319282532</v>
+        <v>0.8809157311916351</v>
       </c>
       <c r="H30" t="n">
-        <v>0.8566639721393585</v>
+        <v>0.8686379790306091</v>
       </c>
       <c r="I30" t="n">
-        <v>0.8563459515571594</v>
+        <v>0.8590868711471558</v>
       </c>
     </row>
     <row r="31">
@@ -1683,27 +1683,27 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t>秋山 英三</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>作道 真理</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t>原田 信行</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>秋山 英三</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>甲斐田 直子</t>
-        </is>
-      </c>
       <c r="G31" t="n">
-        <v>0.8736870586872101</v>
+        <v>0.8641783893108368</v>
       </c>
       <c r="H31" t="n">
-        <v>0.8708910942077637</v>
+        <v>0.8617948591709137</v>
       </c>
       <c r="I31" t="n">
-        <v>0.8651430904865265</v>
+        <v>0.8604422211647034</v>
       </c>
     </row>
     <row r="32">
@@ -1724,27 +1724,27 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t>川島 宏一</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>佐野 幸恵</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t>甲斐田 直子</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>雨宮 護</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>佐野 幸恵</t>
-        </is>
-      </c>
       <c r="G32" t="n">
-        <v>0.8561131954193115</v>
+        <v>0.8584904074668884</v>
       </c>
       <c r="H32" t="n">
-        <v>0.8527567386627197</v>
+        <v>0.8578586578369141</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8503190577030182</v>
+        <v>0.8513690233230591</v>
       </c>
     </row>
     <row r="33">
@@ -1765,27 +1765,27 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>雨宮 護</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>藤井 さやか</t>
+          <t>甲斐田 直子</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>甲斐田 直子</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0.8680321872234344</v>
+        <v>0.863069623708725</v>
       </c>
       <c r="H33" t="n">
-        <v>0.8663512766361237</v>
+        <v>0.8602399826049805</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8609660863876343</v>
+        <v>0.8586323261260986</v>
       </c>
     </row>
     <row r="34">
@@ -1811,22 +1811,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>藤井 さやか</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>渡邉 俊</t>
+          <t>村上 暁信</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0.8717754483222961</v>
+        <v>0.8694185614585876</v>
       </c>
       <c r="H34" t="n">
-        <v>0.8688279688358307</v>
+        <v>0.8680724501609802</v>
       </c>
       <c r="I34" t="n">
-        <v>0.8672304451465607</v>
+        <v>0.8633807599544525</v>
       </c>
     </row>
     <row r="35">
@@ -1847,27 +1847,27 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>藤井 さやか</t>
+          <t>有田 智一</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>渡邉 俊</t>
+          <t>山本 幸子</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>村上 暁信</t>
+          <t>太田 充</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0.8760980069637299</v>
+        <v>0.8825912475585938</v>
       </c>
       <c r="H35" t="n">
-        <v>0.8746935427188873</v>
+        <v>0.8784309923648834</v>
       </c>
       <c r="I35" t="n">
-        <v>0.873765230178833</v>
+        <v>0.8758960366249084</v>
       </c>
     </row>
     <row r="36">
@@ -1888,27 +1888,27 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t>太田 充</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>村上 暁信</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>太田 充</t>
-        </is>
-      </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>甲斐田 直子</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0.8773117661476135</v>
+        <v>0.8779982924461365</v>
       </c>
       <c r="H36" t="n">
-        <v>0.875573992729187</v>
+        <v>0.874761164188385</v>
       </c>
       <c r="I36" t="n">
-        <v>0.8741279244422913</v>
+        <v>0.8702944219112396</v>
       </c>
     </row>
     <row r="37">
@@ -1934,22 +1934,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>岡田 幸彦</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>甲斐田 直子</t>
+          <t>太田 充</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0.8822030425071716</v>
+        <v>0.8806043863296509</v>
       </c>
       <c r="H37" t="n">
-        <v>0.877425342798233</v>
+        <v>0.8754421770572662</v>
       </c>
       <c r="I37" t="n">
-        <v>0.8771246671676636</v>
+        <v>0.875201553106308</v>
       </c>
     </row>
     <row r="38">
@@ -1970,27 +1970,27 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t>川島 宏一</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
           <t>山本 幸子</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>藤井 さやか</t>
-        </is>
-      </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>原田 信行</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0.8677642643451691</v>
+        <v>0.8702716529369354</v>
       </c>
       <c r="H38" t="n">
-        <v>0.8663949072360992</v>
+        <v>0.8665628135204315</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8658533990383148</v>
+        <v>0.8636845648288727</v>
       </c>
     </row>
     <row r="39">
@@ -2011,27 +2011,27 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t>鈴木 勉</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
           <t>川島 宏一</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>雨宮 護</t>
-        </is>
-      </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>太田 充</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0.8803601562976837</v>
+        <v>0.8863994181156158</v>
       </c>
       <c r="H39" t="n">
-        <v>0.8787698745727539</v>
+        <v>0.8796985745429993</v>
       </c>
       <c r="I39" t="n">
-        <v>0.8784969449043274</v>
+        <v>0.8795591592788696</v>
       </c>
     </row>
     <row r="40">
@@ -2052,27 +2052,27 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t>堤 盛人</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
           <t>太田 充</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>堤 盛人</t>
-        </is>
-      </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>甲斐田 直子</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0.884984940290451</v>
+        <v>0.8820393085479736</v>
       </c>
       <c r="H40" t="n">
-        <v>0.8826780319213867</v>
+        <v>0.8811213672161102</v>
       </c>
       <c r="I40" t="n">
-        <v>0.8774478733539581</v>
+        <v>0.8794645071029663</v>
       </c>
     </row>
     <row r="41">
@@ -2093,27 +2093,27 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t>川島 宏一</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
           <t>堤 盛人</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>川島 宏一</t>
-        </is>
-      </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>松原 康介</t>
+          <t>太田 充</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0.8720704913139343</v>
+        <v>0.8671340346336365</v>
       </c>
       <c r="H41" t="n">
-        <v>0.8697050213813782</v>
+        <v>0.8669663369655609</v>
       </c>
       <c r="I41" t="n">
-        <v>0.8684079647064209</v>
+        <v>0.8657203912734985</v>
       </c>
     </row>
     <row r="42">
@@ -2139,22 +2139,22 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>秋山 英三</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>岡田 幸彦</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0.8570056855678558</v>
+        <v>0.8661057353019714</v>
       </c>
       <c r="H42" t="n">
-        <v>0.8475772440433502</v>
+        <v>0.8625563383102417</v>
       </c>
       <c r="I42" t="n">
-        <v>0.8470962643623352</v>
+        <v>0.8523598313331604</v>
       </c>
     </row>
     <row r="43">
@@ -2180,22 +2180,22 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>藤井 さやか</t>
+          <t>雨宮 護</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>雨宮 護</t>
+          <t>村上 暁信</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0.8702762126922607</v>
+        <v>0.8712981641292572</v>
       </c>
       <c r="H43" t="n">
-        <v>0.8699823319911957</v>
+        <v>0.8678552508354187</v>
       </c>
       <c r="I43" t="n">
-        <v>0.8686732649803162</v>
+        <v>0.8676274418830872</v>
       </c>
     </row>
     <row r="44">
@@ -2226,17 +2226,17 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>村上 暁信</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0.8487688601016998</v>
+        <v>0.8639198839664459</v>
       </c>
       <c r="H44" t="n">
-        <v>0.8464263081550598</v>
+        <v>0.8630452156066895</v>
       </c>
       <c r="I44" t="n">
-        <v>0.8433281183242798</v>
+        <v>0.8629290461540222</v>
       </c>
     </row>
     <row r="45">
@@ -2257,27 +2257,27 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t>渡邉 俊</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>藤川 昌樹</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t>松原 康介</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>渡邉 俊</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>藤川 昌樹</t>
-        </is>
-      </c>
       <c r="G45" t="n">
-        <v>0.8856144547462463</v>
+        <v>0.8861710727214813</v>
       </c>
       <c r="H45" t="n">
-        <v>0.8848127126693726</v>
+        <v>0.8844046294689178</v>
       </c>
       <c r="I45" t="n">
-        <v>0.8812952637672424</v>
+        <v>0.8839033246040344</v>
       </c>
     </row>
     <row r="46">
@@ -2298,27 +2298,27 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>岡本 直久</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>渡邉 俊</t>
+          <t>繁野 麻衣子</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>八森 正泰</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0.87106853723526</v>
+        <v>0.8671504259109497</v>
       </c>
       <c r="H46" t="n">
-        <v>0.8708507418632507</v>
+        <v>0.8651044368743896</v>
       </c>
       <c r="I46" t="n">
-        <v>0.8703113496303558</v>
+        <v>0.8631814122200012</v>
       </c>
     </row>
     <row r="47">
@@ -2344,22 +2344,22 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
+          <t>太田 充</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
           <t>有田 智一</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>太田 充</t>
-        </is>
-      </c>
       <c r="G47" t="n">
-        <v>0.8803860545158386</v>
+        <v>0.8827366232872009</v>
       </c>
       <c r="H47" t="n">
-        <v>0.8798553049564362</v>
+        <v>0.8823181688785553</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8788651823997498</v>
+        <v>0.8821680843830109</v>
       </c>
     </row>
     <row r="48">
@@ -2380,27 +2380,27 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t>岡本 直久</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>川島 宏一</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
           <t>甲斐田 直子</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>岡本 直久</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>雨宮 護</t>
-        </is>
-      </c>
       <c r="G48" t="n">
-        <v>0.8730646371841431</v>
+        <v>0.8742204904556274</v>
       </c>
       <c r="H48" t="n">
-        <v>0.8723333775997162</v>
+        <v>0.865276575088501</v>
       </c>
       <c r="I48" t="n">
-        <v>0.868208110332489</v>
+        <v>0.8646620213985443</v>
       </c>
     </row>
     <row r="49">
@@ -2421,27 +2421,27 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t>岡本 直久</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>藤川 昌樹</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
           <t>渡邉 俊</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>太田 充</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>藤川 昌樹</t>
-        </is>
-      </c>
       <c r="G49" t="n">
-        <v>0.8705888986587524</v>
+        <v>0.871150940656662</v>
       </c>
       <c r="H49" t="n">
-        <v>0.8669873476028442</v>
+        <v>0.8686563372612</v>
       </c>
       <c r="I49" t="n">
-        <v>0.8661882281303406</v>
+        <v>0.8679154217243195</v>
       </c>
     </row>
     <row r="50">
@@ -2472,17 +2472,17 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>雨宮 護</t>
+          <t>谷口 綾子</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>0.8833150863647461</v>
+        <v>0.8828504681587219</v>
       </c>
       <c r="H50" t="n">
-        <v>0.8816799223423004</v>
+        <v>0.8822090625762939</v>
       </c>
       <c r="I50" t="n">
-        <v>0.8803482055664062</v>
+        <v>0.8808643221855164</v>
       </c>
     </row>
     <row r="51">
@@ -2508,22 +2508,22 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>秋山 英三</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>岡田 幸彦</t>
+          <t>浦田淳司</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>0.8630247712135315</v>
+        <v>0.8735898435115814</v>
       </c>
       <c r="H51" t="n">
-        <v>0.8506519198417664</v>
+        <v>0.8624788522720337</v>
       </c>
       <c r="I51" t="n">
-        <v>0.8482785820960999</v>
+        <v>0.8617882430553436</v>
       </c>
     </row>
     <row r="52">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>岡田 幸彦</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2558,13 +2558,13 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>0.8618446588516235</v>
+        <v>0.8638397455215454</v>
       </c>
       <c r="H52" t="n">
-        <v>0.8603324294090271</v>
+        <v>0.861793041229248</v>
       </c>
       <c r="I52" t="n">
-        <v>0.8595001697540283</v>
+        <v>0.8616099953651428</v>
       </c>
     </row>
     <row r="53">
@@ -2585,27 +2585,27 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>藤井 さやか</t>
+          <t>太田 充</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>雨宮 護</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>渡邉 俊</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>0.880888044834137</v>
+        <v>0.8731994032859802</v>
       </c>
       <c r="H53" t="n">
-        <v>0.8738102912902832</v>
+        <v>0.872426450252533</v>
       </c>
       <c r="I53" t="n">
-        <v>0.8714291453361511</v>
+        <v>0.8680101335048676</v>
       </c>
     </row>
     <row r="54">
@@ -2631,22 +2631,22 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>雨宮 護</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>村上 暁信</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>0.8651339709758759</v>
+        <v>0.8633367717266083</v>
       </c>
       <c r="H54" t="n">
-        <v>0.859698623418808</v>
+        <v>0.862301766872406</v>
       </c>
       <c r="I54" t="n">
-        <v>0.8588502407073975</v>
+        <v>0.8590896129608154</v>
       </c>
     </row>
     <row r="55">
@@ -2672,22 +2672,22 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>堤 盛人</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>甲斐田 直子</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>0.8542676866054535</v>
+        <v>0.8567630350589752</v>
       </c>
       <c r="H55" t="n">
-        <v>0.8511963486671448</v>
+        <v>0.8559862971305847</v>
       </c>
       <c r="I55" t="n">
-        <v>0.849749356508255</v>
+        <v>0.8537361323833466</v>
       </c>
     </row>
     <row r="56">
@@ -2708,27 +2708,27 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>山本 幸子</t>
+          <t>岡本 直久</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>藤井 さやか</t>
+          <t>和田 健太郎</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>和田 健太郎</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>0.859814316034317</v>
+        <v>0.8790489733219147</v>
       </c>
       <c r="H56" t="n">
-        <v>0.859036386013031</v>
+        <v>0.8749516904354095</v>
       </c>
       <c r="I56" t="n">
-        <v>0.8581754565238953</v>
+        <v>0.8738730251789093</v>
       </c>
     </row>
     <row r="57">
@@ -2754,22 +2754,22 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>岡田 幸彦</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>上市 秀雄</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>0.8475391864776611</v>
+        <v>0.8533106446266174</v>
       </c>
       <c r="H57" t="n">
-        <v>0.8461900353431702</v>
+        <v>0.8527741730213165</v>
       </c>
       <c r="I57" t="n">
-        <v>0.8431481719017029</v>
+        <v>0.8522745966911316</v>
       </c>
     </row>
     <row r="58">
@@ -2790,27 +2790,27 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>和田 健太郎</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>作道 真理</t>
+          <t>浦田淳司</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>岡田 幸彦</t>
+          <t>甲斐田 直子</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>0.8584452867507935</v>
+        <v>0.8704012036323547</v>
       </c>
       <c r="H58" t="n">
-        <v>0.8539338707923889</v>
+        <v>0.8699492812156677</v>
       </c>
       <c r="I58" t="n">
-        <v>0.8530483841896057</v>
+        <v>0.8684483170509338</v>
       </c>
     </row>
     <row r="59">
@@ -2831,12 +2831,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>大西 正輝</t>
+          <t>岡本 直久</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Phung-Duc Tuan</t>
+          <t>和田 健太郎</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2845,13 +2845,13 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>0.8807176947593689</v>
+        <v>0.8815852403640747</v>
       </c>
       <c r="H59" t="n">
-        <v>0.8800468444824219</v>
+        <v>0.8759791851043701</v>
       </c>
       <c r="I59" t="n">
-        <v>0.8795809149742126</v>
+        <v>0.8754019439220428</v>
       </c>
     </row>
     <row r="60">
@@ -2872,27 +2872,27 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>飛田 幹男</t>
+          <t>黒瀬 雄大</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>黒瀬 雄大</t>
+          <t>浦田淳司</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>浦田淳司</t>
+          <t>雨宮 護</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>0.8769747614860535</v>
+        <v>0.8791487216949463</v>
       </c>
       <c r="H60" t="n">
-        <v>0.87520432472229</v>
+        <v>0.8711142539978027</v>
       </c>
       <c r="I60" t="n">
-        <v>0.8735997974872589</v>
+        <v>0.8695277869701385</v>
       </c>
     </row>
     <row r="61">
@@ -2918,22 +2918,22 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
+          <t>川島 宏一</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
           <t>村上 暁信</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>渡邉 俊</t>
-        </is>
-      </c>
       <c r="G61" t="n">
-        <v>0.8747804462909698</v>
+        <v>0.8794030249118805</v>
       </c>
       <c r="H61" t="n">
-        <v>0.8732750713825226</v>
+        <v>0.8770883679389954</v>
       </c>
       <c r="I61" t="n">
-        <v>0.8700069189071655</v>
+        <v>0.8749685883522034</v>
       </c>
     </row>
     <row r="62">
@@ -2954,27 +2954,27 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
+          <t>佐野 幸恵</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
           <t>藤川 昌樹</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>太田 充</t>
-        </is>
-      </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>0.8412084877490997</v>
+        <v>0.8362932205200195</v>
       </c>
       <c r="H62" t="n">
-        <v>0.8337130546569824</v>
+        <v>0.8355565071105957</v>
       </c>
       <c r="I62" t="n">
-        <v>0.8296669721603394</v>
+        <v>0.8333501219749451</v>
       </c>
     </row>
     <row r="63">
@@ -3000,22 +3000,22 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>岡田 幸彦</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>0.8578905463218689</v>
+        <v>0.866408497095108</v>
       </c>
       <c r="H63" t="n">
-        <v>0.8514300584793091</v>
+        <v>0.8644002377986908</v>
       </c>
       <c r="I63" t="n">
-        <v>0.8506066501140594</v>
+        <v>0.8616088330745697</v>
       </c>
     </row>
     <row r="64">
@@ -3041,22 +3041,22 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>秋山 英三</t>
+          <t>谷口 綾子</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>岡田 幸彦</t>
+          <t>奥島 真一郎</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>0.8607906699180603</v>
+        <v>0.8800965547561646</v>
       </c>
       <c r="H64" t="n">
-        <v>0.8573346734046936</v>
+        <v>0.8643222451210022</v>
       </c>
       <c r="I64" t="n">
-        <v>0.8567694127559662</v>
+        <v>0.8599986732006073</v>
       </c>
     </row>
     <row r="65">
@@ -3077,27 +3077,27 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
+          <t>有田 智一</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
           <t>渡邉 俊</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>有田 智一</t>
-        </is>
-      </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>藤井 さやか</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>0.8773432672023773</v>
+        <v>0.87774258852005</v>
       </c>
       <c r="H65" t="n">
-        <v>0.8766514658927917</v>
+        <v>0.8765729069709778</v>
       </c>
       <c r="I65" t="n">
-        <v>0.8733845949172974</v>
+        <v>0.8751640915870667</v>
       </c>
     </row>
     <row r="66">
@@ -3123,22 +3123,22 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>甲斐田 直子</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>渡邉 俊</t>
+          <t>有田 智一</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>0.8660189807415009</v>
+        <v>0.8760607540607452</v>
       </c>
       <c r="H66" t="n">
-        <v>0.8657122552394867</v>
+        <v>0.868501752614975</v>
       </c>
       <c r="I66" t="n">
-        <v>0.8648081421852112</v>
+        <v>0.8683378994464874</v>
       </c>
     </row>
     <row r="67">
@@ -3159,27 +3159,27 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>雨宮 護</t>
+          <t>有田 智一</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
+          <t>川島 宏一</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
           <t>渡邉 俊</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>岡田 幸彦</t>
-        </is>
-      </c>
       <c r="G67" t="n">
-        <v>0.8575069308280945</v>
+        <v>0.8713784515857697</v>
       </c>
       <c r="H67" t="n">
-        <v>0.8562852144241333</v>
+        <v>0.8710208237171173</v>
       </c>
       <c r="I67" t="n">
-        <v>0.8543129563331604</v>
+        <v>0.8702171146869659</v>
       </c>
     </row>
     <row r="68">
@@ -3200,27 +3200,27 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
+          <t>秋山 英三</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>上市 秀雄</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
           <t>澤 亮治</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>岡田 幸彦</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>原田 信行</t>
-        </is>
-      </c>
       <c r="G68" t="n">
-        <v>0.8587094247341156</v>
+        <v>0.8584946990013123</v>
       </c>
       <c r="H68" t="n">
-        <v>0.8550151884555817</v>
+        <v>0.8546058237552643</v>
       </c>
       <c r="I68" t="n">
-        <v>0.8549315929412842</v>
+        <v>0.8525292575359344</v>
       </c>
     </row>
     <row r="69">
@@ -3246,22 +3246,22 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>雨宮 護</t>
+          <t>作道 真理</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>甲斐田 直子</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>0.8701651096343994</v>
+        <v>0.8676148355007172</v>
       </c>
       <c r="H69" t="n">
-        <v>0.8668938279151917</v>
+        <v>0.8644678592681885</v>
       </c>
       <c r="I69" t="n">
-        <v>0.8668799698352814</v>
+        <v>0.8629213571548462</v>
       </c>
     </row>
     <row r="70">
@@ -3287,22 +3287,22 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>原田 信行</t>
+          <t>作道 真理</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>岡田 幸彦</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>0.8791024386882782</v>
+        <v>0.8750825822353363</v>
       </c>
       <c r="H70" t="n">
-        <v>0.8728480637073517</v>
+        <v>0.8746155500411987</v>
       </c>
       <c r="I70" t="n">
-        <v>0.8702419698238373</v>
+        <v>0.8739151060581207</v>
       </c>
     </row>
     <row r="71">
@@ -3323,27 +3323,27 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
+          <t>原田 信行</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
           <t>甲斐田 直子</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>原田 信行</t>
-        </is>
-      </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>堤 盛人</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>0.8686790764331818</v>
+        <v>0.871713787317276</v>
       </c>
       <c r="H71" t="n">
-        <v>0.8682980537414551</v>
+        <v>0.8697263896465302</v>
       </c>
       <c r="I71" t="n">
-        <v>0.8650796711444855</v>
+        <v>0.8666638731956482</v>
       </c>
     </row>
     <row r="72">
@@ -3364,27 +3364,27 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>八森 正泰</t>
+          <t>村上 暁信</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
+          <t>太田 充</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
           <t>飛田 幹男</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>浦田淳司</t>
-        </is>
-      </c>
       <c r="G72" t="n">
-        <v>0.8655970394611359</v>
+        <v>0.8630807399749756</v>
       </c>
       <c r="H72" t="n">
-        <v>0.8654685616493225</v>
+        <v>0.8613697290420532</v>
       </c>
       <c r="I72" t="n">
-        <v>0.8631964921951294</v>
+        <v>0.8606661856174469</v>
       </c>
     </row>
     <row r="73">
@@ -3405,27 +3405,27 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Phung-Duc Tuan</t>
+          <t>岡本 直久</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>大西 正輝</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>和田 健太郎</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>0.8710783421993256</v>
+        <v>0.8718512058258057</v>
       </c>
       <c r="H73" t="n">
-        <v>0.8704829216003418</v>
+        <v>0.8703760504722595</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8681328892707825</v>
+        <v>0.8697851598262787</v>
       </c>
     </row>
     <row r="74">
@@ -3446,27 +3446,27 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
+          <t>浦田淳司</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>太田 充</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
           <t>甲斐田 直子</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>浦田淳司</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>繁野 麻衣子</t>
-        </is>
-      </c>
       <c r="G74" t="n">
-        <v>0.877896249294281</v>
+        <v>0.8781124651432037</v>
       </c>
       <c r="H74" t="n">
-        <v>0.8770155608654022</v>
+        <v>0.8701009154319763</v>
       </c>
       <c r="I74" t="n">
-        <v>0.875188946723938</v>
+        <v>0.8684175610542297</v>
       </c>
     </row>
     <row r="75">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>大西 正輝</t>
+          <t>和田 健太郎</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3497,17 +3497,17 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>0.8937357366085052</v>
+        <v>0.8810763657093048</v>
       </c>
       <c r="H75" t="n">
-        <v>0.882947713136673</v>
+        <v>0.8769265115261078</v>
       </c>
       <c r="I75" t="n">
-        <v>0.8791115880012512</v>
+        <v>0.8759317398071289</v>
       </c>
     </row>
     <row r="76">
@@ -3528,27 +3528,27 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>大西 正輝</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Phung-Duc Tuan</t>
+          <t>和田 健太郎</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>作道 真理</t>
+          <t>岡本 直久</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>0.8748579323291779</v>
+        <v>0.8613660037517548</v>
       </c>
       <c r="H76" t="n">
-        <v>0.8651790022850037</v>
+        <v>0.8581895232200623</v>
       </c>
       <c r="I76" t="n">
-        <v>0.8583352863788605</v>
+        <v>0.8555910587310791</v>
       </c>
     </row>
     <row r="77">
@@ -3569,12 +3569,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>大西 正輝</t>
+          <t>繁野 麻衣子</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>和田 健太郎</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3583,13 +3583,13 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>0.8886218667030334</v>
+        <v>0.872856616973877</v>
       </c>
       <c r="H77" t="n">
-        <v>0.8746299743652344</v>
+        <v>0.8727848827838898</v>
       </c>
       <c r="I77" t="n">
-        <v>0.8740542829036713</v>
+        <v>0.8703022599220276</v>
       </c>
     </row>
     <row r="78">
@@ -3615,22 +3615,22 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>秋山 英三</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>甲斐田 直子</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>0.880220502614975</v>
+        <v>0.8818720877170563</v>
       </c>
       <c r="H78" t="n">
-        <v>0.8740869164466858</v>
+        <v>0.8740076422691345</v>
       </c>
       <c r="I78" t="n">
-        <v>0.8736548125743866</v>
+        <v>0.8737394213676453</v>
       </c>
     </row>
     <row r="79">
@@ -3651,27 +3651,27 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>甲斐田 直子</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>渡邉 俊</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>雨宮 護</t>
+          <t>岡田 幸彦</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>0.8804406523704529</v>
+        <v>0.8754933774471283</v>
       </c>
       <c r="H79" t="n">
-        <v>0.8778083324432373</v>
+        <v>0.8700396716594696</v>
       </c>
       <c r="I79" t="n">
-        <v>0.8772007524967194</v>
+        <v>0.8682321310043335</v>
       </c>
     </row>
     <row r="80">
@@ -3697,22 +3697,22 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
+          <t>牛島 光一</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
           <t>秋山 英三</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>甲斐田 直子</t>
-        </is>
-      </c>
       <c r="G80" t="n">
-        <v>0.865395188331604</v>
+        <v>0.8568066656589508</v>
       </c>
       <c r="H80" t="n">
-        <v>0.8596368134021759</v>
+        <v>0.8566449582576752</v>
       </c>
       <c r="I80" t="n">
-        <v>0.8592325747013092</v>
+        <v>0.8551899194717407</v>
       </c>
     </row>
     <row r="81">
@@ -3747,13 +3747,13 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>0.8603357672691345</v>
+        <v>0.8677469193935394</v>
       </c>
       <c r="H81" t="n">
-        <v>0.8560177385807037</v>
+        <v>0.858636885881424</v>
       </c>
       <c r="I81" t="n">
-        <v>0.8558715879917145</v>
+        <v>0.8584713041782379</v>
       </c>
     </row>
     <row r="82">
@@ -3774,27 +3774,27 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>原田 信行</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>甲斐田 直子</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
+          <t>上市 秀雄</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>0.8518300950527191</v>
+        <v>0.8579146862030029</v>
       </c>
       <c r="H82" t="n">
-        <v>0.8514336049556732</v>
+        <v>0.8535605072975159</v>
       </c>
       <c r="I82" t="n">
-        <v>0.8513353765010834</v>
+        <v>0.849486380815506</v>
       </c>
     </row>
     <row r="83">
@@ -3815,27 +3815,27 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
+          <t>作道 真理</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
           <t>原田 信行</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>甲斐田 直子</t>
-        </is>
-      </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>作道 真理</t>
+          <t>太田 充</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>0.8639160990715027</v>
+        <v>0.8581055998802185</v>
       </c>
       <c r="H83" t="n">
-        <v>0.8579046726226807</v>
+        <v>0.8570418357849121</v>
       </c>
       <c r="I83" t="n">
-        <v>0.8572237193584442</v>
+        <v>0.8521462678909302</v>
       </c>
     </row>
     <row r="84">
@@ -3856,27 +3856,27 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>甲斐田 直子</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>岡田 幸彦</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>村上 暁信</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>0.8577942550182343</v>
+        <v>0.8484123051166534</v>
       </c>
       <c r="H84" t="n">
-        <v>0.8510209619998932</v>
+        <v>0.8476902544498444</v>
       </c>
       <c r="I84" t="n">
-        <v>0.8502745926380157</v>
+        <v>0.8469191193580627</v>
       </c>
     </row>
   </sheetData>
@@ -3958,27 +3958,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>イリチュ 美佳</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>佐野 幸恵</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>高野 祐一</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>吉瀬 章子</t>
-        </is>
-      </c>
       <c r="G2" t="n">
-        <v>0.862188994884491</v>
+        <v>0.8655994832515717</v>
       </c>
       <c r="H2" t="n">
-        <v>0.858819305896759</v>
+        <v>0.8584177494049072</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8546646237373352</v>
+        <v>0.8582044243812561</v>
       </c>
     </row>
     <row r="3">
@@ -3999,27 +3999,27 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>雨宮 護</t>
+          <t>吉瀬 章子</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>浦田淳司</t>
+          <t>繁野 麻衣子</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>繆 瑩</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.8571438193321228</v>
+        <v>0.8599178791046143</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8564046025276184</v>
+        <v>0.856866717338562</v>
       </c>
       <c r="I3" t="n">
-        <v>0.855046272277832</v>
+        <v>0.850815623998642</v>
       </c>
     </row>
     <row r="4">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>大西 正輝</t>
+          <t>吉瀬 章子</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -4050,17 +4050,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>吉瀬 章子</t>
+          <t>高野 祐一</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.8557466268539429</v>
+        <v>0.8536908626556396</v>
       </c>
       <c r="H4" t="n">
-        <v>0.853240042924881</v>
+        <v>0.8510599136352539</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8521353006362915</v>
+        <v>0.8434899747371674</v>
       </c>
     </row>
     <row r="5">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>大西 正輝</t>
+          <t>繁野 麻衣子</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>吉瀬 章子</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -4095,13 +4095,13 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.875066727399826</v>
+        <v>0.8755005896091461</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8710565567016602</v>
+        <v>0.8733445703983307</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8685732483863831</v>
+        <v>0.8610541224479675</v>
       </c>
     </row>
     <row r="6">
@@ -4122,27 +4122,27 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>イリチュ 美佳</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>佐野 幸恵</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>上市 秀雄</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>雨宮 護</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>佐野 幸恵</t>
-        </is>
-      </c>
       <c r="G6" t="n">
-        <v>0.871045708656311</v>
+        <v>0.8764640092849731</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8696443438529968</v>
+        <v>0.8743419647216797</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8690361082553864</v>
+        <v>0.8740573525428772</v>
       </c>
     </row>
     <row r="7">
@@ -4168,22 +4168,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>上市 秀雄</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>繁野 麻衣子</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>秋山 英三</t>
-        </is>
-      </c>
       <c r="G7" t="n">
-        <v>0.8687897622585297</v>
+        <v>0.887189507484436</v>
       </c>
       <c r="H7" t="n">
-        <v>0.860876590013504</v>
+        <v>0.8698042631149292</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8586911857128143</v>
+        <v>0.8610810935497284</v>
       </c>
     </row>
     <row r="8">
@@ -4204,27 +4204,27 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>大西 正輝</t>
+          <t>繁野 麻衣子</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>繆 瑩</t>
+          <t>吉瀬 章子</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>高野 祐一</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.8762173652648926</v>
+        <v>0.8727676868438721</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8738330900669098</v>
+        <v>0.8723370432853699</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8689559698104858</v>
+        <v>0.8690331280231476</v>
       </c>
     </row>
     <row r="9">
@@ -4245,27 +4245,27 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>高野 祐一</t>
+          <t>岡田 幸彦</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>岡田 幸彦</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>イリチュ 美佳</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.8533464968204498</v>
+        <v>0.8713008165359497</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8533048927783966</v>
+        <v>0.8693908452987671</v>
       </c>
       <c r="I9" t="n">
-        <v>0.850794792175293</v>
+        <v>0.8662359416484833</v>
       </c>
     </row>
     <row r="10">
@@ -4286,27 +4286,27 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>吉瀬 章子</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>繁野 麻衣子</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>吉瀬 章子</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>澤 亮治</t>
+          <t>髙橋裕紀</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.8619266152381897</v>
+        <v>0.8638443946838379</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8615545630455017</v>
+        <v>0.8611145615577698</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8611488342285156</v>
+        <v>0.8536087870597839</v>
       </c>
     </row>
     <row r="11">
@@ -4327,27 +4327,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>イリチュ 美佳</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>岡田 幸彦</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>繁野 麻衣子</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>高野 祐一</t>
+          <t>髙橋裕紀</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.8465540111064911</v>
+        <v>0.8799342513084412</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8464995324611664</v>
+        <v>0.8656601309776306</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8445603251457214</v>
+        <v>0.8637024164199829</v>
       </c>
     </row>
     <row r="12">
@@ -4373,22 +4373,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>高野 祐一</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>岡田 幸彦</t>
+          <t>黒瀬 雄大</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.8796535432338715</v>
+        <v>0.8852237164974213</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8640227913856506</v>
+        <v>0.8602020144462585</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8568365573883057</v>
+        <v>0.8592531085014343</v>
       </c>
     </row>
     <row r="13">
@@ -4414,22 +4414,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>岡田 幸彦</t>
+          <t>上市 秀雄</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>上市 秀雄</t>
+          <t>イリチュ 美佳</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.8531846702098846</v>
+        <v>0.8827695846557617</v>
       </c>
       <c r="H13" t="n">
-        <v>0.843764066696167</v>
+        <v>0.8713669776916504</v>
       </c>
       <c r="I13" t="n">
-        <v>0.842092365026474</v>
+        <v>0.857954204082489</v>
       </c>
     </row>
     <row r="14">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>岡田 幸彦</t>
+          <t>イリチュ 美佳</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -4460,17 +4460,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>高野 祐一</t>
+          <t>髙橋裕紀</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.8570942282676697</v>
+        <v>0.8514187932014465</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8538691699504852</v>
+        <v>0.85108882188797</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8538650572299957</v>
+        <v>0.8484852015972137</v>
       </c>
     </row>
     <row r="15">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>黒瀬 雄大</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>黒瀬 雄大</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.8393575847148895</v>
+        <v>0.8624188005924225</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8330047726631165</v>
+        <v>0.8561882376670837</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8324172794818878</v>
+        <v>0.8552936315536499</v>
       </c>
     </row>
     <row r="16">
@@ -4532,27 +4532,27 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>大西 正輝</t>
+          <t>繁野 麻衣子</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>八森 正泰</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Phung-Duc Tuan</t>
+          <t>吉瀬 章子</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.8683789074420929</v>
+        <v>0.8731126487255096</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8614305257797241</v>
+        <v>0.8647971451282501</v>
       </c>
       <c r="I16" t="n">
-        <v>0.85704305768013</v>
+        <v>0.8619018793106079</v>
       </c>
     </row>
     <row r="17">
@@ -4573,27 +4573,27 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>高野 祐一</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>繁野 麻衣子</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>高野 祐一</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>吉瀬 章子</t>
+          <t>髙橋裕紀</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0.8672901391983032</v>
+        <v>0.870884120464325</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8645013272762299</v>
+        <v>0.8654924631118774</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8597360551357269</v>
+        <v>0.865092396736145</v>
       </c>
     </row>
     <row r="18">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>岡本 直久</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -4624,17 +4624,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>岡本 直久</t>
+          <t>髙橋裕紀</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0.8459638953208923</v>
+        <v>0.8637301027774811</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8379291594028473</v>
+        <v>0.8542537987232208</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8348133265972137</v>
+        <v>0.8541643619537354</v>
       </c>
     </row>
     <row r="19">
@@ -4660,22 +4660,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>大西 正輝</t>
+          <t>繁野 麻衣子</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0.8622571527957916</v>
+        <v>0.870453953742981</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8603937029838562</v>
+        <v>0.8658804893493652</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8602149486541748</v>
+        <v>0.8593435287475586</v>
       </c>
     </row>
     <row r="20">
@@ -4696,27 +4696,27 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>上市 秀雄</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>イリチュ 美佳</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>岡田 幸彦</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>澤 亮治</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>秋山 英三</t>
-        </is>
-      </c>
       <c r="G20" t="n">
-        <v>0.8785312175750732</v>
+        <v>0.8740392327308655</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8755816221237183</v>
+        <v>0.8692725598812103</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8698488175868988</v>
+        <v>0.8674855530261993</v>
       </c>
     </row>
     <row r="21">
@@ -4737,12 +4737,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>大西 正輝</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>雨宮 護</t>
+          <t>吉瀬 章子</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4751,13 +4751,13 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0.8697235882282257</v>
+        <v>0.8658023476600647</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8666972517967224</v>
+        <v>0.8634548485279083</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8661553859710693</v>
+        <v>0.8619240820407867</v>
       </c>
     </row>
     <row r="22">
@@ -4778,27 +4778,27 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>作道 真理</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>原田 信行</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>岡田 幸彦</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>黒瀬 雄大</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.8749107420444489</v>
+        <v>0.8738839030265808</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8701186776161194</v>
+        <v>0.8722674250602722</v>
       </c>
       <c r="I22" t="n">
-        <v>0.868733823299408</v>
+        <v>0.8667078912258148</v>
       </c>
     </row>
   </sheetData>

--- a/generated/committee_recommendations.xlsx
+++ b/generated/committee_recommendations.xlsx
@@ -499,22 +499,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>髙橋裕紀</t>
+          <t>秋山 英三</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>秋山 英三</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.8622280657291412</v>
+        <v>0.8637408018112183</v>
       </c>
       <c r="H2" t="n">
-        <v>0.860817015171051</v>
+        <v>0.8561815619468689</v>
       </c>
       <c r="I2" t="n">
-        <v>0.856243759393692</v>
+        <v>0.8561266660690308</v>
       </c>
     </row>
     <row r="3">
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.867502748966217</v>
+        <v>0.8734617531299591</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8587009906768799</v>
+        <v>0.8607054650783539</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8585590720176697</v>
+        <v>0.8574923276901245</v>
       </c>
     </row>
     <row r="4">
@@ -581,7 +581,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>髙橋裕紀</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -590,13 +590,13 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.8694976568222046</v>
+        <v>0.8704100847244263</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8618543148040771</v>
+        <v>0.8587318658828735</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8569416403770447</v>
+        <v>0.8560931086540222</v>
       </c>
     </row>
     <row r="5">
@@ -627,17 +627,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>髙橋裕紀</t>
+          <t>上市 秀雄</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.8732118904590607</v>
+        <v>0.8748835027217865</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8708003759384155</v>
+        <v>0.8693714141845703</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8691686987876892</v>
+        <v>0.8666558861732483</v>
       </c>
     </row>
     <row r="6">
@@ -658,7 +658,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>作道 真理</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -672,13 +672,13 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.8707860708236694</v>
+        <v>0.8622949421405792</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8629058003425598</v>
+        <v>0.8608851730823517</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8617391288280487</v>
+        <v>0.8604684770107269</v>
       </c>
     </row>
     <row r="7">
@@ -704,22 +704,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>甲斐田 直子</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>秋山 英三</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>甲斐田 直子</t>
-        </is>
-      </c>
       <c r="G7" t="n">
-        <v>0.8775012493133545</v>
+        <v>0.8782476484775543</v>
       </c>
       <c r="H7" t="n">
-        <v>0.873183935880661</v>
+        <v>0.8727595508098602</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8704139590263367</v>
+        <v>0.8720541596412659</v>
       </c>
     </row>
     <row r="8">
@@ -750,17 +750,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>繆 瑩</t>
+          <t>和田 健太郎</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.8788286447525024</v>
+        <v>0.8723167479038239</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8646557033061981</v>
+        <v>0.8555609583854675</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8591321110725403</v>
+        <v>0.8544269800186157</v>
       </c>
     </row>
     <row r="9">
@@ -791,17 +791,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>黒瀬 雄大</t>
+          <t>八森 正泰</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.868406355381012</v>
+        <v>0.8737589120864868</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8616978526115417</v>
+        <v>0.8660922646522522</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8596908450126648</v>
+        <v>0.8622945547103882</v>
       </c>
     </row>
     <row r="10">
@@ -822,27 +822,27 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>太田 充</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>鈴木 勉</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>太田 充</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>堤 盛人</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.8736737668514252</v>
+        <v>0.8714622557163239</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8708745837211609</v>
+        <v>0.8703478574752808</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8708597719669342</v>
+        <v>0.8688311576843262</v>
       </c>
     </row>
     <row r="11">
@@ -868,22 +868,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>八森 正泰</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>浦田淳司</t>
+          <t>有馬 澄佳</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.871646523475647</v>
+        <v>0.8717465400695801</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8702176809310913</v>
+        <v>0.8668537437915802</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8686382174491882</v>
+        <v>0.8666412830352783</v>
       </c>
     </row>
     <row r="12">
@@ -904,27 +904,27 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>澤 亮治</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>川島 宏一</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>佐野 幸恵</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>澤 亮治</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>上市 秀雄</t>
-        </is>
-      </c>
       <c r="G12" t="n">
-        <v>0.8563922941684723</v>
+        <v>0.8546874523162842</v>
       </c>
       <c r="H12" t="n">
-        <v>0.853992760181427</v>
+        <v>0.8504401743412018</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8530559241771698</v>
+        <v>0.8490931987762451</v>
       </c>
     </row>
     <row r="13">
@@ -955,17 +955,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>繆 瑩</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.8606098890304565</v>
+        <v>0.8592478334903717</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8565657436847687</v>
+        <v>0.846853107213974</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8463118970394135</v>
+        <v>0.8349056243896484</v>
       </c>
     </row>
     <row r="14">
@@ -996,17 +996,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.8741859197616577</v>
+        <v>0.8779064118862152</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8717276751995087</v>
+        <v>0.8726606070995331</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8688391745090485</v>
+        <v>0.8708367943763733</v>
       </c>
     </row>
     <row r="15">
@@ -1037,17 +1037,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>吉瀬 章子</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.8765020668506622</v>
+        <v>0.8802605867385864</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8727556467056274</v>
+        <v>0.8750885725021362</v>
       </c>
       <c r="I15" t="n">
-        <v>0.871123731136322</v>
+        <v>0.8705006837844849</v>
       </c>
     </row>
     <row r="16">
@@ -1073,22 +1073,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>吉瀬 章子</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>繁野 麻衣子</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>吉瀬 章子</t>
-        </is>
-      </c>
       <c r="G16" t="n">
-        <v>0.880088746547699</v>
+        <v>0.8758190870285034</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8798215389251709</v>
+        <v>0.8685945868492126</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8703469336032867</v>
+        <v>0.8660972416400909</v>
       </c>
     </row>
     <row r="17">
@@ -1109,27 +1109,27 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>髙橋裕紀</t>
+          <t>上市 秀雄</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>澤 亮治</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>秋山 英三</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>上市 秀雄</t>
-        </is>
-      </c>
       <c r="G17" t="n">
-        <v>0.860830545425415</v>
+        <v>0.8586440086364746</v>
       </c>
       <c r="H17" t="n">
-        <v>0.860471248626709</v>
+        <v>0.8549793362617493</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8592727482318878</v>
+        <v>0.8542280793190002</v>
       </c>
     </row>
     <row r="18">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>黒瀬 雄大</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0.8734438419342041</v>
+        <v>0.8756992518901825</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8697305023670197</v>
+        <v>0.8693471550941467</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8687523305416107</v>
+        <v>0.8683554232120514</v>
       </c>
     </row>
     <row r="19">
@@ -1205,13 +1205,13 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0.8666941523551941</v>
+        <v>0.8647384345531464</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8642557859420776</v>
+        <v>0.8633520305156708</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8628633618354797</v>
+        <v>0.8614738583564758</v>
       </c>
     </row>
     <row r="20">
@@ -1242,17 +1242,17 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>秋山 英三</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0.8812617063522339</v>
+        <v>0.8822429776191711</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8769907653331757</v>
+        <v>0.8785501420497894</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8655136823654175</v>
+        <v>0.8663562834262848</v>
       </c>
     </row>
     <row r="21">
@@ -1278,22 +1278,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>吉瀬 章子</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>吉瀬 章子</t>
+          <t>有馬 澄佳</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0.8566152155399323</v>
+        <v>0.8621289730072021</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8559147119522095</v>
+        <v>0.8556961417198181</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8549613058567047</v>
+        <v>0.8524527847766876</v>
       </c>
     </row>
     <row r="22">
@@ -1314,27 +1314,27 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>鈴木 勉</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>渡邉 俊</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>浦田淳司</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>鈴木 勉</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>渡邉 俊</t>
-        </is>
-      </c>
       <c r="G22" t="n">
-        <v>0.8830437958240509</v>
+        <v>0.8789419531822205</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8812804818153381</v>
+        <v>0.8760955929756165</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8750165104866028</v>
+        <v>0.8730508089065552</v>
       </c>
     </row>
     <row r="23">
@@ -1355,27 +1355,27 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>牛島 光一</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>佐野 幸恵</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>黒瀬 雄大</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>牛島 光一</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>佐野 幸恵</t>
-        </is>
-      </c>
       <c r="G23" t="n">
-        <v>0.8554224669933319</v>
+        <v>0.8591336905956268</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8533744513988495</v>
+        <v>0.8517085015773773</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8531850874423981</v>
+        <v>0.8514227271080017</v>
       </c>
     </row>
     <row r="24">
@@ -1396,27 +1396,27 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>上市 秀雄</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>川島 宏一</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t>イリチュ 美佳</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>原田 信行</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>作道 真理</t>
-        </is>
-      </c>
       <c r="G24" t="n">
-        <v>0.8565972447395325</v>
+        <v>0.8527725040912628</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8563653528690338</v>
+        <v>0.8512898087501526</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8553677499294281</v>
+        <v>0.8512193560600281</v>
       </c>
     </row>
     <row r="25">
@@ -1442,22 +1442,22 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>作道 真理</t>
+          <t>上市 秀雄</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>上市 秀雄</t>
+          <t>高野 祐一</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0.8749534487724304</v>
+        <v>0.8706742227077484</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8748263418674469</v>
+        <v>0.8638857305049896</v>
       </c>
       <c r="I25" t="n">
-        <v>0.8660167157649994</v>
+        <v>0.8618723750114441</v>
       </c>
     </row>
     <row r="26">
@@ -1478,27 +1478,27 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>作道 真理</t>
+          <t>秋山 英三</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>秋山 英三</t>
+          <t>黒瀬 雄大</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>黒瀬 雄大</t>
+          <t>高野 祐一</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0.8669944107532501</v>
+        <v>0.8637948930263519</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8630058169364929</v>
+        <v>0.8582098484039307</v>
       </c>
       <c r="I26" t="n">
-        <v>0.8572041392326355</v>
+        <v>0.8576050400733948</v>
       </c>
     </row>
     <row r="27">
@@ -1533,13 +1533,13 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0.861872673034668</v>
+        <v>0.8603377938270569</v>
       </c>
       <c r="H27" t="n">
-        <v>0.8589910268783569</v>
+        <v>0.8578148186206818</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8534484505653381</v>
+        <v>0.8570154905319214</v>
       </c>
     </row>
     <row r="28">
@@ -1560,27 +1560,27 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>有馬 澄佳</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>吉瀬 章子</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t>繁野 麻衣子</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>有馬 澄佳</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>吉瀬 章子</t>
-        </is>
-      </c>
       <c r="G28" t="n">
-        <v>0.8814447820186615</v>
+        <v>0.8752446472644806</v>
       </c>
       <c r="H28" t="n">
-        <v>0.8795143067836761</v>
+        <v>0.8709458708763123</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8726982176303864</v>
+        <v>0.8677204847335815</v>
       </c>
     </row>
     <row r="29">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>岡田 幸彦</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0.8719902336597443</v>
+        <v>0.8728598952293396</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8634964525699615</v>
+        <v>0.8667237460613251</v>
       </c>
       <c r="I29" t="n">
-        <v>0.8624171614646912</v>
+        <v>0.862547755241394</v>
       </c>
     </row>
     <row r="30">
@@ -1647,22 +1647,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>髙橋裕紀</t>
+          <t>岡田 幸彦</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>岡田 幸彦</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0.8809157311916351</v>
+        <v>0.8834352493286133</v>
       </c>
       <c r="H30" t="n">
-        <v>0.8686379790306091</v>
+        <v>0.8568967878818512</v>
       </c>
       <c r="I30" t="n">
-        <v>0.8590868711471558</v>
+        <v>0.855995774269104</v>
       </c>
     </row>
     <row r="31">
@@ -1688,22 +1688,22 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>作道 真理</t>
+          <t>黒瀬 雄大</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>原田 信行</t>
+          <t>有田 智一</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0.8641783893108368</v>
+        <v>0.8618856966495514</v>
       </c>
       <c r="H31" t="n">
-        <v>0.8617948591709137</v>
+        <v>0.8590705394744873</v>
       </c>
       <c r="I31" t="n">
-        <v>0.8604422211647034</v>
+        <v>0.8540639877319336</v>
       </c>
     </row>
     <row r="32">
@@ -1729,22 +1729,22 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
+          <t>甲斐田 直子</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t>佐野 幸恵</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>甲斐田 直子</t>
-        </is>
-      </c>
       <c r="G32" t="n">
-        <v>0.8584904074668884</v>
+        <v>0.8575133681297302</v>
       </c>
       <c r="H32" t="n">
-        <v>0.8578586578369141</v>
+        <v>0.8523845374584198</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8513690233230591</v>
+        <v>0.8516231775283813</v>
       </c>
     </row>
     <row r="33">
@@ -1770,22 +1770,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
+          <t>川島 宏一</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t>甲斐田 直子</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>川島 宏一</t>
-        </is>
-      </c>
       <c r="G33" t="n">
-        <v>0.863069623708725</v>
+        <v>0.8604612350463867</v>
       </c>
       <c r="H33" t="n">
-        <v>0.8602399826049805</v>
+        <v>0.8577742874622345</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8586323261260986</v>
+        <v>0.8568277060985565</v>
       </c>
     </row>
     <row r="34">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>村上 暁信</t>
+          <t>山本 幸子</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0.8694185614585876</v>
+        <v>0.8634571731090546</v>
       </c>
       <c r="H34" t="n">
-        <v>0.8680724501609802</v>
+        <v>0.8626152873039246</v>
       </c>
       <c r="I34" t="n">
-        <v>0.8633807599544525</v>
+        <v>0.8595913052558899</v>
       </c>
     </row>
     <row r="35">
@@ -1857,17 +1857,17 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>太田 充</t>
+          <t>渡邉 俊</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0.8825912475585938</v>
+        <v>0.8803420662879944</v>
       </c>
       <c r="H35" t="n">
-        <v>0.8784309923648834</v>
+        <v>0.8801654279232025</v>
       </c>
       <c r="I35" t="n">
-        <v>0.8758960366249084</v>
+        <v>0.8745454549789429</v>
       </c>
     </row>
     <row r="36">
@@ -1893,22 +1893,22 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>村上 暁信</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0.8779982924461365</v>
+        <v>0.8759266436100006</v>
       </c>
       <c r="H36" t="n">
-        <v>0.874761164188385</v>
+        <v>0.8738082349300385</v>
       </c>
       <c r="I36" t="n">
-        <v>0.8702944219112396</v>
+        <v>0.8677709102630615</v>
       </c>
     </row>
     <row r="37">
@@ -1943,13 +1943,13 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0.8806043863296509</v>
+        <v>0.8812141418457031</v>
       </c>
       <c r="H37" t="n">
-        <v>0.8754421770572662</v>
+        <v>0.8779473304748535</v>
       </c>
       <c r="I37" t="n">
-        <v>0.875201553106308</v>
+        <v>0.8733148872852325</v>
       </c>
     </row>
     <row r="38">
@@ -1970,27 +1970,27 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t>山本 幸子</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
           <t>川島 宏一</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>山本 幸子</t>
-        </is>
-      </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>原田 信行</t>
+          <t>渡邉 俊</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0.8702716529369354</v>
+        <v>0.8687264025211334</v>
       </c>
       <c r="H38" t="n">
-        <v>0.8665628135204315</v>
+        <v>0.8683319687843323</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8636845648288727</v>
+        <v>0.8629850745201111</v>
       </c>
     </row>
     <row r="39">
@@ -2021,17 +2021,17 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>太田 充</t>
+          <t>有田 智一</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0.8863994181156158</v>
+        <v>0.8841175734996796</v>
       </c>
       <c r="H39" t="n">
-        <v>0.8796985745429993</v>
+        <v>0.8798271417617798</v>
       </c>
       <c r="I39" t="n">
-        <v>0.8795591592788696</v>
+        <v>0.879041850566864</v>
       </c>
     </row>
     <row r="40">
@@ -2066,13 +2066,13 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0.8820393085479736</v>
+        <v>0.883649080991745</v>
       </c>
       <c r="H40" t="n">
-        <v>0.8811213672161102</v>
+        <v>0.8805911242961884</v>
       </c>
       <c r="I40" t="n">
-        <v>0.8794645071029663</v>
+        <v>0.8768988847732544</v>
       </c>
     </row>
     <row r="41">
@@ -2093,27 +2093,27 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t>堤 盛人</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
           <t>川島 宏一</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>堤 盛人</t>
-        </is>
-      </c>
       <c r="F41" t="inlineStr">
         <is>
           <t>太田 充</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0.8671340346336365</v>
+        <v>0.8722117841243744</v>
       </c>
       <c r="H41" t="n">
-        <v>0.8669663369655609</v>
+        <v>0.8708105385303497</v>
       </c>
       <c r="I41" t="n">
-        <v>0.8657203912734985</v>
+        <v>0.8650574684143066</v>
       </c>
     </row>
     <row r="42">
@@ -2144,17 +2144,17 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
+          <t>浦田淳司</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0.8661057353019714</v>
+        <v>0.8621289134025574</v>
       </c>
       <c r="H42" t="n">
-        <v>0.8625563383102417</v>
+        <v>0.8617661893367767</v>
       </c>
       <c r="I42" t="n">
-        <v>0.8523598313331604</v>
+        <v>0.8485496342182159</v>
       </c>
     </row>
     <row r="43">
@@ -2180,22 +2180,22 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>雨宮 護</t>
+          <t>堤 盛人</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>村上 暁信</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0.8712981641292572</v>
+        <v>0.8732402920722961</v>
       </c>
       <c r="H43" t="n">
-        <v>0.8678552508354187</v>
+        <v>0.8674532473087311</v>
       </c>
       <c r="I43" t="n">
-        <v>0.8676274418830872</v>
+        <v>0.8664050996303558</v>
       </c>
     </row>
     <row r="44">
@@ -2216,27 +2216,27 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t>川島 宏一</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>藤川 昌樹</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t>雨宮 護</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>太田 充</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>村上 暁信</t>
-        </is>
-      </c>
       <c r="G44" t="n">
-        <v>0.8639198839664459</v>
+        <v>0.8610956370830536</v>
       </c>
       <c r="H44" t="n">
-        <v>0.8630452156066895</v>
+        <v>0.8599763512611389</v>
       </c>
       <c r="I44" t="n">
-        <v>0.8629290461540222</v>
+        <v>0.85889932513237</v>
       </c>
     </row>
     <row r="45">
@@ -2271,13 +2271,13 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0.8861710727214813</v>
+        <v>0.88481405377388</v>
       </c>
       <c r="H45" t="n">
-        <v>0.8844046294689178</v>
+        <v>0.8846468329429626</v>
       </c>
       <c r="I45" t="n">
-        <v>0.8839033246040344</v>
+        <v>0.881380170583725</v>
       </c>
     </row>
     <row r="46">
@@ -2303,22 +2303,22 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>八森 正泰</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>八森 正泰</t>
+          <t>山本 幸子</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0.8671504259109497</v>
+        <v>0.8624061048030853</v>
       </c>
       <c r="H46" t="n">
-        <v>0.8651044368743896</v>
+        <v>0.8623032569885254</v>
       </c>
       <c r="I46" t="n">
-        <v>0.8631814122200012</v>
+        <v>0.8606871068477631</v>
       </c>
     </row>
     <row r="47">
@@ -2349,17 +2349,17 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>有田 智一</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>0.8827366232872009</v>
+        <v>0.8822457492351532</v>
       </c>
       <c r="H47" t="n">
-        <v>0.8823181688785553</v>
+        <v>0.8808684051036835</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8821680843830109</v>
+        <v>0.8808216154575348</v>
       </c>
     </row>
     <row r="48">
@@ -2385,22 +2385,22 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
+          <t>牛島 光一</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
           <t>川島 宏一</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>甲斐田 直子</t>
-        </is>
-      </c>
       <c r="G48" t="n">
-        <v>0.8742204904556274</v>
+        <v>0.876221776008606</v>
       </c>
       <c r="H48" t="n">
-        <v>0.865276575088501</v>
+        <v>0.8661503791809082</v>
       </c>
       <c r="I48" t="n">
-        <v>0.8646620213985443</v>
+        <v>0.8655958473682404</v>
       </c>
     </row>
     <row r="49">
@@ -2435,13 +2435,13 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>0.871150940656662</v>
+        <v>0.8662878572940826</v>
       </c>
       <c r="H49" t="n">
-        <v>0.8686563372612</v>
+        <v>0.8649434447288513</v>
       </c>
       <c r="I49" t="n">
-        <v>0.8679154217243195</v>
+        <v>0.864597499370575</v>
       </c>
     </row>
     <row r="50">
@@ -2472,17 +2472,17 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>谷口 綾子</t>
+          <t>和田 健太郎</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>0.8828504681587219</v>
+        <v>0.8805749118328094</v>
       </c>
       <c r="H50" t="n">
-        <v>0.8822090625762939</v>
+        <v>0.8783854246139526</v>
       </c>
       <c r="I50" t="n">
-        <v>0.8808643221855164</v>
+        <v>0.8773878812789917</v>
       </c>
     </row>
     <row r="51">
@@ -2513,17 +2513,17 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>浦田淳司</t>
+          <t>有田 智一</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>0.8735898435115814</v>
+        <v>0.8623651564121246</v>
       </c>
       <c r="H51" t="n">
-        <v>0.8624788522720337</v>
+        <v>0.855972558259964</v>
       </c>
       <c r="I51" t="n">
-        <v>0.8617882430553436</v>
+        <v>0.8509648144245148</v>
       </c>
     </row>
     <row r="52">
@@ -2544,27 +2544,27 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
+          <t>牛島 光一</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
           <t>川島 宏一</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>牛島 光一</t>
-        </is>
-      </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>雨宮 護</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>0.8638397455215454</v>
+        <v>0.8601011633872986</v>
       </c>
       <c r="H52" t="n">
-        <v>0.861793041229248</v>
+        <v>0.8564841449260712</v>
       </c>
       <c r="I52" t="n">
-        <v>0.8616099953651428</v>
+        <v>0.8554677963256836</v>
       </c>
     </row>
     <row r="53">
@@ -2585,27 +2585,27 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
+          <t>牛島 光一</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
           <t>太田 充</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>牛島 光一</t>
-        </is>
-      </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>甲斐田 直子</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>0.8731994032859802</v>
+        <v>0.8770773708820343</v>
       </c>
       <c r="H53" t="n">
-        <v>0.872426450252533</v>
+        <v>0.8713475167751312</v>
       </c>
       <c r="I53" t="n">
-        <v>0.8680101335048676</v>
+        <v>0.8681096136569977</v>
       </c>
     </row>
     <row r="54">
@@ -2626,27 +2626,27 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
+          <t>鈴木 勉</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
           <t>堤 盛人</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>鈴木 勉</t>
-        </is>
-      </c>
       <c r="F54" t="inlineStr">
         <is>
           <t>川島 宏一</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>0.8633367717266083</v>
+        <v>0.8658912181854248</v>
       </c>
       <c r="H54" t="n">
-        <v>0.862301766872406</v>
+        <v>0.8628571927547455</v>
       </c>
       <c r="I54" t="n">
-        <v>0.8590896129608154</v>
+        <v>0.8591557145118713</v>
       </c>
     </row>
     <row r="55">
@@ -2667,27 +2667,27 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>雨宮 護</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>甲斐田 直子</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
+          <t>太田 充</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>0.8567630350589752</v>
+        <v>0.8445272147655487</v>
       </c>
       <c r="H55" t="n">
-        <v>0.8559862971305847</v>
+        <v>0.8444044291973114</v>
       </c>
       <c r="I55" t="n">
-        <v>0.8537361323833466</v>
+        <v>0.8435723185539246</v>
       </c>
     </row>
     <row r="56">
@@ -2722,13 +2722,13 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>0.8790489733219147</v>
+        <v>0.8806582093238831</v>
       </c>
       <c r="H56" t="n">
-        <v>0.8749516904354095</v>
+        <v>0.8783489763736725</v>
       </c>
       <c r="I56" t="n">
-        <v>0.8738730251789093</v>
+        <v>0.8719048202037811</v>
       </c>
     </row>
     <row r="57">
@@ -2749,27 +2749,27 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>松原 康介</t>
+          <t>上市 秀雄</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
+          <t>岡田 幸彦</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
           <t>佐野 幸恵</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>上市 秀雄</t>
-        </is>
-      </c>
       <c r="G57" t="n">
-        <v>0.8533106446266174</v>
+        <v>0.844330906867981</v>
       </c>
       <c r="H57" t="n">
-        <v>0.8527741730213165</v>
+        <v>0.8426342308521271</v>
       </c>
       <c r="I57" t="n">
-        <v>0.8522745966911316</v>
+        <v>0.8422442376613617</v>
       </c>
     </row>
     <row r="58">
@@ -2790,27 +2790,27 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
+          <t>牛島 光一</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
           <t>和田 健太郎</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>浦田淳司</t>
-        </is>
-      </c>
       <c r="F58" t="inlineStr">
         <is>
           <t>甲斐田 直子</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>0.8704012036323547</v>
+        <v>0.8724232614040375</v>
       </c>
       <c r="H58" t="n">
-        <v>0.8699492812156677</v>
+        <v>0.8723962903022766</v>
       </c>
       <c r="I58" t="n">
-        <v>0.8684483170509338</v>
+        <v>0.86982461810112</v>
       </c>
     </row>
     <row r="59">
@@ -2841,17 +2841,17 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>浦田淳司</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>0.8815852403640747</v>
+        <v>0.8817901909351349</v>
       </c>
       <c r="H59" t="n">
-        <v>0.8759791851043701</v>
+        <v>0.8764764666557312</v>
       </c>
       <c r="I59" t="n">
-        <v>0.8754019439220428</v>
+        <v>0.8761448860168457</v>
       </c>
     </row>
     <row r="60">
@@ -2877,22 +2877,22 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>浦田淳司</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>雨宮 護</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>0.8791487216949463</v>
+        <v>0.8743585348129272</v>
       </c>
       <c r="H60" t="n">
-        <v>0.8711142539978027</v>
+        <v>0.8707767426967621</v>
       </c>
       <c r="I60" t="n">
-        <v>0.8695277869701385</v>
+        <v>0.8681854009628296</v>
       </c>
     </row>
     <row r="61">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>村上 暁信</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>0.8794030249118805</v>
+        <v>0.8797606825828552</v>
       </c>
       <c r="H61" t="n">
-        <v>0.8770883679389954</v>
+        <v>0.8760299682617188</v>
       </c>
       <c r="I61" t="n">
-        <v>0.8749685883522034</v>
+        <v>0.8728488087654114</v>
       </c>
     </row>
     <row r="62">
@@ -2954,27 +2954,27 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>藤川 昌樹</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>澤 亮治</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>0.8362932205200195</v>
+        <v>0.8302424252033234</v>
       </c>
       <c r="H62" t="n">
-        <v>0.8355565071105957</v>
+        <v>0.8261333405971527</v>
       </c>
       <c r="I62" t="n">
-        <v>0.8333501219749451</v>
+        <v>0.8258854150772095</v>
       </c>
     </row>
     <row r="63">
@@ -3000,22 +3000,22 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
+          <t>川島 宏一</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
           <t>佐野 幸恵</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>川島 宏一</t>
-        </is>
-      </c>
       <c r="G63" t="n">
-        <v>0.866408497095108</v>
+        <v>0.8613007962703705</v>
       </c>
       <c r="H63" t="n">
-        <v>0.8644002377986908</v>
+        <v>0.8604454696178436</v>
       </c>
       <c r="I63" t="n">
-        <v>0.8616088330745697</v>
+        <v>0.8575853407382965</v>
       </c>
     </row>
     <row r="64">
@@ -3041,22 +3041,22 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>谷口 綾子</t>
+          <t>澤 亮治</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>奥島 真一郎</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>0.8800965547561646</v>
+        <v>0.8834521174430847</v>
       </c>
       <c r="H64" t="n">
-        <v>0.8643222451210022</v>
+        <v>0.8635226488113403</v>
       </c>
       <c r="I64" t="n">
-        <v>0.8599986732006073</v>
+        <v>0.8611138761043549</v>
       </c>
     </row>
     <row r="65">
@@ -3077,27 +3077,27 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
+          <t>渡邉 俊</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
           <t>有田 智一</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>渡邉 俊</t>
-        </is>
-      </c>
       <c r="F65" t="inlineStr">
         <is>
           <t>川島 宏一</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>0.87774258852005</v>
+        <v>0.8763948082923889</v>
       </c>
       <c r="H65" t="n">
-        <v>0.8765729069709778</v>
+        <v>0.8742636442184448</v>
       </c>
       <c r="I65" t="n">
-        <v>0.8751640915870667</v>
+        <v>0.8731106519699097</v>
       </c>
     </row>
     <row r="66">
@@ -3128,17 +3128,17 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>有田 智一</t>
+          <t>渡邉 俊</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>0.8760607540607452</v>
+        <v>0.8665136098861694</v>
       </c>
       <c r="H66" t="n">
-        <v>0.868501752614975</v>
+        <v>0.8654606640338898</v>
       </c>
       <c r="I66" t="n">
-        <v>0.8683378994464874</v>
+        <v>0.8637252449989319</v>
       </c>
     </row>
     <row r="67">
@@ -3159,27 +3159,27 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
+          <t>渡邉 俊</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
           <t>有田 智一</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>川島 宏一</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>渡邉 俊</t>
-        </is>
-      </c>
       <c r="G67" t="n">
-        <v>0.8713784515857697</v>
+        <v>0.8704354763031006</v>
       </c>
       <c r="H67" t="n">
-        <v>0.8710208237171173</v>
+        <v>0.8700944781303406</v>
       </c>
       <c r="I67" t="n">
-        <v>0.8702171146869659</v>
+        <v>0.8686460852622986</v>
       </c>
     </row>
     <row r="68">
@@ -3214,13 +3214,13 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>0.8584946990013123</v>
+        <v>0.8532235026359558</v>
       </c>
       <c r="H68" t="n">
-        <v>0.8546058237552643</v>
+        <v>0.8512569665908813</v>
       </c>
       <c r="I68" t="n">
-        <v>0.8525292575359344</v>
+        <v>0.8432158827781677</v>
       </c>
     </row>
     <row r="69">
@@ -3246,22 +3246,22 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>作道 真理</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>岡田 幸彦</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>0.8676148355007172</v>
+        <v>0.8667275011539459</v>
       </c>
       <c r="H69" t="n">
-        <v>0.8644678592681885</v>
+        <v>0.8648611903190613</v>
       </c>
       <c r="I69" t="n">
-        <v>0.8629213571548462</v>
+        <v>0.8611284792423248</v>
       </c>
     </row>
     <row r="70">
@@ -3287,22 +3287,22 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>作道 真理</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>0.8750825822353363</v>
+        <v>0.8745884299278259</v>
       </c>
       <c r="H70" t="n">
-        <v>0.8746155500411987</v>
+        <v>0.8734764456748962</v>
       </c>
       <c r="I70" t="n">
-        <v>0.8739151060581207</v>
+        <v>0.8721948862075806</v>
       </c>
     </row>
     <row r="71">
@@ -3323,27 +3323,27 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>原田 信行</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
+          <t>牛島 光一</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
           <t>甲斐田 直子</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>川島 宏一</t>
-        </is>
-      </c>
       <c r="G71" t="n">
-        <v>0.871713787317276</v>
+        <v>0.8696563243865967</v>
       </c>
       <c r="H71" t="n">
-        <v>0.8697263896465302</v>
+        <v>0.8688327670097351</v>
       </c>
       <c r="I71" t="n">
-        <v>0.8666638731956482</v>
+        <v>0.8680279850959778</v>
       </c>
     </row>
     <row r="72">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>村上 暁信</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3374,17 +3374,17 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>飛田 幹男</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>0.8630807399749756</v>
+        <v>0.8609508275985718</v>
       </c>
       <c r="H72" t="n">
-        <v>0.8613697290420532</v>
+        <v>0.8593298196792603</v>
       </c>
       <c r="I72" t="n">
-        <v>0.8606661856174469</v>
+        <v>0.8565828204154968</v>
       </c>
     </row>
     <row r="73">
@@ -3405,27 +3405,27 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
+          <t>和田 健太郎</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
           <t>岡本 直久</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>鈴木 勉</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>和田 健太郎</t>
-        </is>
-      </c>
       <c r="G73" t="n">
-        <v>0.8718512058258057</v>
+        <v>0.8722729384899139</v>
       </c>
       <c r="H73" t="n">
-        <v>0.8703760504722595</v>
+        <v>0.8718547224998474</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8697851598262787</v>
+        <v>0.8710871338844299</v>
       </c>
     </row>
     <row r="74">
@@ -3451,22 +3451,22 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>太田 充</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>甲斐田 直子</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>0.8781124651432037</v>
+        <v>0.8737937211990356</v>
       </c>
       <c r="H74" t="n">
-        <v>0.8701009154319763</v>
+        <v>0.8721552789211273</v>
       </c>
       <c r="I74" t="n">
-        <v>0.8684175610542297</v>
+        <v>0.8709364831447601</v>
       </c>
     </row>
     <row r="75">
@@ -3497,17 +3497,17 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>0.8810763657093048</v>
+        <v>0.8804771602153778</v>
       </c>
       <c r="H75" t="n">
-        <v>0.8769265115261078</v>
+        <v>0.8803759813308716</v>
       </c>
       <c r="I75" t="n">
-        <v>0.8759317398071289</v>
+        <v>0.8761863708496094</v>
       </c>
     </row>
     <row r="76">
@@ -3542,13 +3542,13 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>0.8613660037517548</v>
+        <v>0.8619394898414612</v>
       </c>
       <c r="H76" t="n">
-        <v>0.8581895232200623</v>
+        <v>0.8587501049041748</v>
       </c>
       <c r="I76" t="n">
-        <v>0.8555910587310791</v>
+        <v>0.8567723035812378</v>
       </c>
     </row>
     <row r="77">
@@ -3569,27 +3569,27 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
+          <t>八森 正泰</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
           <t>和田 健太郎</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Phung-Duc Tuan</t>
-        </is>
-      </c>
       <c r="G77" t="n">
-        <v>0.872856616973877</v>
+        <v>0.8736216723918915</v>
       </c>
       <c r="H77" t="n">
-        <v>0.8727848827838898</v>
+        <v>0.872369110584259</v>
       </c>
       <c r="I77" t="n">
-        <v>0.8703022599220276</v>
+        <v>0.8709968030452728</v>
       </c>
     </row>
     <row r="78">
@@ -3615,22 +3615,22 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>堤 盛人</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>0.8818720877170563</v>
+        <v>0.8803968131542206</v>
       </c>
       <c r="H78" t="n">
-        <v>0.8740076422691345</v>
+        <v>0.8765251338481903</v>
       </c>
       <c r="I78" t="n">
-        <v>0.8737394213676453</v>
+        <v>0.8699567019939423</v>
       </c>
     </row>
     <row r="79">
@@ -3656,22 +3656,22 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
+          <t>鈴木 勉</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
           <t>佐野 幸恵</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>岡田 幸彦</t>
-        </is>
-      </c>
       <c r="G79" t="n">
-        <v>0.8754933774471283</v>
+        <v>0.8760639429092407</v>
       </c>
       <c r="H79" t="n">
-        <v>0.8700396716594696</v>
+        <v>0.8648146092891693</v>
       </c>
       <c r="I79" t="n">
-        <v>0.8682321310043335</v>
+        <v>0.8647044599056244</v>
       </c>
     </row>
     <row r="80">
@@ -3692,27 +3692,27 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
+          <t>牛島 光一</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
           <t>太田 充</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>牛島 光一</t>
-        </is>
-      </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>秋山 英三</t>
+          <t>上市 秀雄</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>0.8568066656589508</v>
+        <v>0.856104701757431</v>
       </c>
       <c r="H80" t="n">
-        <v>0.8566449582576752</v>
+        <v>0.854439914226532</v>
       </c>
       <c r="I80" t="n">
-        <v>0.8551899194717407</v>
+        <v>0.8523488640785217</v>
       </c>
     </row>
     <row r="81">
@@ -3738,22 +3738,22 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>雨宮 護</t>
+          <t>岡本 直久</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>堤 盛人</t>
+          <t>浦田淳司</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>0.8677469193935394</v>
+        <v>0.8559111952781677</v>
       </c>
       <c r="H81" t="n">
-        <v>0.858636885881424</v>
+        <v>0.8549925088882446</v>
       </c>
       <c r="I81" t="n">
-        <v>0.8584713041782379</v>
+        <v>0.8529223501682281</v>
       </c>
     </row>
     <row r="82">
@@ -3788,13 +3788,13 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>0.8579146862030029</v>
+        <v>0.8549389541149139</v>
       </c>
       <c r="H82" t="n">
-        <v>0.8535605072975159</v>
+        <v>0.853016585111618</v>
       </c>
       <c r="I82" t="n">
-        <v>0.849486380815506</v>
+        <v>0.8502903878688812</v>
       </c>
     </row>
     <row r="83">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>作道 真理</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3829,13 +3829,13 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>0.8581055998802185</v>
+        <v>0.8522348999977112</v>
       </c>
       <c r="H83" t="n">
-        <v>0.8570418357849121</v>
+        <v>0.8515084087848663</v>
       </c>
       <c r="I83" t="n">
-        <v>0.8521462678909302</v>
+        <v>0.8499585092067719</v>
       </c>
     </row>
     <row r="84">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3866,17 +3866,17 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>村上 暁信</t>
+          <t>イリチュ 美佳</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>0.8484123051166534</v>
+        <v>0.8504599630832672</v>
       </c>
       <c r="H84" t="n">
-        <v>0.8476902544498444</v>
+        <v>0.8449656069278717</v>
       </c>
       <c r="I84" t="n">
-        <v>0.8469191193580627</v>
+        <v>0.8425630629062653</v>
       </c>
     </row>
   </sheetData>
@@ -3963,22 +3963,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
+          <t>高野 祐一</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>高野 祐一</t>
+          <t>上市 秀雄</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.8655994832515717</v>
+        <v>0.8631241023540497</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8584177494049072</v>
+        <v>0.8607469499111176</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8582044243812561</v>
+        <v>0.8565534055233002</v>
       </c>
     </row>
     <row r="3">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>八森 正泰</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -4013,13 +4013,13 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.8599178791046143</v>
+        <v>0.8609103560447693</v>
       </c>
       <c r="H3" t="n">
-        <v>0.856866717338562</v>
+        <v>0.8535879850387573</v>
       </c>
       <c r="I3" t="n">
-        <v>0.850815623998642</v>
+        <v>0.852259486913681</v>
       </c>
     </row>
     <row r="4">
@@ -4045,22 +4045,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>高野 祐一</t>
+          <t>八森 正泰</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.8536908626556396</v>
+        <v>0.8563421070575714</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8510599136352539</v>
+        <v>0.8478223383426666</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8434899747371674</v>
+        <v>0.8461344838142395</v>
       </c>
     </row>
     <row r="5">
@@ -4081,27 +4081,27 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>吉瀬 章子</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>繁野 麻衣子</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>吉瀬 章子</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>有馬 澄佳</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.8755005896091461</v>
+        <v>0.8748292922973633</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8733445703983307</v>
+        <v>0.8652165830135345</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8610541224479675</v>
+        <v>0.8614690005779266</v>
       </c>
     </row>
     <row r="6">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -4136,13 +4136,13 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.8764640092849731</v>
+        <v>0.8760461509227753</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8743419647216797</v>
+        <v>0.8752144277095795</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8740573525428772</v>
+        <v>0.8724835813045502</v>
       </c>
     </row>
     <row r="7">
@@ -4173,17 +4173,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>岡田 幸彦</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.887189507484436</v>
+        <v>0.8824881315231323</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8698042631149292</v>
+        <v>0.8651013672351837</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8610810935497284</v>
+        <v>0.8542527854442596</v>
       </c>
     </row>
     <row r="8">
@@ -4204,27 +4204,27 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>吉瀬 章子</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>吉瀬 章子</t>
+          <t>高野 祐一</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>高野 祐一</t>
+          <t>八森 正泰</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.8727676868438721</v>
+        <v>0.8712441325187683</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8723370432853699</v>
+        <v>0.8706216514110565</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8690331280231476</v>
+        <v>0.8673337697982788</v>
       </c>
     </row>
     <row r="9">
@@ -4245,27 +4245,27 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>川島 宏一</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>岡田 幸彦</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>川島 宏一</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>イリチュ 美佳</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.8713008165359497</v>
+        <v>0.872202605009079</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8693908452987671</v>
+        <v>0.8711293339729309</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8662359416484833</v>
+        <v>0.8628892600536346</v>
       </c>
     </row>
     <row r="10">
@@ -4291,22 +4291,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>有馬 澄佳</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>繁野 麻衣子</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>髙橋裕紀</t>
-        </is>
-      </c>
       <c r="G10" t="n">
-        <v>0.8638443946838379</v>
+        <v>0.8638104796409607</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8611145615577698</v>
+        <v>0.8521934747695923</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8536087870597839</v>
+        <v>0.8515247106552124</v>
       </c>
     </row>
     <row r="11">
@@ -4337,17 +4337,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>髙橋裕紀</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.8799342513084412</v>
+        <v>0.8786357045173645</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8656601309776306</v>
+        <v>0.8642593622207642</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8637024164199829</v>
+        <v>0.860405832529068</v>
       </c>
     </row>
     <row r="12">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.8852237164974213</v>
+        <v>0.8868876993656158</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8602020144462585</v>
+        <v>0.8567197620868683</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8592531085014343</v>
+        <v>0.8518258035182953</v>
       </c>
     </row>
     <row r="13">
@@ -4423,13 +4423,13 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.8827695846557617</v>
+        <v>0.8796600997447968</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8713669776916504</v>
+        <v>0.8722549974918365</v>
       </c>
       <c r="I13" t="n">
-        <v>0.857954204082489</v>
+        <v>0.8572300374507904</v>
       </c>
     </row>
     <row r="14">
@@ -4450,27 +4450,27 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>高野 祐一</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>黒瀬 雄大</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>イリチュ 美佳</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>黒瀬 雄大</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>髙橋裕紀</t>
-        </is>
-      </c>
       <c r="G14" t="n">
-        <v>0.8514187932014465</v>
+        <v>0.84958815574646</v>
       </c>
       <c r="H14" t="n">
-        <v>0.85108882188797</v>
+        <v>0.8485821783542633</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8484852015972137</v>
+        <v>0.8477443158626556</v>
       </c>
     </row>
     <row r="15">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>黒瀬 雄大</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.8624188005924225</v>
+        <v>0.8557057082653046</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8561882376670837</v>
+        <v>0.8450488448143005</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8552936315536499</v>
+        <v>0.842248797416687</v>
       </c>
     </row>
     <row r="16">
@@ -4532,12 +4532,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>八森 正泰</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>八森 正泰</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -4546,13 +4546,13 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.8731126487255096</v>
+        <v>0.8684133589267731</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8647971451282501</v>
+        <v>0.8607102632522583</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8619018793106079</v>
+        <v>0.8606576025485992</v>
       </c>
     </row>
     <row r="17">
@@ -4583,17 +4583,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>髙橋裕紀</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0.870884120464325</v>
+        <v>0.8662374019622803</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8654924631118774</v>
+        <v>0.8516285419464111</v>
       </c>
       <c r="I17" t="n">
-        <v>0.865092396736145</v>
+        <v>0.8516241312026978</v>
       </c>
     </row>
     <row r="18">
@@ -4619,22 +4619,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>浦田淳司</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>岡田 幸彦</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>髙橋裕紀</t>
-        </is>
-      </c>
       <c r="G18" t="n">
-        <v>0.8637301027774811</v>
+        <v>0.8556589782238007</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8542537987232208</v>
+        <v>0.8480800688266754</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8541643619537354</v>
+        <v>0.8461096286773682</v>
       </c>
     </row>
     <row r="19">
@@ -4660,22 +4660,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Phung-Duc Tuan</t>
+          <t>八森 正泰</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0.870453953742981</v>
+        <v>0.8692283034324646</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8658804893493652</v>
+        <v>0.8580313920974731</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8593435287475586</v>
+        <v>0.8552308678627014</v>
       </c>
     </row>
     <row r="20">
@@ -4701,22 +4701,22 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>岡田 幸彦</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>イリチュ 美佳</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>岡田 幸彦</t>
-        </is>
-      </c>
       <c r="G20" t="n">
-        <v>0.8740392327308655</v>
+        <v>0.8761183619499207</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8692725598812103</v>
+        <v>0.867241382598877</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8674855530261993</v>
+        <v>0.86562180519104</v>
       </c>
     </row>
     <row r="21">
@@ -4747,17 +4747,17 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>浦田淳司</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0.8658023476600647</v>
+        <v>0.8668003678321838</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8634548485279083</v>
+        <v>0.8634408414363861</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8619240820407867</v>
+        <v>0.8633632361888885</v>
       </c>
     </row>
     <row r="22">
@@ -4778,27 +4778,27 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>作道 真理</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>原田 信行</t>
+          <t>堤 盛人</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>黒瀬 雄大</t>
+          <t>岡田 幸彦</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.8738839030265808</v>
+        <v>0.8656387031078339</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8722674250602722</v>
+        <v>0.8634596467018127</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8667078912258148</v>
+        <v>0.8629354536533356</v>
       </c>
     </row>
   </sheetData>

--- a/generated/committee_recommendations.xlsx
+++ b/generated/committee_recommendations.xlsx
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.8734617531299591</v>
+        <v>0.8734618127346039</v>
       </c>
       <c r="H3" t="n">
         <v>0.8607054650783539</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8574923276901245</v>
+        <v>0.8574923872947693</v>
       </c>
     </row>
     <row r="4">
@@ -637,7 +637,7 @@
         <v>0.8693714141845703</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8666558861732483</v>
+        <v>0.8666558563709259</v>
       </c>
     </row>
     <row r="6">
@@ -672,13 +672,13 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.8622949421405792</v>
+        <v>0.8622950315475464</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8608851730823517</v>
+        <v>0.8608852624893188</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8604684770107269</v>
+        <v>0.8604684472084045</v>
       </c>
     </row>
     <row r="7">
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.8782476484775543</v>
+        <v>0.8782475590705872</v>
       </c>
       <c r="H7" t="n">
         <v>0.8727595508098602</v>
@@ -836,13 +836,13 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.8714622557163239</v>
+        <v>0.8714622259140015</v>
       </c>
       <c r="H10" t="n">
         <v>0.8703478574752808</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8688311576843262</v>
+        <v>0.8688310980796814</v>
       </c>
     </row>
     <row r="11">
@@ -965,7 +965,7 @@
         <v>0.846853107213974</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8349056243896484</v>
+        <v>0.834905594587326</v>
       </c>
     </row>
     <row r="14">
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.8779064118862152</v>
+        <v>0.8779063522815704</v>
       </c>
       <c r="H14" t="n">
         <v>0.8726606070995331</v>
@@ -1044,10 +1044,10 @@
         <v>0.8802605867385864</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8750885725021362</v>
+        <v>0.875088632106781</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8705006837844849</v>
+        <v>0.8705006539821625</v>
       </c>
     </row>
     <row r="16">
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0.8586440086364746</v>
+        <v>0.8586438894271851</v>
       </c>
       <c r="H17" t="n">
         <v>0.8549793362617493</v>
@@ -1208,7 +1208,7 @@
         <v>0.8647384345531464</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8633520305156708</v>
+        <v>0.8633520007133484</v>
       </c>
       <c r="I19" t="n">
         <v>0.8614738583564758</v>
@@ -1249,7 +1249,7 @@
         <v>0.8822429776191711</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8785501420497894</v>
+        <v>0.8785502910614014</v>
       </c>
       <c r="I20" t="n">
         <v>0.8663562834262848</v>
@@ -1328,10 +1328,10 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.8789419531822205</v>
+        <v>0.8789419233798981</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8760955929756165</v>
+        <v>0.8760957717895508</v>
       </c>
       <c r="I22" t="n">
         <v>0.8730508089065552</v>
@@ -1369,13 +1369,13 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0.8591336905956268</v>
+        <v>0.8591337203979492</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8517085015773773</v>
+        <v>0.8517085313796997</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8514227271080017</v>
+        <v>0.8514226973056793</v>
       </c>
     </row>
     <row r="24">
@@ -1413,7 +1413,7 @@
         <v>0.8527725040912628</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8512898087501526</v>
+        <v>0.8512897491455078</v>
       </c>
       <c r="I24" t="n">
         <v>0.8512193560600281</v>
@@ -1451,10 +1451,10 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0.8706742227077484</v>
+        <v>0.8706742525100708</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8638857305049896</v>
+        <v>0.8638857007026672</v>
       </c>
       <c r="I25" t="n">
         <v>0.8618723750114441</v>
@@ -1495,7 +1495,7 @@
         <v>0.8637948930263519</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8582098484039307</v>
+        <v>0.8582097887992859</v>
       </c>
       <c r="I26" t="n">
         <v>0.8576050400733948</v>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0.8603377938270569</v>
+        <v>0.8603377342224121</v>
       </c>
       <c r="H27" t="n">
         <v>0.8578148186206818</v>
@@ -1618,7 +1618,7 @@
         <v>0.8728598952293396</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8667237460613251</v>
+        <v>0.8667237758636475</v>
       </c>
       <c r="I29" t="n">
         <v>0.862547755241394</v>
@@ -1659,7 +1659,7 @@
         <v>0.8834352493286133</v>
       </c>
       <c r="H30" t="n">
-        <v>0.8568967878818512</v>
+        <v>0.8568968176841736</v>
       </c>
       <c r="I30" t="n">
         <v>0.855995774269104</v>
@@ -1738,13 +1738,13 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0.8575133681297302</v>
+        <v>0.857513427734375</v>
       </c>
       <c r="H32" t="n">
-        <v>0.8523845374584198</v>
+        <v>0.852384477853775</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8516231775283813</v>
+        <v>0.8516232371330261</v>
       </c>
     </row>
     <row r="33">
@@ -1782,10 +1782,10 @@
         <v>0.8604612350463867</v>
       </c>
       <c r="H33" t="n">
-        <v>0.8577742874622345</v>
+        <v>0.8577743470668793</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8568277060985565</v>
+        <v>0.8568276762962341</v>
       </c>
     </row>
     <row r="34">
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0.8634571731090546</v>
+        <v>0.8634571433067322</v>
       </c>
       <c r="H34" t="n">
         <v>0.8626152873039246</v>
@@ -1902,10 +1902,10 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0.8759266436100006</v>
+        <v>0.875926673412323</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8738082349300385</v>
+        <v>0.8738082647323608</v>
       </c>
       <c r="I36" t="n">
         <v>0.8677709102630615</v>
@@ -1943,13 +1943,13 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0.8812141418457031</v>
+        <v>0.8812141716480255</v>
       </c>
       <c r="H37" t="n">
-        <v>0.8779473304748535</v>
+        <v>0.8779473602771759</v>
       </c>
       <c r="I37" t="n">
-        <v>0.8733148872852325</v>
+        <v>0.8733149170875549</v>
       </c>
     </row>
     <row r="38">
@@ -1990,7 +1990,7 @@
         <v>0.8683319687843323</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8629850745201111</v>
+        <v>0.8629851043224335</v>
       </c>
     </row>
     <row r="39">
@@ -2025,10 +2025,10 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0.8841175734996796</v>
+        <v>0.8841176629066467</v>
       </c>
       <c r="H39" t="n">
-        <v>0.8798271417617798</v>
+        <v>0.8798271715641022</v>
       </c>
       <c r="I39" t="n">
         <v>0.879041850566864</v>
@@ -2066,13 +2066,13 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0.883649080991745</v>
+        <v>0.8836490213871002</v>
       </c>
       <c r="H40" t="n">
-        <v>0.8805911242961884</v>
+        <v>0.8805910348892212</v>
       </c>
       <c r="I40" t="n">
-        <v>0.8768988847732544</v>
+        <v>0.8768989443778992</v>
       </c>
     </row>
     <row r="41">
@@ -2113,7 +2113,7 @@
         <v>0.8708105385303497</v>
       </c>
       <c r="I41" t="n">
-        <v>0.8650574684143066</v>
+        <v>0.8650574386119843</v>
       </c>
     </row>
     <row r="42">
@@ -2148,13 +2148,13 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0.8621289134025574</v>
+        <v>0.8621288537979126</v>
       </c>
       <c r="H42" t="n">
-        <v>0.8617661893367767</v>
+        <v>0.8617662489414215</v>
       </c>
       <c r="I42" t="n">
-        <v>0.8485496342182159</v>
+        <v>0.8485495746135712</v>
       </c>
     </row>
     <row r="43">
@@ -2195,7 +2195,7 @@
         <v>0.8674532473087311</v>
       </c>
       <c r="I43" t="n">
-        <v>0.8664050996303558</v>
+        <v>0.8664051592350006</v>
       </c>
     </row>
     <row r="44">
@@ -2230,13 +2230,13 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0.8610956370830536</v>
+        <v>0.861095666885376</v>
       </c>
       <c r="H44" t="n">
         <v>0.8599763512611389</v>
       </c>
       <c r="I44" t="n">
-        <v>0.85889932513237</v>
+        <v>0.8588992655277252</v>
       </c>
     </row>
     <row r="45">
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0.88481405377388</v>
+        <v>0.8848140835762024</v>
       </c>
       <c r="H45" t="n">
         <v>0.8846468329429626</v>
@@ -2312,7 +2312,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0.8624061048030853</v>
+        <v>0.8624060153961182</v>
       </c>
       <c r="H46" t="n">
         <v>0.8623032569885254</v>
@@ -2353,13 +2353,13 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>0.8822457492351532</v>
+        <v>0.8822457790374756</v>
       </c>
       <c r="H47" t="n">
-        <v>0.8808684051036835</v>
+        <v>0.8808684349060059</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8808216154575348</v>
+        <v>0.8808216452598572</v>
       </c>
     </row>
     <row r="48">
@@ -2400,7 +2400,7 @@
         <v>0.8661503791809082</v>
       </c>
       <c r="I48" t="n">
-        <v>0.8655958473682404</v>
+        <v>0.8655959069728851</v>
       </c>
     </row>
     <row r="49">
@@ -2441,7 +2441,7 @@
         <v>0.8649434447288513</v>
       </c>
       <c r="I49" t="n">
-        <v>0.864597499370575</v>
+        <v>0.8645975291728973</v>
       </c>
     </row>
     <row r="50">
@@ -2479,10 +2479,10 @@
         <v>0.8805749118328094</v>
       </c>
       <c r="H50" t="n">
-        <v>0.8783854246139526</v>
+        <v>0.8783853054046631</v>
       </c>
       <c r="I50" t="n">
-        <v>0.8773878812789917</v>
+        <v>0.8773879110813141</v>
       </c>
     </row>
     <row r="51">
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>0.8623651564121246</v>
+        <v>0.8623651266098022</v>
       </c>
       <c r="H51" t="n">
-        <v>0.855972558259964</v>
+        <v>0.8559726178646088</v>
       </c>
       <c r="I51" t="n">
         <v>0.8509648144245148</v>
@@ -2558,10 +2558,10 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>0.8601011633872986</v>
+        <v>0.860101193189621</v>
       </c>
       <c r="H52" t="n">
-        <v>0.8564841449260712</v>
+        <v>0.8564842045307159</v>
       </c>
       <c r="I52" t="n">
         <v>0.8554677963256836</v>
@@ -2602,10 +2602,10 @@
         <v>0.8770773708820343</v>
       </c>
       <c r="H53" t="n">
-        <v>0.8713475167751312</v>
+        <v>0.8713475465774536</v>
       </c>
       <c r="I53" t="n">
-        <v>0.8681096136569977</v>
+        <v>0.8681095838546753</v>
       </c>
     </row>
     <row r="54">
@@ -2640,10 +2640,10 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>0.8658912181854248</v>
+        <v>0.86589115858078</v>
       </c>
       <c r="H54" t="n">
-        <v>0.8628571927547455</v>
+        <v>0.8628572523593903</v>
       </c>
       <c r="I54" t="n">
         <v>0.8591557145118713</v>
@@ -2681,13 +2681,13 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>0.8445272147655487</v>
+        <v>0.8445272743701935</v>
       </c>
       <c r="H55" t="n">
-        <v>0.8444044291973114</v>
+        <v>0.8444043695926666</v>
       </c>
       <c r="I55" t="n">
-        <v>0.8435723185539246</v>
+        <v>0.8435723483562469</v>
       </c>
     </row>
     <row r="56">
@@ -2725,10 +2725,10 @@
         <v>0.8806582093238831</v>
       </c>
       <c r="H56" t="n">
-        <v>0.8783489763736725</v>
+        <v>0.8783490359783173</v>
       </c>
       <c r="I56" t="n">
-        <v>0.8719048202037811</v>
+        <v>0.8719048798084259</v>
       </c>
     </row>
     <row r="57">
@@ -2763,7 +2763,7 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>0.844330906867981</v>
+        <v>0.8443308770656586</v>
       </c>
       <c r="H57" t="n">
         <v>0.8426342308521271</v>
@@ -2807,10 +2807,10 @@
         <v>0.8724232614040375</v>
       </c>
       <c r="H58" t="n">
-        <v>0.8723962903022766</v>
+        <v>0.8723962604999542</v>
       </c>
       <c r="I58" t="n">
-        <v>0.86982461810112</v>
+        <v>0.8698245584964752</v>
       </c>
     </row>
     <row r="59">
@@ -2886,13 +2886,13 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>0.8743585348129272</v>
+        <v>0.8743585646152496</v>
       </c>
       <c r="H60" t="n">
-        <v>0.8707767426967621</v>
+        <v>0.8707767724990845</v>
       </c>
       <c r="I60" t="n">
-        <v>0.8681854009628296</v>
+        <v>0.8681853413581848</v>
       </c>
     </row>
     <row r="61">
@@ -2927,13 +2927,13 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>0.8797606825828552</v>
+        <v>0.8797605931758881</v>
       </c>
       <c r="H61" t="n">
-        <v>0.8760299682617188</v>
+        <v>0.8760299980640411</v>
       </c>
       <c r="I61" t="n">
-        <v>0.8728488087654114</v>
+        <v>0.8728488683700562</v>
       </c>
     </row>
     <row r="62">
@@ -2968,10 +2968,10 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>0.8302424252033234</v>
+        <v>0.8302424550056458</v>
       </c>
       <c r="H62" t="n">
-        <v>0.8261333405971527</v>
+        <v>0.8261333703994751</v>
       </c>
       <c r="I62" t="n">
         <v>0.8258854150772095</v>
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>0.8613007962703705</v>
+        <v>0.8613007366657257</v>
       </c>
       <c r="H63" t="n">
-        <v>0.8604454696178436</v>
+        <v>0.8604455292224884</v>
       </c>
       <c r="I63" t="n">
-        <v>0.8575853407382965</v>
+        <v>0.8575854003429413</v>
       </c>
     </row>
     <row r="64">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>0.8834521174430847</v>
+        <v>0.8834521770477295</v>
       </c>
       <c r="H64" t="n">
         <v>0.8635226488113403</v>
       </c>
       <c r="I64" t="n">
-        <v>0.8611138761043549</v>
+        <v>0.861113965511322</v>
       </c>
     </row>
     <row r="65">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>0.8763948082923889</v>
+        <v>0.8763948380947113</v>
       </c>
       <c r="H65" t="n">
         <v>0.8742636442184448</v>
@@ -3132,13 +3132,13 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>0.8665136098861694</v>
+        <v>0.8665135502815247</v>
       </c>
       <c r="H66" t="n">
         <v>0.8654606640338898</v>
       </c>
       <c r="I66" t="n">
-        <v>0.8637252449989319</v>
+        <v>0.8637252748012543</v>
       </c>
     </row>
     <row r="67">
@@ -3173,13 +3173,13 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>0.8704354763031006</v>
+        <v>0.8704354465007782</v>
       </c>
       <c r="H67" t="n">
         <v>0.8700944781303406</v>
       </c>
       <c r="I67" t="n">
-        <v>0.8686460852622986</v>
+        <v>0.868646115064621</v>
       </c>
     </row>
     <row r="68">
@@ -3258,10 +3258,10 @@
         <v>0.8667275011539459</v>
       </c>
       <c r="H69" t="n">
-        <v>0.8648611903190613</v>
+        <v>0.8648612201213837</v>
       </c>
       <c r="I69" t="n">
-        <v>0.8611284792423248</v>
+        <v>0.8611284494400024</v>
       </c>
     </row>
     <row r="70">
@@ -3296,13 +3296,13 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>0.8745884299278259</v>
+        <v>0.8745883405208588</v>
       </c>
       <c r="H70" t="n">
-        <v>0.8734764456748962</v>
+        <v>0.8734764754772186</v>
       </c>
       <c r="I70" t="n">
-        <v>0.8721948862075806</v>
+        <v>0.872194916009903</v>
       </c>
     </row>
     <row r="71">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>0.8609508275985718</v>
+        <v>0.8609508872032166</v>
       </c>
       <c r="H72" t="n">
-        <v>0.8593298196792603</v>
+        <v>0.859329879283905</v>
       </c>
       <c r="I72" t="n">
-        <v>0.8565828204154968</v>
+        <v>0.8565827906131744</v>
       </c>
     </row>
     <row r="73">
@@ -3419,13 +3419,13 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>0.8722729384899139</v>
+        <v>0.8722729086875916</v>
       </c>
       <c r="H73" t="n">
         <v>0.8718547224998474</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8710871338844299</v>
+        <v>0.8710871636867523</v>
       </c>
     </row>
     <row r="74">
@@ -3463,10 +3463,10 @@
         <v>0.8737937211990356</v>
       </c>
       <c r="H74" t="n">
-        <v>0.8721552789211273</v>
+        <v>0.8721553683280945</v>
       </c>
       <c r="I74" t="n">
-        <v>0.8709364831447601</v>
+        <v>0.8709365725517273</v>
       </c>
     </row>
     <row r="75">
@@ -3501,13 +3501,13 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>0.8804771602153778</v>
+        <v>0.8804772198200226</v>
       </c>
       <c r="H75" t="n">
         <v>0.8803759813308716</v>
       </c>
       <c r="I75" t="n">
-        <v>0.8761863708496094</v>
+        <v>0.8761864006519318</v>
       </c>
     </row>
     <row r="76">
@@ -3545,7 +3545,7 @@
         <v>0.8619394898414612</v>
       </c>
       <c r="H76" t="n">
-        <v>0.8587501049041748</v>
+        <v>0.8587501347064972</v>
       </c>
       <c r="I76" t="n">
         <v>0.8567723035812378</v>
@@ -3624,13 +3624,13 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>0.8803968131542206</v>
+        <v>0.880396842956543</v>
       </c>
       <c r="H78" t="n">
-        <v>0.8765251338481903</v>
+        <v>0.8765251636505127</v>
       </c>
       <c r="I78" t="n">
-        <v>0.8699567019939423</v>
+        <v>0.8699566721916199</v>
       </c>
     </row>
     <row r="79">
@@ -3665,13 +3665,13 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>0.8760639429092407</v>
+        <v>0.8760638833045959</v>
       </c>
       <c r="H79" t="n">
-        <v>0.8648146092891693</v>
+        <v>0.8648146986961365</v>
       </c>
       <c r="I79" t="n">
-        <v>0.8647044599056244</v>
+        <v>0.8647044897079468</v>
       </c>
     </row>
     <row r="80">
@@ -3706,13 +3706,13 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>0.856104701757431</v>
+        <v>0.8561046719551086</v>
       </c>
       <c r="H80" t="n">
         <v>0.854439914226532</v>
       </c>
       <c r="I80" t="n">
-        <v>0.8523488640785217</v>
+        <v>0.852348804473877</v>
       </c>
     </row>
     <row r="81">
@@ -3753,7 +3753,7 @@
         <v>0.8549925088882446</v>
       </c>
       <c r="I81" t="n">
-        <v>0.8529223501682281</v>
+        <v>0.8529223203659058</v>
       </c>
     </row>
     <row r="82">
@@ -3791,10 +3791,10 @@
         <v>0.8549389541149139</v>
       </c>
       <c r="H82" t="n">
-        <v>0.853016585111618</v>
+        <v>0.8530166149139404</v>
       </c>
       <c r="I82" t="n">
-        <v>0.8502903878688812</v>
+        <v>0.8502903282642365</v>
       </c>
     </row>
     <row r="83">
@@ -3835,7 +3835,7 @@
         <v>0.8515084087848663</v>
       </c>
       <c r="I83" t="n">
-        <v>0.8499585092067719</v>
+        <v>0.8499585688114166</v>
       </c>
     </row>
     <row r="84">
@@ -3870,7 +3870,7 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>0.8504599630832672</v>
+        <v>0.850460022687912</v>
       </c>
       <c r="H84" t="n">
         <v>0.8449656069278717</v>
@@ -4139,10 +4139,10 @@
         <v>0.8760461509227753</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8752144277095795</v>
+        <v>0.8752143979072571</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8724835813045502</v>
+        <v>0.8724835515022278</v>
       </c>
     </row>
     <row r="7">
@@ -4183,7 +4183,7 @@
         <v>0.8651013672351837</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8542527854442596</v>
+        <v>0.854252815246582</v>
       </c>
     </row>
     <row r="8">
@@ -4259,10 +4259,10 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.872202605009079</v>
+        <v>0.8722025752067566</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8711293339729309</v>
+        <v>0.8711293041706085</v>
       </c>
       <c r="I9" t="n">
         <v>0.8628892600536346</v>
@@ -4388,7 +4388,7 @@
         <v>0.8567197620868683</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8518258035182953</v>
+        <v>0.8518259227275848</v>
       </c>
     </row>
     <row r="13">
@@ -4423,10 +4423,10 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.8796600997447968</v>
+        <v>0.8796601295471191</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8722549974918365</v>
+        <v>0.8722549676895142</v>
       </c>
       <c r="I13" t="n">
         <v>0.8572300374507904</v>
@@ -4508,7 +4508,7 @@
         <v>0.8557057082653046</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8450488448143005</v>
+        <v>0.8450488150119781</v>
       </c>
       <c r="I15" t="n">
         <v>0.842248797416687</v>
@@ -4593,7 +4593,7 @@
         <v>0.8516285419464111</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8516241312026978</v>
+        <v>0.8516241908073425</v>
       </c>
     </row>
     <row r="18">
@@ -4631,10 +4631,10 @@
         <v>0.8556589782238007</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8480800688266754</v>
+        <v>0.8480800986289978</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8461096286773682</v>
+        <v>0.8461095988750458</v>
       </c>
     </row>
     <row r="19">
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0.8761183619499207</v>
+        <v>0.8761183023452759</v>
       </c>
       <c r="H20" t="n">
         <v>0.867241382598877</v>
@@ -4757,7 +4757,7 @@
         <v>0.8634408414363861</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8633632361888885</v>
+        <v>0.8633631765842438</v>
       </c>
     </row>
     <row r="22">
@@ -4792,10 +4792,10 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.8656387031078339</v>
+        <v>0.8656386435031891</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8634596467018127</v>
+        <v>0.8634596168994904</v>
       </c>
       <c r="I22" t="n">
         <v>0.8629354536533356</v>

--- a/generated/committee_recommendations.xlsx
+++ b/generated/committee_recommendations.xlsx
@@ -508,13 +508,13 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.8637408018112183</v>
+        <v>0.8637408316135406</v>
       </c>
       <c r="H2" t="n">
         <v>0.8561815619468689</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8561266660690308</v>
+        <v>0.856126606464386</v>
       </c>
     </row>
     <row r="3">
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.8734618127346039</v>
+        <v>0.8734617829322815</v>
       </c>
       <c r="H3" t="n">
         <v>0.8607054650783539</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8574923872947693</v>
+        <v>0.8574922978878021</v>
       </c>
     </row>
     <row r="4">
@@ -590,10 +590,10 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.8704100847244263</v>
+        <v>0.8704101145267487</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8587318658828735</v>
+        <v>0.8587318062782288</v>
       </c>
       <c r="I4" t="n">
         <v>0.8560931086540222</v>
@@ -637,7 +637,7 @@
         <v>0.8693714141845703</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8666558563709259</v>
+        <v>0.8666557967662811</v>
       </c>
     </row>
     <row r="6">
@@ -672,13 +672,13 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.8622950315475464</v>
+        <v>0.8622949123382568</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8608852624893188</v>
+        <v>0.8608852028846741</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8604684472084045</v>
+        <v>0.8604684770107269</v>
       </c>
     </row>
     <row r="7">
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.8782475590705872</v>
+        <v>0.8782475888729095</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8727595508098602</v>
+        <v>0.8727595210075378</v>
       </c>
       <c r="I7" t="n">
         <v>0.8720541596412659</v>
@@ -836,13 +836,13 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.8714622259140015</v>
+        <v>0.8714621663093567</v>
       </c>
       <c r="H10" t="n">
         <v>0.8703478574752808</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8688310980796814</v>
+        <v>0.868831068277359</v>
       </c>
     </row>
     <row r="11">
@@ -921,10 +921,10 @@
         <v>0.8546874523162842</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8504401743412018</v>
+        <v>0.8504403233528137</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8490931987762451</v>
+        <v>0.8490931689739227</v>
       </c>
     </row>
     <row r="13">
@@ -962,7 +962,7 @@
         <v>0.8592478334903717</v>
       </c>
       <c r="H13" t="n">
-        <v>0.846853107213974</v>
+        <v>0.8465917408466339</v>
       </c>
       <c r="I13" t="n">
         <v>0.834905594587326</v>
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.8779063522815704</v>
+        <v>0.8779064118862152</v>
       </c>
       <c r="H14" t="n">
         <v>0.8726606070995331</v>
@@ -1044,10 +1044,10 @@
         <v>0.8802605867385864</v>
       </c>
       <c r="H15" t="n">
-        <v>0.875088632106781</v>
+        <v>0.8750886023044586</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8705006539821625</v>
+        <v>0.8705006837844849</v>
       </c>
     </row>
     <row r="16">
@@ -1088,7 +1088,7 @@
         <v>0.8685945868492126</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8660972416400909</v>
+        <v>0.8661127984523773</v>
       </c>
     </row>
     <row r="17">
@@ -1208,10 +1208,10 @@
         <v>0.8647384345531464</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8633520007133484</v>
+        <v>0.8633520305156708</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8614738583564758</v>
+        <v>0.8614737987518311</v>
       </c>
     </row>
     <row r="20">
@@ -1249,7 +1249,7 @@
         <v>0.8822429776191711</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8785502910614014</v>
+        <v>0.8785503208637238</v>
       </c>
       <c r="I20" t="n">
         <v>0.8663562834262848</v>
@@ -1328,10 +1328,10 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.8789419233798981</v>
+        <v>0.8789419531822205</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8760957717895508</v>
+        <v>0.876095712184906</v>
       </c>
       <c r="I22" t="n">
         <v>0.8730508089065552</v>
@@ -1369,13 +1369,13 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0.8591337203979492</v>
+        <v>0.8591337502002716</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8517085313796997</v>
+        <v>0.8517085015773773</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8514226973056793</v>
+        <v>0.8514227271080017</v>
       </c>
     </row>
     <row r="24">
@@ -1410,10 +1410,10 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0.8527725040912628</v>
+        <v>0.8527725636959076</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8512897491455078</v>
+        <v>0.8512898087501526</v>
       </c>
       <c r="I24" t="n">
         <v>0.8512193560600281</v>
@@ -1451,10 +1451,10 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0.8706742525100708</v>
+        <v>0.8706742823123932</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8638857007026672</v>
+        <v>0.863885760307312</v>
       </c>
       <c r="I25" t="n">
         <v>0.8618723750114441</v>
@@ -1495,7 +1495,7 @@
         <v>0.8637948930263519</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8582097887992859</v>
+        <v>0.8582098484039307</v>
       </c>
       <c r="I26" t="n">
         <v>0.8576050400733948</v>
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0.8603377342224121</v>
+        <v>0.8603377640247345</v>
       </c>
       <c r="H27" t="n">
-        <v>0.8578148186206818</v>
+        <v>0.8578147888183594</v>
       </c>
       <c r="I27" t="n">
         <v>0.8570154905319214</v>
@@ -1580,7 +1580,7 @@
         <v>0.8709458708763123</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8677204847335815</v>
+        <v>0.8677360415458679</v>
       </c>
     </row>
     <row r="29">
@@ -1659,10 +1659,10 @@
         <v>0.8834352493286133</v>
       </c>
       <c r="H30" t="n">
-        <v>0.8568968176841736</v>
+        <v>0.8568967878818512</v>
       </c>
       <c r="I30" t="n">
-        <v>0.855995774269104</v>
+        <v>0.8559958040714264</v>
       </c>
     </row>
     <row r="31">
@@ -1738,13 +1738,13 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0.857513427734375</v>
+        <v>0.8575133681297302</v>
       </c>
       <c r="H32" t="n">
-        <v>0.852384477853775</v>
+        <v>0.8523843884468079</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8516232371330261</v>
+        <v>0.8516231775283813</v>
       </c>
     </row>
     <row r="33">
@@ -1782,7 +1782,7 @@
         <v>0.8604612350463867</v>
       </c>
       <c r="H33" t="n">
-        <v>0.8577743470668793</v>
+        <v>0.8577743172645569</v>
       </c>
       <c r="I33" t="n">
         <v>0.8568276762962341</v>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0.8634571433067322</v>
+        <v>0.8634571135044098</v>
       </c>
       <c r="H34" t="n">
         <v>0.8626152873039246</v>
@@ -1867,7 +1867,7 @@
         <v>0.8801654279232025</v>
       </c>
       <c r="I35" t="n">
-        <v>0.8745454549789429</v>
+        <v>0.8745455145835876</v>
       </c>
     </row>
     <row r="36">
@@ -1905,10 +1905,10 @@
         <v>0.875926673412323</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8738082647323608</v>
+        <v>0.8738082945346832</v>
       </c>
       <c r="I36" t="n">
-        <v>0.8677709102630615</v>
+        <v>0.8677709400653839</v>
       </c>
     </row>
     <row r="37">
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0.8812141716480255</v>
+        <v>0.8812141120433807</v>
       </c>
       <c r="H37" t="n">
-        <v>0.8779473602771759</v>
+        <v>0.8779473900794983</v>
       </c>
       <c r="I37" t="n">
         <v>0.8733149170875549</v>
@@ -2025,10 +2025,10 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0.8841176629066467</v>
+        <v>0.884117603302002</v>
       </c>
       <c r="H39" t="n">
-        <v>0.8798271715641022</v>
+        <v>0.8798272013664246</v>
       </c>
       <c r="I39" t="n">
         <v>0.879041850566864</v>
@@ -2072,7 +2072,7 @@
         <v>0.8805910348892212</v>
       </c>
       <c r="I40" t="n">
-        <v>0.8768989443778992</v>
+        <v>0.8768988847732544</v>
       </c>
     </row>
     <row r="41">
@@ -2107,13 +2107,13 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0.8722117841243744</v>
+        <v>0.8722117245197296</v>
       </c>
       <c r="H41" t="n">
-        <v>0.8708105385303497</v>
+        <v>0.8708105683326721</v>
       </c>
       <c r="I41" t="n">
-        <v>0.8650574386119843</v>
+        <v>0.8650574684143066</v>
       </c>
     </row>
     <row r="42">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0.8621288537979126</v>
+        <v>0.8621289134025574</v>
       </c>
       <c r="H42" t="n">
-        <v>0.8617662489414215</v>
+        <v>0.8617661893367767</v>
       </c>
       <c r="I42" t="n">
         <v>0.8485495746135712</v>
@@ -2192,10 +2192,10 @@
         <v>0.8732402920722961</v>
       </c>
       <c r="H43" t="n">
-        <v>0.8674532473087311</v>
+        <v>0.8674532175064087</v>
       </c>
       <c r="I43" t="n">
-        <v>0.8664051592350006</v>
+        <v>0.8664050698280334</v>
       </c>
     </row>
     <row r="44">
@@ -2236,7 +2236,7 @@
         <v>0.8599763512611389</v>
       </c>
       <c r="I44" t="n">
-        <v>0.8588992655277252</v>
+        <v>0.8588992953300476</v>
       </c>
     </row>
     <row r="45">
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0.8848140835762024</v>
+        <v>0.8848141133785248</v>
       </c>
       <c r="H45" t="n">
         <v>0.8846468329429626</v>
@@ -2312,7 +2312,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0.8624060153961182</v>
+        <v>0.8624061048030853</v>
       </c>
       <c r="H46" t="n">
         <v>0.8623032569885254</v>
@@ -2353,13 +2353,13 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>0.8822457790374756</v>
+        <v>0.8822457194328308</v>
       </c>
       <c r="H47" t="n">
         <v>0.8808684349060059</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8808216452598572</v>
+        <v>0.8808216750621796</v>
       </c>
     </row>
     <row r="48">
@@ -2397,7 +2397,7 @@
         <v>0.876221776008606</v>
       </c>
       <c r="H48" t="n">
-        <v>0.8661503791809082</v>
+        <v>0.8661504089832306</v>
       </c>
       <c r="I48" t="n">
         <v>0.8655959069728851</v>
@@ -2441,7 +2441,7 @@
         <v>0.8649434447288513</v>
       </c>
       <c r="I49" t="n">
-        <v>0.8645975291728973</v>
+        <v>0.8645976185798645</v>
       </c>
     </row>
     <row r="50">
@@ -2479,10 +2479,10 @@
         <v>0.8805749118328094</v>
       </c>
       <c r="H50" t="n">
-        <v>0.8783853054046631</v>
+        <v>0.8783853352069855</v>
       </c>
       <c r="I50" t="n">
-        <v>0.8773879110813141</v>
+        <v>0.8773880302906036</v>
       </c>
     </row>
     <row r="51">
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>0.8623651266098022</v>
+        <v>0.8623650968074799</v>
       </c>
       <c r="H51" t="n">
-        <v>0.8559726178646088</v>
+        <v>0.8559725880622864</v>
       </c>
       <c r="I51" t="n">
         <v>0.8509648144245148</v>
@@ -2558,7 +2558,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>0.860101193189621</v>
+        <v>0.8601012527942657</v>
       </c>
       <c r="H52" t="n">
         <v>0.8564842045307159</v>
@@ -2599,13 +2599,13 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>0.8770773708820343</v>
+        <v>0.8770774304866791</v>
       </c>
       <c r="H53" t="n">
-        <v>0.8713475465774536</v>
+        <v>0.8713475167751312</v>
       </c>
       <c r="I53" t="n">
-        <v>0.8681095838546753</v>
+        <v>0.8681094348430634</v>
       </c>
     </row>
     <row r="54">
@@ -2643,10 +2643,10 @@
         <v>0.86589115858078</v>
       </c>
       <c r="H54" t="n">
-        <v>0.8628572523593903</v>
+        <v>0.8628571629524231</v>
       </c>
       <c r="I54" t="n">
-        <v>0.8591557145118713</v>
+        <v>0.8591557741165161</v>
       </c>
     </row>
     <row r="55">
@@ -2681,13 +2681,13 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>0.8445272743701935</v>
+        <v>0.8445272147655487</v>
       </c>
       <c r="H55" t="n">
-        <v>0.8444043695926666</v>
+        <v>0.8444043397903442</v>
       </c>
       <c r="I55" t="n">
-        <v>0.8435723483562469</v>
+        <v>0.8435723185539246</v>
       </c>
     </row>
     <row r="56">
@@ -2725,7 +2725,7 @@
         <v>0.8806582093238831</v>
       </c>
       <c r="H56" t="n">
-        <v>0.8783490359783173</v>
+        <v>0.8783490061759949</v>
       </c>
       <c r="I56" t="n">
         <v>0.8719048798084259</v>
@@ -2763,13 +2763,13 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>0.8443308770656586</v>
+        <v>0.8443309366703033</v>
       </c>
       <c r="H57" t="n">
         <v>0.8426342308521271</v>
       </c>
       <c r="I57" t="n">
-        <v>0.8422442376613617</v>
+        <v>0.8422442972660065</v>
       </c>
     </row>
     <row r="58">
@@ -2804,13 +2804,13 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>0.8724232614040375</v>
+        <v>0.8724232316017151</v>
       </c>
       <c r="H58" t="n">
-        <v>0.8723962604999542</v>
+        <v>0.8723962008953094</v>
       </c>
       <c r="I58" t="n">
-        <v>0.8698245584964752</v>
+        <v>0.8698244690895081</v>
       </c>
     </row>
     <row r="59">
@@ -2848,7 +2848,7 @@
         <v>0.8817901909351349</v>
       </c>
       <c r="H59" t="n">
-        <v>0.8764764666557312</v>
+        <v>0.876476526260376</v>
       </c>
       <c r="I59" t="n">
         <v>0.8761448860168457</v>
@@ -2886,13 +2886,13 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>0.8743585646152496</v>
+        <v>0.8743585348129272</v>
       </c>
       <c r="H60" t="n">
         <v>0.8707767724990845</v>
       </c>
       <c r="I60" t="n">
-        <v>0.8681853413581848</v>
+        <v>0.8681853711605072</v>
       </c>
     </row>
     <row r="61">
@@ -2927,13 +2927,13 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>0.8797605931758881</v>
+        <v>0.8797605037689209</v>
       </c>
       <c r="H61" t="n">
-        <v>0.8760299980640411</v>
+        <v>0.8760300278663635</v>
       </c>
       <c r="I61" t="n">
-        <v>0.8728488683700562</v>
+        <v>0.8728488087654114</v>
       </c>
     </row>
     <row r="62">
@@ -2968,10 +2968,10 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>0.8302424550056458</v>
+        <v>0.8302423655986786</v>
       </c>
       <c r="H62" t="n">
-        <v>0.8261333703994751</v>
+        <v>0.8261334300041199</v>
       </c>
       <c r="I62" t="n">
         <v>0.8258854150772095</v>
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>0.8613007366657257</v>
+        <v>0.8613006472587585</v>
       </c>
       <c r="H63" t="n">
-        <v>0.8604455292224884</v>
+        <v>0.8604454696178436</v>
       </c>
       <c r="I63" t="n">
-        <v>0.8575854003429413</v>
+        <v>0.8575853407382965</v>
       </c>
     </row>
     <row r="64">
@@ -3046,17 +3046,17 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>村上 暁信</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>0.8834521770477295</v>
+        <v>0.8834520876407623</v>
       </c>
       <c r="H64" t="n">
         <v>0.8635226488113403</v>
       </c>
       <c r="I64" t="n">
-        <v>0.861113965511322</v>
+        <v>0.8623507022857666</v>
       </c>
     </row>
     <row r="65">
@@ -3173,13 +3173,13 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>0.8704354465007782</v>
+        <v>0.8704355359077454</v>
       </c>
       <c r="H67" t="n">
         <v>0.8700944781303406</v>
       </c>
       <c r="I67" t="n">
-        <v>0.868646115064621</v>
+        <v>0.8686460852622986</v>
       </c>
     </row>
     <row r="68">
@@ -3217,7 +3217,7 @@
         <v>0.8532235026359558</v>
       </c>
       <c r="H68" t="n">
-        <v>0.8512569665908813</v>
+        <v>0.851256936788559</v>
       </c>
       <c r="I68" t="n">
         <v>0.8432158827781677</v>
@@ -3258,10 +3258,10 @@
         <v>0.8667275011539459</v>
       </c>
       <c r="H69" t="n">
-        <v>0.8648612201213837</v>
+        <v>0.8648612499237061</v>
       </c>
       <c r="I69" t="n">
-        <v>0.8611284494400024</v>
+        <v>0.8611284792423248</v>
       </c>
     </row>
     <row r="70">
@@ -3296,13 +3296,13 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>0.8745883405208588</v>
+        <v>0.8745883107185364</v>
       </c>
       <c r="H70" t="n">
-        <v>0.8734764754772186</v>
+        <v>0.873476505279541</v>
       </c>
       <c r="I70" t="n">
-        <v>0.872194916009903</v>
+        <v>0.8721948862075806</v>
       </c>
     </row>
     <row r="71">
@@ -3337,13 +3337,13 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>0.8696563243865967</v>
+        <v>0.8696563839912415</v>
       </c>
       <c r="H71" t="n">
-        <v>0.8688327670097351</v>
+        <v>0.8688327968120575</v>
       </c>
       <c r="I71" t="n">
-        <v>0.8680279850959778</v>
+        <v>0.8680278658866882</v>
       </c>
     </row>
     <row r="72">
@@ -3381,10 +3381,10 @@
         <v>0.8609508872032166</v>
       </c>
       <c r="H72" t="n">
-        <v>0.859329879283905</v>
+        <v>0.8593298196792603</v>
       </c>
       <c r="I72" t="n">
-        <v>0.8565827906131744</v>
+        <v>0.8565827608108521</v>
       </c>
     </row>
     <row r="73">
@@ -3425,7 +3425,7 @@
         <v>0.8718547224998474</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8710871636867523</v>
+        <v>0.8710870742797852</v>
       </c>
     </row>
     <row r="74">
@@ -3460,13 +3460,13 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>0.8737937211990356</v>
+        <v>0.87379390001297</v>
       </c>
       <c r="H74" t="n">
         <v>0.8721553683280945</v>
       </c>
       <c r="I74" t="n">
-        <v>0.8709365725517273</v>
+        <v>0.8709365427494049</v>
       </c>
     </row>
     <row r="75">
@@ -3507,7 +3507,7 @@
         <v>0.8803759813308716</v>
       </c>
       <c r="I75" t="n">
-        <v>0.8761864006519318</v>
+        <v>0.8761864602565765</v>
       </c>
     </row>
     <row r="76">
@@ -3545,7 +3545,7 @@
         <v>0.8619394898414612</v>
       </c>
       <c r="H76" t="n">
-        <v>0.8587501347064972</v>
+        <v>0.8587501645088196</v>
       </c>
       <c r="I76" t="n">
         <v>0.8567723035812378</v>
@@ -3589,7 +3589,7 @@
         <v>0.872369110584259</v>
       </c>
       <c r="I77" t="n">
-        <v>0.8709968030452728</v>
+        <v>0.8709968626499176</v>
       </c>
     </row>
     <row r="78">
@@ -3627,10 +3627,10 @@
         <v>0.880396842956543</v>
       </c>
       <c r="H78" t="n">
-        <v>0.8765251636505127</v>
+        <v>0.8765251934528351</v>
       </c>
       <c r="I78" t="n">
-        <v>0.8699566721916199</v>
+        <v>0.8699566125869751</v>
       </c>
     </row>
     <row r="79">
@@ -3668,10 +3668,10 @@
         <v>0.8760638833045959</v>
       </c>
       <c r="H79" t="n">
-        <v>0.8648146986961365</v>
+        <v>0.8648147284984589</v>
       </c>
       <c r="I79" t="n">
-        <v>0.8647044897079468</v>
+        <v>0.8647045493125916</v>
       </c>
     </row>
     <row r="80">
@@ -3706,7 +3706,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>0.8561046719551086</v>
+        <v>0.8561047315597534</v>
       </c>
       <c r="H80" t="n">
         <v>0.854439914226532</v>
@@ -3747,13 +3747,13 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>0.8559111952781677</v>
+        <v>0.8559112250804901</v>
       </c>
       <c r="H81" t="n">
         <v>0.8549925088882446</v>
       </c>
       <c r="I81" t="n">
-        <v>0.8529223203659058</v>
+        <v>0.8529223799705505</v>
       </c>
     </row>
     <row r="82">
@@ -3788,13 +3788,13 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>0.8549389541149139</v>
+        <v>0.8549389243125916</v>
       </c>
       <c r="H82" t="n">
-        <v>0.8530166149139404</v>
+        <v>0.8530166447162628</v>
       </c>
       <c r="I82" t="n">
-        <v>0.8502903282642365</v>
+        <v>0.8502903580665588</v>
       </c>
     </row>
     <row r="83">
@@ -3829,13 +3829,13 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>0.8522348999977112</v>
+        <v>0.8522348403930664</v>
       </c>
       <c r="H83" t="n">
         <v>0.8515084087848663</v>
       </c>
       <c r="I83" t="n">
-        <v>0.8499585688114166</v>
+        <v>0.8499585092067719</v>
       </c>
     </row>
     <row r="84">
@@ -3870,10 +3870,10 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>0.850460022687912</v>
+        <v>0.8504600822925568</v>
       </c>
       <c r="H84" t="n">
-        <v>0.8449656069278717</v>
+        <v>0.8449656367301941</v>
       </c>
       <c r="I84" t="n">
         <v>0.8425630629062653</v>
@@ -3978,7 +3978,7 @@
         <v>0.8607469499111176</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8565534055233002</v>
+        <v>0.8565534651279449</v>
       </c>
     </row>
     <row r="3">
@@ -4098,7 +4098,7 @@
         <v>0.8748292922973633</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8652165830135345</v>
+        <v>0.8649005591869354</v>
       </c>
       <c r="I5" t="n">
         <v>0.8614690005779266</v>
@@ -4139,10 +4139,10 @@
         <v>0.8760461509227753</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8752143979072571</v>
+        <v>0.8752145171165466</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8724835515022278</v>
+        <v>0.8724835813045502</v>
       </c>
     </row>
     <row r="7">
@@ -4180,10 +4180,10 @@
         <v>0.8824881315231323</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8651013672351837</v>
+        <v>0.8651013374328613</v>
       </c>
       <c r="I7" t="n">
-        <v>0.854252815246582</v>
+        <v>0.8542527556419373</v>
       </c>
     </row>
     <row r="8">
@@ -4259,10 +4259,10 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.8722025752067566</v>
+        <v>0.8722026646137238</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8711293041706085</v>
+        <v>0.8711293637752533</v>
       </c>
       <c r="I9" t="n">
         <v>0.8628892600536346</v>
@@ -4306,7 +4306,7 @@
         <v>0.8521934747695923</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8515247106552124</v>
+        <v>0.8513410091400146</v>
       </c>
     </row>
     <row r="11">
@@ -4344,7 +4344,7 @@
         <v>0.8786357045173645</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8642593622207642</v>
+        <v>0.8642593026161194</v>
       </c>
       <c r="I11" t="n">
         <v>0.860405832529068</v>
@@ -4388,7 +4388,7 @@
         <v>0.8567197620868683</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8518259227275848</v>
+        <v>0.8518258035182953</v>
       </c>
     </row>
     <row r="13">
@@ -4423,10 +4423,10 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.8796601295471191</v>
+        <v>0.8796600997447968</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8722549676895142</v>
+        <v>0.8722550570964813</v>
       </c>
       <c r="I13" t="n">
         <v>0.8572300374507904</v>
@@ -4511,7 +4511,7 @@
         <v>0.8450488150119781</v>
       </c>
       <c r="I15" t="n">
-        <v>0.842248797416687</v>
+        <v>0.8422488570213318</v>
       </c>
     </row>
     <row r="16">
@@ -4578,22 +4578,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>牛島 光一</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>繁野 麻衣子</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>牛島 光一</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>0.8662374019622803</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8516285419464111</v>
+        <v>0.8516241908073425</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8516241908073425</v>
+        <v>0.8506606221199036</v>
       </c>
     </row>
     <row r="18">
@@ -4631,7 +4631,7 @@
         <v>0.8556589782238007</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8480800986289978</v>
+        <v>0.848080039024353</v>
       </c>
       <c r="I18" t="n">
         <v>0.8461095988750458</v>
@@ -4713,7 +4713,7 @@
         <v>0.8761183023452759</v>
       </c>
       <c r="H20" t="n">
-        <v>0.867241382598877</v>
+        <v>0.8672414720058441</v>
       </c>
       <c r="I20" t="n">
         <v>0.86562180519104</v>
@@ -4757,7 +4757,7 @@
         <v>0.8634408414363861</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8633631765842438</v>
+        <v>0.8633632063865662</v>
       </c>
     </row>
     <row r="22">
@@ -4792,7 +4792,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.8656386435031891</v>
+        <v>0.8656386733055115</v>
       </c>
       <c r="H22" t="n">
         <v>0.8634596168994904</v>

--- a/generated/committee_recommendations.xlsx
+++ b/generated/committee_recommendations.xlsx
@@ -508,13 +508,13 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.8637408316135406</v>
+        <v>0.8637407720088959</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8561815619468689</v>
+        <v>0.8561812937259674</v>
       </c>
       <c r="I2" t="n">
-        <v>0.856126606464386</v>
+        <v>0.8561264872550964</v>
       </c>
     </row>
     <row r="3">
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.8734617829322815</v>
+        <v>0.8734613358974457</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8607054650783539</v>
+        <v>0.8607051074504852</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8574922978878021</v>
+        <v>0.8574919700622559</v>
       </c>
     </row>
     <row r="4">
@@ -590,13 +590,13 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.8704101145267487</v>
+        <v>0.8704100549221039</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8587318062782288</v>
+        <v>0.858731746673584</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8560931086540222</v>
+        <v>0.8560929298400879</v>
       </c>
     </row>
     <row r="5">
@@ -631,13 +631,13 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.8748835027217865</v>
+        <v>0.8748833835124969</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8693714141845703</v>
+        <v>0.869371235370636</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8666557967662811</v>
+        <v>0.8666556477546692</v>
       </c>
     </row>
     <row r="6">
@@ -672,13 +672,13 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.8622949123382568</v>
+        <v>0.8622947633266449</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8608852028846741</v>
+        <v>0.860884815454483</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8604684770107269</v>
+        <v>0.8604680597782135</v>
       </c>
     </row>
     <row r="7">
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.8782475888729095</v>
+        <v>0.8782474100589752</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8727595210075378</v>
+        <v>0.8727590441703796</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8720541596412659</v>
+        <v>0.872053861618042</v>
       </c>
     </row>
     <row r="8">
@@ -754,13 +754,13 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.8723167479038239</v>
+        <v>0.872316300868988</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8555609583854675</v>
+        <v>0.8555606007575989</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8544269800186157</v>
+        <v>0.8544267117977142</v>
       </c>
     </row>
     <row r="9">
@@ -795,13 +795,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.8737589120864868</v>
+        <v>0.873758852481842</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8660922646522522</v>
+        <v>0.8660920858383179</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8622945547103882</v>
+        <v>0.8622942864894867</v>
       </c>
     </row>
     <row r="10">
@@ -836,13 +836,13 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.8714621663093567</v>
+        <v>0.871461808681488</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8703478574752808</v>
+        <v>0.8703476190567017</v>
       </c>
       <c r="I10" t="n">
-        <v>0.868831068277359</v>
+        <v>0.8688306212425232</v>
       </c>
     </row>
     <row r="11">
@@ -877,13 +877,13 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.8717465400695801</v>
+        <v>0.8717465102672577</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8668537437915802</v>
+        <v>0.8668534755706787</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8666412830352783</v>
+        <v>0.866641104221344</v>
       </c>
     </row>
     <row r="12">
@@ -918,13 +918,13 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.8546874523162842</v>
+        <v>0.854686975479126</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8504403233528137</v>
+        <v>0.850439727306366</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8490931689739227</v>
+        <v>0.8490930199623108</v>
       </c>
     </row>
     <row r="13">
@@ -959,13 +959,13 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.8592478334903717</v>
+        <v>0.8592474460601807</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8465917408466339</v>
+        <v>0.8462692201137543</v>
       </c>
       <c r="I13" t="n">
-        <v>0.834905594587326</v>
+        <v>0.8349055051803589</v>
       </c>
     </row>
     <row r="14">
@@ -1000,13 +1000,13 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.8779064118862152</v>
+        <v>0.8779061734676361</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8726606070995331</v>
+        <v>0.8726603388786316</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8708367943763733</v>
+        <v>0.8708363771438599</v>
       </c>
     </row>
     <row r="15">
@@ -1041,13 +1041,13 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.8802605867385864</v>
+        <v>0.8802604079246521</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8750886023044586</v>
+        <v>0.8750883340835571</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8705006837844849</v>
+        <v>0.8705005943775177</v>
       </c>
     </row>
     <row r="16">
@@ -1082,13 +1082,13 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.8758190870285034</v>
+        <v>0.8758190274238586</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8685945868492126</v>
+        <v>0.868594616651535</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8661127984523773</v>
+        <v>0.8665702342987061</v>
       </c>
     </row>
     <row r="17">
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0.8586438894271851</v>
+        <v>0.8586437702178955</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8549793362617493</v>
+        <v>0.8549792468547821</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8542280793190002</v>
+        <v>0.8542279303073883</v>
       </c>
     </row>
     <row r="18">
@@ -1164,13 +1164,13 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0.8756992518901825</v>
+        <v>0.8756991922855377</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8693471550941467</v>
+        <v>0.8693469762802124</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8683554232120514</v>
+        <v>0.8683551251888275</v>
       </c>
     </row>
     <row r="19">
@@ -1208,10 +1208,10 @@
         <v>0.8647384345531464</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8633520305156708</v>
+        <v>0.863351970911026</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8614737987518311</v>
+        <v>0.8614735007286072</v>
       </c>
     </row>
     <row r="20">
@@ -1246,13 +1246,13 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0.8822429776191711</v>
+        <v>0.8822426795959473</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8785503208637238</v>
+        <v>0.8785499632358551</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8663562834262848</v>
+        <v>0.8663559854030609</v>
       </c>
     </row>
     <row r="21">
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0.8621289730072021</v>
+        <v>0.8621286451816559</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8556961417198181</v>
+        <v>0.8556958138942719</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8524527847766876</v>
+        <v>0.8524523377418518</v>
       </c>
     </row>
     <row r="22">
@@ -1328,13 +1328,13 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.8789419531822205</v>
+        <v>0.8789417147636414</v>
       </c>
       <c r="H22" t="n">
-        <v>0.876095712184906</v>
+        <v>0.8760956525802612</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8730508089065552</v>
+        <v>0.8730506002902985</v>
       </c>
     </row>
     <row r="23">
@@ -1369,13 +1369,13 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0.8591337502002716</v>
+        <v>0.8591337203979492</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8517085015773773</v>
+        <v>0.8517081737518311</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8514227271080017</v>
+        <v>0.851422518491745</v>
       </c>
     </row>
     <row r="24">
@@ -1410,13 +1410,13 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0.8527725636959076</v>
+        <v>0.8527723550796509</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8512898087501526</v>
+        <v>0.8512894809246063</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8512193560600281</v>
+        <v>0.8512190282344818</v>
       </c>
     </row>
     <row r="25">
@@ -1451,13 +1451,13 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0.8706742823123932</v>
+        <v>0.870673805475235</v>
       </c>
       <c r="H25" t="n">
-        <v>0.863885760307312</v>
+        <v>0.8638855218887329</v>
       </c>
       <c r="I25" t="n">
-        <v>0.8618723750114441</v>
+        <v>0.8618720471858978</v>
       </c>
     </row>
     <row r="26">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0.8637948930263519</v>
+        <v>0.8637948632240295</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8582098484039307</v>
+        <v>0.8582093119621277</v>
       </c>
       <c r="I26" t="n">
-        <v>0.8576050400733948</v>
+        <v>0.8576047420501709</v>
       </c>
     </row>
     <row r="27">
@@ -1533,13 +1533,13 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0.8603377640247345</v>
+        <v>0.860337495803833</v>
       </c>
       <c r="H27" t="n">
-        <v>0.8578147888183594</v>
+        <v>0.8578143715858459</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8570154905319214</v>
+        <v>0.8570152521133423</v>
       </c>
     </row>
     <row r="28">
@@ -1574,13 +1574,13 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0.8752446472644806</v>
+        <v>0.8752445578575134</v>
       </c>
       <c r="H28" t="n">
-        <v>0.8709458708763123</v>
+        <v>0.8709458112716675</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8677360415458679</v>
+        <v>0.8681935667991638</v>
       </c>
     </row>
     <row r="29">
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0.8728598952293396</v>
+        <v>0.8728594183921814</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8667237758636475</v>
+        <v>0.8667238354682922</v>
       </c>
       <c r="I29" t="n">
-        <v>0.862547755241394</v>
+        <v>0.8625471591949463</v>
       </c>
     </row>
     <row r="30">
@@ -1656,13 +1656,13 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0.8834352493286133</v>
+        <v>0.8834348917007446</v>
       </c>
       <c r="H30" t="n">
-        <v>0.8568967878818512</v>
+        <v>0.8568965196609497</v>
       </c>
       <c r="I30" t="n">
-        <v>0.8559958040714264</v>
+        <v>0.8559956848621368</v>
       </c>
     </row>
     <row r="31">
@@ -1697,10 +1697,10 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0.8618856966495514</v>
+        <v>0.8618855476379395</v>
       </c>
       <c r="H31" t="n">
-        <v>0.8590705394744873</v>
+        <v>0.859070360660553</v>
       </c>
       <c r="I31" t="n">
         <v>0.8540639877319336</v>
@@ -1738,13 +1738,13 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0.8575133681297302</v>
+        <v>0.8575132787227631</v>
       </c>
       <c r="H32" t="n">
-        <v>0.8523843884468079</v>
+        <v>0.8523842990398407</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8516231775283813</v>
+        <v>0.8516227602958679</v>
       </c>
     </row>
     <row r="33">
@@ -1779,13 +1779,13 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0.8604612350463867</v>
+        <v>0.8604608178138733</v>
       </c>
       <c r="H33" t="n">
-        <v>0.8577743172645569</v>
+        <v>0.857774019241333</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8568276762962341</v>
+        <v>0.8568276166915894</v>
       </c>
     </row>
     <row r="34">
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0.8634571135044098</v>
+        <v>0.8634569942951202</v>
       </c>
       <c r="H34" t="n">
-        <v>0.8626152873039246</v>
+        <v>0.8626150786876678</v>
       </c>
       <c r="I34" t="n">
-        <v>0.8595913052558899</v>
+        <v>0.8595910668373108</v>
       </c>
     </row>
     <row r="35">
@@ -1861,13 +1861,13 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0.8803420662879944</v>
+        <v>0.8803417384624481</v>
       </c>
       <c r="H35" t="n">
-        <v>0.8801654279232025</v>
+        <v>0.8801652789115906</v>
       </c>
       <c r="I35" t="n">
-        <v>0.8745455145835876</v>
+        <v>0.874545156955719</v>
       </c>
     </row>
     <row r="36">
@@ -1902,13 +1902,13 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0.875926673412323</v>
+        <v>0.8759260773658752</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8738082945346832</v>
+        <v>0.8738081753253937</v>
       </c>
       <c r="I36" t="n">
-        <v>0.8677709400653839</v>
+        <v>0.86777064204216</v>
       </c>
     </row>
     <row r="37">
@@ -1943,13 +1943,13 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0.8812141120433807</v>
+        <v>0.8812137842178345</v>
       </c>
       <c r="H37" t="n">
-        <v>0.8779473900794983</v>
+        <v>0.877947211265564</v>
       </c>
       <c r="I37" t="n">
-        <v>0.8733149170875549</v>
+        <v>0.8733144998550415</v>
       </c>
     </row>
     <row r="38">
@@ -1984,13 +1984,13 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0.8687264025211334</v>
+        <v>0.8687264919281006</v>
       </c>
       <c r="H38" t="n">
-        <v>0.8683319687843323</v>
+        <v>0.8683316707611084</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8629851043224335</v>
+        <v>0.8629849255084991</v>
       </c>
     </row>
     <row r="39">
@@ -2025,13 +2025,13 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0.884117603302002</v>
+        <v>0.8841173052787781</v>
       </c>
       <c r="H39" t="n">
-        <v>0.8798272013664246</v>
+        <v>0.8798267543315887</v>
       </c>
       <c r="I39" t="n">
-        <v>0.879041850566864</v>
+        <v>0.8790417909622192</v>
       </c>
     </row>
     <row r="40">
@@ -2066,13 +2066,13 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0.8836490213871002</v>
+        <v>0.8836487531661987</v>
       </c>
       <c r="H40" t="n">
-        <v>0.8805910348892212</v>
+        <v>0.8805907964706421</v>
       </c>
       <c r="I40" t="n">
-        <v>0.8768988847732544</v>
+        <v>0.8768987655639648</v>
       </c>
     </row>
     <row r="41">
@@ -2107,13 +2107,13 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0.8722117245197296</v>
+        <v>0.8722112476825714</v>
       </c>
       <c r="H41" t="n">
-        <v>0.8708105683326721</v>
+        <v>0.8708103895187378</v>
       </c>
       <c r="I41" t="n">
-        <v>0.8650574684143066</v>
+        <v>0.8650570511817932</v>
       </c>
     </row>
     <row r="42">
@@ -2148,13 +2148,13 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0.8621289134025574</v>
+        <v>0.8621284961700439</v>
       </c>
       <c r="H42" t="n">
-        <v>0.8617661893367767</v>
+        <v>0.8617660105228424</v>
       </c>
       <c r="I42" t="n">
-        <v>0.8485495746135712</v>
+        <v>0.8485491871833801</v>
       </c>
     </row>
     <row r="43">
@@ -2189,10 +2189,10 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0.8732402920722961</v>
+        <v>0.8732399344444275</v>
       </c>
       <c r="H43" t="n">
-        <v>0.8674532175064087</v>
+        <v>0.8674529492855072</v>
       </c>
       <c r="I43" t="n">
         <v>0.8664050698280334</v>
@@ -2230,13 +2230,13 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0.861095666885376</v>
+        <v>0.8610953688621521</v>
       </c>
       <c r="H44" t="n">
-        <v>0.8599763512611389</v>
+        <v>0.8599761724472046</v>
       </c>
       <c r="I44" t="n">
-        <v>0.8588992953300476</v>
+        <v>0.8588990569114685</v>
       </c>
     </row>
     <row r="45">
@@ -2271,13 +2271,13 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0.8848141133785248</v>
+        <v>0.8848139941692352</v>
       </c>
       <c r="H45" t="n">
-        <v>0.8846468329429626</v>
+        <v>0.884646475315094</v>
       </c>
       <c r="I45" t="n">
-        <v>0.881380170583725</v>
+        <v>0.881379634141922</v>
       </c>
     </row>
     <row r="46">
@@ -2312,13 +2312,13 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0.8624061048030853</v>
+        <v>0.8624057769775391</v>
       </c>
       <c r="H46" t="n">
-        <v>0.8623032569885254</v>
+        <v>0.8623030185699463</v>
       </c>
       <c r="I46" t="n">
-        <v>0.8606871068477631</v>
+        <v>0.8606868982315063</v>
       </c>
     </row>
     <row r="47">
@@ -2353,13 +2353,13 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>0.8822457194328308</v>
+        <v>0.8822456002235413</v>
       </c>
       <c r="H47" t="n">
-        <v>0.8808684349060059</v>
+        <v>0.8808680772781372</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8808216750621796</v>
+        <v>0.8808214664459229</v>
       </c>
     </row>
     <row r="48">
@@ -2394,13 +2394,13 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>0.876221776008606</v>
+        <v>0.8762213587760925</v>
       </c>
       <c r="H48" t="n">
-        <v>0.8661504089832306</v>
+        <v>0.8661500513553619</v>
       </c>
       <c r="I48" t="n">
-        <v>0.8655959069728851</v>
+        <v>0.865595281124115</v>
       </c>
     </row>
     <row r="49">
@@ -2435,13 +2435,13 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>0.8662878572940826</v>
+        <v>0.8662874400615692</v>
       </c>
       <c r="H49" t="n">
-        <v>0.8649434447288513</v>
+        <v>0.8649430572986603</v>
       </c>
       <c r="I49" t="n">
-        <v>0.8645976185798645</v>
+        <v>0.8645971715450287</v>
       </c>
     </row>
     <row r="50">
@@ -2476,13 +2476,13 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>0.8805749118328094</v>
+        <v>0.8805746138095856</v>
       </c>
       <c r="H50" t="n">
-        <v>0.8783853352069855</v>
+        <v>0.8783849775791168</v>
       </c>
       <c r="I50" t="n">
-        <v>0.8773880302906036</v>
+        <v>0.8773877024650574</v>
       </c>
     </row>
     <row r="51">
@@ -2517,13 +2517,13 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>0.8623650968074799</v>
+        <v>0.8623651266098022</v>
       </c>
       <c r="H51" t="n">
-        <v>0.8559725880622864</v>
+        <v>0.8559722304344177</v>
       </c>
       <c r="I51" t="n">
-        <v>0.8509648144245148</v>
+        <v>0.8509646058082581</v>
       </c>
     </row>
     <row r="52">
@@ -2558,13 +2558,13 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>0.8601012527942657</v>
+        <v>0.8601007461547852</v>
       </c>
       <c r="H52" t="n">
-        <v>0.8564842045307159</v>
+        <v>0.8564839959144592</v>
       </c>
       <c r="I52" t="n">
-        <v>0.8554677963256836</v>
+        <v>0.8554676175117493</v>
       </c>
     </row>
     <row r="53">
@@ -2599,13 +2599,13 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>0.8770774304866791</v>
+        <v>0.8770770728588104</v>
       </c>
       <c r="H53" t="n">
-        <v>0.8713475167751312</v>
+        <v>0.8713474571704865</v>
       </c>
       <c r="I53" t="n">
-        <v>0.8681094348430634</v>
+        <v>0.8681096136569977</v>
       </c>
     </row>
     <row r="54">
@@ -2640,13 +2640,13 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>0.86589115858078</v>
+        <v>0.8658909201622009</v>
       </c>
       <c r="H54" t="n">
-        <v>0.8628571629524231</v>
+        <v>0.8628571033477783</v>
       </c>
       <c r="I54" t="n">
-        <v>0.8591557741165161</v>
+        <v>0.859155535697937</v>
       </c>
     </row>
     <row r="55">
@@ -2681,13 +2681,13 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>0.8445272147655487</v>
+        <v>0.8445272445678711</v>
       </c>
       <c r="H55" t="n">
-        <v>0.8444043397903442</v>
+        <v>0.8444041013717651</v>
       </c>
       <c r="I55" t="n">
-        <v>0.8435723185539246</v>
+        <v>0.8435719907283783</v>
       </c>
     </row>
     <row r="56">
@@ -2722,13 +2722,13 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>0.8806582093238831</v>
+        <v>0.8806580901145935</v>
       </c>
       <c r="H56" t="n">
-        <v>0.8783490061759949</v>
+        <v>0.8783487677574158</v>
       </c>
       <c r="I56" t="n">
-        <v>0.8719048798084259</v>
+        <v>0.8719048500061035</v>
       </c>
     </row>
     <row r="57">
@@ -2763,13 +2763,13 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>0.8443309366703033</v>
+        <v>0.8443306088447571</v>
       </c>
       <c r="H57" t="n">
-        <v>0.8426342308521271</v>
+        <v>0.8426340222358704</v>
       </c>
       <c r="I57" t="n">
-        <v>0.8422442972660065</v>
+        <v>0.842244029045105</v>
       </c>
     </row>
     <row r="58">
@@ -2804,13 +2804,13 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>0.8724232316017151</v>
+        <v>0.8724230825901031</v>
       </c>
       <c r="H58" t="n">
-        <v>0.8723962008953094</v>
+        <v>0.8723960220813751</v>
       </c>
       <c r="I58" t="n">
-        <v>0.8698244690895081</v>
+        <v>0.8698239922523499</v>
       </c>
     </row>
     <row r="59">
@@ -2845,13 +2845,13 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>0.8817901909351349</v>
+        <v>0.8817898035049438</v>
       </c>
       <c r="H59" t="n">
-        <v>0.876476526260376</v>
+        <v>0.8764763474464417</v>
       </c>
       <c r="I59" t="n">
-        <v>0.8761448860168457</v>
+        <v>0.8761445879936218</v>
       </c>
     </row>
     <row r="60">
@@ -2886,13 +2886,13 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>0.8743585348129272</v>
+        <v>0.8743581771850586</v>
       </c>
       <c r="H60" t="n">
-        <v>0.8707767724990845</v>
+        <v>0.8707766830921173</v>
       </c>
       <c r="I60" t="n">
-        <v>0.8681853711605072</v>
+        <v>0.8681854009628296</v>
       </c>
     </row>
     <row r="61">
@@ -2927,13 +2927,13 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>0.8797605037689209</v>
+        <v>0.8797598779201508</v>
       </c>
       <c r="H61" t="n">
-        <v>0.8760300278663635</v>
+        <v>0.8760296702384949</v>
       </c>
       <c r="I61" t="n">
-        <v>0.8728488087654114</v>
+        <v>0.8728485107421875</v>
       </c>
     </row>
     <row r="62">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>0.8302423655986786</v>
+        <v>0.8302420377731323</v>
       </c>
       <c r="H62" t="n">
-        <v>0.8261334300041199</v>
+        <v>0.8261329233646393</v>
       </c>
       <c r="I62" t="n">
-        <v>0.8258854150772095</v>
+        <v>0.8258852362632751</v>
       </c>
     </row>
     <row r="63">
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>0.8613006472587585</v>
+        <v>0.8613004684448242</v>
       </c>
       <c r="H63" t="n">
-        <v>0.8604454696178436</v>
+        <v>0.8604451417922974</v>
       </c>
       <c r="I63" t="n">
-        <v>0.8575853407382965</v>
+        <v>0.8575851023197174</v>
       </c>
     </row>
     <row r="64">
@@ -3046,17 +3046,17 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>村上 暁信</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>0.8834520876407623</v>
+        <v>0.8834516704082489</v>
       </c>
       <c r="H64" t="n">
-        <v>0.8635226488113403</v>
+        <v>0.8635225594043732</v>
       </c>
       <c r="I64" t="n">
-        <v>0.8623507022857666</v>
+        <v>0.861113429069519</v>
       </c>
     </row>
     <row r="65">
@@ -3091,13 +3091,13 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>0.8763948380947113</v>
+        <v>0.8763948678970337</v>
       </c>
       <c r="H65" t="n">
-        <v>0.8742636442184448</v>
+        <v>0.8742632567882538</v>
       </c>
       <c r="I65" t="n">
-        <v>0.8731106519699097</v>
+        <v>0.8731103539466858</v>
       </c>
     </row>
     <row r="66">
@@ -3132,13 +3132,13 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>0.8665135502815247</v>
+        <v>0.8665132522583008</v>
       </c>
       <c r="H66" t="n">
-        <v>0.8654606640338898</v>
+        <v>0.865460216999054</v>
       </c>
       <c r="I66" t="n">
-        <v>0.8637252748012543</v>
+        <v>0.8637251555919647</v>
       </c>
     </row>
     <row r="67">
@@ -3176,10 +3176,10 @@
         <v>0.8704355359077454</v>
       </c>
       <c r="H67" t="n">
-        <v>0.8700944781303406</v>
+        <v>0.8700940907001495</v>
       </c>
       <c r="I67" t="n">
-        <v>0.8686460852622986</v>
+        <v>0.8686460256576538</v>
       </c>
     </row>
     <row r="68">
@@ -3214,13 +3214,13 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>0.8532235026359558</v>
+        <v>0.8532232940196991</v>
       </c>
       <c r="H68" t="n">
-        <v>0.851256936788559</v>
+        <v>0.8512569069862366</v>
       </c>
       <c r="I68" t="n">
-        <v>0.8432158827781677</v>
+        <v>0.8432158231735229</v>
       </c>
     </row>
     <row r="69">
@@ -3255,13 +3255,13 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>0.8667275011539459</v>
+        <v>0.8667273223400116</v>
       </c>
       <c r="H69" t="n">
-        <v>0.8648612499237061</v>
+        <v>0.8648608326911926</v>
       </c>
       <c r="I69" t="n">
-        <v>0.8611284792423248</v>
+        <v>0.8611282706260681</v>
       </c>
     </row>
     <row r="70">
@@ -3296,13 +3296,13 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>0.8745883107185364</v>
+        <v>0.8745879828929901</v>
       </c>
       <c r="H70" t="n">
-        <v>0.873476505279541</v>
+        <v>0.8734760284423828</v>
       </c>
       <c r="I70" t="n">
-        <v>0.8721948862075806</v>
+        <v>0.8721945583820343</v>
       </c>
     </row>
     <row r="71">
@@ -3337,13 +3337,13 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>0.8696563839912415</v>
+        <v>0.8696559071540833</v>
       </c>
       <c r="H71" t="n">
-        <v>0.8688327968120575</v>
+        <v>0.8688324987888336</v>
       </c>
       <c r="I71" t="n">
-        <v>0.8680278658866882</v>
+        <v>0.8680274486541748</v>
       </c>
     </row>
     <row r="72">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>0.8609508872032166</v>
+        <v>0.8609506487846375</v>
       </c>
       <c r="H72" t="n">
-        <v>0.8593298196792603</v>
+        <v>0.8593294322490692</v>
       </c>
       <c r="I72" t="n">
-        <v>0.8565827608108521</v>
+        <v>0.8565827012062073</v>
       </c>
     </row>
     <row r="73">
@@ -3419,13 +3419,13 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>0.8722729086875916</v>
+        <v>0.8722727000713348</v>
       </c>
       <c r="H73" t="n">
-        <v>0.8718547224998474</v>
+        <v>0.8718544840812683</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8710870742797852</v>
+        <v>0.8710868656635284</v>
       </c>
     </row>
     <row r="74">
@@ -3460,13 +3460,13 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>0.87379390001297</v>
+        <v>0.8737935125827789</v>
       </c>
       <c r="H74" t="n">
-        <v>0.8721553683280945</v>
+        <v>0.8721547722816467</v>
       </c>
       <c r="I74" t="n">
-        <v>0.8709365427494049</v>
+        <v>0.8709360361099243</v>
       </c>
     </row>
     <row r="75">
@@ -3501,13 +3501,13 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>0.8804772198200226</v>
+        <v>0.8804770112037659</v>
       </c>
       <c r="H75" t="n">
-        <v>0.8803759813308716</v>
+        <v>0.880375862121582</v>
       </c>
       <c r="I75" t="n">
-        <v>0.8761864602565765</v>
+        <v>0.8761859536170959</v>
       </c>
     </row>
     <row r="76">
@@ -3542,13 +3542,13 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>0.8619394898414612</v>
+        <v>0.8619393706321716</v>
       </c>
       <c r="H76" t="n">
-        <v>0.8587501645088196</v>
+        <v>0.8587498664855957</v>
       </c>
       <c r="I76" t="n">
-        <v>0.8567723035812378</v>
+        <v>0.8567719459533691</v>
       </c>
     </row>
     <row r="77">
@@ -3583,13 +3583,13 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>0.8736216723918915</v>
+        <v>0.8736216425895691</v>
       </c>
       <c r="H77" t="n">
-        <v>0.872369110584259</v>
+        <v>0.8723689317703247</v>
       </c>
       <c r="I77" t="n">
-        <v>0.8709968626499176</v>
+        <v>0.8709964752197266</v>
       </c>
     </row>
     <row r="78">
@@ -3624,10 +3624,10 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>0.880396842956543</v>
+        <v>0.8803965449333191</v>
       </c>
       <c r="H78" t="n">
-        <v>0.8765251934528351</v>
+        <v>0.8765251040458679</v>
       </c>
       <c r="I78" t="n">
         <v>0.8699566125869751</v>
@@ -3665,13 +3665,13 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>0.8760638833045959</v>
+        <v>0.8760635256767273</v>
       </c>
       <c r="H79" t="n">
-        <v>0.8648147284984589</v>
+        <v>0.8648145496845245</v>
       </c>
       <c r="I79" t="n">
-        <v>0.8647045493125916</v>
+        <v>0.8647039234638214</v>
       </c>
     </row>
     <row r="80">
@@ -3706,13 +3706,13 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>0.8561047315597534</v>
+        <v>0.8561045527458191</v>
       </c>
       <c r="H80" t="n">
-        <v>0.854439914226532</v>
+        <v>0.8544396162033081</v>
       </c>
       <c r="I80" t="n">
-        <v>0.852348804473877</v>
+        <v>0.8523486256599426</v>
       </c>
     </row>
     <row r="81">
@@ -3747,13 +3747,13 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>0.8559112250804901</v>
+        <v>0.8559110462665558</v>
       </c>
       <c r="H81" t="n">
-        <v>0.8549925088882446</v>
+        <v>0.8549920916557312</v>
       </c>
       <c r="I81" t="n">
-        <v>0.8529223799705505</v>
+        <v>0.8529218137264252</v>
       </c>
     </row>
     <row r="82">
@@ -3788,13 +3788,13 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>0.8549389243125916</v>
+        <v>0.8549385368824005</v>
       </c>
       <c r="H82" t="n">
-        <v>0.8530166447162628</v>
+        <v>0.8530160486698151</v>
       </c>
       <c r="I82" t="n">
-        <v>0.8502903580665588</v>
+        <v>0.850290060043335</v>
       </c>
     </row>
     <row r="83">
@@ -3829,13 +3829,13 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>0.8522348403930664</v>
+        <v>0.8522346019744873</v>
       </c>
       <c r="H83" t="n">
-        <v>0.8515084087848663</v>
+        <v>0.8515082001686096</v>
       </c>
       <c r="I83" t="n">
-        <v>0.8499585092067719</v>
+        <v>0.8499580323696136</v>
       </c>
     </row>
     <row r="84">
@@ -3870,13 +3870,13 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>0.8504600822925568</v>
+        <v>0.8504597544670105</v>
       </c>
       <c r="H84" t="n">
-        <v>0.8449656367301941</v>
+        <v>0.8449654281139374</v>
       </c>
       <c r="I84" t="n">
-        <v>0.8425630629062653</v>
+        <v>0.8425625562667847</v>
       </c>
     </row>
   </sheetData>
@@ -3972,13 +3972,13 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.8631241023540497</v>
+        <v>0.863123744726181</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8607469499111176</v>
+        <v>0.8607465028762817</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8565534651279449</v>
+        <v>0.8565530180931091</v>
       </c>
     </row>
     <row r="3">
@@ -4013,13 +4013,13 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.8609103560447693</v>
+        <v>0.8609102368354797</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8535879850387573</v>
+        <v>0.8535879254341125</v>
       </c>
       <c r="I3" t="n">
-        <v>0.852259486913681</v>
+        <v>0.8522591888904572</v>
       </c>
     </row>
     <row r="4">
@@ -4054,13 +4054,13 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.8563421070575714</v>
+        <v>0.8563421368598938</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8478223383426666</v>
+        <v>0.8478220701217651</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8461344838142395</v>
+        <v>0.8461341559886932</v>
       </c>
     </row>
     <row r="5">
@@ -4095,13 +4095,13 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.8748292922973633</v>
+        <v>0.8748290538787842</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8649005591869354</v>
+        <v>0.8650575578212738</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8614690005779266</v>
+        <v>0.8614687025547028</v>
       </c>
     </row>
     <row r="6">
@@ -4136,13 +4136,13 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.8760461509227753</v>
+        <v>0.8760460615158081</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8752145171165466</v>
+        <v>0.8752140700817108</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8724835813045502</v>
+        <v>0.8724832534790039</v>
       </c>
     </row>
     <row r="7">
@@ -4177,13 +4177,13 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.8824881315231323</v>
+        <v>0.8824878931045532</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8651013374328613</v>
+        <v>0.8651009798049927</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8542527556419373</v>
+        <v>0.8542524576187134</v>
       </c>
     </row>
     <row r="8">
@@ -4218,13 +4218,13 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.8712441325187683</v>
+        <v>0.8712438941001892</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8706216514110565</v>
+        <v>0.870621383190155</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8673337697982788</v>
+        <v>0.8673335313796997</v>
       </c>
     </row>
     <row r="9">
@@ -4259,13 +4259,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.8722026646137238</v>
+        <v>0.8722023069858551</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8711293637752533</v>
+        <v>0.8711291551589966</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8628892600536346</v>
+        <v>0.8628890514373779</v>
       </c>
     </row>
     <row r="10">
@@ -4300,13 +4300,13 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.8638104796409607</v>
+        <v>0.8638100922107697</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8521934747695923</v>
+        <v>0.8521930575370789</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8513410091400146</v>
+        <v>0.8518615663051605</v>
       </c>
     </row>
     <row r="11">
@@ -4341,13 +4341,13 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.8786357045173645</v>
+        <v>0.8786354064941406</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8642593026161194</v>
+        <v>0.8642589747905731</v>
       </c>
       <c r="I11" t="n">
-        <v>0.860405832529068</v>
+        <v>0.8604055047035217</v>
       </c>
     </row>
     <row r="12">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.8868876993656158</v>
+        <v>0.8868874311447144</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8567197620868683</v>
+        <v>0.8567194938659668</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8518258035182953</v>
+        <v>0.8518254160881042</v>
       </c>
     </row>
     <row r="13">
@@ -4423,13 +4423,13 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.8796600997447968</v>
+        <v>0.8796598017215729</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8722550570964813</v>
+        <v>0.8722546398639679</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8572300374507904</v>
+        <v>0.8572297394275665</v>
       </c>
     </row>
     <row r="14">
@@ -4464,13 +4464,13 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.84958815574646</v>
+        <v>0.8495877385139465</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8485821783542633</v>
+        <v>0.8485817015171051</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8477443158626556</v>
+        <v>0.847743958234787</v>
       </c>
     </row>
     <row r="15">
@@ -4505,13 +4505,13 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.8557057082653046</v>
+        <v>0.8557053804397583</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8450488150119781</v>
+        <v>0.8450484871864319</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8422488570213318</v>
+        <v>0.8422485589981079</v>
       </c>
     </row>
     <row r="16">
@@ -4546,13 +4546,13 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.8684133589267731</v>
+        <v>0.8684130012989044</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8607102632522583</v>
+        <v>0.860710084438324</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8606576025485992</v>
+        <v>0.8606573045253754</v>
       </c>
     </row>
     <row r="17">
@@ -4578,22 +4578,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>繁野 麻衣子</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>牛島 光一</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>繁野 麻衣子</t>
-        </is>
-      </c>
       <c r="G17" t="n">
-        <v>0.8662374019622803</v>
+        <v>0.8662371933460236</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8516241908073425</v>
+        <v>0.8523014783859253</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8506606221199036</v>
+        <v>0.8516239523887634</v>
       </c>
     </row>
     <row r="18">
@@ -4628,13 +4628,13 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0.8556589782238007</v>
+        <v>0.8556585013866425</v>
       </c>
       <c r="H18" t="n">
-        <v>0.848080039024353</v>
+        <v>0.8480796813964844</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8461095988750458</v>
+        <v>0.8461092710494995</v>
       </c>
     </row>
     <row r="19">
@@ -4669,13 +4669,13 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0.8692283034324646</v>
+        <v>0.8692281544208527</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8580313920974731</v>
+        <v>0.858031153678894</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8552308678627014</v>
+        <v>0.8552306592464447</v>
       </c>
     </row>
     <row r="20">
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0.8761183023452759</v>
+        <v>0.8761181235313416</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8672414720058441</v>
+        <v>0.8672411441802979</v>
       </c>
       <c r="I20" t="n">
-        <v>0.86562180519104</v>
+        <v>0.8656215667724609</v>
       </c>
     </row>
     <row r="21">
@@ -4751,13 +4751,13 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0.8668003678321838</v>
+        <v>0.86680006980896</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8634408414363861</v>
+        <v>0.8634406328201294</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8633632063865662</v>
+        <v>0.8633630573749542</v>
       </c>
     </row>
     <row r="22">
@@ -4792,13 +4792,13 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.8656386733055115</v>
+        <v>0.8656384646892548</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8634596168994904</v>
+        <v>0.8634596467018127</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8629354536533356</v>
+        <v>0.8629352152347565</v>
       </c>
     </row>
   </sheetData>

--- a/generated/committee_recommendations.xlsx
+++ b/generated/committee_recommendations.xlsx
@@ -508,13 +508,13 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.8637407720088959</v>
+        <v>0.8637408018112183</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8561812937259674</v>
+        <v>0.8561815619468689</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8561264872550964</v>
+        <v>0.8561266660690308</v>
       </c>
     </row>
     <row r="3">
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.8734613358974457</v>
+        <v>0.8734617531299591</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8607051074504852</v>
+        <v>0.8607054650783539</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8574919700622559</v>
+        <v>0.8574923276901245</v>
       </c>
     </row>
     <row r="4">
@@ -590,13 +590,13 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.8704100549221039</v>
+        <v>0.8704100847244263</v>
       </c>
       <c r="H4" t="n">
-        <v>0.858731746673584</v>
+        <v>0.8587318658828735</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8560929298400879</v>
+        <v>0.8560931086540222</v>
       </c>
     </row>
     <row r="5">
@@ -631,13 +631,13 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.8748833835124969</v>
+        <v>0.8748835027217865</v>
       </c>
       <c r="H5" t="n">
-        <v>0.869371235370636</v>
+        <v>0.8693714141845703</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8666556477546692</v>
+        <v>0.8666558861732483</v>
       </c>
     </row>
     <row r="6">
@@ -672,13 +672,13 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.8622947633266449</v>
+        <v>0.8622949421405792</v>
       </c>
       <c r="H6" t="n">
-        <v>0.860884815454483</v>
+        <v>0.8608851730823517</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8604680597782135</v>
+        <v>0.8604684770107269</v>
       </c>
     </row>
     <row r="7">
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.8782474100589752</v>
+        <v>0.8782476484775543</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8727590441703796</v>
+        <v>0.8727595508098602</v>
       </c>
       <c r="I7" t="n">
-        <v>0.872053861618042</v>
+        <v>0.8720541596412659</v>
       </c>
     </row>
     <row r="8">
@@ -754,13 +754,13 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.872316300868988</v>
+        <v>0.8723167479038239</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8555606007575989</v>
+        <v>0.8555609583854675</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8544267117977142</v>
+        <v>0.8544269800186157</v>
       </c>
     </row>
     <row r="9">
@@ -795,13 +795,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.873758852481842</v>
+        <v>0.8737589120864868</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8660920858383179</v>
+        <v>0.8660922646522522</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8622942864894867</v>
+        <v>0.8622945547103882</v>
       </c>
     </row>
     <row r="10">
@@ -836,13 +836,13 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.871461808681488</v>
+        <v>0.8714622557163239</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8703476190567017</v>
+        <v>0.8703478574752808</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8688306212425232</v>
+        <v>0.8688311576843262</v>
       </c>
     </row>
     <row r="11">
@@ -877,13 +877,13 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.8717465102672577</v>
+        <v>0.8717465400695801</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8668534755706787</v>
+        <v>0.8668537437915802</v>
       </c>
       <c r="I11" t="n">
-        <v>0.866641104221344</v>
+        <v>0.8666412830352783</v>
       </c>
     </row>
     <row r="12">
@@ -918,13 +918,13 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.854686975479126</v>
+        <v>0.8546874523162842</v>
       </c>
       <c r="H12" t="n">
-        <v>0.850439727306366</v>
+        <v>0.8504401743412018</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8490930199623108</v>
+        <v>0.8490931987762451</v>
       </c>
     </row>
     <row r="13">
@@ -959,13 +959,13 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.8592474460601807</v>
+        <v>0.8592478334903717</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8462692201137543</v>
+        <v>0.8458518385887146</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8349055051803589</v>
+        <v>0.8349056243896484</v>
       </c>
     </row>
     <row r="14">
@@ -1000,13 +1000,13 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.8779061734676361</v>
+        <v>0.8779064118862152</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8726603388786316</v>
+        <v>0.8726606070995331</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8708363771438599</v>
+        <v>0.8708367943763733</v>
       </c>
     </row>
     <row r="15">
@@ -1041,13 +1041,13 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.8802604079246521</v>
+        <v>0.8802605867385864</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8750883340835571</v>
+        <v>0.8750885725021362</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8705005943775177</v>
+        <v>0.8705006837844849</v>
       </c>
     </row>
     <row r="16">
@@ -1082,13 +1082,13 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.8758190274238586</v>
+        <v>0.8758190870285034</v>
       </c>
       <c r="H16" t="n">
-        <v>0.868594616651535</v>
+        <v>0.8685945868492126</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8665702342987061</v>
+        <v>0.8666940629482269</v>
       </c>
     </row>
     <row r="17">
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0.8586437702178955</v>
+        <v>0.8586440086364746</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8549792468547821</v>
+        <v>0.8549793362617493</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8542279303073883</v>
+        <v>0.8542280793190002</v>
       </c>
     </row>
     <row r="18">
@@ -1164,13 +1164,13 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0.8756991922855377</v>
+        <v>0.8756992518901825</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8693469762802124</v>
+        <v>0.8693471550941467</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8683551251888275</v>
+        <v>0.8683554232120514</v>
       </c>
     </row>
     <row r="19">
@@ -1208,10 +1208,10 @@
         <v>0.8647384345531464</v>
       </c>
       <c r="H19" t="n">
-        <v>0.863351970911026</v>
+        <v>0.8633520305156708</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8614735007286072</v>
+        <v>0.8614738583564758</v>
       </c>
     </row>
     <row r="20">
@@ -1246,13 +1246,13 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0.8822426795959473</v>
+        <v>0.8822429776191711</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8785499632358551</v>
+        <v>0.8785501420497894</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8663559854030609</v>
+        <v>0.8663562834262848</v>
       </c>
     </row>
     <row r="21">
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0.8621286451816559</v>
+        <v>0.8621289730072021</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8556958138942719</v>
+        <v>0.8556961417198181</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8524523377418518</v>
+        <v>0.8524527847766876</v>
       </c>
     </row>
     <row r="22">
@@ -1328,13 +1328,13 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.8789417147636414</v>
+        <v>0.8789419531822205</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8760956525802612</v>
+        <v>0.8760955929756165</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8730506002902985</v>
+        <v>0.8730508089065552</v>
       </c>
     </row>
     <row r="23">
@@ -1369,13 +1369,13 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0.8591337203979492</v>
+        <v>0.8591336905956268</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8517081737518311</v>
+        <v>0.8517085015773773</v>
       </c>
       <c r="I23" t="n">
-        <v>0.851422518491745</v>
+        <v>0.8514227271080017</v>
       </c>
     </row>
     <row r="24">
@@ -1410,13 +1410,13 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0.8527723550796509</v>
+        <v>0.8527725040912628</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8512894809246063</v>
+        <v>0.8512898087501526</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8512190282344818</v>
+        <v>0.8512193560600281</v>
       </c>
     </row>
     <row r="25">
@@ -1451,13 +1451,13 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0.870673805475235</v>
+        <v>0.8706742227077484</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8638855218887329</v>
+        <v>0.8638857305049896</v>
       </c>
       <c r="I25" t="n">
-        <v>0.8618720471858978</v>
+        <v>0.8618723750114441</v>
       </c>
     </row>
     <row r="26">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0.8637948632240295</v>
+        <v>0.8637948930263519</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8582093119621277</v>
+        <v>0.8582098484039307</v>
       </c>
       <c r="I26" t="n">
-        <v>0.8576047420501709</v>
+        <v>0.8576050400733948</v>
       </c>
     </row>
     <row r="27">
@@ -1533,13 +1533,13 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0.860337495803833</v>
+        <v>0.8603377938270569</v>
       </c>
       <c r="H27" t="n">
-        <v>0.8578143715858459</v>
+        <v>0.8578148186206818</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8570152521133423</v>
+        <v>0.8570154905319214</v>
       </c>
     </row>
     <row r="28">
@@ -1574,13 +1574,13 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0.8752445578575134</v>
+        <v>0.8752446472644806</v>
       </c>
       <c r="H28" t="n">
-        <v>0.8709458112716675</v>
+        <v>0.8709458708763123</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8681935667991638</v>
+        <v>0.8683173060417175</v>
       </c>
     </row>
     <row r="29">
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0.8728594183921814</v>
+        <v>0.8728598952293396</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8667238354682922</v>
+        <v>0.8667237460613251</v>
       </c>
       <c r="I29" t="n">
-        <v>0.8625471591949463</v>
+        <v>0.862547755241394</v>
       </c>
     </row>
     <row r="30">
@@ -1656,13 +1656,13 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0.8834348917007446</v>
+        <v>0.8834352493286133</v>
       </c>
       <c r="H30" t="n">
-        <v>0.8568965196609497</v>
+        <v>0.8568967878818512</v>
       </c>
       <c r="I30" t="n">
-        <v>0.8559956848621368</v>
+        <v>0.855995774269104</v>
       </c>
     </row>
     <row r="31">
@@ -1697,10 +1697,10 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0.8618855476379395</v>
+        <v>0.8618856966495514</v>
       </c>
       <c r="H31" t="n">
-        <v>0.859070360660553</v>
+        <v>0.8590705394744873</v>
       </c>
       <c r="I31" t="n">
         <v>0.8540639877319336</v>
@@ -1738,13 +1738,13 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0.8575132787227631</v>
+        <v>0.8575133681297302</v>
       </c>
       <c r="H32" t="n">
-        <v>0.8523842990398407</v>
+        <v>0.8523845374584198</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8516227602958679</v>
+        <v>0.8516231775283813</v>
       </c>
     </row>
     <row r="33">
@@ -1779,13 +1779,13 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0.8604608178138733</v>
+        <v>0.8604612350463867</v>
       </c>
       <c r="H33" t="n">
-        <v>0.857774019241333</v>
+        <v>0.8577742874622345</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8568276166915894</v>
+        <v>0.8568277060985565</v>
       </c>
     </row>
     <row r="34">
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0.8634569942951202</v>
+        <v>0.8634571731090546</v>
       </c>
       <c r="H34" t="n">
-        <v>0.8626150786876678</v>
+        <v>0.8626152873039246</v>
       </c>
       <c r="I34" t="n">
-        <v>0.8595910668373108</v>
+        <v>0.8595913052558899</v>
       </c>
     </row>
     <row r="35">
@@ -1861,13 +1861,13 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0.8803417384624481</v>
+        <v>0.8803420662879944</v>
       </c>
       <c r="H35" t="n">
-        <v>0.8801652789115906</v>
+        <v>0.8801654279232025</v>
       </c>
       <c r="I35" t="n">
-        <v>0.874545156955719</v>
+        <v>0.8745454549789429</v>
       </c>
     </row>
     <row r="36">
@@ -1902,13 +1902,13 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0.8759260773658752</v>
+        <v>0.8759266436100006</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8738081753253937</v>
+        <v>0.8738082349300385</v>
       </c>
       <c r="I36" t="n">
-        <v>0.86777064204216</v>
+        <v>0.8677709102630615</v>
       </c>
     </row>
     <row r="37">
@@ -1943,13 +1943,13 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0.8812137842178345</v>
+        <v>0.8812141418457031</v>
       </c>
       <c r="H37" t="n">
-        <v>0.877947211265564</v>
+        <v>0.8779473304748535</v>
       </c>
       <c r="I37" t="n">
-        <v>0.8733144998550415</v>
+        <v>0.8733148872852325</v>
       </c>
     </row>
     <row r="38">
@@ -1984,13 +1984,13 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0.8687264919281006</v>
+        <v>0.8687264025211334</v>
       </c>
       <c r="H38" t="n">
-        <v>0.8683316707611084</v>
+        <v>0.8683319687843323</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8629849255084991</v>
+        <v>0.8629850745201111</v>
       </c>
     </row>
     <row r="39">
@@ -2025,13 +2025,13 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0.8841173052787781</v>
+        <v>0.8841175734996796</v>
       </c>
       <c r="H39" t="n">
-        <v>0.8798267543315887</v>
+        <v>0.8798271417617798</v>
       </c>
       <c r="I39" t="n">
-        <v>0.8790417909622192</v>
+        <v>0.879041850566864</v>
       </c>
     </row>
     <row r="40">
@@ -2066,13 +2066,13 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0.8836487531661987</v>
+        <v>0.883649080991745</v>
       </c>
       <c r="H40" t="n">
-        <v>0.8805907964706421</v>
+        <v>0.8805911242961884</v>
       </c>
       <c r="I40" t="n">
-        <v>0.8768987655639648</v>
+        <v>0.8768988847732544</v>
       </c>
     </row>
     <row r="41">
@@ -2107,13 +2107,13 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0.8722112476825714</v>
+        <v>0.8722117841243744</v>
       </c>
       <c r="H41" t="n">
-        <v>0.8708103895187378</v>
+        <v>0.8708105385303497</v>
       </c>
       <c r="I41" t="n">
-        <v>0.8650570511817932</v>
+        <v>0.8650574684143066</v>
       </c>
     </row>
     <row r="42">
@@ -2148,13 +2148,13 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0.8621284961700439</v>
+        <v>0.8621289134025574</v>
       </c>
       <c r="H42" t="n">
-        <v>0.8617660105228424</v>
+        <v>0.8617661893367767</v>
       </c>
       <c r="I42" t="n">
-        <v>0.8485491871833801</v>
+        <v>0.8485496342182159</v>
       </c>
     </row>
     <row r="43">
@@ -2189,13 +2189,13 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0.8732399344444275</v>
+        <v>0.8732402920722961</v>
       </c>
       <c r="H43" t="n">
-        <v>0.8674529492855072</v>
+        <v>0.8674532473087311</v>
       </c>
       <c r="I43" t="n">
-        <v>0.8664050698280334</v>
+        <v>0.8664050996303558</v>
       </c>
     </row>
     <row r="44">
@@ -2230,13 +2230,13 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0.8610953688621521</v>
+        <v>0.8610956370830536</v>
       </c>
       <c r="H44" t="n">
-        <v>0.8599761724472046</v>
+        <v>0.8599763512611389</v>
       </c>
       <c r="I44" t="n">
-        <v>0.8588990569114685</v>
+        <v>0.85889932513237</v>
       </c>
     </row>
     <row r="45">
@@ -2271,13 +2271,13 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0.8848139941692352</v>
+        <v>0.88481405377388</v>
       </c>
       <c r="H45" t="n">
-        <v>0.884646475315094</v>
+        <v>0.8846468329429626</v>
       </c>
       <c r="I45" t="n">
-        <v>0.881379634141922</v>
+        <v>0.881380170583725</v>
       </c>
     </row>
     <row r="46">
@@ -2312,13 +2312,13 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0.8624057769775391</v>
+        <v>0.8624061048030853</v>
       </c>
       <c r="H46" t="n">
-        <v>0.8623030185699463</v>
+        <v>0.8623032569885254</v>
       </c>
       <c r="I46" t="n">
-        <v>0.8606868982315063</v>
+        <v>0.8606871068477631</v>
       </c>
     </row>
     <row r="47">
@@ -2353,13 +2353,13 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>0.8822456002235413</v>
+        <v>0.8822457492351532</v>
       </c>
       <c r="H47" t="n">
-        <v>0.8808680772781372</v>
+        <v>0.8808684051036835</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8808214664459229</v>
+        <v>0.8808216154575348</v>
       </c>
     </row>
     <row r="48">
@@ -2394,13 +2394,13 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>0.8762213587760925</v>
+        <v>0.876221776008606</v>
       </c>
       <c r="H48" t="n">
-        <v>0.8661500513553619</v>
+        <v>0.8661503791809082</v>
       </c>
       <c r="I48" t="n">
-        <v>0.865595281124115</v>
+        <v>0.8655958473682404</v>
       </c>
     </row>
     <row r="49">
@@ -2435,13 +2435,13 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>0.8662874400615692</v>
+        <v>0.8662878572940826</v>
       </c>
       <c r="H49" t="n">
-        <v>0.8649430572986603</v>
+        <v>0.8649434447288513</v>
       </c>
       <c r="I49" t="n">
-        <v>0.8645971715450287</v>
+        <v>0.864597499370575</v>
       </c>
     </row>
     <row r="50">
@@ -2476,13 +2476,13 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>0.8805746138095856</v>
+        <v>0.8805749118328094</v>
       </c>
       <c r="H50" t="n">
-        <v>0.8783849775791168</v>
+        <v>0.8783854246139526</v>
       </c>
       <c r="I50" t="n">
-        <v>0.8773877024650574</v>
+        <v>0.8773878812789917</v>
       </c>
     </row>
     <row r="51">
@@ -2517,13 +2517,13 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>0.8623651266098022</v>
+        <v>0.8623651564121246</v>
       </c>
       <c r="H51" t="n">
-        <v>0.8559722304344177</v>
+        <v>0.855972558259964</v>
       </c>
       <c r="I51" t="n">
-        <v>0.8509646058082581</v>
+        <v>0.8509648144245148</v>
       </c>
     </row>
     <row r="52">
@@ -2558,13 +2558,13 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>0.8601007461547852</v>
+        <v>0.8601011633872986</v>
       </c>
       <c r="H52" t="n">
-        <v>0.8564839959144592</v>
+        <v>0.8564841449260712</v>
       </c>
       <c r="I52" t="n">
-        <v>0.8554676175117493</v>
+        <v>0.8554677963256836</v>
       </c>
     </row>
     <row r="53">
@@ -2599,10 +2599,10 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>0.8770770728588104</v>
+        <v>0.8770773708820343</v>
       </c>
       <c r="H53" t="n">
-        <v>0.8713474571704865</v>
+        <v>0.8713475167751312</v>
       </c>
       <c r="I53" t="n">
         <v>0.8681096136569977</v>
@@ -2640,13 +2640,13 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>0.8658909201622009</v>
+        <v>0.8658912181854248</v>
       </c>
       <c r="H54" t="n">
-        <v>0.8628571033477783</v>
+        <v>0.8628571927547455</v>
       </c>
       <c r="I54" t="n">
-        <v>0.859155535697937</v>
+        <v>0.8591557145118713</v>
       </c>
     </row>
     <row r="55">
@@ -2681,13 +2681,13 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>0.8445272445678711</v>
+        <v>0.8445272147655487</v>
       </c>
       <c r="H55" t="n">
-        <v>0.8444041013717651</v>
+        <v>0.8444044291973114</v>
       </c>
       <c r="I55" t="n">
-        <v>0.8435719907283783</v>
+        <v>0.8435723185539246</v>
       </c>
     </row>
     <row r="56">
@@ -2722,13 +2722,13 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>0.8806580901145935</v>
+        <v>0.8806582093238831</v>
       </c>
       <c r="H56" t="n">
-        <v>0.8783487677574158</v>
+        <v>0.8783489763736725</v>
       </c>
       <c r="I56" t="n">
-        <v>0.8719048500061035</v>
+        <v>0.8719048202037811</v>
       </c>
     </row>
     <row r="57">
@@ -2763,13 +2763,13 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>0.8443306088447571</v>
+        <v>0.844330906867981</v>
       </c>
       <c r="H57" t="n">
-        <v>0.8426340222358704</v>
+        <v>0.8426342308521271</v>
       </c>
       <c r="I57" t="n">
-        <v>0.842244029045105</v>
+        <v>0.8422442376613617</v>
       </c>
     </row>
     <row r="58">
@@ -2804,13 +2804,13 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>0.8724230825901031</v>
+        <v>0.8724232614040375</v>
       </c>
       <c r="H58" t="n">
-        <v>0.8723960220813751</v>
+        <v>0.8723962903022766</v>
       </c>
       <c r="I58" t="n">
-        <v>0.8698239922523499</v>
+        <v>0.86982461810112</v>
       </c>
     </row>
     <row r="59">
@@ -2845,13 +2845,13 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>0.8817898035049438</v>
+        <v>0.8817901909351349</v>
       </c>
       <c r="H59" t="n">
-        <v>0.8764763474464417</v>
+        <v>0.8764764666557312</v>
       </c>
       <c r="I59" t="n">
-        <v>0.8761445879936218</v>
+        <v>0.8761448860168457</v>
       </c>
     </row>
     <row r="60">
@@ -2886,10 +2886,10 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>0.8743581771850586</v>
+        <v>0.8743585348129272</v>
       </c>
       <c r="H60" t="n">
-        <v>0.8707766830921173</v>
+        <v>0.8707767426967621</v>
       </c>
       <c r="I60" t="n">
         <v>0.8681854009628296</v>
@@ -2927,13 +2927,13 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>0.8797598779201508</v>
+        <v>0.8797606825828552</v>
       </c>
       <c r="H61" t="n">
-        <v>0.8760296702384949</v>
+        <v>0.8760299682617188</v>
       </c>
       <c r="I61" t="n">
-        <v>0.8728485107421875</v>
+        <v>0.8728488087654114</v>
       </c>
     </row>
     <row r="62">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>0.8302420377731323</v>
+        <v>0.8302424252033234</v>
       </c>
       <c r="H62" t="n">
-        <v>0.8261329233646393</v>
+        <v>0.8261333405971527</v>
       </c>
       <c r="I62" t="n">
-        <v>0.8258852362632751</v>
+        <v>0.8258854150772095</v>
       </c>
     </row>
     <row r="63">
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>0.8613004684448242</v>
+        <v>0.8613007962703705</v>
       </c>
       <c r="H63" t="n">
-        <v>0.8604451417922974</v>
+        <v>0.8604454696178436</v>
       </c>
       <c r="I63" t="n">
-        <v>0.8575851023197174</v>
+        <v>0.8575853407382965</v>
       </c>
     </row>
     <row r="64">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>0.8834516704082489</v>
+        <v>0.8834521174430847</v>
       </c>
       <c r="H64" t="n">
-        <v>0.8635225594043732</v>
+        <v>0.8635226488113403</v>
       </c>
       <c r="I64" t="n">
-        <v>0.861113429069519</v>
+        <v>0.8611138761043549</v>
       </c>
     </row>
     <row r="65">
@@ -3091,13 +3091,13 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>0.8763948678970337</v>
+        <v>0.8763948082923889</v>
       </c>
       <c r="H65" t="n">
-        <v>0.8742632567882538</v>
+        <v>0.8742636442184448</v>
       </c>
       <c r="I65" t="n">
-        <v>0.8731103539466858</v>
+        <v>0.8731106519699097</v>
       </c>
     </row>
     <row r="66">
@@ -3132,13 +3132,13 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>0.8665132522583008</v>
+        <v>0.8665136098861694</v>
       </c>
       <c r="H66" t="n">
-        <v>0.865460216999054</v>
+        <v>0.8654606640338898</v>
       </c>
       <c r="I66" t="n">
-        <v>0.8637251555919647</v>
+        <v>0.8637252449989319</v>
       </c>
     </row>
     <row r="67">
@@ -3173,13 +3173,13 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>0.8704355359077454</v>
+        <v>0.8704354763031006</v>
       </c>
       <c r="H67" t="n">
-        <v>0.8700940907001495</v>
+        <v>0.8700944781303406</v>
       </c>
       <c r="I67" t="n">
-        <v>0.8686460256576538</v>
+        <v>0.8686460852622986</v>
       </c>
     </row>
     <row r="68">
@@ -3214,13 +3214,13 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>0.8532232940196991</v>
+        <v>0.8532235026359558</v>
       </c>
       <c r="H68" t="n">
-        <v>0.8512569069862366</v>
+        <v>0.8512569665908813</v>
       </c>
       <c r="I68" t="n">
-        <v>0.8432158231735229</v>
+        <v>0.8432158827781677</v>
       </c>
     </row>
     <row r="69">
@@ -3255,13 +3255,13 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>0.8667273223400116</v>
+        <v>0.8667275011539459</v>
       </c>
       <c r="H69" t="n">
-        <v>0.8648608326911926</v>
+        <v>0.8648611903190613</v>
       </c>
       <c r="I69" t="n">
-        <v>0.8611282706260681</v>
+        <v>0.8611284792423248</v>
       </c>
     </row>
     <row r="70">
@@ -3296,13 +3296,13 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>0.8745879828929901</v>
+        <v>0.8745884299278259</v>
       </c>
       <c r="H70" t="n">
-        <v>0.8734760284423828</v>
+        <v>0.8734764456748962</v>
       </c>
       <c r="I70" t="n">
-        <v>0.8721945583820343</v>
+        <v>0.8721948862075806</v>
       </c>
     </row>
     <row r="71">
@@ -3337,13 +3337,13 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>0.8696559071540833</v>
+        <v>0.8696563243865967</v>
       </c>
       <c r="H71" t="n">
-        <v>0.8688324987888336</v>
+        <v>0.8688327670097351</v>
       </c>
       <c r="I71" t="n">
-        <v>0.8680274486541748</v>
+        <v>0.8680279850959778</v>
       </c>
     </row>
     <row r="72">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>0.8609506487846375</v>
+        <v>0.8609508275985718</v>
       </c>
       <c r="H72" t="n">
-        <v>0.8593294322490692</v>
+        <v>0.8593298196792603</v>
       </c>
       <c r="I72" t="n">
-        <v>0.8565827012062073</v>
+        <v>0.8565828204154968</v>
       </c>
     </row>
     <row r="73">
@@ -3419,13 +3419,13 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>0.8722727000713348</v>
+        <v>0.8722729384899139</v>
       </c>
       <c r="H73" t="n">
-        <v>0.8718544840812683</v>
+        <v>0.8718547224998474</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8710868656635284</v>
+        <v>0.8710871338844299</v>
       </c>
     </row>
     <row r="74">
@@ -3460,13 +3460,13 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>0.8737935125827789</v>
+        <v>0.8737937211990356</v>
       </c>
       <c r="H74" t="n">
-        <v>0.8721547722816467</v>
+        <v>0.8721552789211273</v>
       </c>
       <c r="I74" t="n">
-        <v>0.8709360361099243</v>
+        <v>0.8709364831447601</v>
       </c>
     </row>
     <row r="75">
@@ -3501,13 +3501,13 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>0.8804770112037659</v>
+        <v>0.8804771602153778</v>
       </c>
       <c r="H75" t="n">
-        <v>0.880375862121582</v>
+        <v>0.8803759813308716</v>
       </c>
       <c r="I75" t="n">
-        <v>0.8761859536170959</v>
+        <v>0.8761863708496094</v>
       </c>
     </row>
     <row r="76">
@@ -3542,13 +3542,13 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>0.8619393706321716</v>
+        <v>0.8619394898414612</v>
       </c>
       <c r="H76" t="n">
-        <v>0.8587498664855957</v>
+        <v>0.8587501049041748</v>
       </c>
       <c r="I76" t="n">
-        <v>0.8567719459533691</v>
+        <v>0.8567723035812378</v>
       </c>
     </row>
     <row r="77">
@@ -3583,13 +3583,13 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>0.8736216425895691</v>
+        <v>0.8736216723918915</v>
       </c>
       <c r="H77" t="n">
-        <v>0.8723689317703247</v>
+        <v>0.872369110584259</v>
       </c>
       <c r="I77" t="n">
-        <v>0.8709964752197266</v>
+        <v>0.8709968030452728</v>
       </c>
     </row>
     <row r="78">
@@ -3624,13 +3624,13 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>0.8803965449333191</v>
+        <v>0.8803968131542206</v>
       </c>
       <c r="H78" t="n">
-        <v>0.8765251040458679</v>
+        <v>0.8765251338481903</v>
       </c>
       <c r="I78" t="n">
-        <v>0.8699566125869751</v>
+        <v>0.8699567019939423</v>
       </c>
     </row>
     <row r="79">
@@ -3665,13 +3665,13 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>0.8760635256767273</v>
+        <v>0.8760639429092407</v>
       </c>
       <c r="H79" t="n">
-        <v>0.8648145496845245</v>
+        <v>0.8648146092891693</v>
       </c>
       <c r="I79" t="n">
-        <v>0.8647039234638214</v>
+        <v>0.8647044599056244</v>
       </c>
     </row>
     <row r="80">
@@ -3706,13 +3706,13 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>0.8561045527458191</v>
+        <v>0.856104701757431</v>
       </c>
       <c r="H80" t="n">
-        <v>0.8544396162033081</v>
+        <v>0.854439914226532</v>
       </c>
       <c r="I80" t="n">
-        <v>0.8523486256599426</v>
+        <v>0.8523488640785217</v>
       </c>
     </row>
     <row r="81">
@@ -3747,13 +3747,13 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>0.8559110462665558</v>
+        <v>0.8559111952781677</v>
       </c>
       <c r="H81" t="n">
-        <v>0.8549920916557312</v>
+        <v>0.8549925088882446</v>
       </c>
       <c r="I81" t="n">
-        <v>0.8529218137264252</v>
+        <v>0.8529223501682281</v>
       </c>
     </row>
     <row r="82">
@@ -3788,13 +3788,13 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>0.8549385368824005</v>
+        <v>0.8549389541149139</v>
       </c>
       <c r="H82" t="n">
-        <v>0.8530160486698151</v>
+        <v>0.853016585111618</v>
       </c>
       <c r="I82" t="n">
-        <v>0.850290060043335</v>
+        <v>0.8502903878688812</v>
       </c>
     </row>
     <row r="83">
@@ -3829,13 +3829,13 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>0.8522346019744873</v>
+        <v>0.8522348999977112</v>
       </c>
       <c r="H83" t="n">
-        <v>0.8515082001686096</v>
+        <v>0.8515084087848663</v>
       </c>
       <c r="I83" t="n">
-        <v>0.8499580323696136</v>
+        <v>0.8499585092067719</v>
       </c>
     </row>
     <row r="84">
@@ -3870,13 +3870,13 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>0.8504597544670105</v>
+        <v>0.8504599630832672</v>
       </c>
       <c r="H84" t="n">
-        <v>0.8449654281139374</v>
+        <v>0.8449656069278717</v>
       </c>
       <c r="I84" t="n">
-        <v>0.8425625562667847</v>
+        <v>0.8425630629062653</v>
       </c>
     </row>
   </sheetData>
@@ -3972,13 +3972,13 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.863123744726181</v>
+        <v>0.8631241023540497</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8607465028762817</v>
+        <v>0.8607469499111176</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8565530180931091</v>
+        <v>0.8565534055233002</v>
       </c>
     </row>
     <row r="3">
@@ -4013,13 +4013,13 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.8609102368354797</v>
+        <v>0.8609103560447693</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8535879254341125</v>
+        <v>0.8535879850387573</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8522591888904572</v>
+        <v>0.852259486913681</v>
       </c>
     </row>
     <row r="4">
@@ -4054,13 +4054,13 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.8563421368598938</v>
+        <v>0.8563421070575714</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8478220701217651</v>
+        <v>0.8478223383426666</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8461341559886932</v>
+        <v>0.8461344838142395</v>
       </c>
     </row>
     <row r="5">
@@ -4095,13 +4095,13 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.8748290538787842</v>
+        <v>0.8748292922973633</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8650575578212738</v>
+        <v>0.86557537317276</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8614687025547028</v>
+        <v>0.8614690005779266</v>
       </c>
     </row>
     <row r="6">
@@ -4136,13 +4136,13 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.8760460615158081</v>
+        <v>0.8760461509227753</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8752140700817108</v>
+        <v>0.8752144277095795</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8724832534790039</v>
+        <v>0.8724835813045502</v>
       </c>
     </row>
     <row r="7">
@@ -4177,13 +4177,13 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.8824878931045532</v>
+        <v>0.8824881315231323</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8651009798049927</v>
+        <v>0.8651013672351837</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8542524576187134</v>
+        <v>0.8542527854442596</v>
       </c>
     </row>
     <row r="8">
@@ -4218,13 +4218,13 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.8712438941001892</v>
+        <v>0.8712441325187683</v>
       </c>
       <c r="H8" t="n">
-        <v>0.870621383190155</v>
+        <v>0.8706216514110565</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8673335313796997</v>
+        <v>0.8673337697982788</v>
       </c>
     </row>
     <row r="9">
@@ -4259,13 +4259,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.8722023069858551</v>
+        <v>0.872202605009079</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8711291551589966</v>
+        <v>0.8711293339729309</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8628890514373779</v>
+        <v>0.8628892600536346</v>
       </c>
     </row>
     <row r="10">
@@ -4300,13 +4300,13 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.8638100922107697</v>
+        <v>0.8638104796409607</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8521930575370789</v>
+        <v>0.8521934747695923</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8518615663051605</v>
+        <v>0.8517446219921112</v>
       </c>
     </row>
     <row r="11">
@@ -4341,13 +4341,13 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.8786354064941406</v>
+        <v>0.8786357045173645</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8642589747905731</v>
+        <v>0.8642593622207642</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8604055047035217</v>
+        <v>0.860405832529068</v>
       </c>
     </row>
     <row r="12">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.8868874311447144</v>
+        <v>0.8868876993656158</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8567194938659668</v>
+        <v>0.8567197620868683</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8518254160881042</v>
+        <v>0.8518258035182953</v>
       </c>
     </row>
     <row r="13">
@@ -4423,13 +4423,13 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.8796598017215729</v>
+        <v>0.8796600997447968</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8722546398639679</v>
+        <v>0.8722549974918365</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8572297394275665</v>
+        <v>0.8572300374507904</v>
       </c>
     </row>
     <row r="14">
@@ -4464,13 +4464,13 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.8495877385139465</v>
+        <v>0.84958815574646</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8485817015171051</v>
+        <v>0.8485821783542633</v>
       </c>
       <c r="I14" t="n">
-        <v>0.847743958234787</v>
+        <v>0.8477443158626556</v>
       </c>
     </row>
     <row r="15">
@@ -4505,13 +4505,13 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.8557053804397583</v>
+        <v>0.8557057082653046</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8450484871864319</v>
+        <v>0.8450488448143005</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8422485589981079</v>
+        <v>0.842248797416687</v>
       </c>
     </row>
     <row r="16">
@@ -4546,13 +4546,13 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.8684130012989044</v>
+        <v>0.8684133589267731</v>
       </c>
       <c r="H16" t="n">
-        <v>0.860710084438324</v>
+        <v>0.8607102632522583</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8606573045253754</v>
+        <v>0.8606576025485992</v>
       </c>
     </row>
     <row r="17">
@@ -4578,22 +4578,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>牛島 光一</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>繁野 麻衣子</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>牛島 光一</t>
-        </is>
-      </c>
       <c r="G17" t="n">
-        <v>0.8662371933460236</v>
+        <v>0.8662374019622803</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8523014783859253</v>
+        <v>0.8516241312026978</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8516239523887634</v>
+        <v>0.8510572016239166</v>
       </c>
     </row>
     <row r="18">
@@ -4628,13 +4628,13 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0.8556585013866425</v>
+        <v>0.8556589782238007</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8480796813964844</v>
+        <v>0.8480800688266754</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8461092710494995</v>
+        <v>0.8461096286773682</v>
       </c>
     </row>
     <row r="19">
@@ -4669,13 +4669,13 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0.8692281544208527</v>
+        <v>0.8692283034324646</v>
       </c>
       <c r="H19" t="n">
-        <v>0.858031153678894</v>
+        <v>0.8580313920974731</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8552306592464447</v>
+        <v>0.8552308678627014</v>
       </c>
     </row>
     <row r="20">
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0.8761181235313416</v>
+        <v>0.8761183619499207</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8672411441802979</v>
+        <v>0.867241382598877</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8656215667724609</v>
+        <v>0.86562180519104</v>
       </c>
     </row>
     <row r="21">
@@ -4751,13 +4751,13 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0.86680006980896</v>
+        <v>0.8668003678321838</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8634406328201294</v>
+        <v>0.8634408414363861</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8633630573749542</v>
+        <v>0.8633632361888885</v>
       </c>
     </row>
     <row r="22">
@@ -4792,13 +4792,13 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.8656384646892548</v>
+        <v>0.8656387031078339</v>
       </c>
       <c r="H22" t="n">
         <v>0.8634596467018127</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8629352152347565</v>
+        <v>0.8629354536533356</v>
       </c>
     </row>
   </sheetData>

--- a/generated/committee_recommendations.xlsx
+++ b/generated/committee_recommendations.xlsx
@@ -508,13 +508,13 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.8637408018112183</v>
+        <v>0.8637408316135406</v>
       </c>
       <c r="H2" t="n">
         <v>0.8561815619468689</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8561266660690308</v>
+        <v>0.856126606464386</v>
       </c>
     </row>
     <row r="3">
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.8734617531299591</v>
+        <v>0.8734617829322815</v>
       </c>
       <c r="H3" t="n">
         <v>0.8607054650783539</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8574923276901245</v>
+        <v>0.8574922978878021</v>
       </c>
     </row>
     <row r="4">
@@ -590,10 +590,10 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.8704100847244263</v>
+        <v>0.8704101145267487</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8587318658828735</v>
+        <v>0.8587318062782288</v>
       </c>
       <c r="I4" t="n">
         <v>0.8560931086540222</v>
@@ -637,7 +637,7 @@
         <v>0.8693714141845703</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8666558861732483</v>
+        <v>0.8666557967662811</v>
       </c>
     </row>
     <row r="6">
@@ -672,10 +672,10 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.8622949421405792</v>
+        <v>0.8622949123382568</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8608851730823517</v>
+        <v>0.8608852028846741</v>
       </c>
       <c r="I6" t="n">
         <v>0.8604684770107269</v>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.8782476484775543</v>
+        <v>0.8782475888729095</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8727595508098602</v>
+        <v>0.8727595210075378</v>
       </c>
       <c r="I7" t="n">
         <v>0.8720541596412659</v>
@@ -836,13 +836,13 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.8714622557163239</v>
+        <v>0.8714621663093567</v>
       </c>
       <c r="H10" t="n">
         <v>0.8703478574752808</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8688311576843262</v>
+        <v>0.868831068277359</v>
       </c>
     </row>
     <row r="11">
@@ -921,10 +921,10 @@
         <v>0.8546874523162842</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8504401743412018</v>
+        <v>0.8504403233528137</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8490931987762451</v>
+        <v>0.8490931689739227</v>
       </c>
     </row>
     <row r="13">
@@ -962,10 +962,10 @@
         <v>0.8592478334903717</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8458518385887146</v>
+        <v>0.8457378447055817</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8349056243896484</v>
+        <v>0.834905594587326</v>
       </c>
     </row>
     <row r="14">
@@ -1044,7 +1044,7 @@
         <v>0.8802605867385864</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8750885725021362</v>
+        <v>0.8750886023044586</v>
       </c>
       <c r="I15" t="n">
         <v>0.8705006837844849</v>
@@ -1088,7 +1088,7 @@
         <v>0.8685945868492126</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8666940629482269</v>
+        <v>0.8659052550792694</v>
       </c>
     </row>
     <row r="17">
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0.8586440086364746</v>
+        <v>0.8586438894271851</v>
       </c>
       <c r="H17" t="n">
         <v>0.8549793362617493</v>
@@ -1211,7 +1211,7 @@
         <v>0.8633520305156708</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8614738583564758</v>
+        <v>0.8614737987518311</v>
       </c>
     </row>
     <row r="20">
@@ -1249,7 +1249,7 @@
         <v>0.8822429776191711</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8785501420497894</v>
+        <v>0.8785503208637238</v>
       </c>
       <c r="I20" t="n">
         <v>0.8663562834262848</v>
@@ -1331,10 +1331,10 @@
         <v>0.8789419531822205</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8760955929756165</v>
+        <v>0.876095712184906</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8730508089065552</v>
+        <v>0.8733214437961578</v>
       </c>
     </row>
     <row r="23">
@@ -1369,7 +1369,7 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0.8591336905956268</v>
+        <v>0.8591337502002716</v>
       </c>
       <c r="H23" t="n">
         <v>0.8517085015773773</v>
@@ -1410,7 +1410,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0.8527725040912628</v>
+        <v>0.8527725636959076</v>
       </c>
       <c r="H24" t="n">
         <v>0.8512898087501526</v>
@@ -1451,10 +1451,10 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0.8706742227077484</v>
+        <v>0.8706742823123932</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8638857305049896</v>
+        <v>0.863885760307312</v>
       </c>
       <c r="I25" t="n">
         <v>0.8618723750114441</v>
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0.8603377938270569</v>
+        <v>0.8603377640247345</v>
       </c>
       <c r="H27" t="n">
-        <v>0.8578148186206818</v>
+        <v>0.8578147888183594</v>
       </c>
       <c r="I27" t="n">
         <v>0.8570154905319214</v>
@@ -1580,7 +1580,7 @@
         <v>0.8709458708763123</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8683173060417175</v>
+        <v>0.86752849817276</v>
       </c>
     </row>
     <row r="29">
@@ -1618,7 +1618,7 @@
         <v>0.8728598952293396</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8667237460613251</v>
+        <v>0.8667237758636475</v>
       </c>
       <c r="I29" t="n">
         <v>0.862547755241394</v>
@@ -1662,7 +1662,7 @@
         <v>0.8568967878818512</v>
       </c>
       <c r="I30" t="n">
-        <v>0.855995774269104</v>
+        <v>0.8559958040714264</v>
       </c>
     </row>
     <row r="31">
@@ -1741,7 +1741,7 @@
         <v>0.8575133681297302</v>
       </c>
       <c r="H32" t="n">
-        <v>0.8523845374584198</v>
+        <v>0.8523843884468079</v>
       </c>
       <c r="I32" t="n">
         <v>0.8516231775283813</v>
@@ -1782,10 +1782,10 @@
         <v>0.8604612350463867</v>
       </c>
       <c r="H33" t="n">
-        <v>0.8577742874622345</v>
+        <v>0.8577743172645569</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8568277060985565</v>
+        <v>0.8568276762962341</v>
       </c>
     </row>
     <row r="34">
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0.8634571731090546</v>
+        <v>0.8634571135044098</v>
       </c>
       <c r="H34" t="n">
         <v>0.8626152873039246</v>
@@ -1867,7 +1867,7 @@
         <v>0.8801654279232025</v>
       </c>
       <c r="I35" t="n">
-        <v>0.8745454549789429</v>
+        <v>0.8745455145835876</v>
       </c>
     </row>
     <row r="36">
@@ -1902,13 +1902,13 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0.8759266436100006</v>
+        <v>0.875926673412323</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8738082349300385</v>
+        <v>0.8738082945346832</v>
       </c>
       <c r="I36" t="n">
-        <v>0.8677709102630615</v>
+        <v>0.8677709400653839</v>
       </c>
     </row>
     <row r="37">
@@ -1943,13 +1943,13 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0.8812141418457031</v>
+        <v>0.8812141120433807</v>
       </c>
       <c r="H37" t="n">
-        <v>0.8779473304748535</v>
+        <v>0.8779473900794983</v>
       </c>
       <c r="I37" t="n">
-        <v>0.8733148872852325</v>
+        <v>0.8733149170875549</v>
       </c>
     </row>
     <row r="38">
@@ -1990,7 +1990,7 @@
         <v>0.8683319687843323</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8629850745201111</v>
+        <v>0.8629851043224335</v>
       </c>
     </row>
     <row r="39">
@@ -2025,10 +2025,10 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0.8841175734996796</v>
+        <v>0.884117603302002</v>
       </c>
       <c r="H39" t="n">
-        <v>0.8798271417617798</v>
+        <v>0.8798272013664246</v>
       </c>
       <c r="I39" t="n">
         <v>0.879041850566864</v>
@@ -2066,10 +2066,10 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0.883649080991745</v>
+        <v>0.8836490213871002</v>
       </c>
       <c r="H40" t="n">
-        <v>0.8805911242961884</v>
+        <v>0.8805910348892212</v>
       </c>
       <c r="I40" t="n">
         <v>0.8768988847732544</v>
@@ -2107,10 +2107,10 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0.8722117841243744</v>
+        <v>0.8722117245197296</v>
       </c>
       <c r="H41" t="n">
-        <v>0.8708105385303497</v>
+        <v>0.8708105683326721</v>
       </c>
       <c r="I41" t="n">
         <v>0.8650574684143066</v>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>浦田淳司</t>
+          <t>上市 秀雄</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -2154,7 +2154,7 @@
         <v>0.8617661893367767</v>
       </c>
       <c r="I42" t="n">
-        <v>0.8485496342182159</v>
+        <v>0.8482773900032043</v>
       </c>
     </row>
     <row r="43">
@@ -2192,10 +2192,10 @@
         <v>0.8732402920722961</v>
       </c>
       <c r="H43" t="n">
-        <v>0.8674532473087311</v>
+        <v>0.8674532175064087</v>
       </c>
       <c r="I43" t="n">
-        <v>0.8664050996303558</v>
+        <v>0.8664050698280334</v>
       </c>
     </row>
     <row r="44">
@@ -2230,13 +2230,13 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0.8610956370830536</v>
+        <v>0.861095666885376</v>
       </c>
       <c r="H44" t="n">
         <v>0.8599763512611389</v>
       </c>
       <c r="I44" t="n">
-        <v>0.85889932513237</v>
+        <v>0.8588992953300476</v>
       </c>
     </row>
     <row r="45">
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0.88481405377388</v>
+        <v>0.8848141133785248</v>
       </c>
       <c r="H45" t="n">
         <v>0.8846468329429626</v>
@@ -2353,13 +2353,13 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>0.8822457492351532</v>
+        <v>0.8822457194328308</v>
       </c>
       <c r="H47" t="n">
-        <v>0.8808684051036835</v>
+        <v>0.8808684349060059</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8808216154575348</v>
+        <v>0.8808216750621796</v>
       </c>
     </row>
     <row r="48">
@@ -2397,10 +2397,10 @@
         <v>0.876221776008606</v>
       </c>
       <c r="H48" t="n">
-        <v>0.8661503791809082</v>
+        <v>0.8661504089832306</v>
       </c>
       <c r="I48" t="n">
-        <v>0.8655958473682404</v>
+        <v>0.8655959069728851</v>
       </c>
     </row>
     <row r="49">
@@ -2441,7 +2441,7 @@
         <v>0.8649434447288513</v>
       </c>
       <c r="I49" t="n">
-        <v>0.864597499370575</v>
+        <v>0.8645976185798645</v>
       </c>
     </row>
     <row r="50">
@@ -2479,10 +2479,10 @@
         <v>0.8805749118328094</v>
       </c>
       <c r="H50" t="n">
-        <v>0.8783854246139526</v>
+        <v>0.8783853352069855</v>
       </c>
       <c r="I50" t="n">
-        <v>0.8773878812789917</v>
+        <v>0.8773880302906036</v>
       </c>
     </row>
     <row r="51">
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>0.8623651564121246</v>
+        <v>0.8623650968074799</v>
       </c>
       <c r="H51" t="n">
-        <v>0.855972558259964</v>
+        <v>0.8559725880622864</v>
       </c>
       <c r="I51" t="n">
         <v>0.8509648144245148</v>
@@ -2558,10 +2558,10 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>0.8601011633872986</v>
+        <v>0.8601012527942657</v>
       </c>
       <c r="H52" t="n">
-        <v>0.8564841449260712</v>
+        <v>0.8564842045307159</v>
       </c>
       <c r="I52" t="n">
         <v>0.8554677963256836</v>
@@ -2599,13 +2599,13 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>0.8770773708820343</v>
+        <v>0.8770774304866791</v>
       </c>
       <c r="H53" t="n">
         <v>0.8713475167751312</v>
       </c>
       <c r="I53" t="n">
-        <v>0.8681096136569977</v>
+        <v>0.8681094348430634</v>
       </c>
     </row>
     <row r="54">
@@ -2640,13 +2640,13 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>0.8658912181854248</v>
+        <v>0.86589115858078</v>
       </c>
       <c r="H54" t="n">
-        <v>0.8628571927547455</v>
+        <v>0.8628571629524231</v>
       </c>
       <c r="I54" t="n">
-        <v>0.8591557145118713</v>
+        <v>0.8591557741165161</v>
       </c>
     </row>
     <row r="55">
@@ -2684,7 +2684,7 @@
         <v>0.8445272147655487</v>
       </c>
       <c r="H55" t="n">
-        <v>0.8444044291973114</v>
+        <v>0.8444043397903442</v>
       </c>
       <c r="I55" t="n">
         <v>0.8435723185539246</v>
@@ -2725,10 +2725,10 @@
         <v>0.8806582093238831</v>
       </c>
       <c r="H56" t="n">
-        <v>0.8783489763736725</v>
+        <v>0.8783490061759949</v>
       </c>
       <c r="I56" t="n">
-        <v>0.8719048202037811</v>
+        <v>0.8719048798084259</v>
       </c>
     </row>
     <row r="57">
@@ -2763,13 +2763,13 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>0.844330906867981</v>
+        <v>0.8443309366703033</v>
       </c>
       <c r="H57" t="n">
         <v>0.8426342308521271</v>
       </c>
       <c r="I57" t="n">
-        <v>0.8422442376613617</v>
+        <v>0.8422442972660065</v>
       </c>
     </row>
     <row r="58">
@@ -2804,13 +2804,13 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>0.8724232614040375</v>
+        <v>0.8724232316017151</v>
       </c>
       <c r="H58" t="n">
-        <v>0.8723962903022766</v>
+        <v>0.8723962008953094</v>
       </c>
       <c r="I58" t="n">
-        <v>0.86982461810112</v>
+        <v>0.8698244690895081</v>
       </c>
     </row>
     <row r="59">
@@ -2848,7 +2848,7 @@
         <v>0.8817901909351349</v>
       </c>
       <c r="H59" t="n">
-        <v>0.8764764666557312</v>
+        <v>0.876476526260376</v>
       </c>
       <c r="I59" t="n">
         <v>0.8761448860168457</v>
@@ -2889,10 +2889,10 @@
         <v>0.8743585348129272</v>
       </c>
       <c r="H60" t="n">
-        <v>0.8707767426967621</v>
+        <v>0.8707767724990845</v>
       </c>
       <c r="I60" t="n">
-        <v>0.8681854009628296</v>
+        <v>0.8681853711605072</v>
       </c>
     </row>
     <row r="61">
@@ -2927,10 +2927,10 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>0.8797606825828552</v>
+        <v>0.8797605037689209</v>
       </c>
       <c r="H61" t="n">
-        <v>0.8760299682617188</v>
+        <v>0.8760300278663635</v>
       </c>
       <c r="I61" t="n">
         <v>0.8728488087654114</v>
@@ -2968,10 +2968,10 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>0.8302424252033234</v>
+        <v>0.8302423655986786</v>
       </c>
       <c r="H62" t="n">
-        <v>0.8261333405971527</v>
+        <v>0.8261334300041199</v>
       </c>
       <c r="I62" t="n">
         <v>0.8258854150772095</v>
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>0.8613007962703705</v>
+        <v>0.8613006472587585</v>
       </c>
       <c r="H63" t="n">
         <v>0.8604454696178436</v>
@@ -3046,17 +3046,17 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>村上 暁信</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>0.8834521174430847</v>
+        <v>0.8834520876407623</v>
       </c>
       <c r="H64" t="n">
         <v>0.8635226488113403</v>
       </c>
       <c r="I64" t="n">
-        <v>0.8611138761043549</v>
+        <v>0.8611682057380676</v>
       </c>
     </row>
     <row r="65">
@@ -3091,7 +3091,7 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>0.8763948082923889</v>
+        <v>0.8763948380947113</v>
       </c>
       <c r="H65" t="n">
         <v>0.8742636442184448</v>
@@ -3132,13 +3132,13 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>0.8665136098861694</v>
+        <v>0.8665135502815247</v>
       </c>
       <c r="H66" t="n">
         <v>0.8654606640338898</v>
       </c>
       <c r="I66" t="n">
-        <v>0.8637252449989319</v>
+        <v>0.8637252748012543</v>
       </c>
     </row>
     <row r="67">
@@ -3173,7 +3173,7 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>0.8704354763031006</v>
+        <v>0.8704355359077454</v>
       </c>
       <c r="H67" t="n">
         <v>0.8700944781303406</v>
@@ -3217,7 +3217,7 @@
         <v>0.8532235026359558</v>
       </c>
       <c r="H68" t="n">
-        <v>0.8512569665908813</v>
+        <v>0.851256936788559</v>
       </c>
       <c r="I68" t="n">
         <v>0.8432158827781677</v>
@@ -3258,7 +3258,7 @@
         <v>0.8667275011539459</v>
       </c>
       <c r="H69" t="n">
-        <v>0.8648611903190613</v>
+        <v>0.8648612499237061</v>
       </c>
       <c r="I69" t="n">
         <v>0.8611284792423248</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>0.8745884299278259</v>
+        <v>0.8745883107185364</v>
       </c>
       <c r="H70" t="n">
-        <v>0.8734764456748962</v>
+        <v>0.873476505279541</v>
       </c>
       <c r="I70" t="n">
         <v>0.8721948862075806</v>
@@ -3337,13 +3337,13 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>0.8696563243865967</v>
+        <v>0.8696563839912415</v>
       </c>
       <c r="H71" t="n">
-        <v>0.8688327670097351</v>
+        <v>0.8688327968120575</v>
       </c>
       <c r="I71" t="n">
-        <v>0.8680279850959778</v>
+        <v>0.8680278658866882</v>
       </c>
     </row>
     <row r="72">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>0.8609508275985718</v>
+        <v>0.8609508872032166</v>
       </c>
       <c r="H72" t="n">
         <v>0.8593298196792603</v>
       </c>
       <c r="I72" t="n">
-        <v>0.8565828204154968</v>
+        <v>0.8565827608108521</v>
       </c>
     </row>
     <row r="73">
@@ -3419,13 +3419,13 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>0.8722729384899139</v>
+        <v>0.8722729086875916</v>
       </c>
       <c r="H73" t="n">
         <v>0.8718547224998474</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8710871338844299</v>
+        <v>0.8710870742797852</v>
       </c>
     </row>
     <row r="74">
@@ -3460,13 +3460,13 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>0.8737937211990356</v>
+        <v>0.8738634884357452</v>
       </c>
       <c r="H74" t="n">
-        <v>0.8721552789211273</v>
+        <v>0.8721553683280945</v>
       </c>
       <c r="I74" t="n">
-        <v>0.8709364831447601</v>
+        <v>0.8709365427494049</v>
       </c>
     </row>
     <row r="75">
@@ -3501,13 +3501,13 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>0.8804771602153778</v>
+        <v>0.8804772198200226</v>
       </c>
       <c r="H75" t="n">
         <v>0.8803759813308716</v>
       </c>
       <c r="I75" t="n">
-        <v>0.8761863708496094</v>
+        <v>0.8761864602565765</v>
       </c>
     </row>
     <row r="76">
@@ -3545,7 +3545,7 @@
         <v>0.8619394898414612</v>
       </c>
       <c r="H76" t="n">
-        <v>0.8587501049041748</v>
+        <v>0.8587501645088196</v>
       </c>
       <c r="I76" t="n">
         <v>0.8567723035812378</v>
@@ -3589,7 +3589,7 @@
         <v>0.872369110584259</v>
       </c>
       <c r="I77" t="n">
-        <v>0.8709968030452728</v>
+        <v>0.8709968626499176</v>
       </c>
     </row>
     <row r="78">
@@ -3624,13 +3624,13 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>0.8803968131542206</v>
+        <v>0.880396842956543</v>
       </c>
       <c r="H78" t="n">
-        <v>0.8765251338481903</v>
+        <v>0.8765251934528351</v>
       </c>
       <c r="I78" t="n">
-        <v>0.8699567019939423</v>
+        <v>0.8699566125869751</v>
       </c>
     </row>
     <row r="79">
@@ -3665,13 +3665,13 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>0.8760639429092407</v>
+        <v>0.8760638833045959</v>
       </c>
       <c r="H79" t="n">
-        <v>0.8648146092891693</v>
+        <v>0.8648147284984589</v>
       </c>
       <c r="I79" t="n">
-        <v>0.8647044599056244</v>
+        <v>0.8647045493125916</v>
       </c>
     </row>
     <row r="80">
@@ -3706,13 +3706,13 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>0.856104701757431</v>
+        <v>0.8561047315597534</v>
       </c>
       <c r="H80" t="n">
         <v>0.854439914226532</v>
       </c>
       <c r="I80" t="n">
-        <v>0.8523488640785217</v>
+        <v>0.852348804473877</v>
       </c>
     </row>
     <row r="81">
@@ -3747,13 +3747,13 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>0.8559111952781677</v>
+        <v>0.8559112250804901</v>
       </c>
       <c r="H81" t="n">
         <v>0.8549925088882446</v>
       </c>
       <c r="I81" t="n">
-        <v>0.8529223501682281</v>
+        <v>0.852196604013443</v>
       </c>
     </row>
     <row r="82">
@@ -3788,13 +3788,13 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>0.8549389541149139</v>
+        <v>0.8549389243125916</v>
       </c>
       <c r="H82" t="n">
-        <v>0.853016585111618</v>
+        <v>0.8530166447162628</v>
       </c>
       <c r="I82" t="n">
-        <v>0.8502903878688812</v>
+        <v>0.8502903580665588</v>
       </c>
     </row>
     <row r="83">
@@ -3829,7 +3829,7 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>0.8522348999977112</v>
+        <v>0.8522348403930664</v>
       </c>
       <c r="H83" t="n">
         <v>0.8515084087848663</v>
@@ -3870,10 +3870,10 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>0.8504599630832672</v>
+        <v>0.8504600822925568</v>
       </c>
       <c r="H84" t="n">
-        <v>0.8449656069278717</v>
+        <v>0.8449656367301941</v>
       </c>
       <c r="I84" t="n">
         <v>0.8425630629062653</v>
@@ -3978,7 +3978,7 @@
         <v>0.8607469499111176</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8565534055233002</v>
+        <v>0.8565534651279449</v>
       </c>
     </row>
     <row r="3">
@@ -4098,7 +4098,7 @@
         <v>0.8748292922973633</v>
       </c>
       <c r="H5" t="n">
-        <v>0.86557537317276</v>
+        <v>0.8643404841423035</v>
       </c>
       <c r="I5" t="n">
         <v>0.8614690005779266</v>
@@ -4139,7 +4139,7 @@
         <v>0.8760461509227753</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8752144277095795</v>
+        <v>0.8752145171165466</v>
       </c>
       <c r="I6" t="n">
         <v>0.8724835813045502</v>
@@ -4180,10 +4180,10 @@
         <v>0.8824881315231323</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8651013672351837</v>
+        <v>0.8651013374328613</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8542527854442596</v>
+        <v>0.8542527556419373</v>
       </c>
     </row>
     <row r="8">
@@ -4259,10 +4259,10 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.872202605009079</v>
+        <v>0.8722026646137238</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8711293339729309</v>
+        <v>0.8711293637752533</v>
       </c>
       <c r="I9" t="n">
         <v>0.8628892600536346</v>
@@ -4306,7 +4306,7 @@
         <v>0.8521934747695923</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8517446219921112</v>
+        <v>0.8508499264717102</v>
       </c>
     </row>
     <row r="11">
@@ -4344,7 +4344,7 @@
         <v>0.8786357045173645</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8642593622207642</v>
+        <v>0.8642593026161194</v>
       </c>
       <c r="I11" t="n">
         <v>0.860405832529068</v>
@@ -4426,7 +4426,7 @@
         <v>0.8796600997447968</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8722549974918365</v>
+        <v>0.8722550570964813</v>
       </c>
       <c r="I13" t="n">
         <v>0.8572300374507904</v>
@@ -4508,10 +4508,10 @@
         <v>0.8557057082653046</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8450488448143005</v>
+        <v>0.8450488150119781</v>
       </c>
       <c r="I15" t="n">
-        <v>0.842248797416687</v>
+        <v>0.8422488570213318</v>
       </c>
     </row>
     <row r="16">
@@ -4590,10 +4590,10 @@
         <v>0.8662374019622803</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8516241312026978</v>
+        <v>0.8516241908073425</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8510572016239166</v>
+        <v>0.8515234887599945</v>
       </c>
     </row>
     <row r="18">
@@ -4631,10 +4631,10 @@
         <v>0.8556589782238007</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8480800688266754</v>
+        <v>0.8470976948738098</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8461096286773682</v>
+        <v>0.8461095988750458</v>
       </c>
     </row>
     <row r="19">
@@ -4710,10 +4710,10 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0.8761183619499207</v>
+        <v>0.8761183023452759</v>
       </c>
       <c r="H20" t="n">
-        <v>0.867241382598877</v>
+        <v>0.8672414720058441</v>
       </c>
       <c r="I20" t="n">
         <v>0.86562180519104</v>
@@ -4757,7 +4757,7 @@
         <v>0.8634408414363861</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8633632361888885</v>
+        <v>0.8633632063865662</v>
       </c>
     </row>
     <row r="22">
@@ -4792,10 +4792,10 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.8656387031078339</v>
+        <v>0.8656386733055115</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8634596467018127</v>
+        <v>0.8634596168994904</v>
       </c>
       <c r="I22" t="n">
         <v>0.8629354536533356</v>

--- a/generated/committee_recommendations.xlsx
+++ b/generated/committee_recommendations.xlsx
@@ -508,13 +508,13 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.8637408316135406</v>
+        <v>0.8637408018112183</v>
       </c>
       <c r="H2" t="n">
         <v>0.8561815619468689</v>
       </c>
       <c r="I2" t="n">
-        <v>0.856126606464386</v>
+        <v>0.8561266660690308</v>
       </c>
     </row>
     <row r="3">
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.8734617829322815</v>
+        <v>0.8734618127346039</v>
       </c>
       <c r="H3" t="n">
         <v>0.8607054650783539</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8574922978878021</v>
+        <v>0.8574923872947693</v>
       </c>
     </row>
     <row r="4">
@@ -590,10 +590,10 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.8704101145267487</v>
+        <v>0.8704100847244263</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8587318062782288</v>
+        <v>0.8587318658828735</v>
       </c>
       <c r="I4" t="n">
         <v>0.8560931086540222</v>
@@ -637,7 +637,7 @@
         <v>0.8693714141845703</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8666557967662811</v>
+        <v>0.8666558563709259</v>
       </c>
     </row>
     <row r="6">
@@ -672,13 +672,13 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.8622949123382568</v>
+        <v>0.8622950315475464</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8608852028846741</v>
+        <v>0.8608852624893188</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8604684770107269</v>
+        <v>0.8604684472084045</v>
       </c>
     </row>
     <row r="7">
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.8782475888729095</v>
+        <v>0.8782475590705872</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8727595210075378</v>
+        <v>0.8727595508098602</v>
       </c>
       <c r="I7" t="n">
         <v>0.8720541596412659</v>
@@ -836,13 +836,13 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.8714621663093567</v>
+        <v>0.8714622259140015</v>
       </c>
       <c r="H10" t="n">
         <v>0.8703478574752808</v>
       </c>
       <c r="I10" t="n">
-        <v>0.868831068277359</v>
+        <v>0.8688310980796814</v>
       </c>
     </row>
     <row r="11">
@@ -921,10 +921,10 @@
         <v>0.8546874523162842</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8504403233528137</v>
+        <v>0.8504401743412018</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8490931689739227</v>
+        <v>0.8490931987762451</v>
       </c>
     </row>
     <row r="13">
@@ -962,7 +962,7 @@
         <v>0.8592478334903717</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8457378447055817</v>
+        <v>0.8457583487033844</v>
       </c>
       <c r="I13" t="n">
         <v>0.834905594587326</v>
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.8779064118862152</v>
+        <v>0.8779063522815704</v>
       </c>
       <c r="H14" t="n">
         <v>0.8726606070995331</v>
@@ -1044,10 +1044,10 @@
         <v>0.8802605867385864</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8750886023044586</v>
+        <v>0.875088632106781</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8705006837844849</v>
+        <v>0.8705006539821625</v>
       </c>
     </row>
     <row r="16">
@@ -1088,7 +1088,7 @@
         <v>0.8685945868492126</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8659052550792694</v>
+        <v>0.8643802106380463</v>
       </c>
     </row>
     <row r="17">
@@ -1208,10 +1208,10 @@
         <v>0.8647384345531464</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8633520305156708</v>
+        <v>0.8633520007133484</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8614737987518311</v>
+        <v>0.8614738583564758</v>
       </c>
     </row>
     <row r="20">
@@ -1249,7 +1249,7 @@
         <v>0.8822429776191711</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8785503208637238</v>
+        <v>0.8785502910614014</v>
       </c>
       <c r="I20" t="n">
         <v>0.8663562834262848</v>
@@ -1328,13 +1328,13 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.8789419531822205</v>
+        <v>0.8789419233798981</v>
       </c>
       <c r="H22" t="n">
-        <v>0.876095712184906</v>
+        <v>0.8760957717895508</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8733214437961578</v>
+        <v>0.8733214735984802</v>
       </c>
     </row>
     <row r="23">
@@ -1369,13 +1369,13 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0.8591337502002716</v>
+        <v>0.8591337203979492</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8517085015773773</v>
+        <v>0.8517085313796997</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8514227271080017</v>
+        <v>0.8514226973056793</v>
       </c>
     </row>
     <row r="24">
@@ -1410,10 +1410,10 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0.8527725636959076</v>
+        <v>0.8527725040912628</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8512898087501526</v>
+        <v>0.8512897491455078</v>
       </c>
       <c r="I24" t="n">
         <v>0.8512193560600281</v>
@@ -1451,10 +1451,10 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0.8706742823123932</v>
+        <v>0.8706742525100708</v>
       </c>
       <c r="H25" t="n">
-        <v>0.863885760307312</v>
+        <v>0.8638857007026672</v>
       </c>
       <c r="I25" t="n">
         <v>0.8618723750114441</v>
@@ -1495,7 +1495,7 @@
         <v>0.8637948930263519</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8582098484039307</v>
+        <v>0.8582097887992859</v>
       </c>
       <c r="I26" t="n">
         <v>0.8576050400733948</v>
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0.8603377640247345</v>
+        <v>0.8603377342224121</v>
       </c>
       <c r="H27" t="n">
-        <v>0.8578147888183594</v>
+        <v>0.8578148186206818</v>
       </c>
       <c r="I27" t="n">
         <v>0.8570154905319214</v>
@@ -1580,7 +1580,7 @@
         <v>0.8709458708763123</v>
       </c>
       <c r="I28" t="n">
-        <v>0.86752849817276</v>
+        <v>0.8660034537315369</v>
       </c>
     </row>
     <row r="29">
@@ -1659,10 +1659,10 @@
         <v>0.8834352493286133</v>
       </c>
       <c r="H30" t="n">
-        <v>0.8568967878818512</v>
+        <v>0.8568968176841736</v>
       </c>
       <c r="I30" t="n">
-        <v>0.8559958040714264</v>
+        <v>0.855995774269104</v>
       </c>
     </row>
     <row r="31">
@@ -1738,13 +1738,13 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0.8575133681297302</v>
+        <v>0.857513427734375</v>
       </c>
       <c r="H32" t="n">
-        <v>0.8523843884468079</v>
+        <v>0.852384477853775</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8516231775283813</v>
+        <v>0.8516232371330261</v>
       </c>
     </row>
     <row r="33">
@@ -1782,7 +1782,7 @@
         <v>0.8604612350463867</v>
       </c>
       <c r="H33" t="n">
-        <v>0.8577743172645569</v>
+        <v>0.8577743470668793</v>
       </c>
       <c r="I33" t="n">
         <v>0.8568276762962341</v>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0.8634571135044098</v>
+        <v>0.8634571433067322</v>
       </c>
       <c r="H34" t="n">
         <v>0.8626152873039246</v>
@@ -1867,7 +1867,7 @@
         <v>0.8801654279232025</v>
       </c>
       <c r="I35" t="n">
-        <v>0.8745455145835876</v>
+        <v>0.8745454549789429</v>
       </c>
     </row>
     <row r="36">
@@ -1905,10 +1905,10 @@
         <v>0.875926673412323</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8738082945346832</v>
+        <v>0.8738082647323608</v>
       </c>
       <c r="I36" t="n">
-        <v>0.8677709400653839</v>
+        <v>0.8677709102630615</v>
       </c>
     </row>
     <row r="37">
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0.8812141120433807</v>
+        <v>0.8812141716480255</v>
       </c>
       <c r="H37" t="n">
-        <v>0.8779473900794983</v>
+        <v>0.8779473602771759</v>
       </c>
       <c r="I37" t="n">
         <v>0.8733149170875549</v>
@@ -2025,10 +2025,10 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0.884117603302002</v>
+        <v>0.8841176629066467</v>
       </c>
       <c r="H39" t="n">
-        <v>0.8798272013664246</v>
+        <v>0.8798271715641022</v>
       </c>
       <c r="I39" t="n">
         <v>0.879041850566864</v>
@@ -2072,7 +2072,7 @@
         <v>0.8805910348892212</v>
       </c>
       <c r="I40" t="n">
-        <v>0.8768988847732544</v>
+        <v>0.8768989443778992</v>
       </c>
     </row>
     <row r="41">
@@ -2107,13 +2107,13 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0.8722117245197296</v>
+        <v>0.8722117841243744</v>
       </c>
       <c r="H41" t="n">
-        <v>0.8708105683326721</v>
+        <v>0.8708105385303497</v>
       </c>
       <c r="I41" t="n">
-        <v>0.8650574684143066</v>
+        <v>0.8650574386119843</v>
       </c>
     </row>
     <row r="42">
@@ -2148,13 +2148,13 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0.8621289134025574</v>
+        <v>0.8621288537979126</v>
       </c>
       <c r="H42" t="n">
-        <v>0.8617661893367767</v>
+        <v>0.8617662489414215</v>
       </c>
       <c r="I42" t="n">
-        <v>0.8482773900032043</v>
+        <v>0.848277360200882</v>
       </c>
     </row>
     <row r="43">
@@ -2192,10 +2192,10 @@
         <v>0.8732402920722961</v>
       </c>
       <c r="H43" t="n">
-        <v>0.8674532175064087</v>
+        <v>0.8674532473087311</v>
       </c>
       <c r="I43" t="n">
-        <v>0.8664050698280334</v>
+        <v>0.8664051592350006</v>
       </c>
     </row>
     <row r="44">
@@ -2236,7 +2236,7 @@
         <v>0.8599763512611389</v>
       </c>
       <c r="I44" t="n">
-        <v>0.8588992953300476</v>
+        <v>0.8588992655277252</v>
       </c>
     </row>
     <row r="45">
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0.8848141133785248</v>
+        <v>0.8848140835762024</v>
       </c>
       <c r="H45" t="n">
         <v>0.8846468329429626</v>
@@ -2312,7 +2312,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0.8624061048030853</v>
+        <v>0.8624060153961182</v>
       </c>
       <c r="H46" t="n">
         <v>0.8623032569885254</v>
@@ -2353,13 +2353,13 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>0.8822457194328308</v>
+        <v>0.8822457790374756</v>
       </c>
       <c r="H47" t="n">
         <v>0.8808684349060059</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8808216750621796</v>
+        <v>0.8808216452598572</v>
       </c>
     </row>
     <row r="48">
@@ -2397,7 +2397,7 @@
         <v>0.876221776008606</v>
       </c>
       <c r="H48" t="n">
-        <v>0.8661504089832306</v>
+        <v>0.8661503791809082</v>
       </c>
       <c r="I48" t="n">
         <v>0.8655959069728851</v>
@@ -2441,7 +2441,7 @@
         <v>0.8649434447288513</v>
       </c>
       <c r="I49" t="n">
-        <v>0.8645976185798645</v>
+        <v>0.8645975291728973</v>
       </c>
     </row>
     <row r="50">
@@ -2479,10 +2479,10 @@
         <v>0.8805749118328094</v>
       </c>
       <c r="H50" t="n">
-        <v>0.8783853352069855</v>
+        <v>0.8783853054046631</v>
       </c>
       <c r="I50" t="n">
-        <v>0.8773880302906036</v>
+        <v>0.8773879110813141</v>
       </c>
     </row>
     <row r="51">
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>0.8623650968074799</v>
+        <v>0.8623651266098022</v>
       </c>
       <c r="H51" t="n">
-        <v>0.8559725880622864</v>
+        <v>0.8559726178646088</v>
       </c>
       <c r="I51" t="n">
         <v>0.8509648144245148</v>
@@ -2558,7 +2558,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>0.8601012527942657</v>
+        <v>0.860101193189621</v>
       </c>
       <c r="H52" t="n">
         <v>0.8564842045307159</v>
@@ -2599,13 +2599,13 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>0.8770774304866791</v>
+        <v>0.8770773708820343</v>
       </c>
       <c r="H53" t="n">
-        <v>0.8713475167751312</v>
+        <v>0.8713475465774536</v>
       </c>
       <c r="I53" t="n">
-        <v>0.8681094348430634</v>
+        <v>0.8681095838546753</v>
       </c>
     </row>
     <row r="54">
@@ -2643,10 +2643,10 @@
         <v>0.86589115858078</v>
       </c>
       <c r="H54" t="n">
-        <v>0.8628571629524231</v>
+        <v>0.8628572523593903</v>
       </c>
       <c r="I54" t="n">
-        <v>0.8591557741165161</v>
+        <v>0.8591557145118713</v>
       </c>
     </row>
     <row r="55">
@@ -2681,13 +2681,13 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>0.8445272147655487</v>
+        <v>0.8445272743701935</v>
       </c>
       <c r="H55" t="n">
-        <v>0.8444043397903442</v>
+        <v>0.8444043695926666</v>
       </c>
       <c r="I55" t="n">
-        <v>0.8435723185539246</v>
+        <v>0.8435723483562469</v>
       </c>
     </row>
     <row r="56">
@@ -2725,7 +2725,7 @@
         <v>0.8806582093238831</v>
       </c>
       <c r="H56" t="n">
-        <v>0.8783490061759949</v>
+        <v>0.8783490359783173</v>
       </c>
       <c r="I56" t="n">
         <v>0.8719048798084259</v>
@@ -2763,13 +2763,13 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>0.8443309366703033</v>
+        <v>0.8443308770656586</v>
       </c>
       <c r="H57" t="n">
         <v>0.8426342308521271</v>
       </c>
       <c r="I57" t="n">
-        <v>0.8422442972660065</v>
+        <v>0.8422442376613617</v>
       </c>
     </row>
     <row r="58">
@@ -2804,13 +2804,13 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>0.8724232316017151</v>
+        <v>0.8724232614040375</v>
       </c>
       <c r="H58" t="n">
-        <v>0.8723962008953094</v>
+        <v>0.8723962604999542</v>
       </c>
       <c r="I58" t="n">
-        <v>0.8698244690895081</v>
+        <v>0.8698245584964752</v>
       </c>
     </row>
     <row r="59">
@@ -2848,7 +2848,7 @@
         <v>0.8817901909351349</v>
       </c>
       <c r="H59" t="n">
-        <v>0.876476526260376</v>
+        <v>0.8764764666557312</v>
       </c>
       <c r="I59" t="n">
         <v>0.8761448860168457</v>
@@ -2886,13 +2886,13 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>0.8743585348129272</v>
+        <v>0.8743585646152496</v>
       </c>
       <c r="H60" t="n">
         <v>0.8707767724990845</v>
       </c>
       <c r="I60" t="n">
-        <v>0.8681853711605072</v>
+        <v>0.8681853413581848</v>
       </c>
     </row>
     <row r="61">
@@ -2927,13 +2927,13 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>0.8797605037689209</v>
+        <v>0.8797605931758881</v>
       </c>
       <c r="H61" t="n">
-        <v>0.8760300278663635</v>
+        <v>0.8760299980640411</v>
       </c>
       <c r="I61" t="n">
-        <v>0.8728488087654114</v>
+        <v>0.8728488683700562</v>
       </c>
     </row>
     <row r="62">
@@ -2968,10 +2968,10 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>0.8302423655986786</v>
+        <v>0.8302424550056458</v>
       </c>
       <c r="H62" t="n">
-        <v>0.8261334300041199</v>
+        <v>0.8261333703994751</v>
       </c>
       <c r="I62" t="n">
         <v>0.8258854150772095</v>
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>0.8613006472587585</v>
+        <v>0.8613007366657257</v>
       </c>
       <c r="H63" t="n">
-        <v>0.8604454696178436</v>
+        <v>0.8604455292224884</v>
       </c>
       <c r="I63" t="n">
-        <v>0.8575853407382965</v>
+        <v>0.8575854003429413</v>
       </c>
     </row>
     <row r="64">
@@ -3046,17 +3046,17 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>村上 暁信</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>0.8834520876407623</v>
+        <v>0.8834521770477295</v>
       </c>
       <c r="H64" t="n">
         <v>0.8635226488113403</v>
       </c>
       <c r="I64" t="n">
-        <v>0.8611682057380676</v>
+        <v>0.861113965511322</v>
       </c>
     </row>
     <row r="65">
@@ -3173,13 +3173,13 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>0.8704355359077454</v>
+        <v>0.8704354465007782</v>
       </c>
       <c r="H67" t="n">
         <v>0.8700944781303406</v>
       </c>
       <c r="I67" t="n">
-        <v>0.8686460852622986</v>
+        <v>0.868646115064621</v>
       </c>
     </row>
     <row r="68">
@@ -3217,7 +3217,7 @@
         <v>0.8532235026359558</v>
       </c>
       <c r="H68" t="n">
-        <v>0.851256936788559</v>
+        <v>0.8512569665908813</v>
       </c>
       <c r="I68" t="n">
         <v>0.8432158827781677</v>
@@ -3258,10 +3258,10 @@
         <v>0.8667275011539459</v>
       </c>
       <c r="H69" t="n">
-        <v>0.8648612499237061</v>
+        <v>0.8648612201213837</v>
       </c>
       <c r="I69" t="n">
-        <v>0.8611284792423248</v>
+        <v>0.8611284494400024</v>
       </c>
     </row>
     <row r="70">
@@ -3296,13 +3296,13 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>0.8745883107185364</v>
+        <v>0.8745883405208588</v>
       </c>
       <c r="H70" t="n">
-        <v>0.873476505279541</v>
+        <v>0.8734764754772186</v>
       </c>
       <c r="I70" t="n">
-        <v>0.8721948862075806</v>
+        <v>0.872194916009903</v>
       </c>
     </row>
     <row r="71">
@@ -3337,13 +3337,13 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>0.8696563839912415</v>
+        <v>0.8696563243865967</v>
       </c>
       <c r="H71" t="n">
-        <v>0.8688327968120575</v>
+        <v>0.8688327670097351</v>
       </c>
       <c r="I71" t="n">
-        <v>0.8680278658866882</v>
+        <v>0.8680279850959778</v>
       </c>
     </row>
     <row r="72">
@@ -3381,10 +3381,10 @@
         <v>0.8609508872032166</v>
       </c>
       <c r="H72" t="n">
-        <v>0.8593298196792603</v>
+        <v>0.859329879283905</v>
       </c>
       <c r="I72" t="n">
-        <v>0.8565827608108521</v>
+        <v>0.8565827906131744</v>
       </c>
     </row>
     <row r="73">
@@ -3425,7 +3425,7 @@
         <v>0.8718547224998474</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8710870742797852</v>
+        <v>0.8710871636867523</v>
       </c>
     </row>
     <row r="74">
@@ -3460,13 +3460,13 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>0.8738634884357452</v>
+        <v>0.8738633990287781</v>
       </c>
       <c r="H74" t="n">
         <v>0.8721553683280945</v>
       </c>
       <c r="I74" t="n">
-        <v>0.8709365427494049</v>
+        <v>0.8709365725517273</v>
       </c>
     </row>
     <row r="75">
@@ -3507,7 +3507,7 @@
         <v>0.8803759813308716</v>
       </c>
       <c r="I75" t="n">
-        <v>0.8761864602565765</v>
+        <v>0.8761864006519318</v>
       </c>
     </row>
     <row r="76">
@@ -3545,7 +3545,7 @@
         <v>0.8619394898414612</v>
       </c>
       <c r="H76" t="n">
-        <v>0.8587501645088196</v>
+        <v>0.8587501347064972</v>
       </c>
       <c r="I76" t="n">
         <v>0.8567723035812378</v>
@@ -3589,7 +3589,7 @@
         <v>0.872369110584259</v>
       </c>
       <c r="I77" t="n">
-        <v>0.8709968626499176</v>
+        <v>0.8709968030452728</v>
       </c>
     </row>
     <row r="78">
@@ -3627,10 +3627,10 @@
         <v>0.880396842956543</v>
       </c>
       <c r="H78" t="n">
-        <v>0.8765251934528351</v>
+        <v>0.8765251636505127</v>
       </c>
       <c r="I78" t="n">
-        <v>0.8699566125869751</v>
+        <v>0.8699566721916199</v>
       </c>
     </row>
     <row r="79">
@@ -3668,10 +3668,10 @@
         <v>0.8760638833045959</v>
       </c>
       <c r="H79" t="n">
-        <v>0.8648147284984589</v>
+        <v>0.8648146986961365</v>
       </c>
       <c r="I79" t="n">
-        <v>0.8647045493125916</v>
+        <v>0.8647044897079468</v>
       </c>
     </row>
     <row r="80">
@@ -3706,7 +3706,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>0.8561047315597534</v>
+        <v>0.8561046719551086</v>
       </c>
       <c r="H80" t="n">
         <v>0.854439914226532</v>
@@ -3747,13 +3747,13 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>0.8559112250804901</v>
+        <v>0.8559111952781677</v>
       </c>
       <c r="H81" t="n">
         <v>0.8549925088882446</v>
       </c>
       <c r="I81" t="n">
-        <v>0.852196604013443</v>
+        <v>0.8521965146064758</v>
       </c>
     </row>
     <row r="82">
@@ -3788,13 +3788,13 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>0.8549389243125916</v>
+        <v>0.8549389541149139</v>
       </c>
       <c r="H82" t="n">
-        <v>0.8530166447162628</v>
+        <v>0.8530166149139404</v>
       </c>
       <c r="I82" t="n">
-        <v>0.8502903580665588</v>
+        <v>0.8502903282642365</v>
       </c>
     </row>
     <row r="83">
@@ -3829,13 +3829,13 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>0.8522348403930664</v>
+        <v>0.8522348999977112</v>
       </c>
       <c r="H83" t="n">
         <v>0.8515084087848663</v>
       </c>
       <c r="I83" t="n">
-        <v>0.8499585092067719</v>
+        <v>0.8499585688114166</v>
       </c>
     </row>
     <row r="84">
@@ -3870,10 +3870,10 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>0.8504600822925568</v>
+        <v>0.850460022687912</v>
       </c>
       <c r="H84" t="n">
-        <v>0.8449656367301941</v>
+        <v>0.8449656069278717</v>
       </c>
       <c r="I84" t="n">
         <v>0.8425630629062653</v>
@@ -3978,7 +3978,7 @@
         <v>0.8607469499111176</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8565534651279449</v>
+        <v>0.8565534055233002</v>
       </c>
     </row>
     <row r="3">
@@ -4098,7 +4098,7 @@
         <v>0.8748292922973633</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8643404841423035</v>
+        <v>0.8632778525352478</v>
       </c>
       <c r="I5" t="n">
         <v>0.8614690005779266</v>
@@ -4139,10 +4139,10 @@
         <v>0.8760461509227753</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8752145171165466</v>
+        <v>0.8752143979072571</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8724835813045502</v>
+        <v>0.8724835515022278</v>
       </c>
     </row>
     <row r="7">
@@ -4180,10 +4180,10 @@
         <v>0.8824881315231323</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8651013374328613</v>
+        <v>0.8651013672351837</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8542527556419373</v>
+        <v>0.854252815246582</v>
       </c>
     </row>
     <row r="8">
@@ -4259,10 +4259,10 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.8722026646137238</v>
+        <v>0.8722025752067566</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8711293637752533</v>
+        <v>0.8711293041706085</v>
       </c>
       <c r="I9" t="n">
         <v>0.8628892600536346</v>
@@ -4306,7 +4306,7 @@
         <v>0.8521934747695923</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8508499264717102</v>
+        <v>0.8498798012733459</v>
       </c>
     </row>
     <row r="11">
@@ -4344,7 +4344,7 @@
         <v>0.8786357045173645</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8642593026161194</v>
+        <v>0.8642593622207642</v>
       </c>
       <c r="I11" t="n">
         <v>0.860405832529068</v>
@@ -4388,7 +4388,7 @@
         <v>0.8567197620868683</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8518258035182953</v>
+        <v>0.8518259227275848</v>
       </c>
     </row>
     <row r="13">
@@ -4423,10 +4423,10 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.8796600997447968</v>
+        <v>0.8796601295471191</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8722550570964813</v>
+        <v>0.8722549676895142</v>
       </c>
       <c r="I13" t="n">
         <v>0.8572300374507904</v>
@@ -4511,7 +4511,7 @@
         <v>0.8450488150119781</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8422488570213318</v>
+        <v>0.842248797416687</v>
       </c>
     </row>
     <row r="16">
@@ -4583,7 +4583,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>岡田 幸彦</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4593,7 +4593,7 @@
         <v>0.8516241908073425</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8515234887599945</v>
+        <v>0.8498719036579132</v>
       </c>
     </row>
     <row r="18">
@@ -4631,7 +4631,7 @@
         <v>0.8556589782238007</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8470976948738098</v>
+        <v>0.8470975756645203</v>
       </c>
       <c r="I18" t="n">
         <v>0.8461095988750458</v>
@@ -4713,7 +4713,7 @@
         <v>0.8761183023452759</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8672414720058441</v>
+        <v>0.867241382598877</v>
       </c>
       <c r="I20" t="n">
         <v>0.86562180519104</v>
@@ -4757,7 +4757,7 @@
         <v>0.8634408414363861</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8633632063865662</v>
+        <v>0.8633631765842438</v>
       </c>
     </row>
     <row r="22">
@@ -4792,7 +4792,7 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.8656386733055115</v>
+        <v>0.8656386435031891</v>
       </c>
       <c r="H22" t="n">
         <v>0.8634596168994904</v>

--- a/generated/committee_recommendations.xlsx
+++ b/generated/committee_recommendations.xlsx
@@ -514,7 +514,7 @@
         <v>0.8561815619468689</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8561266660690308</v>
+        <v>0.8561266958713531</v>
       </c>
     </row>
     <row r="3">
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.8734618127346039</v>
+        <v>0.8734617531299591</v>
       </c>
       <c r="H3" t="n">
         <v>0.8607054650783539</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8574923872947693</v>
+        <v>0.8574922680854797</v>
       </c>
     </row>
     <row r="4">
@@ -593,7 +593,7 @@
         <v>0.8704100847244263</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8587318658828735</v>
+        <v>0.8587318956851959</v>
       </c>
       <c r="I4" t="n">
         <v>0.8560931086540222</v>
@@ -637,7 +637,7 @@
         <v>0.8693714141845703</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8666558563709259</v>
+        <v>0.8666558265686035</v>
       </c>
     </row>
     <row r="6">
@@ -672,13 +672,13 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.8622950315475464</v>
+        <v>0.862295001745224</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8608852624893188</v>
+        <v>0.8608852028846741</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8604684472084045</v>
+        <v>0.8604685068130493</v>
       </c>
     </row>
     <row r="7">
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.8782475590705872</v>
+        <v>0.8782475888729095</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8727595508098602</v>
+        <v>0.8727594912052155</v>
       </c>
       <c r="I7" t="n">
         <v>0.8720541596412659</v>
@@ -760,7 +760,7 @@
         <v>0.8555609583854675</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8544269800186157</v>
+        <v>0.8544270396232605</v>
       </c>
     </row>
     <row r="9">
@@ -839,10 +839,10 @@
         <v>0.8714622259140015</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8703478574752808</v>
+        <v>0.8703478872776031</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8688310980796814</v>
+        <v>0.8688310384750366</v>
       </c>
     </row>
     <row r="11">
@@ -924,7 +924,7 @@
         <v>0.8504401743412018</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8490931987762451</v>
+        <v>0.8490932285785675</v>
       </c>
     </row>
     <row r="13">
@@ -962,10 +962,10 @@
         <v>0.8592478334903717</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8457583487033844</v>
+        <v>0.8466725647449493</v>
       </c>
       <c r="I13" t="n">
-        <v>0.834905594587326</v>
+        <v>0.8349055647850037</v>
       </c>
     </row>
     <row r="14">
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.8779063522815704</v>
+        <v>0.8779064118862152</v>
       </c>
       <c r="H14" t="n">
         <v>0.8726606070995331</v>
@@ -1044,10 +1044,10 @@
         <v>0.8802605867385864</v>
       </c>
       <c r="H15" t="n">
-        <v>0.875088632106781</v>
+        <v>0.8750887215137482</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8705006539821625</v>
+        <v>0.8705007433891296</v>
       </c>
     </row>
     <row r="16">
@@ -1088,7 +1088,7 @@
         <v>0.8685945868492126</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8643802106380463</v>
+        <v>0.8663046360015869</v>
       </c>
     </row>
     <row r="17">
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0.8586438894271851</v>
+        <v>0.8586439490318298</v>
       </c>
       <c r="H17" t="n">
         <v>0.8549793362617493</v>
@@ -1208,7 +1208,7 @@
         <v>0.8647384345531464</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8633520007133484</v>
+        <v>0.8633520305156708</v>
       </c>
       <c r="I19" t="n">
         <v>0.8614738583564758</v>
@@ -1249,7 +1249,7 @@
         <v>0.8822429776191711</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8785502910614014</v>
+        <v>0.8785503208637238</v>
       </c>
       <c r="I20" t="n">
         <v>0.8663562834262848</v>
@@ -1328,13 +1328,13 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.8789419233798981</v>
+        <v>0.8789420127868652</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8760957717895508</v>
+        <v>0.8760957419872284</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8733214735984802</v>
+        <v>0.873321533203125</v>
       </c>
     </row>
     <row r="23">
@@ -1372,10 +1372,10 @@
         <v>0.8591337203979492</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8517085313796997</v>
+        <v>0.8517085015773773</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8514226973056793</v>
+        <v>0.8514226675033569</v>
       </c>
     </row>
     <row r="24">
@@ -1410,7 +1410,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0.8527725040912628</v>
+        <v>0.8527725636959076</v>
       </c>
       <c r="H24" t="n">
         <v>0.8512897491455078</v>
@@ -1451,10 +1451,10 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0.8706742525100708</v>
+        <v>0.8706742227077484</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8638857007026672</v>
+        <v>0.8638857305049896</v>
       </c>
       <c r="I25" t="n">
         <v>0.8618723750114441</v>
@@ -1495,7 +1495,7 @@
         <v>0.8637948930263519</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8582097887992859</v>
+        <v>0.8582098484039307</v>
       </c>
       <c r="I26" t="n">
         <v>0.8576050400733948</v>
@@ -1536,7 +1536,7 @@
         <v>0.8603377342224121</v>
       </c>
       <c r="H27" t="n">
-        <v>0.8578148186206818</v>
+        <v>0.8578149080276489</v>
       </c>
       <c r="I27" t="n">
         <v>0.8570154905319214</v>
@@ -1580,7 +1580,7 @@
         <v>0.8709458708763123</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8660034537315369</v>
+        <v>0.8679278790950775</v>
       </c>
     </row>
     <row r="29">
@@ -1738,13 +1738,13 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0.857513427734375</v>
+        <v>0.8575133085250854</v>
       </c>
       <c r="H32" t="n">
-        <v>0.852384477853775</v>
+        <v>0.8523845374584198</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8516232371330261</v>
+        <v>0.8516231775283813</v>
       </c>
     </row>
     <row r="33">
@@ -1782,10 +1782,10 @@
         <v>0.8604612350463867</v>
       </c>
       <c r="H33" t="n">
-        <v>0.8577743470668793</v>
+        <v>0.8577742576599121</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8568276762962341</v>
+        <v>0.8568277955055237</v>
       </c>
     </row>
     <row r="34">
@@ -1820,10 +1820,10 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0.8634571433067322</v>
+        <v>0.8634571731090546</v>
       </c>
       <c r="H34" t="n">
-        <v>0.8626152873039246</v>
+        <v>0.8626152276992798</v>
       </c>
       <c r="I34" t="n">
         <v>0.8595913052558899</v>
@@ -1902,13 +1902,13 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0.875926673412323</v>
+        <v>0.8759266138076782</v>
       </c>
       <c r="H36" t="n">
         <v>0.8738082647323608</v>
       </c>
       <c r="I36" t="n">
-        <v>0.8677709102630615</v>
+        <v>0.8677709400653839</v>
       </c>
     </row>
     <row r="37">
@@ -1943,13 +1943,13 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0.8812141716480255</v>
+        <v>0.8812141120433807</v>
       </c>
       <c r="H37" t="n">
         <v>0.8779473602771759</v>
       </c>
       <c r="I37" t="n">
-        <v>0.8733149170875549</v>
+        <v>0.8733148574829102</v>
       </c>
     </row>
     <row r="38">
@@ -1987,10 +1987,10 @@
         <v>0.8687264025211334</v>
       </c>
       <c r="H38" t="n">
-        <v>0.8683319687843323</v>
+        <v>0.8683319389820099</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8629851043224335</v>
+        <v>0.8629851341247559</v>
       </c>
     </row>
     <row r="39">
@@ -2025,7 +2025,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0.8841176629066467</v>
+        <v>0.884117603302002</v>
       </c>
       <c r="H39" t="n">
         <v>0.8798271715641022</v>
@@ -2066,13 +2066,13 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0.8836490213871002</v>
+        <v>0.883649080991745</v>
       </c>
       <c r="H40" t="n">
-        <v>0.8805910348892212</v>
+        <v>0.8805910050868988</v>
       </c>
       <c r="I40" t="n">
-        <v>0.8768989443778992</v>
+        <v>0.8768988847732544</v>
       </c>
     </row>
     <row r="41">
@@ -2107,13 +2107,13 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0.8722117841243744</v>
+        <v>0.8722118139266968</v>
       </c>
       <c r="H41" t="n">
         <v>0.8708105385303497</v>
       </c>
       <c r="I41" t="n">
-        <v>0.8650574386119843</v>
+        <v>0.8650574088096619</v>
       </c>
     </row>
     <row r="42">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0.8621288537979126</v>
+        <v>0.8621289134025574</v>
       </c>
       <c r="H42" t="n">
-        <v>0.8617662489414215</v>
+        <v>0.861766129732132</v>
       </c>
       <c r="I42" t="n">
         <v>0.848277360200882</v>
@@ -2192,10 +2192,10 @@
         <v>0.8732402920722961</v>
       </c>
       <c r="H43" t="n">
-        <v>0.8674532473087311</v>
+        <v>0.8674532771110535</v>
       </c>
       <c r="I43" t="n">
-        <v>0.8664051592350006</v>
+        <v>0.866405189037323</v>
       </c>
     </row>
     <row r="44">
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0.861095666885376</v>
+        <v>0.8610956072807312</v>
       </c>
       <c r="H44" t="n">
         <v>0.8599763512611389</v>
@@ -2271,7 +2271,7 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0.8848140835762024</v>
+        <v>0.8848141133785248</v>
       </c>
       <c r="H45" t="n">
         <v>0.8846468329429626</v>
@@ -2312,7 +2312,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0.8624060153961182</v>
+        <v>0.8624060451984406</v>
       </c>
       <c r="H46" t="n">
         <v>0.8623032569885254</v>
@@ -2353,10 +2353,10 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>0.8822457790374756</v>
+        <v>0.8822457194328308</v>
       </c>
       <c r="H47" t="n">
-        <v>0.8808684349060059</v>
+        <v>0.8808683753013611</v>
       </c>
       <c r="I47" t="n">
         <v>0.8808216452598572</v>
@@ -2397,10 +2397,10 @@
         <v>0.876221776008606</v>
       </c>
       <c r="H48" t="n">
-        <v>0.8661503791809082</v>
+        <v>0.8661504089832306</v>
       </c>
       <c r="I48" t="n">
-        <v>0.8655959069728851</v>
+        <v>0.8655958473682404</v>
       </c>
     </row>
     <row r="49">
@@ -2479,10 +2479,10 @@
         <v>0.8805749118328094</v>
       </c>
       <c r="H50" t="n">
-        <v>0.8783853054046631</v>
+        <v>0.8783854246139526</v>
       </c>
       <c r="I50" t="n">
-        <v>0.8773879110813141</v>
+        <v>0.8773880302906036</v>
       </c>
     </row>
     <row r="51">
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>0.8623651266098022</v>
+        <v>0.8623651564121246</v>
       </c>
       <c r="H51" t="n">
-        <v>0.8559726178646088</v>
+        <v>0.8559725284576416</v>
       </c>
       <c r="I51" t="n">
         <v>0.8509648144245148</v>
@@ -2558,13 +2558,13 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>0.860101193189621</v>
+        <v>0.8601011335849762</v>
       </c>
       <c r="H52" t="n">
-        <v>0.8564842045307159</v>
+        <v>0.8564841747283936</v>
       </c>
       <c r="I52" t="n">
-        <v>0.8554677963256836</v>
+        <v>0.8554678857326508</v>
       </c>
     </row>
     <row r="53">
@@ -2599,13 +2599,13 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>0.8770773708820343</v>
+        <v>0.8770773410797119</v>
       </c>
       <c r="H53" t="n">
-        <v>0.8713475465774536</v>
+        <v>0.8713474869728088</v>
       </c>
       <c r="I53" t="n">
-        <v>0.8681095838546753</v>
+        <v>0.8681096434593201</v>
       </c>
     </row>
     <row r="54">
@@ -2640,13 +2640,13 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>0.86589115858078</v>
+        <v>0.8658912181854248</v>
       </c>
       <c r="H54" t="n">
-        <v>0.8628572523593903</v>
+        <v>0.8628571331501007</v>
       </c>
       <c r="I54" t="n">
-        <v>0.8591557145118713</v>
+        <v>0.859155684709549</v>
       </c>
     </row>
     <row r="55">
@@ -2684,10 +2684,10 @@
         <v>0.8445272743701935</v>
       </c>
       <c r="H55" t="n">
-        <v>0.8444043695926666</v>
+        <v>0.844404399394989</v>
       </c>
       <c r="I55" t="n">
-        <v>0.8435723483562469</v>
+        <v>0.8435723185539246</v>
       </c>
     </row>
     <row r="56">
@@ -2725,10 +2725,10 @@
         <v>0.8806582093238831</v>
       </c>
       <c r="H56" t="n">
-        <v>0.8783490359783173</v>
+        <v>0.8783490061759949</v>
       </c>
       <c r="I56" t="n">
-        <v>0.8719048798084259</v>
+        <v>0.8719048500061035</v>
       </c>
     </row>
     <row r="57">
@@ -2763,13 +2763,13 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>0.8443308770656586</v>
+        <v>0.844330906867981</v>
       </c>
       <c r="H57" t="n">
-        <v>0.8426342308521271</v>
+        <v>0.8426342606544495</v>
       </c>
       <c r="I57" t="n">
-        <v>0.8422442376613617</v>
+        <v>0.8422442972660065</v>
       </c>
     </row>
     <row r="58">
@@ -2807,10 +2807,10 @@
         <v>0.8724232614040375</v>
       </c>
       <c r="H58" t="n">
-        <v>0.8723962604999542</v>
+        <v>0.8723962903022766</v>
       </c>
       <c r="I58" t="n">
-        <v>0.8698245584964752</v>
+        <v>0.8698245882987976</v>
       </c>
     </row>
     <row r="59">
@@ -2848,7 +2848,7 @@
         <v>0.8817901909351349</v>
       </c>
       <c r="H59" t="n">
-        <v>0.8764764666557312</v>
+        <v>0.876476526260376</v>
       </c>
       <c r="I59" t="n">
         <v>0.8761448860168457</v>
@@ -2886,13 +2886,13 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>0.8743585646152496</v>
+        <v>0.8743585050106049</v>
       </c>
       <c r="H60" t="n">
         <v>0.8707767724990845</v>
       </c>
       <c r="I60" t="n">
-        <v>0.8681853413581848</v>
+        <v>0.8681853115558624</v>
       </c>
     </row>
     <row r="61">
@@ -2927,10 +2927,10 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>0.8797605931758881</v>
+        <v>0.8797606825828552</v>
       </c>
       <c r="H61" t="n">
-        <v>0.8760299980640411</v>
+        <v>0.876029908657074</v>
       </c>
       <c r="I61" t="n">
         <v>0.8728488683700562</v>
@@ -2968,10 +2968,10 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>0.8302424550056458</v>
+        <v>0.8302423655986786</v>
       </c>
       <c r="H62" t="n">
-        <v>0.8261333703994751</v>
+        <v>0.8261333405971527</v>
       </c>
       <c r="I62" t="n">
         <v>0.8258854150772095</v>
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>0.8613007366657257</v>
+        <v>0.8613007962703705</v>
       </c>
       <c r="H63" t="n">
-        <v>0.8604455292224884</v>
+        <v>0.8604454100131989</v>
       </c>
       <c r="I63" t="n">
-        <v>0.8575854003429413</v>
+        <v>0.8575853407382965</v>
       </c>
     </row>
     <row r="64">
@@ -3091,13 +3091,13 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>0.8763948380947113</v>
+        <v>0.8763948678970337</v>
       </c>
       <c r="H65" t="n">
         <v>0.8742636442184448</v>
       </c>
       <c r="I65" t="n">
-        <v>0.8731106519699097</v>
+        <v>0.8731106221675873</v>
       </c>
     </row>
     <row r="66">
@@ -3132,13 +3132,13 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>0.8665135502815247</v>
+        <v>0.8665136098861694</v>
       </c>
       <c r="H66" t="n">
-        <v>0.8654606640338898</v>
+        <v>0.8654606342315674</v>
       </c>
       <c r="I66" t="n">
-        <v>0.8637252748012543</v>
+        <v>0.8637253046035767</v>
       </c>
     </row>
     <row r="67">
@@ -3179,7 +3179,7 @@
         <v>0.8700944781303406</v>
       </c>
       <c r="I67" t="n">
-        <v>0.868646115064621</v>
+        <v>0.8686460852622986</v>
       </c>
     </row>
     <row r="68">
@@ -3258,10 +3258,10 @@
         <v>0.8667275011539459</v>
       </c>
       <c r="H69" t="n">
-        <v>0.8648612201213837</v>
+        <v>0.8648612499237061</v>
       </c>
       <c r="I69" t="n">
-        <v>0.8611284494400024</v>
+        <v>0.8611284792423248</v>
       </c>
     </row>
     <row r="70">
@@ -3296,13 +3296,13 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>0.8745883405208588</v>
+        <v>0.8745884299278259</v>
       </c>
       <c r="H70" t="n">
-        <v>0.8734764754772186</v>
+        <v>0.873476505279541</v>
       </c>
       <c r="I70" t="n">
-        <v>0.872194916009903</v>
+        <v>0.8721948862075806</v>
       </c>
     </row>
     <row r="71">
@@ -3337,13 +3337,13 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>0.8696563243865967</v>
+        <v>0.8696562945842743</v>
       </c>
       <c r="H71" t="n">
         <v>0.8688327670097351</v>
       </c>
       <c r="I71" t="n">
-        <v>0.8680279850959778</v>
+        <v>0.8680280447006226</v>
       </c>
     </row>
     <row r="72">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>0.8609508872032166</v>
+        <v>0.8609508574008942</v>
       </c>
       <c r="H72" t="n">
-        <v>0.859329879283905</v>
+        <v>0.8593298196792603</v>
       </c>
       <c r="I72" t="n">
-        <v>0.8565827906131744</v>
+        <v>0.8565828800201416</v>
       </c>
     </row>
     <row r="73">
@@ -3419,13 +3419,13 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>0.8722729086875916</v>
+        <v>0.8722729682922363</v>
       </c>
       <c r="H73" t="n">
         <v>0.8718547224998474</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8710871636867523</v>
+        <v>0.8710871338844299</v>
       </c>
     </row>
     <row r="74">
@@ -3460,13 +3460,13 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>0.8738633990287781</v>
+        <v>0.8738634586334229</v>
       </c>
       <c r="H74" t="n">
-        <v>0.8721553683280945</v>
+        <v>0.8721552789211273</v>
       </c>
       <c r="I74" t="n">
-        <v>0.8709365725517273</v>
+        <v>0.8709365129470825</v>
       </c>
     </row>
     <row r="75">
@@ -3501,13 +3501,13 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>0.8804772198200226</v>
+        <v>0.8804771900177002</v>
       </c>
       <c r="H75" t="n">
         <v>0.8803759813308716</v>
       </c>
       <c r="I75" t="n">
-        <v>0.8761864006519318</v>
+        <v>0.8761864304542542</v>
       </c>
     </row>
     <row r="76">
@@ -3589,7 +3589,7 @@
         <v>0.872369110584259</v>
       </c>
       <c r="I77" t="n">
-        <v>0.8709968030452728</v>
+        <v>0.8709968328475952</v>
       </c>
     </row>
     <row r="78">
@@ -3624,13 +3624,13 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>0.880396842956543</v>
+        <v>0.8803967833518982</v>
       </c>
       <c r="H78" t="n">
         <v>0.8765251636505127</v>
       </c>
       <c r="I78" t="n">
-        <v>0.8699566721916199</v>
+        <v>0.8699567317962646</v>
       </c>
     </row>
     <row r="79">
@@ -3668,10 +3668,10 @@
         <v>0.8760638833045959</v>
       </c>
       <c r="H79" t="n">
-        <v>0.8648146986961365</v>
+        <v>0.8648147284984589</v>
       </c>
       <c r="I79" t="n">
-        <v>0.8647044897079468</v>
+        <v>0.8647045493125916</v>
       </c>
     </row>
     <row r="80">
@@ -3706,10 +3706,10 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>0.8561046719551086</v>
+        <v>0.856104701757431</v>
       </c>
       <c r="H80" t="n">
-        <v>0.854439914226532</v>
+        <v>0.8544398546218872</v>
       </c>
       <c r="I80" t="n">
         <v>0.852348804473877</v>
@@ -3747,7 +3747,7 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>0.8559111952781677</v>
+        <v>0.8559112250804901</v>
       </c>
       <c r="H81" t="n">
         <v>0.8549925088882446</v>
@@ -3788,10 +3788,10 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>0.8549389541149139</v>
+        <v>0.8549389839172363</v>
       </c>
       <c r="H82" t="n">
-        <v>0.8530166149139404</v>
+        <v>0.8530166447162628</v>
       </c>
       <c r="I82" t="n">
         <v>0.8502903282642365</v>
@@ -3835,7 +3835,7 @@
         <v>0.8515084087848663</v>
       </c>
       <c r="I83" t="n">
-        <v>0.8499585688114166</v>
+        <v>0.8499584496021271</v>
       </c>
     </row>
     <row r="84">
@@ -3873,7 +3873,7 @@
         <v>0.850460022687912</v>
       </c>
       <c r="H84" t="n">
-        <v>0.8449656069278717</v>
+        <v>0.8449655771255493</v>
       </c>
       <c r="I84" t="n">
         <v>0.8425630629062653</v>
@@ -4098,7 +4098,7 @@
         <v>0.8748292922973633</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8632778525352478</v>
+        <v>0.8653301596641541</v>
       </c>
       <c r="I5" t="n">
         <v>0.8614690005779266</v>
@@ -4139,10 +4139,10 @@
         <v>0.8760461509227753</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8752143979072571</v>
+        <v>0.8752144277095795</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8724835515022278</v>
+        <v>0.8724835813045502</v>
       </c>
     </row>
     <row r="7">
@@ -4180,7 +4180,7 @@
         <v>0.8824881315231323</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8651013672351837</v>
+        <v>0.8651012778282166</v>
       </c>
       <c r="I7" t="n">
         <v>0.854252815246582</v>
@@ -4259,10 +4259,10 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.8722025752067566</v>
+        <v>0.872202605009079</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8711293041706085</v>
+        <v>0.8711293339729309</v>
       </c>
       <c r="I9" t="n">
         <v>0.8628892600536346</v>
@@ -4306,7 +4306,7 @@
         <v>0.8521934747695923</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8498798012733459</v>
+        <v>0.8518113493919373</v>
       </c>
     </row>
     <row r="11">
@@ -4344,10 +4344,10 @@
         <v>0.8786357045173645</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8642593622207642</v>
+        <v>0.8642593324184418</v>
       </c>
       <c r="I11" t="n">
-        <v>0.860405832529068</v>
+        <v>0.8604058921337128</v>
       </c>
     </row>
     <row r="12">
@@ -4388,7 +4388,7 @@
         <v>0.8567197620868683</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8518259227275848</v>
+        <v>0.8518258035182953</v>
       </c>
     </row>
     <row r="13">
@@ -4423,10 +4423,10 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.8796601295471191</v>
+        <v>0.8796601593494415</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8722549676895142</v>
+        <v>0.8722549378871918</v>
       </c>
       <c r="I13" t="n">
         <v>0.8572300374507904</v>
@@ -4467,7 +4467,7 @@
         <v>0.84958815574646</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8485821783542633</v>
+        <v>0.8485822081565857</v>
       </c>
       <c r="I14" t="n">
         <v>0.8477443158626556</v>
@@ -4505,10 +4505,10 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.8557057082653046</v>
+        <v>0.855705738067627</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8450488150119781</v>
+        <v>0.8450487852096558</v>
       </c>
       <c r="I15" t="n">
         <v>0.842248797416687</v>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>岡田 幸彦</t>
+          <t>繁野 麻衣子</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4593,7 +4593,7 @@
         <v>0.8516241908073425</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8498719036579132</v>
+        <v>0.8513609170913696</v>
       </c>
     </row>
     <row r="18">
@@ -4631,10 +4631,10 @@
         <v>0.8556589782238007</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8470975756645203</v>
+        <v>0.847097635269165</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8461095988750458</v>
+        <v>0.8461096286773682</v>
       </c>
     </row>
     <row r="19">
@@ -4713,7 +4713,7 @@
         <v>0.8761183023452759</v>
       </c>
       <c r="H20" t="n">
-        <v>0.867241382598877</v>
+        <v>0.8672414124011993</v>
       </c>
       <c r="I20" t="n">
         <v>0.86562180519104</v>
@@ -4792,13 +4792,13 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.8656386435031891</v>
+        <v>0.8656387031078339</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8634596168994904</v>
+        <v>0.8634596765041351</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8629354536533356</v>
+        <v>0.8629355728626251</v>
       </c>
     </row>
   </sheetData>

--- a/generated/committee_recommendations.xlsx
+++ b/generated/committee_recommendations.xlsx
@@ -508,13 +508,13 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.8637408018112183</v>
+        <v>0.8637407720088959</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8561815619468689</v>
+        <v>0.8561812937259674</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8561266958713531</v>
+        <v>0.8561264872550964</v>
       </c>
     </row>
     <row r="3">
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.8734617531299591</v>
+        <v>0.8734613358974457</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8607054650783539</v>
+        <v>0.8607051074504852</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8574922680854797</v>
+        <v>0.8574919700622559</v>
       </c>
     </row>
     <row r="4">
@@ -590,13 +590,13 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.8704100847244263</v>
+        <v>0.8704100549221039</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8587318956851959</v>
+        <v>0.858731746673584</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8560931086540222</v>
+        <v>0.8560929298400879</v>
       </c>
     </row>
     <row r="5">
@@ -631,13 +631,13 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.8748835027217865</v>
+        <v>0.8748833835124969</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8693714141845703</v>
+        <v>0.869371235370636</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8666558265686035</v>
+        <v>0.8666556477546692</v>
       </c>
     </row>
     <row r="6">
@@ -672,13 +672,13 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.862295001745224</v>
+        <v>0.8622947633266449</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8608852028846741</v>
+        <v>0.860884815454483</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8604685068130493</v>
+        <v>0.8604680597782135</v>
       </c>
     </row>
     <row r="7">
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.8782475888729095</v>
+        <v>0.8782474100589752</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8727594912052155</v>
+        <v>0.8727590441703796</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8720541596412659</v>
+        <v>0.872053861618042</v>
       </c>
     </row>
     <row r="8">
@@ -754,13 +754,13 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.8723167479038239</v>
+        <v>0.872316300868988</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8555609583854675</v>
+        <v>0.8555606007575989</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8544270396232605</v>
+        <v>0.8544267117977142</v>
       </c>
     </row>
     <row r="9">
@@ -795,13 +795,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.8737589120864868</v>
+        <v>0.873758852481842</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8660922646522522</v>
+        <v>0.8660920858383179</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8622945547103882</v>
+        <v>0.8622942864894867</v>
       </c>
     </row>
     <row r="10">
@@ -836,13 +836,13 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.8714622259140015</v>
+        <v>0.871461808681488</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8703478872776031</v>
+        <v>0.8703476190567017</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8688310384750366</v>
+        <v>0.8688306212425232</v>
       </c>
     </row>
     <row r="11">
@@ -877,13 +877,13 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.8717465400695801</v>
+        <v>0.8717465102672577</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8668537437915802</v>
+        <v>0.8668534755706787</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8666412830352783</v>
+        <v>0.866641104221344</v>
       </c>
     </row>
     <row r="12">
@@ -918,13 +918,13 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.8546874523162842</v>
+        <v>0.854686975479126</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8504401743412018</v>
+        <v>0.850439727306366</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8490932285785675</v>
+        <v>0.8490930199623108</v>
       </c>
     </row>
     <row r="13">
@@ -959,13 +959,13 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.8592478334903717</v>
+        <v>0.8592474460601807</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8466725647449493</v>
+        <v>0.8445872962474823</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8349055647850037</v>
+        <v>0.8349055051803589</v>
       </c>
     </row>
     <row r="14">
@@ -1000,13 +1000,13 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.8779064118862152</v>
+        <v>0.8779061734676361</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8726606070995331</v>
+        <v>0.8726603388786316</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8708367943763733</v>
+        <v>0.8708363771438599</v>
       </c>
     </row>
     <row r="15">
@@ -1041,13 +1041,13 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.8802605867385864</v>
+        <v>0.8802604079246521</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8750887215137482</v>
+        <v>0.8750883340835571</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8705007433891296</v>
+        <v>0.8705005943775177</v>
       </c>
     </row>
     <row r="16">
@@ -1082,13 +1082,13 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.8758190870285034</v>
+        <v>0.8758189976215363</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8685945868492126</v>
+        <v>0.868594616651535</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8663046360015869</v>
+        <v>0.8643146753311157</v>
       </c>
     </row>
     <row r="17">
@@ -1123,13 +1123,13 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0.8586439490318298</v>
+        <v>0.8586437702178955</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8549793362617493</v>
+        <v>0.8549792468547821</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8542280793190002</v>
+        <v>0.8542279303073883</v>
       </c>
     </row>
     <row r="18">
@@ -1164,13 +1164,13 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0.8756992518901825</v>
+        <v>0.8756991922855377</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8693471550941467</v>
+        <v>0.8693470358848572</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8683554232120514</v>
+        <v>0.8683551251888275</v>
       </c>
     </row>
     <row r="19">
@@ -1208,10 +1208,10 @@
         <v>0.8647384345531464</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8633520305156708</v>
+        <v>0.863351970911026</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8614738583564758</v>
+        <v>0.8614735007286072</v>
       </c>
     </row>
     <row r="20">
@@ -1246,13 +1246,13 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0.8822429776191711</v>
+        <v>0.8822426795959473</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8785503208637238</v>
+        <v>0.8785499632358551</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8663562834262848</v>
+        <v>0.8663559854030609</v>
       </c>
     </row>
     <row r="21">
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0.8621289730072021</v>
+        <v>0.8621286451816559</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8556961417198181</v>
+        <v>0.8556958138942719</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8524527847766876</v>
+        <v>0.8524525165557861</v>
       </c>
     </row>
     <row r="22">
@@ -1328,13 +1328,13 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.8789420127868652</v>
+        <v>0.8789417147636414</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8760957419872284</v>
+        <v>0.8760956525802612</v>
       </c>
       <c r="I22" t="n">
-        <v>0.873321533203125</v>
+        <v>0.8733214735984802</v>
       </c>
     </row>
     <row r="23">
@@ -1372,10 +1372,10 @@
         <v>0.8591337203979492</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8517085015773773</v>
+        <v>0.8517081737518311</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8514226675033569</v>
+        <v>0.851422518491745</v>
       </c>
     </row>
     <row r="24">
@@ -1410,13 +1410,13 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0.8527725636959076</v>
+        <v>0.8527723550796509</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8512897491455078</v>
+        <v>0.8512894809246063</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8512193560600281</v>
+        <v>0.8512190282344818</v>
       </c>
     </row>
     <row r="25">
@@ -1451,13 +1451,13 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0.8706742227077484</v>
+        <v>0.870673805475235</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8638857305049896</v>
+        <v>0.8638855218887329</v>
       </c>
       <c r="I25" t="n">
-        <v>0.8618723750114441</v>
+        <v>0.8618720471858978</v>
       </c>
     </row>
     <row r="26">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0.8637948930263519</v>
+        <v>0.8637948632240295</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8582098484039307</v>
+        <v>0.8582093119621277</v>
       </c>
       <c r="I26" t="n">
-        <v>0.8576050400733948</v>
+        <v>0.8576047420501709</v>
       </c>
     </row>
     <row r="27">
@@ -1533,13 +1533,13 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0.8603377342224121</v>
+        <v>0.860337495803833</v>
       </c>
       <c r="H27" t="n">
-        <v>0.8578149080276489</v>
+        <v>0.8578143715858459</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8570154905319214</v>
+        <v>0.8570152521133423</v>
       </c>
     </row>
     <row r="28">
@@ -1574,13 +1574,13 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>0.8752446472644806</v>
+        <v>0.875244528055191</v>
       </c>
       <c r="H28" t="n">
-        <v>0.8709458708763123</v>
+        <v>0.8709458112716675</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8679278790950775</v>
+        <v>0.8659380078315735</v>
       </c>
     </row>
     <row r="29">
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>0.8728598952293396</v>
+        <v>0.8728594481945038</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8667237758636475</v>
+        <v>0.8667238354682922</v>
       </c>
       <c r="I29" t="n">
-        <v>0.862547755241394</v>
+        <v>0.8625471591949463</v>
       </c>
     </row>
     <row r="30">
@@ -1656,13 +1656,13 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0.8834352493286133</v>
+        <v>0.8834348917007446</v>
       </c>
       <c r="H30" t="n">
-        <v>0.8568968176841736</v>
+        <v>0.8568965196609497</v>
       </c>
       <c r="I30" t="n">
-        <v>0.855995774269104</v>
+        <v>0.8559956848621368</v>
       </c>
     </row>
     <row r="31">
@@ -1697,10 +1697,10 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0.8618856966495514</v>
+        <v>0.8618855476379395</v>
       </c>
       <c r="H31" t="n">
-        <v>0.8590705394744873</v>
+        <v>0.859070360660553</v>
       </c>
       <c r="I31" t="n">
         <v>0.8540639877319336</v>
@@ -1738,13 +1738,13 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0.8575133085250854</v>
+        <v>0.8575132787227631</v>
       </c>
       <c r="H32" t="n">
-        <v>0.8523845374584198</v>
+        <v>0.8523842990398407</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8516231775283813</v>
+        <v>0.8516227602958679</v>
       </c>
     </row>
     <row r="33">
@@ -1779,13 +1779,13 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0.8604612350463867</v>
+        <v>0.8604608178138733</v>
       </c>
       <c r="H33" t="n">
-        <v>0.8577742576599121</v>
+        <v>0.857774019241333</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8568277955055237</v>
+        <v>0.8568276166915894</v>
       </c>
     </row>
     <row r="34">
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0.8634571731090546</v>
+        <v>0.8634569942951202</v>
       </c>
       <c r="H34" t="n">
-        <v>0.8626152276992798</v>
+        <v>0.8626150786876678</v>
       </c>
       <c r="I34" t="n">
-        <v>0.8595913052558899</v>
+        <v>0.8595910668373108</v>
       </c>
     </row>
     <row r="35">
@@ -1861,13 +1861,13 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>0.8803420662879944</v>
+        <v>0.8803417384624481</v>
       </c>
       <c r="H35" t="n">
-        <v>0.8801654279232025</v>
+        <v>0.8801652789115906</v>
       </c>
       <c r="I35" t="n">
-        <v>0.8745454549789429</v>
+        <v>0.874545156955719</v>
       </c>
     </row>
     <row r="36">
@@ -1902,13 +1902,13 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>0.8759266138076782</v>
+        <v>0.8759260773658752</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8738082647323608</v>
+        <v>0.8738081753253937</v>
       </c>
       <c r="I36" t="n">
-        <v>0.8677709400653839</v>
+        <v>0.86777064204216</v>
       </c>
     </row>
     <row r="37">
@@ -1943,13 +1943,13 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0.8812141120433807</v>
+        <v>0.8812137842178345</v>
       </c>
       <c r="H37" t="n">
-        <v>0.8779473602771759</v>
+        <v>0.877947211265564</v>
       </c>
       <c r="I37" t="n">
-        <v>0.8733148574829102</v>
+        <v>0.8733144998550415</v>
       </c>
     </row>
     <row r="38">
@@ -1984,13 +1984,13 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0.8687264025211334</v>
+        <v>0.8687264919281006</v>
       </c>
       <c r="H38" t="n">
-        <v>0.8683319389820099</v>
+        <v>0.8683316707611084</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8629851341247559</v>
+        <v>0.8629849255084991</v>
       </c>
     </row>
     <row r="39">
@@ -2025,13 +2025,13 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0.884117603302002</v>
+        <v>0.8841173052787781</v>
       </c>
       <c r="H39" t="n">
-        <v>0.8798271715641022</v>
+        <v>0.8798267543315887</v>
       </c>
       <c r="I39" t="n">
-        <v>0.879041850566864</v>
+        <v>0.8790417909622192</v>
       </c>
     </row>
     <row r="40">
@@ -2066,13 +2066,13 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>0.883649080991745</v>
+        <v>0.8836487531661987</v>
       </c>
       <c r="H40" t="n">
-        <v>0.8805910050868988</v>
+        <v>0.8805907964706421</v>
       </c>
       <c r="I40" t="n">
-        <v>0.8768988847732544</v>
+        <v>0.8768987655639648</v>
       </c>
     </row>
     <row r="41">
@@ -2107,13 +2107,13 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0.8722118139266968</v>
+        <v>0.8722112476825714</v>
       </c>
       <c r="H41" t="n">
-        <v>0.8708105385303497</v>
+        <v>0.8708103895187378</v>
       </c>
       <c r="I41" t="n">
-        <v>0.8650574088096619</v>
+        <v>0.8650570511817932</v>
       </c>
     </row>
     <row r="42">
@@ -2148,13 +2148,13 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0.8621289134025574</v>
+        <v>0.8621284961700439</v>
       </c>
       <c r="H42" t="n">
-        <v>0.861766129732132</v>
+        <v>0.8617660105228424</v>
       </c>
       <c r="I42" t="n">
-        <v>0.848277360200882</v>
+        <v>0.8482773900032043</v>
       </c>
     </row>
     <row r="43">
@@ -2189,13 +2189,13 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>0.8732402920722961</v>
+        <v>0.8732399344444275</v>
       </c>
       <c r="H43" t="n">
-        <v>0.8674532771110535</v>
+        <v>0.8674529492855072</v>
       </c>
       <c r="I43" t="n">
-        <v>0.866405189037323</v>
+        <v>0.8664050698280334</v>
       </c>
     </row>
     <row r="44">
@@ -2230,13 +2230,13 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0.8610956072807312</v>
+        <v>0.8610953688621521</v>
       </c>
       <c r="H44" t="n">
-        <v>0.8599763512611389</v>
+        <v>0.8599761724472046</v>
       </c>
       <c r="I44" t="n">
-        <v>0.8588992655277252</v>
+        <v>0.8588990569114685</v>
       </c>
     </row>
     <row r="45">
@@ -2271,13 +2271,13 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>0.8848141133785248</v>
+        <v>0.8848139941692352</v>
       </c>
       <c r="H45" t="n">
-        <v>0.8846468329429626</v>
+        <v>0.884646475315094</v>
       </c>
       <c r="I45" t="n">
-        <v>0.881380170583725</v>
+        <v>0.881379634141922</v>
       </c>
     </row>
     <row r="46">
@@ -2312,13 +2312,13 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0.8624060451984406</v>
+        <v>0.8624057769775391</v>
       </c>
       <c r="H46" t="n">
-        <v>0.8623032569885254</v>
+        <v>0.8623030185699463</v>
       </c>
       <c r="I46" t="n">
-        <v>0.8606871068477631</v>
+        <v>0.8606868982315063</v>
       </c>
     </row>
     <row r="47">
@@ -2353,13 +2353,13 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>0.8822457194328308</v>
+        <v>0.8822456002235413</v>
       </c>
       <c r="H47" t="n">
-        <v>0.8808683753013611</v>
+        <v>0.8808680772781372</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8808216452598572</v>
+        <v>0.8808214664459229</v>
       </c>
     </row>
     <row r="48">
@@ -2394,13 +2394,13 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>0.876221776008606</v>
+        <v>0.8762213587760925</v>
       </c>
       <c r="H48" t="n">
-        <v>0.8661504089832306</v>
+        <v>0.8661500513553619</v>
       </c>
       <c r="I48" t="n">
-        <v>0.8655958473682404</v>
+        <v>0.865595281124115</v>
       </c>
     </row>
     <row r="49">
@@ -2435,13 +2435,13 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>0.8662878572940826</v>
+        <v>0.8662874400615692</v>
       </c>
       <c r="H49" t="n">
-        <v>0.8649434447288513</v>
+        <v>0.8649430572986603</v>
       </c>
       <c r="I49" t="n">
-        <v>0.8645975291728973</v>
+        <v>0.8645971715450287</v>
       </c>
     </row>
     <row r="50">
@@ -2476,13 +2476,13 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>0.8805749118328094</v>
+        <v>0.8805746138095856</v>
       </c>
       <c r="H50" t="n">
-        <v>0.8783854246139526</v>
+        <v>0.8783849775791168</v>
       </c>
       <c r="I50" t="n">
-        <v>0.8773880302906036</v>
+        <v>0.8773877024650574</v>
       </c>
     </row>
     <row r="51">
@@ -2517,13 +2517,13 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>0.8623651564121246</v>
+        <v>0.8623651266098022</v>
       </c>
       <c r="H51" t="n">
-        <v>0.8559725284576416</v>
+        <v>0.8559722304344177</v>
       </c>
       <c r="I51" t="n">
-        <v>0.8509648144245148</v>
+        <v>0.8509646058082581</v>
       </c>
     </row>
     <row r="52">
@@ -2558,13 +2558,13 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>0.8601011335849762</v>
+        <v>0.8601007461547852</v>
       </c>
       <c r="H52" t="n">
-        <v>0.8564841747283936</v>
+        <v>0.8564839959144592</v>
       </c>
       <c r="I52" t="n">
-        <v>0.8554678857326508</v>
+        <v>0.8554676175117493</v>
       </c>
     </row>
     <row r="53">
@@ -2599,13 +2599,13 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>0.8770773410797119</v>
+        <v>0.8770770728588104</v>
       </c>
       <c r="H53" t="n">
-        <v>0.8713474869728088</v>
+        <v>0.8713474571704865</v>
       </c>
       <c r="I53" t="n">
-        <v>0.8681096434593201</v>
+        <v>0.8681096136569977</v>
       </c>
     </row>
     <row r="54">
@@ -2640,13 +2640,13 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>0.8658912181854248</v>
+        <v>0.8658909201622009</v>
       </c>
       <c r="H54" t="n">
-        <v>0.8628571331501007</v>
+        <v>0.8628571033477783</v>
       </c>
       <c r="I54" t="n">
-        <v>0.859155684709549</v>
+        <v>0.859155535697937</v>
       </c>
     </row>
     <row r="55">
@@ -2681,13 +2681,13 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>0.8445272743701935</v>
+        <v>0.8445272445678711</v>
       </c>
       <c r="H55" t="n">
-        <v>0.844404399394989</v>
+        <v>0.8444041013717651</v>
       </c>
       <c r="I55" t="n">
-        <v>0.8435723185539246</v>
+        <v>0.8435719907283783</v>
       </c>
     </row>
     <row r="56">
@@ -2722,10 +2722,10 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>0.8806582093238831</v>
+        <v>0.8806580901145935</v>
       </c>
       <c r="H56" t="n">
-        <v>0.8783490061759949</v>
+        <v>0.8783487677574158</v>
       </c>
       <c r="I56" t="n">
         <v>0.8719048500061035</v>
@@ -2763,13 +2763,13 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>0.844330906867981</v>
+        <v>0.8443306088447571</v>
       </c>
       <c r="H57" t="n">
-        <v>0.8426342606544495</v>
+        <v>0.8426340222358704</v>
       </c>
       <c r="I57" t="n">
-        <v>0.8422442972660065</v>
+        <v>0.842244029045105</v>
       </c>
     </row>
     <row r="58">
@@ -2804,13 +2804,13 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>0.8724232614040375</v>
+        <v>0.8724230825901031</v>
       </c>
       <c r="H58" t="n">
-        <v>0.8723962903022766</v>
+        <v>0.8723960220813751</v>
       </c>
       <c r="I58" t="n">
-        <v>0.8698245882987976</v>
+        <v>0.8698239922523499</v>
       </c>
     </row>
     <row r="59">
@@ -2845,13 +2845,13 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>0.8817901909351349</v>
+        <v>0.8817898035049438</v>
       </c>
       <c r="H59" t="n">
-        <v>0.876476526260376</v>
+        <v>0.8764763474464417</v>
       </c>
       <c r="I59" t="n">
-        <v>0.8761448860168457</v>
+        <v>0.8761445879936218</v>
       </c>
     </row>
     <row r="60">
@@ -2886,13 +2886,13 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>0.8743585050106049</v>
+        <v>0.8743581771850586</v>
       </c>
       <c r="H60" t="n">
-        <v>0.8707767724990845</v>
+        <v>0.8707766830921173</v>
       </c>
       <c r="I60" t="n">
-        <v>0.8681853115558624</v>
+        <v>0.8681854009628296</v>
       </c>
     </row>
     <row r="61">
@@ -2927,13 +2927,13 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>0.8797606825828552</v>
+        <v>0.8797598779201508</v>
       </c>
       <c r="H61" t="n">
-        <v>0.876029908657074</v>
+        <v>0.8760296702384949</v>
       </c>
       <c r="I61" t="n">
-        <v>0.8728488683700562</v>
+        <v>0.8728485107421875</v>
       </c>
     </row>
     <row r="62">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>0.8302423655986786</v>
+        <v>0.8302420377731323</v>
       </c>
       <c r="H62" t="n">
-        <v>0.8261333405971527</v>
+        <v>0.8261329233646393</v>
       </c>
       <c r="I62" t="n">
-        <v>0.8258854150772095</v>
+        <v>0.8258852362632751</v>
       </c>
     </row>
     <row r="63">
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>0.8613007962703705</v>
+        <v>0.8613004684448242</v>
       </c>
       <c r="H63" t="n">
-        <v>0.8604454100131989</v>
+        <v>0.8604451417922974</v>
       </c>
       <c r="I63" t="n">
-        <v>0.8575853407382965</v>
+        <v>0.8575851023197174</v>
       </c>
     </row>
     <row r="64">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>0.8834521770477295</v>
+        <v>0.8834516704082489</v>
       </c>
       <c r="H64" t="n">
-        <v>0.8635226488113403</v>
+        <v>0.8635225594043732</v>
       </c>
       <c r="I64" t="n">
-        <v>0.861113965511322</v>
+        <v>0.861113429069519</v>
       </c>
     </row>
     <row r="65">
@@ -3094,10 +3094,10 @@
         <v>0.8763948678970337</v>
       </c>
       <c r="H65" t="n">
-        <v>0.8742636442184448</v>
+        <v>0.8742632567882538</v>
       </c>
       <c r="I65" t="n">
-        <v>0.8731106221675873</v>
+        <v>0.8731103539466858</v>
       </c>
     </row>
     <row r="66">
@@ -3132,13 +3132,13 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>0.8665136098861694</v>
+        <v>0.8665132522583008</v>
       </c>
       <c r="H66" t="n">
-        <v>0.8654606342315674</v>
+        <v>0.865460216999054</v>
       </c>
       <c r="I66" t="n">
-        <v>0.8637253046035767</v>
+        <v>0.8637251555919647</v>
       </c>
     </row>
     <row r="67">
@@ -3173,13 +3173,13 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>0.8704354465007782</v>
+        <v>0.8704355359077454</v>
       </c>
       <c r="H67" t="n">
-        <v>0.8700944781303406</v>
+        <v>0.8700940907001495</v>
       </c>
       <c r="I67" t="n">
-        <v>0.8686460852622986</v>
+        <v>0.8686460256576538</v>
       </c>
     </row>
     <row r="68">
@@ -3214,13 +3214,13 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>0.8532235026359558</v>
+        <v>0.8532232940196991</v>
       </c>
       <c r="H68" t="n">
-        <v>0.8512569665908813</v>
+        <v>0.8512569069862366</v>
       </c>
       <c r="I68" t="n">
-        <v>0.8432158827781677</v>
+        <v>0.8432158231735229</v>
       </c>
     </row>
     <row r="69">
@@ -3255,13 +3255,13 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>0.8667275011539459</v>
+        <v>0.8667273223400116</v>
       </c>
       <c r="H69" t="n">
-        <v>0.8648612499237061</v>
+        <v>0.8648608326911926</v>
       </c>
       <c r="I69" t="n">
-        <v>0.8611284792423248</v>
+        <v>0.8611282706260681</v>
       </c>
     </row>
     <row r="70">
@@ -3296,13 +3296,13 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>0.8745884299278259</v>
+        <v>0.8745879828929901</v>
       </c>
       <c r="H70" t="n">
-        <v>0.873476505279541</v>
+        <v>0.8734760284423828</v>
       </c>
       <c r="I70" t="n">
-        <v>0.8721948862075806</v>
+        <v>0.8721945583820343</v>
       </c>
     </row>
     <row r="71">
@@ -3337,13 +3337,13 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>0.8696562945842743</v>
+        <v>0.8696559071540833</v>
       </c>
       <c r="H71" t="n">
-        <v>0.8688327670097351</v>
+        <v>0.8688324987888336</v>
       </c>
       <c r="I71" t="n">
-        <v>0.8680280447006226</v>
+        <v>0.8680274486541748</v>
       </c>
     </row>
     <row r="72">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>0.8609508574008942</v>
+        <v>0.8609506487846375</v>
       </c>
       <c r="H72" t="n">
-        <v>0.8593298196792603</v>
+        <v>0.8593294322490692</v>
       </c>
       <c r="I72" t="n">
-        <v>0.8565828800201416</v>
+        <v>0.8565827012062073</v>
       </c>
     </row>
     <row r="73">
@@ -3419,13 +3419,13 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>0.8722729682922363</v>
+        <v>0.8722727000713348</v>
       </c>
       <c r="H73" t="n">
-        <v>0.8718547224998474</v>
+        <v>0.8718544840812683</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8710871338844299</v>
+        <v>0.8710868656635284</v>
       </c>
     </row>
     <row r="74">
@@ -3460,13 +3460,13 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>0.8738634586334229</v>
+        <v>0.873863160610199</v>
       </c>
       <c r="H74" t="n">
-        <v>0.8721552789211273</v>
+        <v>0.8721547722816467</v>
       </c>
       <c r="I74" t="n">
-        <v>0.8709365129470825</v>
+        <v>0.8709360361099243</v>
       </c>
     </row>
     <row r="75">
@@ -3501,13 +3501,13 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>0.8804771900177002</v>
+        <v>0.8804770112037659</v>
       </c>
       <c r="H75" t="n">
-        <v>0.8803759813308716</v>
+        <v>0.880375862121582</v>
       </c>
       <c r="I75" t="n">
-        <v>0.8761864304542542</v>
+        <v>0.8761859536170959</v>
       </c>
     </row>
     <row r="76">
@@ -3542,13 +3542,13 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>0.8619394898414612</v>
+        <v>0.8619393706321716</v>
       </c>
       <c r="H76" t="n">
-        <v>0.8587501347064972</v>
+        <v>0.8587498664855957</v>
       </c>
       <c r="I76" t="n">
-        <v>0.8567723035812378</v>
+        <v>0.8567719459533691</v>
       </c>
     </row>
     <row r="77">
@@ -3583,13 +3583,13 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>0.8736216723918915</v>
+        <v>0.8736216425895691</v>
       </c>
       <c r="H77" t="n">
-        <v>0.872369110584259</v>
+        <v>0.8723689317703247</v>
       </c>
       <c r="I77" t="n">
-        <v>0.8709968328475952</v>
+        <v>0.8709964752197266</v>
       </c>
     </row>
     <row r="78">
@@ -3624,13 +3624,13 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>0.8803967833518982</v>
+        <v>0.8803965449333191</v>
       </c>
       <c r="H78" t="n">
-        <v>0.8765251636505127</v>
+        <v>0.8765251040458679</v>
       </c>
       <c r="I78" t="n">
-        <v>0.8699567317962646</v>
+        <v>0.8699566125869751</v>
       </c>
     </row>
     <row r="79">
@@ -3665,13 +3665,13 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>0.8760638833045959</v>
+        <v>0.8760635256767273</v>
       </c>
       <c r="H79" t="n">
-        <v>0.8648147284984589</v>
+        <v>0.8648145496845245</v>
       </c>
       <c r="I79" t="n">
-        <v>0.8647045493125916</v>
+        <v>0.8647039234638214</v>
       </c>
     </row>
     <row r="80">
@@ -3706,13 +3706,13 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>0.856104701757431</v>
+        <v>0.8561045527458191</v>
       </c>
       <c r="H80" t="n">
-        <v>0.8544398546218872</v>
+        <v>0.8544396162033081</v>
       </c>
       <c r="I80" t="n">
-        <v>0.852348804473877</v>
+        <v>0.8523486256599426</v>
       </c>
     </row>
     <row r="81">
@@ -3747,13 +3747,13 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>0.8559112250804901</v>
+        <v>0.8559110462665558</v>
       </c>
       <c r="H81" t="n">
-        <v>0.8549925088882446</v>
+        <v>0.8549920916557312</v>
       </c>
       <c r="I81" t="n">
-        <v>0.8521965146064758</v>
+        <v>0.8521960377693176</v>
       </c>
     </row>
     <row r="82">
@@ -3788,13 +3788,13 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>0.8549389839172363</v>
+        <v>0.8549385368824005</v>
       </c>
       <c r="H82" t="n">
-        <v>0.8530166447162628</v>
+        <v>0.8530160486698151</v>
       </c>
       <c r="I82" t="n">
-        <v>0.8502903282642365</v>
+        <v>0.850290060043335</v>
       </c>
     </row>
     <row r="83">
@@ -3829,13 +3829,13 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>0.8522348999977112</v>
+        <v>0.8522346019744873</v>
       </c>
       <c r="H83" t="n">
-        <v>0.8515084087848663</v>
+        <v>0.8515082001686096</v>
       </c>
       <c r="I83" t="n">
-        <v>0.8499584496021271</v>
+        <v>0.8499580323696136</v>
       </c>
     </row>
     <row r="84">
@@ -3870,13 +3870,13 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>0.850460022687912</v>
+        <v>0.8504597544670105</v>
       </c>
       <c r="H84" t="n">
-        <v>0.8449655771255493</v>
+        <v>0.8449654281139374</v>
       </c>
       <c r="I84" t="n">
-        <v>0.8425630629062653</v>
+        <v>0.8425625562667847</v>
       </c>
     </row>
   </sheetData>
@@ -3972,13 +3972,13 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.8631241023540497</v>
+        <v>0.863123744726181</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8607469499111176</v>
+        <v>0.8607465028762817</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8565534055233002</v>
+        <v>0.8565530180931091</v>
       </c>
     </row>
     <row r="3">
@@ -4013,13 +4013,13 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.8609103560447693</v>
+        <v>0.8609102368354797</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8535879850387573</v>
+        <v>0.8535879254341125</v>
       </c>
       <c r="I3" t="n">
-        <v>0.852259486913681</v>
+        <v>0.8522591888904572</v>
       </c>
     </row>
     <row r="4">
@@ -4054,13 +4054,13 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.8563421070575714</v>
+        <v>0.8563421368598938</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8478223383426666</v>
+        <v>0.8478220701217651</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8461344838142395</v>
+        <v>0.8461341559886932</v>
       </c>
     </row>
     <row r="5">
@@ -4095,13 +4095,13 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.8748292922973633</v>
+        <v>0.8748290538787842</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8653301596641541</v>
+        <v>0.8628411293029785</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8614690005779266</v>
+        <v>0.8614687025547028</v>
       </c>
     </row>
     <row r="6">
@@ -4136,13 +4136,13 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.8760461509227753</v>
+        <v>0.8760460615158081</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8752144277095795</v>
+        <v>0.8752140700817108</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8724835813045502</v>
+        <v>0.8724832534790039</v>
       </c>
     </row>
     <row r="7">
@@ -4177,13 +4177,13 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.8824881315231323</v>
+        <v>0.8824878931045532</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8651012778282166</v>
+        <v>0.8651009798049927</v>
       </c>
       <c r="I7" t="n">
-        <v>0.854252815246582</v>
+        <v>0.8542524576187134</v>
       </c>
     </row>
     <row r="8">
@@ -4218,13 +4218,13 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.8712441325187683</v>
+        <v>0.8712438941001892</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8706216514110565</v>
+        <v>0.870621383190155</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8673337697982788</v>
+        <v>0.8673335313796997</v>
       </c>
     </row>
     <row r="9">
@@ -4259,13 +4259,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.872202605009079</v>
+        <v>0.8722023069858551</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8711293339729309</v>
+        <v>0.8711291551589966</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8628892600536346</v>
+        <v>0.8628890514373779</v>
       </c>
     </row>
     <row r="10">
@@ -4300,13 +4300,13 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0.8638104796409607</v>
+        <v>0.8638100922107697</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8521934747695923</v>
+        <v>0.8521930575370789</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8518113493919373</v>
+        <v>0.8493417203426361</v>
       </c>
     </row>
     <row r="11">
@@ -4341,13 +4341,13 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0.8786357045173645</v>
+        <v>0.8786354064941406</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8642593324184418</v>
+        <v>0.8642589747905731</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8604058921337128</v>
+        <v>0.8604055047035217</v>
       </c>
     </row>
     <row r="12">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0.8868876993656158</v>
+        <v>0.8868874311447144</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8567197620868683</v>
+        <v>0.8567194938659668</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8518258035182953</v>
+        <v>0.8518254160881042</v>
       </c>
     </row>
     <row r="13">
@@ -4423,13 +4423,13 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.8796601593494415</v>
+        <v>0.8796598017215729</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8722549378871918</v>
+        <v>0.8722546398639679</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8572300374507904</v>
+        <v>0.8572297394275665</v>
       </c>
     </row>
     <row r="14">
@@ -4464,13 +4464,13 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0.84958815574646</v>
+        <v>0.8495877385139465</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8485822081565857</v>
+        <v>0.8485817015171051</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8477443158626556</v>
+        <v>0.847743958234787</v>
       </c>
     </row>
     <row r="15">
@@ -4505,13 +4505,13 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.855705738067627</v>
+        <v>0.8557053804397583</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8450487852096558</v>
+        <v>0.8450484871864319</v>
       </c>
       <c r="I15" t="n">
-        <v>0.842248797416687</v>
+        <v>0.8422485589981079</v>
       </c>
     </row>
     <row r="16">
@@ -4546,13 +4546,13 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.8684133589267731</v>
+        <v>0.8684130012989044</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8607102632522583</v>
+        <v>0.860710084438324</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8606576025485992</v>
+        <v>0.8606573045253754</v>
       </c>
     </row>
     <row r="17">
@@ -4587,13 +4587,13 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0.8662374019622803</v>
+        <v>0.8662371933460236</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8516241908073425</v>
+        <v>0.8516239523887634</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8513609170913696</v>
+        <v>0.8505149185657501</v>
       </c>
     </row>
     <row r="18">
@@ -4628,13 +4628,13 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0.8556589782238007</v>
+        <v>0.8556585013866425</v>
       </c>
       <c r="H18" t="n">
-        <v>0.847097635269165</v>
+        <v>0.8470973670482635</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8461096286773682</v>
+        <v>0.8461092710494995</v>
       </c>
     </row>
     <row r="19">
@@ -4669,13 +4669,13 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0.8692283034324646</v>
+        <v>0.8692281544208527</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8580313920974731</v>
+        <v>0.858031153678894</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8552308678627014</v>
+        <v>0.8552306592464447</v>
       </c>
     </row>
     <row r="20">
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0.8761183023452759</v>
+        <v>0.8761181235313416</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8672414124011993</v>
+        <v>0.8672411441802979</v>
       </c>
       <c r="I20" t="n">
-        <v>0.86562180519104</v>
+        <v>0.8656215667724609</v>
       </c>
     </row>
     <row r="21">
@@ -4751,13 +4751,13 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0.8668003678321838</v>
+        <v>0.86680006980896</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8634408414363861</v>
+        <v>0.8634406328201294</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8633631765842438</v>
+        <v>0.8633630573749542</v>
       </c>
     </row>
     <row r="22">
@@ -4792,13 +4792,13 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0.8656387031078339</v>
+        <v>0.8656384646892548</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8634596765041351</v>
+        <v>0.8634596467018127</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8629355728626251</v>
+        <v>0.8629352152347565</v>
       </c>
     </row>
   </sheetData>

--- a/generated/committee_recommendations.xlsx
+++ b/generated/committee_recommendations.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I84"/>
+  <dimension ref="A1:J84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,35 +442,40 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>student_id</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>title</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>teacher_1</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>teacher_2</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>teacher_3</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>score_1</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>score_2</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>score_3</t>
         </is>
@@ -487,34 +492,35 @@
           <t>中島 元毅</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
         <is>
           <t>日本の就活市場における新卒採用に関する研究</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>上市 秀雄</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>秋山 英三</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>牛島 光一</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>0.8637407720088959</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>原田 信行</t>
+        </is>
       </c>
       <c r="H2" t="n">
-        <v>0.8561812937259674</v>
+        <v>0.8624107241630554</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8561264872550964</v>
+        <v>0.8550395369529724</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.8541027009487152</v>
       </c>
     </row>
     <row r="3">
@@ -528,34 +534,35 @@
           <t>荒金 志紀</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
         <is>
           <t>結婚の意思決定に対する独身税の効果と税制度の提案</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>牛島 光一</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>秋山 英三</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>太田 充</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>0.8734613358974457</v>
-      </c>
       <c r="H3" t="n">
-        <v>0.8607051074504852</v>
+        <v>0.8728691041469574</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8574919700622559</v>
+        <v>0.8579381108283997</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.8574923872947693</v>
       </c>
     </row>
     <row r="4">
@@ -569,34 +576,35 @@
           <t>小峯 拓也</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
         <is>
           <t>学生の選考情報を利用した就活支援サービスに関する研究</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>上市 秀雄</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>牛島 光一</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>秋山 英三</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>0.8704100549221039</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>川島 宏一</t>
+        </is>
       </c>
       <c r="H4" t="n">
-        <v>0.858731746673584</v>
+        <v>0.8692523241043091</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8560929298400879</v>
+        <v>0.8567101061344147</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.8545782268047333</v>
       </c>
     </row>
     <row r="5">
@@ -610,34 +618,35 @@
           <t>貫井 虹希</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
         <is>
           <t>最適停止問題を用いた就活市場の分析と改善提案</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>高野 祐一</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>吉瀬 章子</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>上市 秀雄</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>0.8748833835124969</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>澤 亮治</t>
+        </is>
       </c>
       <c r="H5" t="n">
-        <v>0.869371235370636</v>
+        <v>0.8717089295387268</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8666556477546692</v>
+        <v>0.8693714141845703</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.8665045499801636</v>
       </c>
     </row>
     <row r="6">
@@ -651,34 +660,35 @@
           <t>安達 未晴</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
         <is>
           <t>視線計測を用いた保険加入行動の分析</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>牛島 光一</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>岡田 幸彦</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>佐野 幸恵</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>0.8622947633266449</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>秋山 英三</t>
+        </is>
       </c>
       <c r="H6" t="n">
-        <v>0.860884815454483</v>
+        <v>0.8621914386749268</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8604680597782135</v>
+        <v>0.8600322306156158</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.859343945980072</v>
       </c>
     </row>
     <row r="7">
@@ -692,34 +702,35 @@
           <t>YANG LUXI</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
         <is>
           <t>価値観が失敗の対処行動に与える影響-失敗体験の重大性と領域を考えて-</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>上市 秀雄</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>甲斐田 直子</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>秋山 英三</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>0.8782474100589752</v>
-      </c>
       <c r="H7" t="n">
-        <v>0.8727590441703796</v>
+        <v>0.8779138624668121</v>
       </c>
       <c r="I7" t="n">
-        <v>0.872053861618042</v>
+        <v>0.8710568845272064</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.8709176480770111</v>
       </c>
     </row>
     <row r="8">
@@ -733,34 +744,35 @@
           <t>釆原 周弥</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
         <is>
           <t>Priority-neutral matchingsの集合の格子構造に関する研究</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>澤 亮治</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>八森 正泰</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>和田 健太郎</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>0.872316300868988</v>
-      </c>
       <c r="H8" t="n">
-        <v>0.8555606007575989</v>
+        <v>0.8699048757553101</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8544267117977142</v>
+        <v>0.8567256033420563</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.8535665273666382</v>
       </c>
     </row>
     <row r="9">
@@ -774,34 +786,35 @@
           <t>金井 公亮</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
         <is>
           <t>不確実性下の同質財割当における randomized uniform rule のパレート効率性について</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>澤 亮治</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>八森 正泰</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>高野 祐一</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>八森 正泰</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>0.873758852481842</v>
-      </c>
       <c r="H9" t="n">
-        <v>0.8660920858383179</v>
+        <v>0.8741540312767029</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8622942864894867</v>
+        <v>0.8632310926914215</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.8630319237709045</v>
       </c>
     </row>
     <row r="10">
@@ -815,34 +828,35 @@
           <t>原 笙太</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
         <is>
           <t>都市特性・社会経済要因が外国人居住パターンに与える影響：東京23区の実証・シミュレーション分析</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>鈴木 勉</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>太田 充</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>鈴木 勉</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>堤 盛人</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>0.871461808681488</v>
-      </c>
       <c r="H10" t="n">
-        <v>0.8703476190567017</v>
+        <v>0.8737157583236694</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8688306212425232</v>
+        <v>0.8714622259140015</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.8690856695175171</v>
       </c>
     </row>
     <row r="11">
@@ -856,34 +870,35 @@
           <t>間嶋 大智</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
         <is>
           <t>マルチエージェントシミュレーション&amp;最適化による間取り生成</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>吉瀬 章子</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>八森 正泰</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>有馬 澄佳</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>0.8717465102672577</v>
-      </c>
       <c r="H11" t="n">
-        <v>0.8668534755706787</v>
+        <v>0.8717465400695801</v>
       </c>
       <c r="I11" t="n">
-        <v>0.866641104221344</v>
+        <v>0.8681821823120117</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.8677197694778442</v>
       </c>
     </row>
     <row r="12">
@@ -897,34 +912,35 @@
           <t>山田 幹大</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
         <is>
           <t>eスポーツにおけるチームのプレイスタイル分析</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>澤 亮治</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>川島 宏一</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>佐野 幸恵</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>0.854686975479126</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>秋山 英三</t>
+        </is>
       </c>
       <c r="H12" t="n">
-        <v>0.850439727306366</v>
+        <v>0.8534895181655884</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8490930199623108</v>
+        <v>0.8504401743412018</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.8496212959289551</v>
       </c>
     </row>
     <row r="13">
@@ -938,34 +954,35 @@
           <t>笹木 重聖</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
         <is>
           <t>単位コイングラフにおける部分彩色の拡張</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>八森 正泰</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>繁野 麻衣子</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>佐野 幸恵</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>0.8592474460601807</v>
-      </c>
       <c r="H13" t="n">
-        <v>0.8445872962474823</v>
+        <v>0.8598322868347168</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8349055051803589</v>
+        <v>0.8457445502281189</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.8340944945812225</v>
       </c>
     </row>
     <row r="14">
@@ -979,34 +996,35 @@
           <t>井出 裕二</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
         <is>
           <t>人口を考慮した均等輸送問題による道路ネットワークの連結性の定量化とその最適補強問題</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>鈴木 勉</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Phung-Duc Tuan</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>八森 正泰</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Phung-Duc Tuan</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>0.8779061734676361</v>
-      </c>
       <c r="H14" t="n">
-        <v>0.8726603388786316</v>
+        <v>0.8803897202014923</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8708363771438599</v>
+        <v>0.8714250326156616</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.8703753650188446</v>
       </c>
     </row>
     <row r="15">
@@ -1020,34 +1038,35 @@
           <t>矢中 祥吾</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
         <is>
           <t>消費電力と所要時間の不確実性を考慮した電動バスの運行計画最適化</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Phung-Duc Tuan</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>和田 健太郎</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>鈴木 勉</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>0.8802604079246521</v>
-      </c>
       <c r="H15" t="n">
-        <v>0.8750883340835571</v>
+        <v>0.8797307312488556</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8705005943775177</v>
+        <v>0.8746517896652222</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.8738219439983368</v>
       </c>
     </row>
     <row r="16">
@@ -1061,34 +1080,35 @@
           <t>片岡 弓澄</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
         <is>
           <t>品質保証時間と工場間搬送を考慮した多目的マルチファクトリー・スケジューリング</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>有馬 澄佳</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>吉瀬 章子</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>繁野 麻衣子</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>0.8758189976215363</v>
-      </c>
       <c r="H16" t="n">
-        <v>0.868594616651535</v>
+        <v>0.87470942735672</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8643146753311157</v>
+        <v>0.8685945868492126</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.8665327131748199</v>
       </c>
     </row>
     <row r="17">
@@ -1102,34 +1122,35 @@
           <t>渡邊 悠義</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
         <is>
           <t>自律性モデルに基づくゲーミフィケーションによる安全行動変容</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>秋山 英三</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>上市 秀雄</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>澤 亮治</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>秋山 英三</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>0.8586437702178955</v>
-      </c>
       <c r="H17" t="n">
-        <v>0.8549792468547821</v>
+        <v>0.8568488657474518</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8542279303073883</v>
+        <v>0.856229156255722</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.8532317876815796</v>
       </c>
     </row>
     <row r="18">
@@ -1143,34 +1164,35 @@
           <t>小澤 陽樹</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
         <is>
           <t>確率的最適化による高次元交互作用スパースモデリング~Factorization Machines の発展形態</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>高野 祐一</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>有馬 澄佳</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Phung-Duc Tuan</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>0.8756991922855377</v>
-      </c>
       <c r="H18" t="n">
-        <v>0.8693470358848572</v>
+        <v>0.8732324242591858</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8683551251888275</v>
+        <v>0.8712161481380463</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.8679117560386658</v>
       </c>
     </row>
     <row r="19">
@@ -1184,34 +1206,35 @@
           <t>安田 朗</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
         <is>
           <t>画像と生体計測情報に基づくアクティブラーニングと業務管理</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>イリチュ 美佳</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>岡田 幸彦</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>0.8647384345531464</v>
+          <t>有馬 澄佳</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>川島 宏一</t>
+        </is>
       </c>
       <c r="H19" t="n">
-        <v>0.863351970911026</v>
+        <v>0.8637226223945618</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8614735007286072</v>
+        <v>0.8616419732570648</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.8606040477752686</v>
       </c>
     </row>
     <row r="20">
@@ -1225,34 +1248,35 @@
           <t>古山 雄晟</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
         <is>
           <t>単独と集団を区別したライドシェアモデルにおけるゲーム理論的解析</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>澤 亮治</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>和田 健太郎</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>Phung-Duc Tuan</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>0.8822426795959473</v>
-      </c>
       <c r="H20" t="n">
-        <v>0.8785499632358551</v>
+        <v>0.8796173334121704</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8663559854030609</v>
+        <v>0.8772620558738708</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.8653758466243744</v>
       </c>
     </row>
     <row r="21">
@@ -1266,34 +1290,35 @@
           <t>関田 千隼</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
         <is>
           <t>異なる容量を持つ複数システムの負荷分散</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Phung-Duc Tuan</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>吉瀬 章子</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>有馬 澄佳</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>0.8621286451816559</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>高野 祐一</t>
+        </is>
       </c>
       <c r="H21" t="n">
-        <v>0.8556958138942719</v>
+        <v>0.8639067411422729</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8524525165557861</v>
+        <v>0.8556961417198181</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.8522175550460815</v>
       </c>
     </row>
     <row r="22">
@@ -1307,34 +1332,35 @@
           <t>位曼曼</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
         <is>
           <t>歩車共存空間における歩行者の移動モデルの構築</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>鈴木 勉</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>渡邉 俊</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>浦田淳司</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>0.8789417147636414</v>
-      </c>
       <c r="H22" t="n">
-        <v>0.8760956525802612</v>
+        <v>0.8829725384712219</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8733214735984802</v>
+        <v>0.8760957717895508</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.875944197177887</v>
       </c>
     </row>
     <row r="23">
@@ -1348,34 +1374,35 @@
           <t>三輪 珠嶺</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
         <is>
           <t>骨格に基づく行動認識における関節角の導入</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>牛島 光一</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>佐野 幸恵</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>黒瀬 雄大</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>0.8591337203979492</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>有馬 澄佳</t>
+        </is>
       </c>
       <c r="H23" t="n">
-        <v>0.8517081737518311</v>
+        <v>0.8582464456558228</v>
       </c>
       <c r="I23" t="n">
-        <v>0.851422518491745</v>
+        <v>0.8524556457996368</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.8519751727581024</v>
       </c>
     </row>
     <row r="24">
@@ -1389,34 +1416,35 @@
           <t>加口 貴美子</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
         <is>
           <t>日本における男女の賃金格差の推移</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>上市 秀雄</t>
-        </is>
-      </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>イリチュ 美佳</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t>川島 宏一</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>イリチュ 美佳</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>0.8527723550796509</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>作道 真理</t>
+        </is>
       </c>
       <c r="H24" t="n">
-        <v>0.8512894809246063</v>
+        <v>0.8524296581745148</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8512190282344818</v>
+        <v>0.8512897491455078</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.8504915237426758</v>
       </c>
     </row>
     <row r="25">
@@ -1430,34 +1458,35 @@
           <t>田之口 輝毅</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
         <is>
           <t>SNS上のESGセンチメント</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>佐野 幸恵</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>上市 秀雄</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>高野 祐一</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>0.870673805475235</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>牛島 光一</t>
+        </is>
       </c>
       <c r="H25" t="n">
-        <v>0.8638855218887329</v>
+        <v>0.8711104691028595</v>
       </c>
       <c r="I25" t="n">
-        <v>0.8618720471858978</v>
+        <v>0.8644375801086426</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.8598762452602386</v>
       </c>
     </row>
     <row r="26">
@@ -1471,34 +1500,35 @@
           <t>笹井 大</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
         <is>
           <t>ESG関連インデックスと株式市場</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>秋山 英三</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>黒瀬 雄大</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>高野 祐一</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>0.8637948632240295</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>牛島 光一</t>
+        </is>
       </c>
       <c r="H26" t="n">
-        <v>0.8582093119621277</v>
+        <v>0.8609839081764221</v>
       </c>
       <c r="I26" t="n">
-        <v>0.8576047420501709</v>
+        <v>0.8582097887992859</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.8581588268280029</v>
       </c>
     </row>
     <row r="27">
@@ -1512,34 +1542,35 @@
           <t>水越 知弘</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
         <is>
           <t>介護が労働に与える影響</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>上市 秀雄</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>川島 宏一</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
         <is>
           <t>岡田 幸彦</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>川島 宏一</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>0.860337495803833</v>
-      </c>
       <c r="H27" t="n">
-        <v>0.8578143715858459</v>
+        <v>0.8587647974491119</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8570152521133423</v>
+        <v>0.8570154905319214</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.8559012115001678</v>
       </c>
     </row>
     <row r="28">
@@ -1553,34 +1584,35 @@
           <t>鈴木 優梨歌</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
         <is>
           <t>複数工場間の経路最適化を含む多目的マルチファクトリー・スケジューリング</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>有馬 澄佳</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>吉瀬 章子</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>繁野 麻衣子</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>0.875244528055191</v>
-      </c>
       <c r="H28" t="n">
-        <v>0.8709458112716675</v>
+        <v>0.8741349875926971</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8659380078315735</v>
+        <v>0.8709458708763123</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.8681559562683105</v>
       </c>
     </row>
     <row r="29">
@@ -1594,34 +1626,35 @@
           <t>永井 康友</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
         <is>
           <t>品質検査レイヤーを横断した異常原因探索～画像マルチモーダルアプローチ</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>有馬 澄佳</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>牛島 光一</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>高野 祐一</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>0.8728594481945038</v>
-      </c>
       <c r="H29" t="n">
-        <v>0.8667238354682922</v>
+        <v>0.8854928612709045</v>
       </c>
       <c r="I29" t="n">
-        <v>0.8625471591949463</v>
+        <v>0.8639019131660461</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.8634551465511322</v>
       </c>
     </row>
     <row r="30">
@@ -1635,34 +1668,35 @@
           <t>戴 家成</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
         <is>
           <t>機械サーバと人間サーバが混在するサービスシステムの性能解析</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Phung-Duc Tuan</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>川島 宏一</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
         <is>
           <t>岡田 幸彦</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>川島 宏一</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>0.8834348917007446</v>
-      </c>
       <c r="H30" t="n">
-        <v>0.8568965196609497</v>
+        <v>0.8844201862812042</v>
       </c>
       <c r="I30" t="n">
-        <v>0.8559956848621368</v>
+        <v>0.855995774269104</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.8549236655235291</v>
       </c>
     </row>
     <row r="31">
@@ -1676,34 +1710,35 @@
           <t>神野 大地</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
         <is>
           <t>東京証券取引所によるPBR改善要請の影響は企業特性によって異なるか？</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>黒瀬 雄大</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>秋山 英三</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>黒瀬 雄大</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>有田 智一</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>0.8618855476379395</v>
-      </c>
       <c r="H31" t="n">
-        <v>0.859070360660553</v>
+        <v>0.8590705394744873</v>
       </c>
       <c r="I31" t="n">
-        <v>0.8540639877319336</v>
+        <v>0.8586951196193695</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.8542488515377045</v>
       </c>
     </row>
     <row r="32">
@@ -1717,34 +1752,35 @@
           <t>LU SICHEN</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
         <is>
           <t>四川大震災についての地元住民の記憶とその変容—汶川県映秀鎮と北川県を比較して—</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>川島 宏一</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>甲斐田 直子</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>佐野 幸恵</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>0.8575132787227631</v>
-      </c>
       <c r="H32" t="n">
-        <v>0.8523842990398407</v>
+        <v>0.857513427734375</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8516227602958679</v>
+        <v>0.8518452942371368</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.851026713848114</v>
       </c>
     </row>
     <row r="33">
@@ -1758,34 +1794,35 @@
           <t>石川 夏帆</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
         <is>
           <t>多様な主体が関わる出産祝いによる産後家庭アウトリーチの実態と課題－横浜市戸塚区の認定NPO法人こまちぷらすのウェルカムベビープロジェクトに着目して－</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>佐野 幸恵</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>甲斐田 直子</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
         <is>
           <t>川島 宏一</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>甲斐田 直子</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
-        <v>0.8604608178138733</v>
-      </c>
       <c r="H33" t="n">
-        <v>0.857774019241333</v>
+        <v>0.8624968230724335</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8568276166915894</v>
+        <v>0.8579479455947876</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.8577743470668793</v>
       </c>
     </row>
     <row r="34">
@@ -1799,34 +1836,35 @@
           <t>鳩貝 優太</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
         <is>
           <t>カフェ型居場所の開設・運営プロセスにおける障壁と支援に関する研究－認定NPO法人こまちぷらすの講座に着目して－</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>雨宮 護</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>川島 宏一</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>山本 幸子</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>0.8634569942951202</v>
-      </c>
       <c r="H34" t="n">
-        <v>0.8626150786876678</v>
+        <v>0.8634571433067322</v>
       </c>
       <c r="I34" t="n">
-        <v>0.8595910668373108</v>
+        <v>0.8626152873039246</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.8595913052558899</v>
       </c>
     </row>
     <row r="35">
@@ -1840,34 +1878,35 @@
           <t>畑 颯汰</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
         <is>
           <t>斜面住宅地の存続可能性に関する研究 －段差解消のための共有財の維持管理に着目して－</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>山本 幸子</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>有田 智一</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>山本 幸子</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>渡邉 俊</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>0.8803417384624481</v>
-      </c>
       <c r="H35" t="n">
-        <v>0.8801652789115906</v>
+        <v>0.8801654279232025</v>
       </c>
       <c r="I35" t="n">
-        <v>0.874545156955719</v>
+        <v>0.8784414529800415</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.8745454549789429</v>
       </c>
     </row>
     <row r="36">
@@ -1881,34 +1920,35 @@
           <t>石田 悠人</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
         <is>
           <t>公園の農的利用の効果と課題に関する研究</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>太田 充</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>牛島 光一</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>鈴木 勉</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>0.8759260773658752</v>
-      </c>
       <c r="H36" t="n">
-        <v>0.8738081753253937</v>
+        <v>0.875926673412323</v>
       </c>
       <c r="I36" t="n">
-        <v>0.86777064204216</v>
+        <v>0.8731176853179932</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.8701472282409668</v>
       </c>
     </row>
     <row r="37">
@@ -1922,34 +1962,35 @@
           <t>高橋 慧</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
         <is>
           <t>地方自治体における統計的因果推論に基づく政策分析の適用方法に関する研究</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>川島 宏一</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>牛島 光一</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>太田 充</t>
-        </is>
-      </c>
-      <c r="G37" t="n">
-        <v>0.8812137842178345</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>鈴木 勉</t>
+        </is>
       </c>
       <c r="H37" t="n">
-        <v>0.877947211265564</v>
+        <v>0.8812141716480255</v>
       </c>
       <c r="I37" t="n">
-        <v>0.8733144998550415</v>
+        <v>0.8785417377948761</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.8743589520454407</v>
       </c>
     </row>
     <row r="38">
@@ -1963,34 +2004,35 @@
           <t>酒井 佑</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
         <is>
           <t>地域外の人材を対象とした逆指名による創業支援制度の運用実態と他地域展開の可能性に関する研究</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>山本 幸子</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>川島 宏一</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>渡邉 俊</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>0.8687264919281006</v>
-      </c>
       <c r="H38" t="n">
-        <v>0.8683316707611084</v>
+        <v>0.8687264025211334</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8629849255084991</v>
+        <v>0.8683319687843323</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.8629851043224335</v>
       </c>
     </row>
     <row r="39">
@@ -2004,34 +2046,35 @@
           <t>佐藤 佳乃</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
         <is>
           <t>地籍調査の進捗に関する地理空間分析</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>鈴木 勉</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>川島 宏一</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>有田 智一</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
-        <v>0.8841173052787781</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>渡邉 俊</t>
+        </is>
       </c>
       <c r="H39" t="n">
-        <v>0.8798267543315887</v>
+        <v>0.8869522213935852</v>
       </c>
       <c r="I39" t="n">
-        <v>0.8790417909622192</v>
+        <v>0.8798271715641022</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.8780929744243622</v>
       </c>
     </row>
     <row r="40">
@@ -2045,34 +2088,35 @@
           <t>早坂 遼</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
         <is>
           <t>羽田空港新飛行経路の運用開始が東京都心の不動産価値に与えた影響に関する計量分析</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>鈴木 勉</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>堤 盛人</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>太田 充</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>鈴木 勉</t>
-        </is>
-      </c>
-      <c r="G40" t="n">
-        <v>0.8836487531661987</v>
-      </c>
       <c r="H40" t="n">
-        <v>0.8805907964706421</v>
+        <v>0.8817869424819946</v>
       </c>
       <c r="I40" t="n">
-        <v>0.8768987655639648</v>
+        <v>0.8813001811504364</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.8805910348892212</v>
       </c>
     </row>
     <row r="41">
@@ -2086,34 +2130,35 @@
           <t>釜谷 紘生</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
         <is>
           <t>マニラ都市圏における洪水リスクが不動産価格に与える影響の分析</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>堤 盛人</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>川島 宏一</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>太田 充</t>
-        </is>
-      </c>
-      <c r="G41" t="n">
-        <v>0.8722112476825714</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>鈴木 勉</t>
+        </is>
       </c>
       <c r="H41" t="n">
-        <v>0.8708103895187378</v>
+        <v>0.8820194900035858</v>
       </c>
       <c r="I41" t="n">
-        <v>0.8650570511817932</v>
+        <v>0.8708105385303497</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.8667831718921661</v>
       </c>
     </row>
     <row r="42">
@@ -2127,34 +2172,35 @@
           <t>市川 はるひ</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
         <is>
           <t>冒険遊び場における犯罪被害と運営者の対応の実態解明</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>雨宮 護</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>川島 宏一</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>上市 秀雄</t>
-        </is>
-      </c>
-      <c r="G42" t="n">
-        <v>0.8621284961700439</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>浦田淳司</t>
+        </is>
       </c>
       <c r="H42" t="n">
-        <v>0.8617660105228424</v>
+        <v>0.8621288537979126</v>
       </c>
       <c r="I42" t="n">
-        <v>0.8482773900032043</v>
+        <v>0.8617662489414215</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.8502079844474792</v>
       </c>
     </row>
     <row r="43">
@@ -2168,34 +2214,35 @@
           <t>舩戸 祐汰</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
         <is>
           <t>屋外着座空間への評価と独り好き志向性との関係</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>渡邉 俊</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>堤 盛人</t>
-        </is>
-      </c>
       <c r="F43" t="inlineStr">
         <is>
           <t>鈴木 勉</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>0.8732399344444275</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>雨宮 護</t>
+        </is>
       </c>
       <c r="H43" t="n">
-        <v>0.8674529492855072</v>
+        <v>0.8732402920722961</v>
       </c>
       <c r="I43" t="n">
-        <v>0.8664050698280334</v>
+        <v>0.8673423230648041</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.865800529718399</v>
       </c>
     </row>
     <row r="44">
@@ -2209,34 +2256,35 @@
           <t>廣田 華</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
         <is>
           <t>農村舞台の現状とその保全—ハード・ソフトの両面に着目して—</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>川島 宏一</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>藤川 昌樹</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>雨宮 護</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>0.8610953688621521</v>
-      </c>
       <c r="H44" t="n">
-        <v>0.8599761724472046</v>
+        <v>0.861095666885376</v>
       </c>
       <c r="I44" t="n">
-        <v>0.8588990569114685</v>
+        <v>0.8600713014602661</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.8588992655277252</v>
       </c>
     </row>
     <row r="45">
@@ -2250,34 +2298,35 @@
           <t>陳 泓儒</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
         <is>
           <t>ディープラーニングに基づく武漢の都市イメージの空間構造と都市計画実施に関する研究</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>渡邉 俊</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>藤川 昌樹</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>松原 康介</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>0.8848139941692352</v>
-      </c>
       <c r="H45" t="n">
-        <v>0.884646475315094</v>
+        <v>0.8848140835762024</v>
       </c>
       <c r="I45" t="n">
-        <v>0.881379634141922</v>
+        <v>0.884340912103653</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.8809525370597839</v>
       </c>
     </row>
     <row r="46">
@@ -2291,34 +2340,35 @@
           <t>坂本 怜奈</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
         <is>
           <t>地域ネットワークにおける中間支援組織の役割とマネジメントシステムの構築に関する考察</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>鈴木 勉</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>八森 正泰</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>山本 幸子</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>0.8624057769775391</v>
-      </c>
       <c r="H46" t="n">
-        <v>0.8623030185699463</v>
+        <v>0.8637301623821259</v>
       </c>
       <c r="I46" t="n">
-        <v>0.8606868982315063</v>
+        <v>0.861213207244873</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.8606871068477631</v>
       </c>
     </row>
     <row r="47">
@@ -2332,34 +2382,35 @@
           <t>佐々木 智哉</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
         <is>
           <t>都市再生緊急整備地域における都市再生の政策効果の検証ー地方中核都市の事例を対象として</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>川島 宏一</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>太田 充</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>牛島 光一</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>0.8822456002235413</v>
-      </c>
       <c r="H47" t="n">
-        <v>0.8808680772781372</v>
+        <v>0.8822457790374756</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8808214664459229</v>
+        <v>0.8808684349060059</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.8796663284301758</v>
       </c>
     </row>
     <row r="48">
@@ -2373,34 +2424,35 @@
           <t>髙野 駿</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
         <is>
           <t>観光都市におけるオーバーツーリズムの対策やそれに伴う効果と課題について</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>岡本 直久</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>牛島 光一</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>川島 宏一</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>0.8762213587760925</v>
-      </c>
       <c r="H48" t="n">
-        <v>0.8661500513553619</v>
+        <v>0.876221776008606</v>
       </c>
       <c r="I48" t="n">
-        <v>0.865595281124115</v>
+        <v>0.8687419593334198</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.8655959069728851</v>
       </c>
     </row>
     <row r="49">
@@ -2414,34 +2466,35 @@
           <t>高橋 梨沙子</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
         <is>
           <t>観光地における駅舎建築に関する研究</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>岡本 直久</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>藤川 昌樹</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>渡邉 俊</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>0.8662874400615692</v>
-      </c>
       <c r="H49" t="n">
-        <v>0.8649430572986603</v>
+        <v>0.8662878572940826</v>
       </c>
       <c r="I49" t="n">
-        <v>0.8645971715450287</v>
+        <v>0.8646083772182465</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.8645975291728973</v>
       </c>
     </row>
     <row r="50">
@@ -2455,34 +2508,35 @@
           <t>小松 諒治</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
         <is>
           <t>地域公共交通サービス変化時の活動機会変化の計測に関する研究</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>鈴木 勉</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
         <is>
           <t>岡本 直久</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>鈴木 勉</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>和田 健太郎</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v>0.8805746138095856</v>
-      </c>
       <c r="H50" t="n">
-        <v>0.8783849775791168</v>
+        <v>0.8832988440990448</v>
       </c>
       <c r="I50" t="n">
-        <v>0.8773877024650574</v>
+        <v>0.8805749118328094</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.8780884146690369</v>
       </c>
     </row>
     <row r="51">
@@ -2496,34 +2550,35 @@
           <t>佐光 未帆</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
         <is>
           <t>大学敷地内における大学生の犯罪被害の実態と報告行動の解明</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>雨宮 護</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>川島 宏一</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>有田 智一</t>
-        </is>
-      </c>
-      <c r="G51" t="n">
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>浦田淳司</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
         <v>0.8623651266098022</v>
       </c>
-      <c r="H51" t="n">
-        <v>0.8559722304344177</v>
-      </c>
       <c r="I51" t="n">
-        <v>0.8509646058082581</v>
+        <v>0.8559726178646088</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.8511845171451569</v>
       </c>
     </row>
     <row r="52">
@@ -2537,34 +2592,35 @@
           <t>Tang Xinyu</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
         <is>
           <t>職住近接と生活域の拡がりとの関連：GPSデータを用いた検討</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>鈴木 勉</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
         <is>
           <t>牛島 光一</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>川島 宏一</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>鈴木 勉</t>
-        </is>
-      </c>
-      <c r="G52" t="n">
-        <v>0.8601007461547852</v>
-      </c>
       <c r="H52" t="n">
-        <v>0.8564839959144592</v>
+        <v>0.8600000441074371</v>
       </c>
       <c r="I52" t="n">
-        <v>0.8554676175117493</v>
+        <v>0.8592597246170044</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.8564842045307159</v>
       </c>
     </row>
     <row r="53">
@@ -2578,34 +2634,35 @@
           <t>田上 朋樹</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
         <is>
           <t>人口再配分による食料需給バランス改善への試案 ー「地域で食料が自給できる国土」への視座－</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>牛島 光一</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>太田 充</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>甲斐田 直子</t>
-        </is>
-      </c>
-      <c r="G53" t="n">
-        <v>0.8770770728588104</v>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>鈴木 勉</t>
+        </is>
       </c>
       <c r="H53" t="n">
-        <v>0.8713474571704865</v>
+        <v>0.8757403492927551</v>
       </c>
       <c r="I53" t="n">
-        <v>0.8681096136569977</v>
+        <v>0.8713475465774536</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.8705988526344299</v>
       </c>
     </row>
     <row r="54">
@@ -2619,34 +2676,35 @@
           <t>矢橋 敦之</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
         <is>
           <t>都市サービスの長期的な入れ替わりの実態 －2002年と2022年の２時点比較－</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>鈴木 勉</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>堤 盛人</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>川島 宏一</t>
         </is>
       </c>
-      <c r="G54" t="n">
-        <v>0.8658909201622009</v>
-      </c>
       <c r="H54" t="n">
-        <v>0.8628571033477783</v>
+        <v>0.866838663816452</v>
       </c>
       <c r="I54" t="n">
-        <v>0.859155535697937</v>
+        <v>0.8634084463119507</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.8591557145118713</v>
       </c>
     </row>
     <row r="55">
@@ -2660,34 +2718,35 @@
           <t>松浦 海斗</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
         <is>
           <t>子どもの体験格差の全国横断的把握 ―学校外での生活行動に着目して－</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>牛島 光一</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>太田 充</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
         <is>
           <t>甲斐田 直子</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>太田 充</t>
-        </is>
-      </c>
-      <c r="G55" t="n">
-        <v>0.8445272445678711</v>
-      </c>
       <c r="H55" t="n">
-        <v>0.8444041013717651</v>
+        <v>0.8447581827640533</v>
       </c>
       <c r="I55" t="n">
-        <v>0.8435719907283783</v>
+        <v>0.8435723483562469</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.8434951603412628</v>
       </c>
     </row>
     <row r="56">
@@ -2701,34 +2760,35 @@
           <t>稲葉 翔太</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
         <is>
           <t>シェアサイクル運営者の機会損失改善に向けた自転車再配置における調整台数の検討-茨城県つくば市を事例として-</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>岡本 直久</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>和田 健太郎</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>川島 宏一</t>
-        </is>
-      </c>
-      <c r="G56" t="n">
-        <v>0.8806580901145935</v>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>鈴木 勉</t>
+        </is>
       </c>
       <c r="H56" t="n">
-        <v>0.8783487677574158</v>
+        <v>0.8806582093238831</v>
       </c>
       <c r="I56" t="n">
-        <v>0.8719048500061035</v>
+        <v>0.87824946641922</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.8735233545303345</v>
       </c>
     </row>
     <row r="57">
@@ -2742,34 +2802,35 @@
           <t>三重野 馨</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
         <is>
           <t>アルジェリアにおけるフェルナン・プイヨンのツーリスト・コンプレックスに関する研究</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>上市 秀雄</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>岡田 幸彦</t>
-        </is>
-      </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
-        </is>
-      </c>
-      <c r="G57" t="n">
-        <v>0.8443306088447571</v>
+          <t>甲斐田 直子</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>松原 康介</t>
+        </is>
       </c>
       <c r="H57" t="n">
-        <v>0.8426340222358704</v>
+        <v>0.8431252539157867</v>
       </c>
       <c r="I57" t="n">
-        <v>0.842244029045105</v>
+        <v>0.841835081577301</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.8402625322341919</v>
       </c>
     </row>
     <row r="58">
@@ -2783,34 +2844,35 @@
           <t>犬竹 智哉</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
         <is>
           <t>商用FCVの普及に向けた水素ステーション配置とCO2排出量の予測</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>和田 健太郎</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>鈴木 勉</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
         <is>
           <t>牛島 光一</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>和田 健太郎</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>甲斐田 直子</t>
-        </is>
-      </c>
-      <c r="G58" t="n">
-        <v>0.8724230825901031</v>
-      </c>
       <c r="H58" t="n">
-        <v>0.8723960220813751</v>
+        <v>0.8711833655834198</v>
       </c>
       <c r="I58" t="n">
-        <v>0.8698239922523499</v>
+        <v>0.8702839612960815</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.8700035214424133</v>
       </c>
     </row>
     <row r="59">
@@ -2824,34 +2886,35 @@
           <t>日高 優一</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
         <is>
           <t>基幹交通の組み合わせ利用を考慮した将来交通需要予測に関する研究</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>岡本 直久</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>和田 健太郎</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>Phung-Duc Tuan</t>
         </is>
       </c>
-      <c r="G59" t="n">
-        <v>0.8817898035049438</v>
-      </c>
       <c r="H59" t="n">
-        <v>0.8764763474464417</v>
+        <v>0.8817901909351349</v>
       </c>
       <c r="I59" t="n">
-        <v>0.8761445879936218</v>
+        <v>0.8766685426235199</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0.8756954669952393</v>
       </c>
     </row>
     <row r="60">
@@ -2865,34 +2928,35 @@
           <t>鎌田 晴人</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
         <is>
           <t>ETC2.0プローブデータを活用した旅行時間信頼性の時空間的評価</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>鈴木 勉</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
         <is>
           <t>黒瀬 雄大</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>鈴木 勉</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>川島 宏一</t>
         </is>
       </c>
-      <c r="G60" t="n">
-        <v>0.8743581771850586</v>
-      </c>
       <c r="H60" t="n">
-        <v>0.8707766830921173</v>
+        <v>0.8746653497219086</v>
       </c>
       <c r="I60" t="n">
-        <v>0.8681854009628296</v>
+        <v>0.8743585646152496</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0.8681853413581848</v>
       </c>
     </row>
     <row r="61">
@@ -2906,34 +2970,35 @@
           <t>畑山 公希</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
         <is>
           <t>自治体におけるグリーンインフラの計画的展開を阻害する要因についての研究</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>甲斐田 直子</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>川島 宏一</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>牛島 光一</t>
         </is>
       </c>
-      <c r="G61" t="n">
-        <v>0.8797598779201508</v>
-      </c>
       <c r="H61" t="n">
-        <v>0.8760296702384949</v>
+        <v>0.8799072802066803</v>
       </c>
       <c r="I61" t="n">
-        <v>0.8728485107421875</v>
+        <v>0.8760299980640411</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.874200314283371</v>
       </c>
     </row>
     <row r="62">
@@ -2947,34 +3012,35 @@
           <t>張 宇星</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
         <is>
           <t>清代における祭祀行宮の構成と変容—龍王廟を中心に—</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>鈴木 勉</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>川島 宏一</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>澤 亮治</t>
-        </is>
-      </c>
-      <c r="G62" t="n">
-        <v>0.8302420377731323</v>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>村上 暁信</t>
+        </is>
       </c>
       <c r="H62" t="n">
-        <v>0.8261329233646393</v>
+        <v>0.8276545107364655</v>
       </c>
       <c r="I62" t="n">
-        <v>0.8258852362632751</v>
+        <v>0.8261333703994751</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0.8256785571575165</v>
       </c>
     </row>
     <row r="63">
@@ -2988,34 +3054,35 @@
           <t>森下 陽平</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
         <is>
           <t>騒音問題と自己観の関係性：日本・カナダ比較研究</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>川島 宏一</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
         <is>
           <t>甲斐田 直子</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>川島 宏一</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>佐野 幸恵</t>
         </is>
       </c>
-      <c r="G63" t="n">
-        <v>0.8613004684448242</v>
-      </c>
       <c r="H63" t="n">
-        <v>0.8604451417922974</v>
+        <v>0.8604455292224884</v>
       </c>
       <c r="I63" t="n">
-        <v>0.8575851023197174</v>
+        <v>0.8598350286483765</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0.8570573925971985</v>
       </c>
     </row>
     <row r="64">
@@ -3029,34 +3096,35 @@
           <t>平林 優希</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
         <is>
           <t>環境配慮意識・行動の自他評価の特性と行動意図の関係</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>甲斐田 直子</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>谷口 綾子</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
         <is>
           <t>澤 亮治</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>牛島 光一</t>
-        </is>
-      </c>
-      <c r="G64" t="n">
-        <v>0.8834516704082489</v>
-      </c>
       <c r="H64" t="n">
-        <v>0.8635225594043732</v>
+        <v>0.8832572996616364</v>
       </c>
       <c r="I64" t="n">
-        <v>0.861113429069519</v>
+        <v>0.8624671101570129</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0.8614659905433655</v>
       </c>
     </row>
     <row r="65">
@@ -3070,34 +3138,35 @@
           <t>中澤 光希</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
         <is>
           <t>都市再生特別地区において多様化する域外貢献の実態と課題に関する研究</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>渡邉 俊</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>有田 智一</t>
-        </is>
-      </c>
       <c r="F65" t="inlineStr">
         <is>
           <t>川島 宏一</t>
         </is>
       </c>
-      <c r="G65" t="n">
-        <v>0.8763948678970337</v>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>太田 充</t>
+        </is>
       </c>
       <c r="H65" t="n">
-        <v>0.8742632567882538</v>
+        <v>0.8763948380947113</v>
       </c>
       <c r="I65" t="n">
-        <v>0.8731103539466858</v>
+        <v>0.8731106519699097</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0.8720406591892242</v>
       </c>
     </row>
     <row r="66">
@@ -3111,34 +3180,35 @@
           <t>草田 弦喜</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
         <is>
           <t>銀座ルールと比較した『日本橋らしさ』に関する研究-東京都日本橋地区を対象として-</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>鈴木 勉</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>川島 宏一</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>渡邉 俊</t>
         </is>
       </c>
-      <c r="G66" t="n">
-        <v>0.8665132522583008</v>
-      </c>
       <c r="H66" t="n">
-        <v>0.865460216999054</v>
+        <v>0.8690553307533264</v>
       </c>
       <c r="I66" t="n">
-        <v>0.8637251555919647</v>
+        <v>0.8654606640338898</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0.8637252748012543</v>
       </c>
     </row>
     <row r="67">
@@ -3152,34 +3222,35 @@
           <t>加藤 優弥</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
         <is>
           <t>スタジアム・アリーナの多機能化に伴う公民連携によるエリアマネジメントに関する研究</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>渡邉 俊</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>有田 智一</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>川島 宏一</t>
         </is>
       </c>
-      <c r="G67" t="n">
-        <v>0.8704355359077454</v>
-      </c>
       <c r="H67" t="n">
-        <v>0.8700940907001495</v>
+        <v>0.8704354465007782</v>
       </c>
       <c r="I67" t="n">
-        <v>0.8686460256576538</v>
+        <v>0.8688648343086243</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0.868646115064621</v>
       </c>
     </row>
     <row r="68">
@@ -3193,34 +3264,35 @@
           <t>水野 瑛介</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
         <is>
           <t>メジャーリーグにおける統計的差別と選好的差別</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>秋山 英三</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>上市 秀雄</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>澤 亮治</t>
         </is>
       </c>
-      <c r="G68" t="n">
-        <v>0.8532232940196991</v>
-      </c>
       <c r="H68" t="n">
-        <v>0.8512569069862366</v>
+        <v>0.8518877029418945</v>
       </c>
       <c r="I68" t="n">
-        <v>0.8432158231735229</v>
+        <v>0.8515320122241974</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0.8441035449504852</v>
       </c>
     </row>
     <row r="69">
@@ -3234,34 +3306,35 @@
           <t>山縣 力也</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
         <is>
           <t>非罰則規制の犯罪波及効果：渋谷区の路上飲酒禁止条例を事例として</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>牛島 光一</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
         <is>
           <t>秋山 英三</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>牛島 光一</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>岡田 幸彦</t>
-        </is>
-      </c>
-      <c r="G69" t="n">
-        <v>0.8667273223400116</v>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>堤 盛人</t>
+        </is>
       </c>
       <c r="H69" t="n">
-        <v>0.8648608326911926</v>
+        <v>0.8769175112247467</v>
       </c>
       <c r="I69" t="n">
-        <v>0.8611282706260681</v>
+        <v>0.8631938695907593</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.8606486618518829</v>
       </c>
     </row>
     <row r="70">
@@ -3275,34 +3348,35 @@
           <t>青木 日花</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
         <is>
           <t>アメニティに着目した価値あるオフィスビルの要因分析と効果検証</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>川島 宏一</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>牛島 光一</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
         <is>
           <t>堤 盛人</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>牛島 光一</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>川島 宏一</t>
-        </is>
-      </c>
-      <c r="G70" t="n">
-        <v>0.8745879828929901</v>
-      </c>
       <c r="H70" t="n">
-        <v>0.8734760284423828</v>
+        <v>0.872194916009903</v>
       </c>
       <c r="I70" t="n">
-        <v>0.8721945583820343</v>
+        <v>0.8721113204956055</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.8718703091144562</v>
       </c>
     </row>
     <row r="71">
@@ -3316,34 +3390,35 @@
           <t>GAO WENWEN</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
         <is>
           <t>グリーンビルディング認証がJ-REITのパフォーマンスに与える影響の実証分析</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>川島 宏一</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>牛島 光一</t>
-        </is>
-      </c>
       <c r="F71" t="inlineStr">
         <is>
+          <t>原田 信行</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
           <t>甲斐田 直子</t>
         </is>
       </c>
-      <c r="G71" t="n">
-        <v>0.8696559071540833</v>
-      </c>
       <c r="H71" t="n">
-        <v>0.8688324987888336</v>
+        <v>0.8696563243865967</v>
       </c>
       <c r="I71" t="n">
-        <v>0.8680274486541748</v>
+        <v>0.8675041198730469</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0.8670808076858521</v>
       </c>
     </row>
     <row r="72">
@@ -3357,34 +3432,35 @@
           <t>平野 晴也</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
         <is>
           <t>3次元地図更新のための衛星リモートセンシングによる地形計測手法の開発</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>鈴木 勉</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
         <is>
           <t>牛島 光一</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>太田 充</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>鈴木 勉</t>
-        </is>
-      </c>
-      <c r="G72" t="n">
-        <v>0.8609506487846375</v>
-      </c>
       <c r="H72" t="n">
-        <v>0.8593294322490692</v>
+        <v>0.8607411086559296</v>
       </c>
       <c r="I72" t="n">
-        <v>0.8565827012062073</v>
+        <v>0.8596481382846832</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.859329879283905</v>
       </c>
     </row>
     <row r="73">
@@ -3398,34 +3474,35 @@
           <t>WEI MIAOHENG</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
         <is>
           <t>往復移動と滞在行動を考慮したバス頻度問題</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>鈴木 勉</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
         <is>
           <t>和田 健太郎</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>岡本 直久</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>鈴木 勉</t>
-        </is>
-      </c>
-      <c r="G73" t="n">
-        <v>0.8722727000713348</v>
-      </c>
       <c r="H73" t="n">
-        <v>0.8718544840812683</v>
+        <v>0.8742718994617462</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8710868656635284</v>
+        <v>0.871936708688736</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.8718547224998474</v>
       </c>
     </row>
     <row r="74">
@@ -3439,34 +3516,35 @@
           <t>田村 侑介</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
         <is>
           <t>共同住宅におけるEV充電器設置の意思決定メカニズムの解析</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>浦田淳司</t>
-        </is>
-      </c>
       <c r="E74" t="inlineStr">
         <is>
+          <t>鈴木 勉</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
           <t>牛島 光一</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>川島 宏一</t>
         </is>
       </c>
-      <c r="G74" t="n">
-        <v>0.873863160610199</v>
-      </c>
       <c r="H74" t="n">
-        <v>0.8721547722816467</v>
+        <v>0.871593713760376</v>
       </c>
       <c r="I74" t="n">
-        <v>0.8709360361099243</v>
+        <v>0.8709504902362823</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.8709365725517273</v>
       </c>
     </row>
     <row r="75">
@@ -3480,34 +3558,35 @@
           <t>山田 圭祐</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
         <is>
           <t>ミクロ交通シミュレーション利用における機械学習モデルの有効性検討</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>鈴木 勉</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Phung-Duc Tuan</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
         <is>
           <t>和田 健太郎</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Phung-Duc Tuan</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>牛島 光一</t>
-        </is>
-      </c>
-      <c r="G75" t="n">
-        <v>0.8804770112037659</v>
-      </c>
       <c r="H75" t="n">
-        <v>0.880375862121582</v>
+        <v>0.8804835975170135</v>
       </c>
       <c r="I75" t="n">
-        <v>0.8761859536170959</v>
+        <v>0.879767507314682</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.8787780106067657</v>
       </c>
     </row>
     <row r="76">
@@ -3521,34 +3600,35 @@
           <t>平山 裕紀人</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
         <is>
           <t>マクロ交通流理論に基づくグリッドロック現象の分析：タイ・バンコクを対象として</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>Phung-Duc Tuan</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>鈴木 勉</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
         <is>
           <t>和田 健太郎</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>岡本 直久</t>
-        </is>
-      </c>
-      <c r="G76" t="n">
-        <v>0.8619393706321716</v>
-      </c>
       <c r="H76" t="n">
-        <v>0.8587498664855957</v>
+        <v>0.8646460771560669</v>
       </c>
       <c r="I76" t="n">
-        <v>0.8567719459533691</v>
+        <v>0.858845442533493</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.8584804236888885</v>
       </c>
     </row>
     <row r="77">
@@ -3562,34 +3642,35 @@
           <t>桑原 慶太</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
         <is>
           <t>データ同化手法を用いたネットワーク交通流モデルの精度改善及びパラメータ推定</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>鈴木 勉</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
         <is>
           <t>Phung-Duc Tuan</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>八森 正泰</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>和田 健太郎</t>
-        </is>
-      </c>
-      <c r="G77" t="n">
-        <v>0.8736216425895691</v>
-      </c>
       <c r="H77" t="n">
-        <v>0.8723689317703247</v>
+        <v>0.8770518004894257</v>
       </c>
       <c r="I77" t="n">
-        <v>0.8709964752197266</v>
+        <v>0.8737709820270538</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.8715194463729858</v>
       </c>
     </row>
     <row r="78">
@@ -3603,34 +3684,35 @@
           <t>徐 摯恒</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
         <is>
           <t>高速鉄道の開通が都市経済に与える影響の分析</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>太田 充</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>牛島 光一</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>堤 盛人</t>
         </is>
       </c>
-      <c r="G78" t="n">
-        <v>0.8803965449333191</v>
-      </c>
       <c r="H78" t="n">
-        <v>0.8765251040458679</v>
+        <v>0.880396842956543</v>
       </c>
       <c r="I78" t="n">
-        <v>0.8699566125869751</v>
+        <v>0.8773619830608368</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.8741996884346008</v>
       </c>
     </row>
     <row r="79">
@@ -3644,34 +3726,35 @@
           <t>松場 拓海</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
         <is>
           <t>「認識人口」概念の提案とその実態―市町村に対するポジティブ／ネガティブイメージの分析から－</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>牛島 光一</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>鈴木 勉</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>佐野 幸恵</t>
-        </is>
-      </c>
-      <c r="G79" t="n">
-        <v>0.8760635256767273</v>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>甲斐田 直子</t>
+        </is>
       </c>
       <c r="H79" t="n">
-        <v>0.8648145496845245</v>
+        <v>0.8768567442893982</v>
       </c>
       <c r="I79" t="n">
-        <v>0.8647039234638214</v>
+        <v>0.8671047389507294</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.8661922812461853</v>
       </c>
     </row>
     <row r="80">
@@ -3685,34 +3768,35 @@
           <t>馬場 理彰</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
         <is>
           <t>プロサッカーチームのリーグ昇降格が街並みに与える影響</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>牛島 光一</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>太田 充</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>上市 秀雄</t>
-        </is>
-      </c>
-      <c r="G80" t="n">
-        <v>0.8561045527458191</v>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>堤 盛人</t>
+        </is>
       </c>
       <c r="H80" t="n">
-        <v>0.8544396162033081</v>
+        <v>0.8574393689632416</v>
       </c>
       <c r="I80" t="n">
-        <v>0.8523486256599426</v>
+        <v>0.854439914226532</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.8538867235183716</v>
       </c>
     </row>
     <row r="81">
@@ -3726,34 +3810,35 @@
           <t>佐々木 智哉</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
         <is>
           <t>コロナ禍以降のバイク需要の持続的拡大の要因：経験財理論に基づく考察</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>浦田淳司</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>岡本 直久</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
         <is>
           <t>佐野 幸恵</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>岡本 直久</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>浦田淳司</t>
-        </is>
-      </c>
-      <c r="G81" t="n">
-        <v>0.8559110462665558</v>
-      </c>
       <c r="H81" t="n">
-        <v>0.8549920916557312</v>
+        <v>0.8557762801647186</v>
       </c>
       <c r="I81" t="n">
-        <v>0.8521960377693176</v>
+        <v>0.8549925088882446</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0.8544768095016479</v>
       </c>
     </row>
     <row r="82">
@@ -3767,34 +3852,35 @@
           <t>網野 景介</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
         <is>
           <t>M-1グランプリのシグナリング効果：動画再生数への影響</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>佐野 幸恵</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>牛島 光一</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>上市 秀雄</t>
         </is>
       </c>
-      <c r="G82" t="n">
-        <v>0.8549385368824005</v>
-      </c>
       <c r="H82" t="n">
-        <v>0.8530160486698151</v>
+        <v>0.8526224195957184</v>
       </c>
       <c r="I82" t="n">
-        <v>0.850290060043335</v>
+        <v>0.8521039187908173</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0.8483674824237823</v>
       </c>
     </row>
     <row r="83">
@@ -3808,34 +3894,35 @@
           <t>神尾 瑞貴</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
         <is>
           <t>花粉が経済活動に与える影響</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>牛島 光一</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>原田 信行</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>太田 充</t>
-        </is>
-      </c>
-      <c r="G83" t="n">
-        <v>0.8522346019744873</v>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>上市 秀雄</t>
+        </is>
       </c>
       <c r="H83" t="n">
-        <v>0.8515082001686096</v>
+        <v>0.8530831038951874</v>
       </c>
       <c r="I83" t="n">
-        <v>0.8499580323696136</v>
+        <v>0.8515084087848663</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0.8503591418266296</v>
       </c>
     </row>
     <row r="84">
@@ -3849,34 +3936,35 @@
           <t>柳 千宙</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
         <is>
           <t>分布北限域における南方系海洋生物の北上とその認識</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>牛島 光一</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>川島 宏一</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>イリチュ 美佳</t>
         </is>
       </c>
-      <c r="G84" t="n">
-        <v>0.8504597544670105</v>
-      </c>
       <c r="H84" t="n">
-        <v>0.8449654281139374</v>
+        <v>0.8473111093044281</v>
       </c>
       <c r="I84" t="n">
-        <v>0.8425625562667847</v>
+        <v>0.8449656069278717</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0.8399158716201782</v>
       </c>
     </row>
   </sheetData>
@@ -3890,7 +3978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3906,35 +3994,40 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>student_id</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>title</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>teacher_1</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>teacher_2</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>teacher_3</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>score_1</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>score_2</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>score_3</t>
         </is>
@@ -3951,34 +4044,35 @@
           <t>益子颯太</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
         <is>
           <t>摘要欄情報を用いた仕訳データの異常検知モデルの開発</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>イリチュ 美佳</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>高野 祐一</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>上市 秀雄</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>0.863123744726181</v>
-      </c>
       <c r="H2" t="n">
-        <v>0.8607465028762817</v>
+        <v>0.8635274171829224</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8565530180931091</v>
+        <v>0.8589865863323212</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.8573168516159058</v>
       </c>
     </row>
     <row r="3">
@@ -3992,34 +4086,35 @@
           <t>加田昌杜</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
         <is>
           <t>筑波大学学年歴の曜日変更最小化</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>吉瀬 章子</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>八森 正泰</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Phung-Duc Tuan</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>0.8609102368354797</v>
-      </c>
       <c r="H3" t="n">
-        <v>0.8535879254341125</v>
+        <v>0.8609103560447693</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8522591888904572</v>
+        <v>0.8542723953723907</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.8513311147689819</v>
       </c>
     </row>
     <row r="4">
@@ -4033,34 +4128,35 @@
           <t>吉田響</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
         <is>
           <t>中規模学会における発表スケジュール作成モデル</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>吉瀬 章子</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>八森 正泰</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>Phung-Duc Tuan</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>八森 正泰</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>0.8563421368598938</v>
-      </c>
       <c r="H4" t="n">
-        <v>0.8478220701217651</v>
+        <v>0.8563421070575714</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8461341559886932</v>
+        <v>0.8483154773712158</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.8472438752651215</v>
       </c>
     </row>
     <row r="5">
@@ -4074,34 +4170,35 @@
           <t>佐川翼</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
         <is>
           <t>多段階モデルを用いた修士論文発表会スケジューリングシステムの開発</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>吉瀬 章子</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>繁野 麻衣子</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Phung-Duc Tuan</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>0.8748290538787842</v>
-      </c>
       <c r="H5" t="n">
-        <v>0.8628411293029785</v>
+        <v>0.8748292922973633</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8614687025547028</v>
+        <v>0.8656644821166992</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.8607003390789032</v>
       </c>
     </row>
     <row r="6">
@@ -4115,34 +4212,35 @@
           <t>出口達也</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
         <is>
           <t>日本の慢性腎臓病進行症例患者における地域のソーシャルキャピタルが腎機能低下に及ぼす影響の分析</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>川島 宏一</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>上市 秀雄</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>イリチュ 美佳</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>川島 宏一</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>上市 秀雄</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>0.8760460615158081</v>
-      </c>
       <c r="H6" t="n">
-        <v>0.8752140700817108</v>
+        <v>0.8752143979072571</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8724832534790039</v>
+        <v>0.8730534613132477</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.8719890415668488</v>
       </c>
     </row>
     <row r="7">
@@ -4156,34 +4254,35 @@
           <t>川井貫太朗</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
         <is>
           <t>SNSデータを用いた日本の空気感と単語ネットワーク</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>佐野 幸恵</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>上市 秀雄</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>岡田 幸彦</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>0.8824878931045532</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>鈴木 勉</t>
+        </is>
       </c>
       <c r="H7" t="n">
-        <v>0.8651009798049927</v>
+        <v>0.8805915713310242</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8542524576187134</v>
+        <v>0.8642038404941559</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.8563596308231354</v>
       </c>
     </row>
     <row r="8">
@@ -4197,34 +4296,35 @@
           <t>但木陸</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
         <is>
           <t>大学入試業務の人員配置最適化における暗黙知制約の検知と数理モデルの改良</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>吉瀬 章子</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>高野 祐一</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>八森 正泰</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>0.8712438941001892</v>
-      </c>
       <c r="H8" t="n">
-        <v>0.870621383190155</v>
+        <v>0.8712441325187683</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8673335313796997</v>
+        <v>0.8685609400272369</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.8668279051780701</v>
       </c>
     </row>
     <row r="9">
@@ -4238,34 +4338,35 @@
           <t>中山友琉</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
         <is>
           <t>データ分散状況を想定したプライバシー保護ハザード比推定手法の提案</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>川島 宏一</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>岡田 幸彦</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>イリチュ 美佳</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>0.8722023069858551</v>
-      </c>
       <c r="H9" t="n">
-        <v>0.8711291551589966</v>
+        <v>0.8722025752067566</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8628890514373779</v>
+        <v>0.862546294927597</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.8624857068061829</v>
       </c>
     </row>
     <row r="10">
@@ -4279,34 +4380,35 @@
           <t>中本武志</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
         <is>
           <t>パートタイム労働者を主力とするサービス業におけるシフトスケジューリング</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>吉瀬 章子</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>繁野 麻衣子</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>有馬 澄佳</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>繁野 麻衣子</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>0.8638100922107697</v>
-      </c>
       <c r="H10" t="n">
-        <v>0.8521930575370789</v>
+        <v>0.8638104796409607</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8493417203426361</v>
+        <v>0.8519278466701508</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.8515419661998749</v>
       </c>
     </row>
     <row r="11">
@@ -4320,34 +4422,35 @@
           <t>長谷川弘貴</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
         <is>
           <t>生体データにもとづくサービスデータ解析手法の提案</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>イリチュ 美佳</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>岡田 幸彦</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>佐野 幸恵</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>0.8786354064941406</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>大西 正輝</t>
+        </is>
       </c>
       <c r="H11" t="n">
-        <v>0.8642589747905731</v>
+        <v>0.8766615092754364</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8604055047035217</v>
+        <v>0.858488142490387</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.8581427335739136</v>
       </c>
     </row>
     <row r="12">
@@ -4361,34 +4464,35 @@
           <t>堤敬信</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
         <is>
           <t>待ち行列モデルを用いた機械学習システムの性能分析</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Phung-Duc Tuan</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>高野 祐一</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>黒瀬 雄大</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>0.8868874311447144</v>
-      </c>
       <c r="H12" t="n">
-        <v>0.8567194938659668</v>
+        <v>0.8860654234886169</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8518254160881042</v>
+        <v>0.8564328849315643</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.8518259227275848</v>
       </c>
     </row>
     <row r="13">
@@ -4402,34 +4506,35 @@
           <t>飯田真実</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
         <is>
           <t>HPVワクチン接種に対する意見の変遷とその要因</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>佐野 幸恵</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>上市 秀雄</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>イリチュ 美佳</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>0.8796598017215729</v>
-      </c>
       <c r="H13" t="n">
-        <v>0.8722546398639679</v>
+        <v>0.8769748508930206</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8572297394275665</v>
+        <v>0.870670348405838</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.8549315929412842</v>
       </c>
     </row>
     <row r="14">
@@ -4443,34 +4548,35 @@
           <t>冨樫歩大</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
         <is>
           <t>大規模言語モデルを用いた事業性評価シートのテキスト分析</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>高野 祐一</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>黒瀬 雄大</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>イリチュ 美佳</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>0.8495877385139465</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>岡田 幸彦</t>
+        </is>
       </c>
       <c r="H14" t="n">
-        <v>0.8485817015171051</v>
+        <v>0.8499734103679657</v>
       </c>
       <c r="I14" t="n">
-        <v>0.847743958234787</v>
+        <v>0.8485821783542633</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.8465898633003235</v>
       </c>
     </row>
     <row r="15">
@@ -4484,34 +4590,35 @@
           <t>平井佑樹</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
         <is>
           <t>仕訳データにもとづく利速測定の研究</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>岡田 幸彦</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>鈴木 勉</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>佐野 幸恵</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>川島 宏一</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>0.8557053804397583</v>
-      </c>
       <c r="H15" t="n">
-        <v>0.8450484871864319</v>
+        <v>0.8566751778125763</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8422485589981079</v>
+        <v>0.842991054058075</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.8424454927444458</v>
       </c>
     </row>
     <row r="16">
@@ -4525,34 +4632,35 @@
           <t>李宗晟</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
         <is>
           <t>光ネットワークにおける予約のある資源割り当ての提案</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>八森 正泰</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>Phung-Duc Tuan</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>吉瀬 章子</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>0.8684130012989044</v>
-      </c>
       <c r="H16" t="n">
-        <v>0.860710084438324</v>
+        <v>0.8690818846225739</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8606573045253754</v>
+        <v>0.8608503043651581</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.8606576025485992</v>
       </c>
     </row>
     <row r="17">
@@ -4566,34 +4674,35 @@
           <t>鈴木颯斗</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
         <is>
           <t>クーポン配布における分類モデルの負例抽出</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>高野 祐一</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>繁野 麻衣子</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>牛島 光一</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>繁野 麻衣子</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>0.8662371933460236</v>
-      </c>
       <c r="H17" t="n">
-        <v>0.8516239523887634</v>
+        <v>0.8639224171638489</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8505149185657501</v>
+        <v>0.8513544201850891</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.851314902305603</v>
       </c>
     </row>
     <row r="18">
@@ -4607,34 +4716,35 @@
           <t>崔涵喬</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
         <is>
           <t>クラスター分析を用いた観光客のセグメンテーションとマーケティングへの応用可能性に関する研究</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>岡本 直久</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>浦田淳司</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>岡田 幸彦</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>0.8556585013866425</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>繁野 麻衣子</t>
+        </is>
       </c>
       <c r="H18" t="n">
-        <v>0.8470973670482635</v>
+        <v>0.8556589782238007</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8461092710494995</v>
+        <v>0.8523485958576202</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.8453573286533356</v>
       </c>
     </row>
     <row r="19">
@@ -4648,34 +4758,35 @@
           <t>澤口瑛都</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
         <is>
           <t>列生成法を軸としたバス運行業務の仕業編成</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>吉瀬 章子</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Phung-Duc Tuan</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>八森 正泰</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>0.8692281544208527</v>
-      </c>
       <c r="H19" t="n">
-        <v>0.858031153678894</v>
+        <v>0.8692283034324646</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8552306592464447</v>
+        <v>0.8579657673835754</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.855529397726059</v>
       </c>
     </row>
     <row r="20">
@@ -4689,34 +4800,35 @@
           <t>齋藤彩</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
         <is>
           <t>pLSAによる潜在クラス間の遷移予想と効果検証</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>上市 秀雄</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>岡田 幸彦</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>イリチュ 美佳</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>0.8761181235313416</v>
+          <t>秋山 英三</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>佐野 幸恵</t>
+        </is>
       </c>
       <c r="H20" t="n">
-        <v>0.8672411441802979</v>
+        <v>0.8734315633773804</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8656215667724609</v>
+        <v>0.8657551109790802</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.8657165169715881</v>
       </c>
     </row>
     <row r="21">
@@ -4730,34 +4842,35 @@
           <t>髙橋優介</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
         <is>
           <t>実データを用いた平常時の収益性と災害時の孤立リスクを考慮したドローン配送基地の施設立地最適化</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Phung-Duc Tuan</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>鈴木 勉</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>吉瀬 章子</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>鈴木 勉</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>0.86680006980896</v>
-      </c>
       <c r="H21" t="n">
-        <v>0.8634406328201294</v>
+        <v>0.8677213788032532</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8633630573749542</v>
+        <v>0.8647890388965607</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.8634408414363861</v>
       </c>
     </row>
     <row r="22">
@@ -4771,34 +4884,35 @@
           <t>寺田海渡</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
         <is>
           <t>地域金融機関の預貸金データを用いた中小企業会計品質指標の提案</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>川島 宏一</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>堤 盛人</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>岡田 幸彦</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>0.8656384646892548</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>黒瀬 雄大</t>
+        </is>
       </c>
       <c r="H22" t="n">
-        <v>0.8634596467018127</v>
+        <v>0.8656386435031891</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8629352152347565</v>
+        <v>0.8638789355754852</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.8628188967704773</v>
       </c>
     </row>
   </sheetData>

--- a/generated/committee_recommendations.xlsx
+++ b/generated/committee_recommendations.xlsx
@@ -3030,7 +3030,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>村上 暁信</t>
+          <t>藤川 昌樹</t>
         </is>
       </c>
       <c r="H62" t="n">
@@ -3040,7 +3040,7 @@
         <v>0.8261333703994751</v>
       </c>
       <c r="J62" t="n">
-        <v>0.8256785571575165</v>
+        <v>0.8253505825996399</v>
       </c>
     </row>
     <row r="63">

--- a/generated/committee_recommendations.xlsx
+++ b/generated/committee_recommendations.xlsx
@@ -492,7 +492,11 @@
           <t>中島 元毅</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>202420453</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>日本の就活市場における新卒採用に関する研究</t>
@@ -514,10 +518,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.8624107241630554</v>
+        <v>0.862410843372345</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8550395369529724</v>
+        <v>0.8550395965576172</v>
       </c>
       <c r="J2" t="n">
         <v>0.8541027009487152</v>
@@ -534,7 +538,11 @@
           <t>荒金 志紀</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>202420409</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>結婚の意思決定に対する独身税の効果と税制度の提案</t>
@@ -556,13 +564,13 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.8728691041469574</v>
+        <v>0.872869074344635</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8579381108283997</v>
+        <v>0.8579379916191101</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8574923872947693</v>
+        <v>0.8574922680854797</v>
       </c>
     </row>
     <row r="4">
@@ -576,7 +584,11 @@
           <t>小峯 拓也</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>202420429</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>学生の選考情報を利用した就活支援サービスに関する研究</t>
@@ -598,13 +610,13 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.8692523241043091</v>
+        <v>0.8692524433135986</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8567101061344147</v>
+        <v>0.8567101657390594</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8545782268047333</v>
+        <v>0.8545781970024109</v>
       </c>
     </row>
     <row r="5">
@@ -618,7 +630,11 @@
           <t>貫井 虹希</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>202420454</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>最適停止問題を用いた就活市場の分析と改善提案</t>
@@ -660,7 +676,11 @@
           <t>安達 未晴</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>202420407</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>視線計測を用いた保険加入行動の分析</t>
@@ -682,10 +702,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.8621914386749268</v>
+        <v>0.862191379070282</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8600322306156158</v>
+        <v>0.8600322902202606</v>
       </c>
       <c r="J6" t="n">
         <v>0.859343945980072</v>
@@ -702,7 +722,11 @@
           <t>YANG LUXI</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>202420493</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>価値観が失敗の対処行動に与える影響-失敗体験の重大性と領域を考えて-</t>
@@ -724,13 +748,13 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.8779138624668121</v>
+        <v>0.8779139518737793</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8710568845272064</v>
+        <v>0.8710567951202393</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8709176480770111</v>
+        <v>0.8709175884723663</v>
       </c>
     </row>
     <row r="8">
@@ -744,7 +768,11 @@
           <t>釆原 周弥</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>202420416</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>Priority-neutral matchingsの集合の格子構造に関する研究</t>
@@ -769,10 +797,10 @@
         <v>0.8699048757553101</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8567256033420563</v>
+        <v>0.8567255735397339</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8535665273666382</v>
+        <v>0.8535664677619934</v>
       </c>
     </row>
     <row r="9">
@@ -786,7 +814,11 @@
           <t>金井 公亮</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>202420420</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>不確実性下の同質財割当における randomized uniform rule のパレート効率性について</t>
@@ -811,7 +843,7 @@
         <v>0.8741540312767029</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8632310926914215</v>
+        <v>0.8632310330867767</v>
       </c>
       <c r="J9" t="n">
         <v>0.8630319237709045</v>
@@ -828,7 +860,11 @@
           <t>原 笙太</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>202420460</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>都市特性・社会経済要因が外国人居住パターンに与える影響：東京23区の実証・シミュレーション分析</t>
@@ -856,7 +892,7 @@
         <v>0.8714622259140015</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8690856695175171</v>
+        <v>0.8690856993198395</v>
       </c>
     </row>
     <row r="11">
@@ -870,7 +906,11 @@
           <t>間嶋 大智</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>202420467</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>マルチエージェントシミュレーション&amp;最適化による間取り生成</t>
@@ -895,7 +935,7 @@
         <v>0.8717465400695801</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8681821823120117</v>
+        <v>0.8681822121143341</v>
       </c>
       <c r="J11" t="n">
         <v>0.8677197694778442</v>
@@ -912,7 +952,11 @@
           <t>山田 幹大</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>202420484</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>eスポーツにおけるチームのプレイスタイル分析</t>
@@ -937,10 +981,10 @@
         <v>0.8534895181655884</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8504401743412018</v>
+        <v>0.8504401445388794</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8496212959289551</v>
+        <v>0.8496212363243103</v>
       </c>
     </row>
     <row r="13">
@@ -954,7 +998,11 @@
           <t>笹木 重聖</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>202420434</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
           <t>単位コイングラフにおける部分彩色の拡張</t>
@@ -976,10 +1024,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.8598322868347168</v>
+        <v>0.8598322570323944</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8457445502281189</v>
+        <v>0.846853107213974</v>
       </c>
       <c r="J13" t="n">
         <v>0.8340944945812225</v>
@@ -996,7 +1044,11 @@
           <t>井出 裕二</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>202420412</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>人口を考慮した均等輸送問題による道路ネットワークの連結性の定量化とその最適補強問題</t>
@@ -1024,7 +1076,7 @@
         <v>0.8714250326156616</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8703753650188446</v>
+        <v>0.8703752756118774</v>
       </c>
     </row>
     <row r="15">
@@ -1038,7 +1090,11 @@
           <t>矢中 祥吾</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>202420478</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
           <t>消費電力と所要時間の不確実性を考慮した電動バスの運行計画最適化</t>
@@ -1063,10 +1119,10 @@
         <v>0.8797307312488556</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8746517896652222</v>
+        <v>0.8746517300605774</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8738219439983368</v>
+        <v>0.8738219738006592</v>
       </c>
     </row>
     <row r="16">
@@ -1080,7 +1136,11 @@
           <t>片岡 弓澄</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>202320421</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
           <t>品質保証時間と工場間搬送を考慮した多目的マルチファクトリー・スケジューリング</t>
@@ -1108,7 +1168,7 @@
         <v>0.8685945868492126</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8665327131748199</v>
+        <v>0.8660972416400909</v>
       </c>
     </row>
     <row r="17">
@@ -1122,7 +1182,11 @@
           <t>渡邊 悠義</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>202420485</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>自律性モデルに基づくゲーミフィケーションによる安全行動変容</t>
@@ -1144,10 +1208,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.8568488657474518</v>
+        <v>0.8568487763404846</v>
       </c>
       <c r="I17" t="n">
-        <v>0.856229156255722</v>
+        <v>0.8562292456626892</v>
       </c>
       <c r="J17" t="n">
         <v>0.8532317876815796</v>
@@ -1164,7 +1228,11 @@
           <t>小澤 陽樹</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>202420417</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>確率的最適化による高次元交互作用スパースモデリング~Factorization Machines の発展形態</t>
@@ -1206,7 +1274,11 @@
           <t>安田 朗</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>202420477</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
           <t>画像と生体計測情報に基づくアクティブラーニングと業務管理</t>
@@ -1234,7 +1306,7 @@
         <v>0.8616419732570648</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8606040477752686</v>
+        <v>0.8606039583683014</v>
       </c>
     </row>
     <row r="20">
@@ -1248,7 +1320,11 @@
           <t>古山 雄晟</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>202420430</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>単独と集団を区別したライドシェアモデルにおけるゲーム理論的解析</t>
@@ -1273,7 +1349,7 @@
         <v>0.8796173334121704</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8772620558738708</v>
+        <v>0.8772619664669037</v>
       </c>
       <c r="J20" t="n">
         <v>0.8653758466243744</v>
@@ -1290,7 +1366,11 @@
           <t>関田 千隼</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>202420441</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>異なる容量を持つ複数システムの負荷分散</t>
@@ -1332,7 +1412,11 @@
           <t>位曼曼</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>202420487</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
           <t>歩車共存空間における歩行者の移動モデルの構築</t>
@@ -1357,10 +1441,10 @@
         <v>0.8829725384712219</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8760957717895508</v>
+        <v>0.876095712184906</v>
       </c>
       <c r="J22" t="n">
-        <v>0.875944197177887</v>
+        <v>0.8759442865848541</v>
       </c>
     </row>
     <row r="23">
@@ -1374,7 +1458,11 @@
           <t>三輪 珠嶺</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>202420473</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
           <t>骨格に基づく行動認識における関節角の導入</t>
@@ -1396,7 +1484,7 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0.8582464456558228</v>
+        <v>0.8582464754581451</v>
       </c>
       <c r="I23" t="n">
         <v>0.8524556457996368</v>
@@ -1416,7 +1504,11 @@
           <t>加口 貴美子</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>202420418</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>日本における男女の賃金格差の推移</t>
@@ -1441,7 +1533,7 @@
         <v>0.8524296581745148</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8512897491455078</v>
+        <v>0.851289689540863</v>
       </c>
       <c r="J24" t="n">
         <v>0.8504915237426758</v>
@@ -1458,7 +1550,11 @@
           <t>田之口 輝毅</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>202420447</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
           <t>SNS上のESGセンチメント</t>
@@ -1480,10 +1576,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0.8711104691028595</v>
+        <v>0.8711104393005371</v>
       </c>
       <c r="I25" t="n">
-        <v>0.8644375801086426</v>
+        <v>0.864437609910965</v>
       </c>
       <c r="J25" t="n">
         <v>0.8598762452602386</v>
@@ -1500,7 +1596,11 @@
           <t>笹井 大</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>202420433</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
           <t>ESG関連インデックスと株式市場</t>
@@ -1522,10 +1622,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0.8609839081764221</v>
+        <v>0.8609837889671326</v>
       </c>
       <c r="I26" t="n">
-        <v>0.8582097887992859</v>
+        <v>0.8582098484039307</v>
       </c>
       <c r="J26" t="n">
         <v>0.8581588268280029</v>
@@ -1542,7 +1642,11 @@
           <t>水越 知弘</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>202420471</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
           <t>介護が労働に与える影響</t>
@@ -1564,13 +1668,13 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0.8587647974491119</v>
+        <v>0.8587649166584015</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8570154905319214</v>
+        <v>0.8570154309272766</v>
       </c>
       <c r="J27" t="n">
-        <v>0.8559012115001678</v>
+        <v>0.8559012413024902</v>
       </c>
     </row>
     <row r="28">
@@ -1584,7 +1688,11 @@
           <t>鈴木 優梨歌</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>202420439</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
           <t>複数工場間の経路最適化を含む多目的マルチファクトリー・スケジューリング</t>
@@ -1612,7 +1720,7 @@
         <v>0.8709458708763123</v>
       </c>
       <c r="J28" t="n">
-        <v>0.8681559562683105</v>
+        <v>0.8677204847335815</v>
       </c>
     </row>
     <row r="29">
@@ -1626,7 +1734,11 @@
           <t>永井 康友</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>202420451</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
           <t>品質検査レイヤーを横断した異常原因探索～画像マルチモーダルアプローチ</t>
@@ -1668,7 +1780,11 @@
           <t>戴 家成</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>202420442</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
           <t>機械サーバと人間サーバが混在するサービスシステムの性能解析</t>
@@ -1693,10 +1809,10 @@
         <v>0.8844201862812042</v>
       </c>
       <c r="I30" t="n">
-        <v>0.855995774269104</v>
+        <v>0.8559956848621368</v>
       </c>
       <c r="J30" t="n">
-        <v>0.8549236655235291</v>
+        <v>0.8549237251281738</v>
       </c>
     </row>
     <row r="31">
@@ -1710,7 +1826,11 @@
           <t>神野 大地</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>202420427</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
           <t>東京証券取引所によるPBR改善要請の影響は企業特性によって異なるか？</t>
@@ -1735,7 +1855,7 @@
         <v>0.8590705394744873</v>
       </c>
       <c r="I31" t="n">
-        <v>0.8586951196193695</v>
+        <v>0.8586950898170471</v>
       </c>
       <c r="J31" t="n">
         <v>0.8542488515377045</v>
@@ -1752,7 +1872,11 @@
           <t>LU SICHEN</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>202420494</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
           <t>四川大震災についての地元住民の記憶とその変容—汶川県映秀鎮と北川県を比較して—</t>
@@ -1774,13 +1898,13 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0.857513427734375</v>
+        <v>0.8575133681297302</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8518452942371368</v>
+        <v>0.8518452048301697</v>
       </c>
       <c r="J32" t="n">
-        <v>0.851026713848114</v>
+        <v>0.8510266542434692</v>
       </c>
     </row>
     <row r="33">
@@ -1794,7 +1918,11 @@
           <t>石川 夏帆</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>202420410</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
           <t>多様な主体が関わる出産祝いによる産後家庭アウトリーチの実態と課題－横浜市戸塚区の認定NPO法人こまちぷらすのウェルカムベビープロジェクトに着目して－</t>
@@ -1819,10 +1947,10 @@
         <v>0.8624968230724335</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8579479455947876</v>
+        <v>0.8579478859901428</v>
       </c>
       <c r="J33" t="n">
-        <v>0.8577743470668793</v>
+        <v>0.8577742576599121</v>
       </c>
     </row>
     <row r="34">
@@ -1836,7 +1964,11 @@
           <t>鳩貝 優太</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>202420458</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
           <t>カフェ型居場所の開設・運営プロセスにおける障壁と支援に関する研究－認定NPO法人こまちぷらすの講座に着目して－</t>
@@ -1858,10 +1990,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>0.8634571433067322</v>
+        <v>0.8634572327136993</v>
       </c>
       <c r="I34" t="n">
-        <v>0.8626152873039246</v>
+        <v>0.8626152276992798</v>
       </c>
       <c r="J34" t="n">
         <v>0.8595913052558899</v>
@@ -1878,7 +2010,11 @@
           <t>畑 颯汰</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>202420456</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
           <t>斜面住宅地の存続可能性に関する研究 －段差解消のための共有財の維持管理に着目して－</t>
@@ -1920,7 +2056,11 @@
           <t>石田 悠人</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>202420411</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
           <t>公園の農的利用の効果と課題に関する研究</t>
@@ -1945,10 +2085,10 @@
         <v>0.875926673412323</v>
       </c>
       <c r="I36" t="n">
-        <v>0.8731176853179932</v>
+        <v>0.8731177151203156</v>
       </c>
       <c r="J36" t="n">
-        <v>0.8701472282409668</v>
+        <v>0.870147168636322</v>
       </c>
     </row>
     <row r="37">
@@ -1962,7 +2102,11 @@
           <t>高橋 慧</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>202420444</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
           <t>地方自治体における統計的因果推論に基づく政策分析の適用方法に関する研究</t>
@@ -1984,13 +2128,13 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>0.8812141716480255</v>
+        <v>0.881214052438736</v>
       </c>
       <c r="I37" t="n">
-        <v>0.8785417377948761</v>
+        <v>0.8785417675971985</v>
       </c>
       <c r="J37" t="n">
-        <v>0.8743589520454407</v>
+        <v>0.8743588924407959</v>
       </c>
     </row>
     <row r="38">
@@ -2004,7 +2148,11 @@
           <t>酒井 佑</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>202420431</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
           <t>地域外の人材を対象とした逆指名による創業支援制度の運用実態と他地域展開の可能性に関する研究</t>
@@ -2029,10 +2177,10 @@
         <v>0.8687264025211334</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8683319687843323</v>
+        <v>0.8683319091796875</v>
       </c>
       <c r="J38" t="n">
-        <v>0.8629851043224335</v>
+        <v>0.8629850745201111</v>
       </c>
     </row>
     <row r="39">
@@ -2046,7 +2194,11 @@
           <t>佐藤 佳乃</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>202420437</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
           <t>地籍調査の進捗に関する地理空間分析</t>
@@ -2071,10 +2223,10 @@
         <v>0.8869522213935852</v>
       </c>
       <c r="I39" t="n">
-        <v>0.8798271715641022</v>
+        <v>0.8798271119594574</v>
       </c>
       <c r="J39" t="n">
-        <v>0.8780929744243622</v>
+        <v>0.8780929446220398</v>
       </c>
     </row>
     <row r="40">
@@ -2088,7 +2240,11 @@
           <t>早坂 遼</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>202420547</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
           <t>羽田空港新飛行経路の運用開始が東京都心の不動産価値に与えた影響に関する計量分析</t>
@@ -2113,7 +2269,7 @@
         <v>0.8817869424819946</v>
       </c>
       <c r="I40" t="n">
-        <v>0.8813001811504364</v>
+        <v>0.8813002407550812</v>
       </c>
       <c r="J40" t="n">
         <v>0.8805910348892212</v>
@@ -2130,7 +2286,11 @@
           <t>釜谷 紘生</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>202420422</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
           <t>マニラ都市圏における洪水リスクが不動産価格に与える影響の分析</t>
@@ -2155,10 +2315,10 @@
         <v>0.8820194900035858</v>
       </c>
       <c r="I41" t="n">
-        <v>0.8708105385303497</v>
+        <v>0.870810478925705</v>
       </c>
       <c r="J41" t="n">
-        <v>0.8667831718921661</v>
+        <v>0.8667832314968109</v>
       </c>
     </row>
     <row r="42">
@@ -2172,7 +2332,11 @@
           <t>市川 はるひ</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>202420455</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
           <t>冒険遊び場における犯罪被害と運営者の対応の実態解明</t>
@@ -2194,10 +2358,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>0.8621288537979126</v>
+        <v>0.8621289134025574</v>
       </c>
       <c r="I42" t="n">
-        <v>0.8617662489414215</v>
+        <v>0.8617661893367767</v>
       </c>
       <c r="J42" t="n">
         <v>0.8502079844474792</v>
@@ -2214,7 +2378,11 @@
           <t>舩戸 祐汰</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>202420466</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
           <t>屋外着座空間への評価と独り好き志向性との関係</t>
@@ -2236,13 +2404,13 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>0.8732402920722961</v>
+        <v>0.873240202665329</v>
       </c>
       <c r="I43" t="n">
-        <v>0.8673423230648041</v>
+        <v>0.8673423528671265</v>
       </c>
       <c r="J43" t="n">
-        <v>0.865800529718399</v>
+        <v>0.8658006191253662</v>
       </c>
     </row>
     <row r="44">
@@ -2256,7 +2424,11 @@
           <t>廣田 華</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>202420465</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
           <t>農村舞台の現状とその保全—ハード・ソフトの両面に着目して—</t>
@@ -2278,13 +2450,13 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>0.861095666885376</v>
+        <v>0.8610955774784088</v>
       </c>
       <c r="I44" t="n">
         <v>0.8600713014602661</v>
       </c>
       <c r="J44" t="n">
-        <v>0.8588992655277252</v>
+        <v>0.8588992953300476</v>
       </c>
     </row>
     <row r="45">
@@ -2298,7 +2470,11 @@
           <t>陳 泓儒</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>202420492</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
           <t>ディープラーニングに基づく武漢の都市イメージの空間構造と都市計画実施に関する研究</t>
@@ -2320,13 +2496,13 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0.8848140835762024</v>
+        <v>0.88481405377388</v>
       </c>
       <c r="I45" t="n">
         <v>0.884340912103653</v>
       </c>
       <c r="J45" t="n">
-        <v>0.8809525370597839</v>
+        <v>0.8809525072574615</v>
       </c>
     </row>
     <row r="46">
@@ -2340,7 +2516,11 @@
           <t>坂本 怜奈</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>202420432</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
           <t>地域ネットワークにおける中間支援組織の役割とマネジメントシステムの構築に関する考察</t>
@@ -2362,10 +2542,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>0.8637301623821259</v>
+        <v>0.8637301921844482</v>
       </c>
       <c r="I46" t="n">
-        <v>0.861213207244873</v>
+        <v>0.8612132370471954</v>
       </c>
       <c r="J46" t="n">
         <v>0.8606871068477631</v>
@@ -2382,7 +2562,11 @@
           <t>佐々木 智哉</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>202420435</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
           <t>都市再生緊急整備地域における都市再生の政策効果の検証ー地方中核都市の事例を対象として</t>
@@ -2404,13 +2588,13 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>0.8822457790374756</v>
+        <v>0.882245659828186</v>
       </c>
       <c r="I47" t="n">
         <v>0.8808684349060059</v>
       </c>
       <c r="J47" t="n">
-        <v>0.8796663284301758</v>
+        <v>0.8796663582324982</v>
       </c>
     </row>
     <row r="48">
@@ -2424,7 +2608,11 @@
           <t>髙野 駿</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>202420443</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
           <t>観光都市におけるオーバーツーリズムの対策やそれに伴う効果と課題について</t>
@@ -2452,7 +2640,7 @@
         <v>0.8687419593334198</v>
       </c>
       <c r="J48" t="n">
-        <v>0.8655959069728851</v>
+        <v>0.8655958473682404</v>
       </c>
     </row>
     <row r="49">
@@ -2466,7 +2654,11 @@
           <t>高橋 梨沙子</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>202420445</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr">
         <is>
           <t>観光地における駅舎建築に関する研究</t>
@@ -2494,7 +2686,7 @@
         <v>0.8646083772182465</v>
       </c>
       <c r="J49" t="n">
-        <v>0.8645975291728973</v>
+        <v>0.8645975589752197</v>
       </c>
     </row>
     <row r="50">
@@ -2508,7 +2700,11 @@
           <t>小松 諒治</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>202420428</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr">
         <is>
           <t>地域公共交通サービス変化時の活動機会変化の計測に関する研究</t>
@@ -2536,7 +2732,7 @@
         <v>0.8805749118328094</v>
       </c>
       <c r="J50" t="n">
-        <v>0.8780884146690369</v>
+        <v>0.8780884444713593</v>
       </c>
     </row>
     <row r="51">
@@ -2550,7 +2746,11 @@
           <t>佐光 未帆</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>202420438</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr">
         <is>
           <t>大学敷地内における大学生の犯罪被害の実態と報告行動の解明</t>
@@ -2572,13 +2772,13 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>0.8623651266098022</v>
+        <v>0.862365186214447</v>
       </c>
       <c r="I51" t="n">
-        <v>0.8559726178646088</v>
+        <v>0.8559725284576416</v>
       </c>
       <c r="J51" t="n">
-        <v>0.8511845171451569</v>
+        <v>0.8511845767498016</v>
       </c>
     </row>
     <row r="52">
@@ -2592,7 +2792,11 @@
           <t>Tang Xinyu</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>202420490</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr">
         <is>
           <t>職住近接と生活域の拡がりとの関連：GPSデータを用いた検討</t>
@@ -2614,13 +2818,13 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>0.8600000441074371</v>
+        <v>0.8599999845027924</v>
       </c>
       <c r="I52" t="n">
         <v>0.8592597246170044</v>
       </c>
       <c r="J52" t="n">
-        <v>0.8564842045307159</v>
+        <v>0.8564841449260712</v>
       </c>
     </row>
     <row r="53">
@@ -2634,7 +2838,11 @@
           <t>田上 朋樹</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>202420446</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr">
         <is>
           <t>人口再配分による食料需給バランス改善への試案 ー「地域で食料が自給できる国土」への視座－</t>
@@ -2659,10 +2867,10 @@
         <v>0.8757403492927551</v>
       </c>
       <c r="I53" t="n">
-        <v>0.8713475465774536</v>
+        <v>0.871347576379776</v>
       </c>
       <c r="J53" t="n">
-        <v>0.8705988526344299</v>
+        <v>0.8705988824367523</v>
       </c>
     </row>
     <row r="54">
@@ -2676,7 +2884,11 @@
           <t>矢橋 敦之</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>202420480</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr">
         <is>
           <t>都市サービスの長期的な入れ替わりの実態 －2002年と2022年の２時点比較－</t>
@@ -2698,10 +2910,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>0.866838663816452</v>
+        <v>0.8668387234210968</v>
       </c>
       <c r="I54" t="n">
-        <v>0.8634084463119507</v>
+        <v>0.8634083867073059</v>
       </c>
       <c r="J54" t="n">
         <v>0.8591557145118713</v>
@@ -2718,7 +2930,11 @@
           <t>松浦 海斗</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>202420468</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr">
         <is>
           <t>子どもの体験格差の全国横断的把握 ―学校外での生活行動に着目して－</t>
@@ -2740,13 +2956,13 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0.8447581827640533</v>
+        <v>0.8447581231594086</v>
       </c>
       <c r="I55" t="n">
-        <v>0.8435723483562469</v>
+        <v>0.8435723781585693</v>
       </c>
       <c r="J55" t="n">
-        <v>0.8434951603412628</v>
+        <v>0.8434951305389404</v>
       </c>
     </row>
     <row r="56">
@@ -2760,7 +2976,11 @@
           <t>稲葉 翔太</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>202420413</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
           <t>シェアサイクル運営者の機会損失改善に向けた自転車再配置における調整台数の検討-茨城県つくば市を事例として-</t>
@@ -2785,10 +3005,10 @@
         <v>0.8806582093238831</v>
       </c>
       <c r="I56" t="n">
-        <v>0.87824946641922</v>
+        <v>0.8782493770122528</v>
       </c>
       <c r="J56" t="n">
-        <v>0.8735233545303345</v>
+        <v>0.8735232651233673</v>
       </c>
     </row>
     <row r="57">
@@ -2802,7 +3022,11 @@
           <t>三重野 馨</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>202420470</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr">
         <is>
           <t>アルジェリアにおけるフェルナン・プイヨンのツーリスト・コンプレックスに関する研究</t>
@@ -2824,13 +3048,13 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>0.8431252539157867</v>
+        <v>0.8431252837181091</v>
       </c>
       <c r="I57" t="n">
-        <v>0.841835081577301</v>
+        <v>0.8418350219726562</v>
       </c>
       <c r="J57" t="n">
-        <v>0.8402625322341919</v>
+        <v>0.8402624726295471</v>
       </c>
     </row>
     <row r="58">
@@ -2844,7 +3068,11 @@
           <t>犬竹 智哉</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>202420414</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr">
         <is>
           <t>商用FCVの普及に向けた水素ステーション配置とCO2排出量の予測</t>
@@ -2869,10 +3097,10 @@
         <v>0.8711833655834198</v>
       </c>
       <c r="I58" t="n">
-        <v>0.8702839612960815</v>
+        <v>0.8702839016914368</v>
       </c>
       <c r="J58" t="n">
-        <v>0.8700035214424133</v>
+        <v>0.8700034916400909</v>
       </c>
     </row>
     <row r="59">
@@ -2886,7 +3114,11 @@
           <t>日高 優一</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>202420461</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr">
         <is>
           <t>基幹交通の組み合わせ利用を考慮した将来交通需要予測に関する研究</t>
@@ -2928,7 +3160,11 @@
           <t>鎌田 晴人</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>202420421</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr">
         <is>
           <t>ETC2.0プローブデータを活用した旅行時間信頼性の時空間的評価</t>
@@ -2953,10 +3189,10 @@
         <v>0.8746653497219086</v>
       </c>
       <c r="I60" t="n">
-        <v>0.8743585646152496</v>
+        <v>0.8743585348129272</v>
       </c>
       <c r="J60" t="n">
-        <v>0.8681853413581848</v>
+        <v>0.86818528175354</v>
       </c>
     </row>
     <row r="61">
@@ -2970,7 +3206,11 @@
           <t>畑山 公希</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>202420457</t>
+        </is>
+      </c>
       <c r="D61" t="inlineStr">
         <is>
           <t>自治体におけるグリーンインフラの計画的展開を阻害する要因についての研究</t>
@@ -2992,13 +3232,13 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>0.8799072802066803</v>
+        <v>0.8799073100090027</v>
       </c>
       <c r="I61" t="n">
-        <v>0.8760299980640411</v>
+        <v>0.876029908657074</v>
       </c>
       <c r="J61" t="n">
-        <v>0.874200314283371</v>
+        <v>0.8742002546787262</v>
       </c>
     </row>
     <row r="62">
@@ -3012,7 +3252,11 @@
           <t>張 宇星</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>202420491</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr">
         <is>
           <t>清代における祭祀行宮の構成と変容—龍王廟を中心に—</t>
@@ -3030,17 +3274,17 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>藤川 昌樹</t>
+          <t>村上 暁信</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>0.8276545107364655</v>
+        <v>0.8276543617248535</v>
       </c>
       <c r="I62" t="n">
         <v>0.8261333703994751</v>
       </c>
       <c r="J62" t="n">
-        <v>0.8253505825996399</v>
+        <v>0.8258125185966492</v>
       </c>
     </row>
     <row r="63">
@@ -3054,7 +3298,11 @@
           <t>森下 陽平</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>202420474</t>
+        </is>
+      </c>
       <c r="D63" t="inlineStr">
         <is>
           <t>騒音問題と自己観の関係性：日本・カナダ比較研究</t>
@@ -3076,13 +3324,13 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>0.8604455292224884</v>
+        <v>0.8604454696178436</v>
       </c>
       <c r="I63" t="n">
-        <v>0.8598350286483765</v>
+        <v>0.8598349392414093</v>
       </c>
       <c r="J63" t="n">
-        <v>0.8570573925971985</v>
+        <v>0.8570573329925537</v>
       </c>
     </row>
     <row r="64">
@@ -3096,7 +3344,11 @@
           <t>平林 優希</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr"/>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>202420463</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr">
         <is>
           <t>環境配慮意識・行動の自他評価の特性と行動意図の関係</t>
@@ -3118,10 +3370,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>0.8832572996616364</v>
+        <v>0.883257269859314</v>
       </c>
       <c r="I64" t="n">
-        <v>0.8624671101570129</v>
+        <v>0.8624672293663025</v>
       </c>
       <c r="J64" t="n">
         <v>0.8614659905433655</v>
@@ -3138,7 +3390,11 @@
           <t>中澤 光希</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>202420452</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr">
         <is>
           <t>都市再生特別地区において多様化する域外貢献の実態と課題に関する研究</t>
@@ -3160,13 +3416,13 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>0.8763948380947113</v>
+        <v>0.8763948082923889</v>
       </c>
       <c r="I65" t="n">
-        <v>0.8731106519699097</v>
+        <v>0.8731105923652649</v>
       </c>
       <c r="J65" t="n">
-        <v>0.8720406591892242</v>
+        <v>0.8720406889915466</v>
       </c>
     </row>
     <row r="66">
@@ -3180,7 +3436,11 @@
           <t>草田 弦喜</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>202420424</t>
+        </is>
+      </c>
       <c r="D66" t="inlineStr">
         <is>
           <t>銀座ルールと比較した『日本橋らしさ』に関する研究-東京都日本橋地区を対象として-</t>
@@ -3202,13 +3462,13 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>0.8690553307533264</v>
+        <v>0.8690553903579712</v>
       </c>
       <c r="I66" t="n">
-        <v>0.8654606640338898</v>
+        <v>0.865460604429245</v>
       </c>
       <c r="J66" t="n">
-        <v>0.8637252748012543</v>
+        <v>0.8637252449989319</v>
       </c>
     </row>
     <row r="67">
@@ -3222,7 +3482,11 @@
           <t>加藤 優弥</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>202420419</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr">
         <is>
           <t>スタジアム・アリーナの多機能化に伴う公民連携によるエリアマネジメントに関する研究</t>
@@ -3244,13 +3508,13 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>0.8704354465007782</v>
+        <v>0.8704354166984558</v>
       </c>
       <c r="I67" t="n">
         <v>0.8688648343086243</v>
       </c>
       <c r="J67" t="n">
-        <v>0.868646115064621</v>
+        <v>0.8686460256576538</v>
       </c>
     </row>
     <row r="68">
@@ -3264,7 +3528,11 @@
           <t>水野 瑛介</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr"/>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>202420472</t>
+        </is>
+      </c>
       <c r="D68" t="inlineStr">
         <is>
           <t>メジャーリーグにおける統計的差別と選好的差別</t>
@@ -3286,10 +3554,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>0.8518877029418945</v>
+        <v>0.851887583732605</v>
       </c>
       <c r="I68" t="n">
-        <v>0.8515320122241974</v>
+        <v>0.8515320420265198</v>
       </c>
       <c r="J68" t="n">
         <v>0.8441035449504852</v>
@@ -3306,7 +3574,11 @@
           <t>山縣 力也</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr"/>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>202420481</t>
+        </is>
+      </c>
       <c r="D69" t="inlineStr">
         <is>
           <t>非罰則規制の犯罪波及効果：渋谷区の路上飲酒禁止条例を事例として</t>
@@ -3328,13 +3600,13 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>0.8769175112247467</v>
+        <v>0.8769174814224243</v>
       </c>
       <c r="I69" t="n">
-        <v>0.8631938695907593</v>
+        <v>0.8631938099861145</v>
       </c>
       <c r="J69" t="n">
-        <v>0.8606486618518829</v>
+        <v>0.8606486916542053</v>
       </c>
     </row>
     <row r="70">
@@ -3348,7 +3620,11 @@
           <t>青木 日花</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr"/>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>202420406</t>
+        </is>
+      </c>
       <c r="D70" t="inlineStr">
         <is>
           <t>アメニティに着目した価値あるオフィスビルの要因分析と効果検証</t>
@@ -3370,13 +3646,13 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>0.872194916009903</v>
+        <v>0.8721948266029358</v>
       </c>
       <c r="I70" t="n">
-        <v>0.8721113204956055</v>
+        <v>0.8721112906932831</v>
       </c>
       <c r="J70" t="n">
-        <v>0.8718703091144562</v>
+        <v>0.8718703389167786</v>
       </c>
     </row>
     <row r="71">
@@ -3390,7 +3666,11 @@
           <t>GAO WENWEN</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr"/>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>202420488</t>
+        </is>
+      </c>
       <c r="D71" t="inlineStr">
         <is>
           <t>グリーンビルディング認証がJ-REITのパフォーマンスに与える影響の実証分析</t>
@@ -3412,13 +3692,13 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>0.8696563243865967</v>
+        <v>0.8696562647819519</v>
       </c>
       <c r="I71" t="n">
         <v>0.8675041198730469</v>
       </c>
       <c r="J71" t="n">
-        <v>0.8670808076858521</v>
+        <v>0.8670807778835297</v>
       </c>
     </row>
     <row r="72">
@@ -3432,7 +3712,11 @@
           <t>平野 晴也</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>202420462</t>
+        </is>
+      </c>
       <c r="D72" t="inlineStr">
         <is>
           <t>3次元地図更新のための衛星リモートセンシングによる地形計測手法の開発</t>
@@ -3454,10 +3738,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>0.8607411086559296</v>
+        <v>0.860741138458252</v>
       </c>
       <c r="I72" t="n">
-        <v>0.8596481382846832</v>
+        <v>0.8596481680870056</v>
       </c>
       <c r="J72" t="n">
         <v>0.859329879283905</v>
@@ -3474,7 +3758,11 @@
           <t>WEI MIAOHENG</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr"/>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>202420486</t>
+        </is>
+      </c>
       <c r="D73" t="inlineStr">
         <is>
           <t>往復移動と滞在行動を考慮したバス頻度問題</t>
@@ -3496,10 +3784,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>0.8742718994617462</v>
+        <v>0.8742718696594238</v>
       </c>
       <c r="I73" t="n">
-        <v>0.871936708688736</v>
+        <v>0.8719367384910583</v>
       </c>
       <c r="J73" t="n">
         <v>0.8718547224998474</v>
@@ -3516,7 +3804,11 @@
           <t>田村 侑介</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr"/>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>202420449</t>
+        </is>
+      </c>
       <c r="D74" t="inlineStr">
         <is>
           <t>共同住宅におけるEV充電器設置の意思決定メカニズムの解析</t>
@@ -3538,13 +3830,13 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>0.871593713760376</v>
+        <v>0.8715938031673431</v>
       </c>
       <c r="I74" t="n">
-        <v>0.8709504902362823</v>
+        <v>0.8709505200386047</v>
       </c>
       <c r="J74" t="n">
-        <v>0.8709365725517273</v>
+        <v>0.8709364831447601</v>
       </c>
     </row>
     <row r="75">
@@ -3558,7 +3850,11 @@
           <t>山田 圭祐</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr"/>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>202420483</t>
+        </is>
+      </c>
       <c r="D75" t="inlineStr">
         <is>
           <t>ミクロ交通シミュレーション利用における機械学習モデルの有効性検討</t>
@@ -3580,7 +3876,7 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>0.8804835975170135</v>
+        <v>0.8804836571216583</v>
       </c>
       <c r="I75" t="n">
         <v>0.879767507314682</v>
@@ -3600,7 +3896,11 @@
           <t>平山 裕紀人</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr"/>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>202420464</t>
+        </is>
+      </c>
       <c r="D76" t="inlineStr">
         <is>
           <t>マクロ交通流理論に基づくグリッドロック現象の分析：タイ・バンコクを対象として</t>
@@ -3625,10 +3925,10 @@
         <v>0.8646460771560669</v>
       </c>
       <c r="I76" t="n">
-        <v>0.858845442533493</v>
+        <v>0.8588454723358154</v>
       </c>
       <c r="J76" t="n">
-        <v>0.8584804236888885</v>
+        <v>0.8584803938865662</v>
       </c>
     </row>
     <row r="77">
@@ -3642,7 +3942,11 @@
           <t>桑原 慶太</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr"/>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>202420426</t>
+        </is>
+      </c>
       <c r="D77" t="inlineStr">
         <is>
           <t>データ同化手法を用いたネットワーク交通流モデルの精度改善及びパラメータ推定</t>
@@ -3664,7 +3968,7 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>0.8770518004894257</v>
+        <v>0.8770517706871033</v>
       </c>
       <c r="I77" t="n">
         <v>0.8737709820270538</v>
@@ -3684,7 +3988,11 @@
           <t>徐 摯恒</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr"/>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>202420489</t>
+        </is>
+      </c>
       <c r="D78" t="inlineStr">
         <is>
           <t>高速鉄道の開通が都市経済に与える影響の分析</t>
@@ -3709,10 +4017,10 @@
         <v>0.880396842956543</v>
       </c>
       <c r="I78" t="n">
-        <v>0.8773619830608368</v>
+        <v>0.8773620128631592</v>
       </c>
       <c r="J78" t="n">
-        <v>0.8741996884346008</v>
+        <v>0.8741997182369232</v>
       </c>
     </row>
     <row r="79">
@@ -3726,7 +4034,11 @@
           <t>松場 拓海</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr"/>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>202420469</t>
+        </is>
+      </c>
       <c r="D79" t="inlineStr">
         <is>
           <t>「認識人口」概念の提案とその実態―市町村に対するポジティブ／ネガティブイメージの分析から－</t>
@@ -3751,7 +4063,7 @@
         <v>0.8768567442893982</v>
       </c>
       <c r="I79" t="n">
-        <v>0.8671047389507294</v>
+        <v>0.8671047687530518</v>
       </c>
       <c r="J79" t="n">
         <v>0.8661922812461853</v>
@@ -3768,7 +4080,11 @@
           <t>馬場 理彰</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr"/>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>202420459</t>
+        </is>
+      </c>
       <c r="D80" t="inlineStr">
         <is>
           <t>プロサッカーチームのリーグ昇降格が街並みに与える影響</t>
@@ -3790,10 +4106,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>0.8574393689632416</v>
+        <v>0.8574394285678864</v>
       </c>
       <c r="I80" t="n">
-        <v>0.854439914226532</v>
+        <v>0.8544398546218872</v>
       </c>
       <c r="J80" t="n">
         <v>0.8538867235183716</v>
@@ -3810,7 +4126,11 @@
           <t>佐々木 智哉</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr"/>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>202420436</t>
+        </is>
+      </c>
       <c r="D81" t="inlineStr">
         <is>
           <t>コロナ禍以降のバイク需要の持続的拡大の要因：経験財理論に基づく考察</t>
@@ -3852,7 +4172,11 @@
           <t>網野 景介</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr"/>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>202420408</t>
+        </is>
+      </c>
       <c r="D82" t="inlineStr">
         <is>
           <t>M-1グランプリのシグナリング効果：動画再生数への影響</t>
@@ -3877,10 +4201,10 @@
         <v>0.8526224195957184</v>
       </c>
       <c r="I82" t="n">
-        <v>0.8521039187908173</v>
+        <v>0.8521038889884949</v>
       </c>
       <c r="J82" t="n">
-        <v>0.8483674824237823</v>
+        <v>0.8483676016330719</v>
       </c>
     </row>
     <row r="83">
@@ -3894,7 +4218,11 @@
           <t>神尾 瑞貴</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr"/>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>202420423</t>
+        </is>
+      </c>
       <c r="D83" t="inlineStr">
         <is>
           <t>花粉が経済活動に与える影響</t>
@@ -3922,7 +4250,7 @@
         <v>0.8515084087848663</v>
       </c>
       <c r="J83" t="n">
-        <v>0.8503591418266296</v>
+        <v>0.8503592908382416</v>
       </c>
     </row>
     <row r="84">
@@ -3936,7 +4264,11 @@
           <t>柳 千宙</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr"/>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>202420479</t>
+        </is>
+      </c>
       <c r="D84" t="inlineStr">
         <is>
           <t>分布北限域における南方系海洋生物の北上とその認識</t>
@@ -3958,10 +4290,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>0.8473111093044281</v>
+        <v>0.8473110795021057</v>
       </c>
       <c r="I84" t="n">
-        <v>0.8449656069278717</v>
+        <v>0.8449655175209045</v>
       </c>
       <c r="J84" t="n">
         <v>0.8399158716201782</v>
@@ -4072,7 +4404,7 @@
         <v>0.8589865863323212</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8573168516159058</v>
+        <v>0.8573169112205505</v>
       </c>
     </row>
     <row r="3">
@@ -4195,7 +4527,7 @@
         <v>0.8748292922973633</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8656644821166992</v>
+        <v>0.8652165830135345</v>
       </c>
       <c r="J5" t="n">
         <v>0.8607003390789032</v>
@@ -4237,7 +4569,7 @@
         <v>0.8752143979072571</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8730534613132477</v>
+        <v>0.8730535209178925</v>
       </c>
       <c r="J6" t="n">
         <v>0.8719890415668488</v>
@@ -4276,13 +4608,13 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.8805915713310242</v>
+        <v>0.8805915415287018</v>
       </c>
       <c r="I7" t="n">
         <v>0.8642038404941559</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8563596308231354</v>
+        <v>0.8563596606254578</v>
       </c>
     </row>
     <row r="8">
@@ -4363,7 +4695,7 @@
         <v>0.8722025752067566</v>
       </c>
       <c r="I9" t="n">
-        <v>0.862546294927597</v>
+        <v>0.8625463545322418</v>
       </c>
       <c r="J9" t="n">
         <v>0.8624857068061829</v>
@@ -4393,22 +4725,22 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>有馬 澄佳</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
           <t>繁野 麻衣子</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>有馬 澄佳</t>
         </is>
       </c>
       <c r="H10" t="n">
         <v>0.8638104796409607</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8519278466701508</v>
+        <v>0.8515419661998749</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8515419661998749</v>
+        <v>0.8515247106552124</v>
       </c>
     </row>
     <row r="11">
@@ -4440,17 +4772,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>大西 正輝</t>
+          <t>岡田 幸彦</t>
         </is>
       </c>
       <c r="H11" t="n">
         <v>0.8766615092754364</v>
       </c>
       <c r="I11" t="n">
-        <v>0.858488142490387</v>
+        <v>0.8584881722927094</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8581427335739136</v>
+        <v>0.8555068969726562</v>
       </c>
     </row>
     <row r="12">
@@ -4492,7 +4824,7 @@
         <v>0.8564328849315643</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8518259227275848</v>
+        <v>0.8518258035182953</v>
       </c>
     </row>
     <row r="13">
@@ -4528,10 +4860,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.8769748508930206</v>
+        <v>0.8769748210906982</v>
       </c>
       <c r="I13" t="n">
-        <v>0.870670348405838</v>
+        <v>0.8706704080104828</v>
       </c>
       <c r="J13" t="n">
         <v>0.8549315929412842</v>
@@ -4576,7 +4908,7 @@
         <v>0.8485821783542633</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8465898633003235</v>
+        <v>0.8465899229049683</v>
       </c>
     </row>
     <row r="15">
@@ -4612,13 +4944,13 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0.8566751778125763</v>
+        <v>0.8566752672195435</v>
       </c>
       <c r="I15" t="n">
-        <v>0.842991054058075</v>
+        <v>0.8429910242557526</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8424454927444458</v>
+        <v>0.8424454629421234</v>
       </c>
     </row>
     <row r="16">
@@ -4699,7 +5031,7 @@
         <v>0.8639224171638489</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8513544201850891</v>
+        <v>0.8516285419464111</v>
       </c>
       <c r="J17" t="n">
         <v>0.851314902305603</v>
@@ -4744,7 +5076,7 @@
         <v>0.8523485958576202</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8453573286533356</v>
+        <v>0.8456804156303406</v>
       </c>
     </row>
     <row r="19">
@@ -4822,13 +5154,13 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0.8734315633773804</v>
+        <v>0.8734315931797028</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8657551109790802</v>
+        <v>0.8657550811767578</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8657165169715881</v>
+        <v>0.8657165765762329</v>
       </c>
     </row>
     <row r="21">
@@ -4867,7 +5199,7 @@
         <v>0.8677213788032532</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8647890388965607</v>
+        <v>0.8647889792919159</v>
       </c>
       <c r="J21" t="n">
         <v>0.8634408414363861</v>
@@ -4906,7 +5238,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0.8656386435031891</v>
+        <v>0.8656386137008667</v>
       </c>
       <c r="I22" t="n">
         <v>0.8638789355754852</v>

--- a/generated/committee_recommendations.xlsx
+++ b/generated/committee_recommendations.xlsx
@@ -504,27 +504,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>上市 秀雄</t>
+          <t>上市秀雄</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>小西葉子</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>原田 信行</t>
+          <t>張勇兵</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.862410843372345</v>
+        <v>0.8624107539653778</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8550395965576172</v>
+        <v>0.8566808700561523</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8541027009487152</v>
+        <v>0.8556444644927979</v>
       </c>
     </row>
     <row r="3">
@@ -550,27 +550,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>牛島光一</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>秋山 英三</t>
+          <t>岡本翔平</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>太田 充</t>
+          <t>小西葉子</t>
         </is>
       </c>
       <c r="H3" t="n">
         <v>0.872869074344635</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8579379916191101</v>
+        <v>0.8679050207138062</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8574922680854797</v>
+        <v>0.8613480925559998</v>
       </c>
     </row>
     <row r="4">
@@ -596,27 +596,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>上市 秀雄</t>
+          <t>上市秀雄</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>張勇兵</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>牛島光一</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.8692524433135986</v>
+        <v>0.8692523539066315</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8567101657390594</v>
+        <v>0.8587264716625214</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8545781970024109</v>
+        <v>0.8567101359367371</v>
       </c>
     </row>
     <row r="5">
@@ -642,24 +642,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>高野 祐一</t>
+          <t>高野祐一</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>吉瀬 章子</t>
+          <t>吉瀬章子</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>澤 亮治</t>
+          <t>澤亮治</t>
         </is>
       </c>
       <c r="H5" t="n">
         <v>0.8717089295387268</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8693714141845703</v>
+        <v>0.8693714737892151</v>
       </c>
       <c r="J5" t="n">
         <v>0.8665045499801636</v>
@@ -688,27 +688,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>三崎広海</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>岡田 幸彦</t>
+          <t>牛島光一</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>秋山 英三</t>
+          <t>秋山英三</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.862191379070282</v>
+        <v>0.8649015724658966</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8600322902202606</v>
+        <v>0.8621913194656372</v>
       </c>
       <c r="J6" t="n">
-        <v>0.859343945980072</v>
+        <v>0.8593439757823944</v>
       </c>
     </row>
     <row r="7">
@@ -734,27 +734,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>上市 秀雄</t>
+          <t>上市秀雄</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>甲斐田 直子</t>
+          <t>讃井知</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>秋山 英三</t>
+          <t>甲斐田直子</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.8779139518737793</v>
+        <v>0.8779138922691345</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8710567951202393</v>
+        <v>0.8748931884765625</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8709175884723663</v>
+        <v>0.8710569143295288</v>
       </c>
     </row>
     <row r="8">
@@ -780,27 +780,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>澤 亮治</t>
+          <t>阿武秀和</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>八森 正泰</t>
+          <t>澤亮治</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>和田 健太郎</t>
+          <t>張勇兵</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.8699048757553101</v>
+        <v>0.8727771043777466</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8567255735397339</v>
+        <v>0.8699049353599548</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8535664677619934</v>
+        <v>0.8581907451152802</v>
       </c>
     </row>
     <row r="9">
@@ -826,27 +826,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>澤 亮治</t>
+          <t>阿武秀和</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>八森 正泰</t>
+          <t>澤亮治</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>高野 祐一</t>
+          <t>八森正泰</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.8741540312767029</v>
+        <v>0.8814799785614014</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8632310330867767</v>
+        <v>0.8741540014743805</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8630319237709045</v>
+        <v>0.8632311224937439</v>
       </c>
     </row>
     <row r="10">
@@ -872,27 +872,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>鈴木勉</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>太田 充</t>
+          <t>谷口守</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>堤 盛人</t>
+          <t>太田充</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.8737157583236694</v>
+        <v>0.8737158477306366</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8714622259140015</v>
+        <v>0.8720432817935944</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8690856993198395</v>
+        <v>0.8714621961116791</v>
       </c>
     </row>
     <row r="11">
@@ -918,17 +918,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>吉瀬 章子</t>
+          <t>吉瀬章子</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>八森 正泰</t>
+          <t>八森正泰</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>有馬 澄佳</t>
+          <t>有馬澄佳</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -964,24 +964,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>澤 亮治</t>
+          <t>澤亮治</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>川島宏一</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>秋山 英三</t>
+          <t>秋山英三</t>
         </is>
       </c>
       <c r="H12" t="n">
         <v>0.8534895181655884</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8504401445388794</v>
+        <v>0.8504402041435242</v>
       </c>
       <c r="J12" t="n">
         <v>0.8496212363243103</v>
@@ -1010,27 +1010,27 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>八森 正泰</t>
+          <t>八森正泰</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>繁野麻衣子</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
+          <t>阿武秀和</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.8598322570323944</v>
+        <v>0.8598324656486511</v>
       </c>
       <c r="I13" t="n">
-        <v>0.846853107213974</v>
+        <v>0.8468530178070068</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8340944945812225</v>
+        <v>0.840150386095047</v>
       </c>
     </row>
     <row r="14">
@@ -1056,27 +1056,27 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>鈴木勉</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Phung-Duc Tuan</t>
+          <t>八森正泰</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>八森 正泰</t>
+          <t>和田健太郎</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.8803897202014923</v>
+        <v>0.8803897500038147</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8714250326156616</v>
+        <v>0.8703752756118774</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8703752756118774</v>
+        <v>0.8675501644611359</v>
       </c>
     </row>
     <row r="15">
@@ -1102,27 +1102,27 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Phung-Duc Tuan</t>
+          <t>和田健太郎</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>和田 健太郎</t>
+          <t>鈴木勉</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>岡本直久</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0.8797307312488556</v>
+        <v>0.8746518194675446</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8746517300605774</v>
+        <v>0.8738219439983368</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8738219738006592</v>
+        <v>0.8692348003387451</v>
       </c>
     </row>
     <row r="16">
@@ -1148,24 +1148,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>有馬 澄佳</t>
+          <t>有馬澄佳</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>吉瀬 章子</t>
+          <t>吉瀬章子</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>繁野麻衣子</t>
         </is>
       </c>
       <c r="H16" t="n">
         <v>0.87470942735672</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8685945868492126</v>
+        <v>0.8685948252677917</v>
       </c>
       <c r="J16" t="n">
         <v>0.8660972416400909</v>
@@ -1194,27 +1194,27 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>秋山 英三</t>
+          <t>讃井知</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>上市 秀雄</t>
+          <t>秋山英三</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>澤 亮治</t>
+          <t>上市秀雄</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.8568487763404846</v>
+        <v>0.8663342595100403</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8562292456626892</v>
+        <v>0.856848806142807</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8532317876815796</v>
+        <v>0.8562292158603668</v>
       </c>
     </row>
     <row r="18">
@@ -1240,27 +1240,27 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>高野 祐一</t>
+          <t>高野祐一</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>有馬 澄佳</t>
+          <t>有馬澄佳</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phung-Duc Tuan</t>
+          <t>黒瀬雄大</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0.8732324242591858</v>
+        <v>0.873232513666153</v>
       </c>
       <c r="I18" t="n">
         <v>0.8712161481380463</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8679117560386658</v>
+        <v>0.8647022247314453</v>
       </c>
     </row>
     <row r="19">
@@ -1286,17 +1286,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>イリチュ 美佳</t>
+          <t>イリチュ美佳</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>有馬 澄佳</t>
+          <t>有馬澄佳</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>川島宏一</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -1306,7 +1306,7 @@
         <v>0.8616419732570648</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8606039583683014</v>
+        <v>0.8606040179729462</v>
       </c>
     </row>
     <row r="20">
@@ -1332,27 +1332,27 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>澤 亮治</t>
+          <t>阿武秀和</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>和田 健太郎</t>
+          <t>澤亮治</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phung-Duc Tuan</t>
+          <t>和田健太郎</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0.8796173334121704</v>
+        <v>0.8815976977348328</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8772619664669037</v>
+        <v>0.8796173930168152</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8653758466243744</v>
+        <v>0.877262145280838</v>
       </c>
     </row>
     <row r="21">
@@ -1378,27 +1378,27 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Phung-Duc Tuan</t>
+          <t>吉瀬章子</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>吉瀬 章子</t>
+          <t>高野祐一</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>高野 祐一</t>
+          <t>有馬澄佳</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.8639067411422729</v>
+        <v>0.8556961417198181</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8556961417198181</v>
+        <v>0.8522175550460815</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8522175550460815</v>
+        <v>0.8516494035720825</v>
       </c>
     </row>
     <row r="22">
@@ -1424,12 +1424,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>鈴木勉</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>渡邉 俊</t>
+          <t>渡邉俊</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1441,10 +1441,10 @@
         <v>0.8829725384712219</v>
       </c>
       <c r="I22" t="n">
-        <v>0.876095712184906</v>
+        <v>0.8760957717895508</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8759442865848541</v>
+        <v>0.8759441375732422</v>
       </c>
     </row>
     <row r="23">
@@ -1470,27 +1470,27 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>牛島光一</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
+          <t>佐野幸恵</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>有馬 澄佳</t>
+          <t>有馬澄佳</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0.8582464754581451</v>
+        <v>0.858246386051178</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8524556457996368</v>
+        <v>0.8524554967880249</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8519751727581024</v>
+        <v>0.8519752025604248</v>
       </c>
     </row>
     <row r="24">
@@ -1516,27 +1516,27 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>イリチュ 美佳</t>
+          <t>岡本翔平</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>小西葉子</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>作道 真理</t>
+          <t>イリチュ美佳</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0.8524296581745148</v>
+        <v>0.8589707612991333</v>
       </c>
       <c r="I24" t="n">
-        <v>0.851289689540863</v>
+        <v>0.8557016253471375</v>
       </c>
       <c r="J24" t="n">
-        <v>0.8504915237426758</v>
+        <v>0.8524296879768372</v>
       </c>
     </row>
     <row r="25">
@@ -1562,27 +1562,27 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
+          <t>佐野幸恵</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>上市 秀雄</t>
+          <t>上市秀雄</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>讃井知</t>
         </is>
       </c>
       <c r="H25" t="n">
         <v>0.8711104393005371</v>
       </c>
       <c r="I25" t="n">
-        <v>0.864437609910965</v>
+        <v>0.8644373416900635</v>
       </c>
       <c r="J25" t="n">
-        <v>0.8598762452602386</v>
+        <v>0.8609387874603271</v>
       </c>
     </row>
     <row r="26">
@@ -1608,27 +1608,27 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>秋山 英三</t>
+          <t>秋山英三</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>黒瀬 雄大</t>
+          <t>三崎広海</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>小西葉子</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0.8609837889671326</v>
+        <v>0.8609838783740997</v>
       </c>
       <c r="I26" t="n">
-        <v>0.8582098484039307</v>
+        <v>0.8606992065906525</v>
       </c>
       <c r="J26" t="n">
-        <v>0.8581588268280029</v>
+        <v>0.8603500425815582</v>
       </c>
     </row>
     <row r="27">
@@ -1654,27 +1654,27 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>上市 秀雄</t>
+          <t>上市秀雄</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>川島宏一</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>岡田 幸彦</t>
+          <t>岡本翔平</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0.8587649166584015</v>
+        <v>0.8587648272514343</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8570154309272766</v>
+        <v>0.8570155799388885</v>
       </c>
       <c r="J27" t="n">
-        <v>0.8559012413024902</v>
+        <v>0.8550840020179749</v>
       </c>
     </row>
     <row r="28">
@@ -1700,24 +1700,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>有馬 澄佳</t>
+          <t>有馬澄佳</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>吉瀬 章子</t>
+          <t>吉瀬章子</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>繁野麻衣子</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0.8741349875926971</v>
+        <v>0.8741349577903748</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8709458708763123</v>
+        <v>0.8709459602832794</v>
       </c>
       <c r="J28" t="n">
         <v>0.8677204847335815</v>
@@ -1746,27 +1746,27 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>有馬 澄佳</t>
+          <t>有馬澄佳</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>牛島光一</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>高野 祐一</t>
+          <t>高野祐一</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0.8854928612709045</v>
+        <v>0.8854930698871613</v>
       </c>
       <c r="I29" t="n">
-        <v>0.8639019131660461</v>
+        <v>0.8639018535614014</v>
       </c>
       <c r="J29" t="n">
-        <v>0.8634551465511322</v>
+        <v>0.863455206155777</v>
       </c>
     </row>
     <row r="30">
@@ -1792,27 +1792,27 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Phung-Duc Tuan</t>
+          <t>川島宏一</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>鈴木勉</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>岡田 幸彦</t>
+          <t>張勇兵</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>0.8844201862812042</v>
+        <v>0.8559956550598145</v>
       </c>
       <c r="I30" t="n">
-        <v>0.8559956848621368</v>
+        <v>0.852905809879303</v>
       </c>
       <c r="J30" t="n">
-        <v>0.8549237251281738</v>
+        <v>0.8527995347976685</v>
       </c>
     </row>
     <row r="31">
@@ -1838,17 +1838,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>黒瀬 雄大</t>
+          <t>黒瀬雄大</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>秋山 英三</t>
+          <t>秋山英三</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>有田 智一</t>
+          <t>有田智一</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -1884,27 +1884,27 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>梅本通孝</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>甲斐田 直子</t>
+          <t>川島宏一</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
+          <t>讃井知</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0.8575133681297302</v>
+        <v>0.8718172013759613</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8518452048301697</v>
+        <v>0.857513427734375</v>
       </c>
       <c r="J32" t="n">
-        <v>0.8510266542434692</v>
+        <v>0.8540211617946625</v>
       </c>
     </row>
     <row r="33">
@@ -1930,27 +1930,27 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
+          <t>岡本翔平</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>甲斐田 直子</t>
+          <t>讃井知</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>佐野幸恵</t>
         </is>
       </c>
       <c r="H33" t="n">
+        <v>0.8646641969680786</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.8642511367797852</v>
+      </c>
+      <c r="J33" t="n">
         <v>0.8624968230724335</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.8579478859901428</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0.8577742576599121</v>
       </c>
     </row>
     <row r="34">
@@ -1976,27 +1976,27 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>雨宮 護</t>
+          <t>讃井知</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>雨宮護</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>山本 幸子</t>
+          <t>川島宏一</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>0.8634572327136993</v>
+        <v>0.8659263253211975</v>
       </c>
       <c r="I34" t="n">
-        <v>0.8626152276992798</v>
+        <v>0.8634572923183441</v>
       </c>
       <c r="J34" t="n">
-        <v>0.8595913052558899</v>
+        <v>0.8626151084899902</v>
       </c>
     </row>
     <row r="35">
@@ -2022,27 +2022,27 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>山本 幸子</t>
+          <t>山本幸子</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>有田 智一</t>
+          <t>有田智一</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>渡邉 俊</t>
+          <t>渡邉俊</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>0.8801654279232025</v>
+        <v>0.8801655769348145</v>
       </c>
       <c r="I35" t="n">
-        <v>0.8784414529800415</v>
+        <v>0.8784414231777191</v>
       </c>
       <c r="J35" t="n">
-        <v>0.8745454549789429</v>
+        <v>0.8745453953742981</v>
       </c>
     </row>
     <row r="36">
@@ -2068,27 +2068,27 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>太田 充</t>
+          <t>太田充</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>牛島光一</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>鈴木勉</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>0.875926673412323</v>
+        <v>0.8759267032146454</v>
       </c>
       <c r="I36" t="n">
-        <v>0.8731177151203156</v>
+        <v>0.8731177449226379</v>
       </c>
       <c r="J36" t="n">
-        <v>0.870147168636322</v>
+        <v>0.8701472282409668</v>
       </c>
     </row>
     <row r="37">
@@ -2114,27 +2114,27 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>川島宏一</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>牛島光一</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>鈴木勉</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>0.881214052438736</v>
+        <v>0.8812141716480255</v>
       </c>
       <c r="I37" t="n">
-        <v>0.8785417675971985</v>
+        <v>0.8785417973995209</v>
       </c>
       <c r="J37" t="n">
-        <v>0.8743588924407959</v>
+        <v>0.8743590414524078</v>
       </c>
     </row>
     <row r="38">
@@ -2160,27 +2160,27 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>山本 幸子</t>
+          <t>山本幸子</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>川島宏一</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>渡邉 俊</t>
+          <t>讃井知</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>0.8687264025211334</v>
+        <v>0.8687266111373901</v>
       </c>
       <c r="I38" t="n">
         <v>0.8683319091796875</v>
       </c>
       <c r="J38" t="n">
-        <v>0.8629850745201111</v>
+        <v>0.8674037456512451</v>
       </c>
     </row>
     <row r="39">
@@ -2206,27 +2206,27 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>鈴木勉</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>川島宏一</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>渡邉 俊</t>
+          <t>渡邉俊</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>0.8869522213935852</v>
+        <v>0.8869521021842957</v>
       </c>
       <c r="I39" t="n">
-        <v>0.8798271119594574</v>
+        <v>0.8798272311687469</v>
       </c>
       <c r="J39" t="n">
-        <v>0.8780929446220398</v>
+        <v>0.8780930638313293</v>
       </c>
     </row>
     <row r="40">
@@ -2252,27 +2252,27 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>鈴木勉</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>堤 盛人</t>
+          <t>堤盛人</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>太田 充</t>
+          <t>太田充</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>0.8817869424819946</v>
+        <v>0.8817867934703827</v>
       </c>
       <c r="I40" t="n">
         <v>0.8813002407550812</v>
       </c>
       <c r="J40" t="n">
-        <v>0.8805910348892212</v>
+        <v>0.8805911839008331</v>
       </c>
     </row>
     <row r="41">
@@ -2298,27 +2298,27 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>堤 盛人</t>
+          <t>堤盛人</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>梅本通孝</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>川島宏一</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>0.8820194900035858</v>
+        <v>0.8820194005966187</v>
       </c>
       <c r="I41" t="n">
-        <v>0.870810478925705</v>
+        <v>0.8765389025211334</v>
       </c>
       <c r="J41" t="n">
-        <v>0.8667832314968109</v>
+        <v>0.8708105087280273</v>
       </c>
     </row>
     <row r="42">
@@ -2344,27 +2344,27 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>雨宮 護</t>
+          <t>讃井知</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>雨宮護</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>浦田淳司</t>
+          <t>川島宏一</t>
         </is>
       </c>
       <c r="H42" t="n">
+        <v>0.8671787083148956</v>
+      </c>
+      <c r="I42" t="n">
         <v>0.8621289134025574</v>
       </c>
-      <c r="I42" t="n">
-        <v>0.8617661893367767</v>
-      </c>
       <c r="J42" t="n">
-        <v>0.8502079844474792</v>
+        <v>0.8617662489414215</v>
       </c>
     </row>
     <row r="43">
@@ -2390,27 +2390,27 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>渡邉 俊</t>
+          <t>渡邉俊</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>讃井知</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>雨宮 護</t>
+          <t>鈴木勉</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>0.873240202665329</v>
+        <v>0.8732402622699738</v>
       </c>
       <c r="I43" t="n">
+        <v>0.8722307682037354</v>
+      </c>
+      <c r="J43" t="n">
         <v>0.8673423528671265</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0.8658006191253662</v>
       </c>
     </row>
     <row r="44">
@@ -2436,27 +2436,27 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>川島宏一</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>藤川 昌樹</t>
+          <t>讃井知</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>雨宮 護</t>
+          <t>藤川昌樹</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>0.8610955774784088</v>
+        <v>0.8610954582691193</v>
       </c>
       <c r="I44" t="n">
+        <v>0.8604769706726074</v>
+      </c>
+      <c r="J44" t="n">
         <v>0.8600713014602661</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0.8588992953300476</v>
       </c>
     </row>
     <row r="45">
@@ -2482,21 +2482,21 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>渡邉 俊</t>
+          <t>渡邉俊</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>藤川 昌樹</t>
+          <t>藤川昌樹</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>松原 康介</t>
+          <t>松原康介</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0.88481405377388</v>
+        <v>0.8848141133785248</v>
       </c>
       <c r="I45" t="n">
         <v>0.884340912103653</v>
@@ -2528,27 +2528,27 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>張勇兵</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>八森 正泰</t>
+          <t>鈴木勉</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>山本 幸子</t>
+          <t>八森正泰</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>0.8637301921844482</v>
+        <v>0.8679175674915314</v>
       </c>
       <c r="I46" t="n">
+        <v>0.8637300729751587</v>
+      </c>
+      <c r="J46" t="n">
         <v>0.8612132370471954</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0.8606871068477631</v>
       </c>
     </row>
     <row r="47">
@@ -2574,27 +2574,27 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>川島宏一</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>太田 充</t>
+          <t>太田充</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>牛島光一</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>0.882245659828186</v>
+        <v>0.8822457492351532</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8808684349060059</v>
+        <v>0.8808684647083282</v>
       </c>
       <c r="J47" t="n">
-        <v>0.8796663582324982</v>
+        <v>0.8796663880348206</v>
       </c>
     </row>
     <row r="48">
@@ -2620,27 +2620,27 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>岡本 直久</t>
+          <t>岡本直久</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>牛島光一</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>梅本通孝</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>0.876221776008606</v>
+        <v>0.8762216567993164</v>
       </c>
       <c r="I48" t="n">
         <v>0.8687419593334198</v>
       </c>
       <c r="J48" t="n">
-        <v>0.8655958473682404</v>
+        <v>0.8667345643043518</v>
       </c>
     </row>
     <row r="49">
@@ -2666,27 +2666,27 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>岡本 直久</t>
+          <t>岡本直久</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>藤川 昌樹</t>
+          <t>藤川昌樹</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>渡邉 俊</t>
+          <t>渡邉俊</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0.8662878572940826</v>
+        <v>0.8662877678871155</v>
       </c>
       <c r="I49" t="n">
         <v>0.8646083772182465</v>
       </c>
       <c r="J49" t="n">
-        <v>0.8645975589752197</v>
+        <v>0.8645975291728973</v>
       </c>
     </row>
     <row r="50">
@@ -2712,27 +2712,27 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>鈴木勉</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>岡本 直久</t>
+          <t>岡本直久</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>和田 健太郎</t>
+          <t>和田健太郎</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>0.8832988440990448</v>
+        <v>0.8832989037036896</v>
       </c>
       <c r="I50" t="n">
-        <v>0.8805749118328094</v>
+        <v>0.8805747926235199</v>
       </c>
       <c r="J50" t="n">
-        <v>0.8780884444713593</v>
+        <v>0.878088504076004</v>
       </c>
     </row>
     <row r="51">
@@ -2758,27 +2758,27 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>雨宮 護</t>
+          <t>讃井知</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>雨宮護</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>浦田淳司</t>
+          <t>川島宏一</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>0.862365186214447</v>
+        <v>0.8624387383460999</v>
       </c>
       <c r="I51" t="n">
-        <v>0.8559725284576416</v>
+        <v>0.862365335226059</v>
       </c>
       <c r="J51" t="n">
-        <v>0.8511845767498016</v>
+        <v>0.8559727668762207</v>
       </c>
     </row>
     <row r="52">
@@ -2804,27 +2804,27 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>鈴木勉</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>牛島光一</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>小西葉子</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>0.8599999845027924</v>
+        <v>0.8600000739097595</v>
       </c>
       <c r="I52" t="n">
         <v>0.8592597246170044</v>
       </c>
       <c r="J52" t="n">
-        <v>0.8564841449260712</v>
+        <v>0.8584930300712585</v>
       </c>
     </row>
     <row r="53">
@@ -2850,27 +2850,27 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>岡本翔平</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>太田 充</t>
+          <t>牛島光一</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>太田充</t>
         </is>
       </c>
       <c r="H53" t="n">
+        <v>0.8763241469860077</v>
+      </c>
+      <c r="I53" t="n">
         <v>0.8757403492927551</v>
       </c>
-      <c r="I53" t="n">
-        <v>0.871347576379776</v>
-      </c>
       <c r="J53" t="n">
-        <v>0.8705988824367523</v>
+        <v>0.8713475465774536</v>
       </c>
     </row>
     <row r="54">
@@ -2896,27 +2896,27 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>鈴木勉</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>堤 盛人</t>
+          <t>谷口守</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>堤盛人</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>0.8668387234210968</v>
+        <v>0.866838663816452</v>
       </c>
       <c r="I54" t="n">
+        <v>0.8643345534801483</v>
+      </c>
+      <c r="J54" t="n">
         <v>0.8634083867073059</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0.8591557145118713</v>
       </c>
     </row>
     <row r="55">
@@ -2942,27 +2942,27 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>牛島光一</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>太田 充</t>
+          <t>大久保正勝</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>甲斐田 直子</t>
+          <t>太田充</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0.8447581231594086</v>
+        <v>0.8447581827640533</v>
       </c>
       <c r="I55" t="n">
+        <v>0.8440878391265869</v>
+      </c>
+      <c r="J55" t="n">
         <v>0.8435723781585693</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0.8434951305389404</v>
       </c>
     </row>
     <row r="56">
@@ -2988,27 +2988,27 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>岡本 直久</t>
+          <t>岡本直久</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>和田 健太郎</t>
+          <t>和田健太郎</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>鈴木勉</t>
         </is>
       </c>
       <c r="H56" t="n">
         <v>0.8806582093238831</v>
       </c>
       <c r="I56" t="n">
-        <v>0.8782493770122528</v>
+        <v>0.87824946641922</v>
       </c>
       <c r="J56" t="n">
-        <v>0.8735232651233673</v>
+        <v>0.8735235035419464</v>
       </c>
     </row>
     <row r="57">
@@ -3034,27 +3034,27 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>上市 秀雄</t>
+          <t>讃井知</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>甲斐田 直子</t>
+          <t>上市秀雄</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>松原 康介</t>
+          <t>甲斐田直子</t>
         </is>
       </c>
       <c r="H57" t="n">
+        <v>0.8453637659549713</v>
+      </c>
+      <c r="I57" t="n">
         <v>0.8431252837181091</v>
       </c>
-      <c r="I57" t="n">
-        <v>0.8418350219726562</v>
-      </c>
       <c r="J57" t="n">
-        <v>0.8402624726295471</v>
+        <v>0.8418351113796234</v>
       </c>
     </row>
     <row r="58">
@@ -3080,27 +3080,27 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>和田 健太郎</t>
+          <t>和田健太郎</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>鈴木勉</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>牛島光一</t>
         </is>
       </c>
       <c r="H58" t="n">
         <v>0.8711833655834198</v>
       </c>
       <c r="I58" t="n">
-        <v>0.8702839016914368</v>
+        <v>0.8702840805053711</v>
       </c>
       <c r="J58" t="n">
-        <v>0.8700034916400909</v>
+        <v>0.8700034618377686</v>
       </c>
     </row>
     <row r="59">
@@ -3126,27 +3126,27 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>岡本 直久</t>
+          <t>長崎滉大</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>和田 健太郎</t>
+          <t>岡本直久</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phung-Duc Tuan</t>
+          <t>和田健太郎</t>
         </is>
       </c>
       <c r="H59" t="n">
+        <v>0.8824211359024048</v>
+      </c>
+      <c r="I59" t="n">
         <v>0.8817901909351349</v>
       </c>
-      <c r="I59" t="n">
-        <v>0.8766685426235199</v>
-      </c>
       <c r="J59" t="n">
-        <v>0.8756954669952393</v>
+        <v>0.8766686320304871</v>
       </c>
     </row>
     <row r="60">
@@ -3172,27 +3172,27 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>鈴木勉</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>黒瀬 雄大</t>
+          <t>黒瀬雄大</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>川島宏一</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>0.8746653497219086</v>
+        <v>0.874665379524231</v>
       </c>
       <c r="I60" t="n">
         <v>0.8743585348129272</v>
       </c>
       <c r="J60" t="n">
-        <v>0.86818528175354</v>
+        <v>0.8681854605674744</v>
       </c>
     </row>
     <row r="61">
@@ -3218,27 +3218,27 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>甲斐田 直子</t>
+          <t>甲斐田直子</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>川島宏一</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>讃井知</t>
         </is>
       </c>
       <c r="H61" t="n">
         <v>0.8799073100090027</v>
       </c>
       <c r="I61" t="n">
-        <v>0.876029908657074</v>
+        <v>0.8760300278663635</v>
       </c>
       <c r="J61" t="n">
-        <v>0.8742002546787262</v>
+        <v>0.874771922826767</v>
       </c>
     </row>
     <row r="62">
@@ -3264,27 +3264,27 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>梅本通孝</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>鈴木勉</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>村上 暁信</t>
+          <t>讃井知</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>0.8276543617248535</v>
+        <v>0.8310251235961914</v>
       </c>
       <c r="I62" t="n">
-        <v>0.8261333703994751</v>
+        <v>0.8276545107364655</v>
       </c>
       <c r="J62" t="n">
-        <v>0.8258125185966492</v>
+        <v>0.827650785446167</v>
       </c>
     </row>
     <row r="63">
@@ -3310,27 +3310,27 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>讃井知</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>甲斐田 直子</t>
+          <t>川島宏一</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
+          <t>甲斐田直子</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>0.8604454696178436</v>
+        <v>0.8619557023048401</v>
       </c>
       <c r="I63" t="n">
-        <v>0.8598349392414093</v>
+        <v>0.8604455292224884</v>
       </c>
       <c r="J63" t="n">
-        <v>0.8570573329925537</v>
+        <v>0.8598349094390869</v>
       </c>
     </row>
     <row r="64">
@@ -3356,24 +3356,24 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>甲斐田 直子</t>
+          <t>甲斐田直子</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>谷口 綾子</t>
+          <t>谷口綾子</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>澤 亮治</t>
+          <t>澤亮治</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>0.883257269859314</v>
+        <v>0.8832572996616364</v>
       </c>
       <c r="I64" t="n">
-        <v>0.8624672293663025</v>
+        <v>0.8624671101570129</v>
       </c>
       <c r="J64" t="n">
         <v>0.8614659905433655</v>
@@ -3402,27 +3402,27 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>渡邉 俊</t>
+          <t>渡邉俊</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>川島宏一</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>太田 充</t>
+          <t>太田充</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>0.8763948082923889</v>
+        <v>0.8763947486877441</v>
       </c>
       <c r="I65" t="n">
-        <v>0.8731105923652649</v>
+        <v>0.8731106221675873</v>
       </c>
       <c r="J65" t="n">
-        <v>0.8720406889915466</v>
+        <v>0.8720408380031586</v>
       </c>
     </row>
     <row r="66">
@@ -3448,27 +3448,27 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>鈴木勉</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>川島宏一</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>渡邉 俊</t>
+          <t>渡邉俊</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>0.8690553903579712</v>
+        <v>0.8690553307533264</v>
       </c>
       <c r="I66" t="n">
         <v>0.865460604429245</v>
       </c>
       <c r="J66" t="n">
-        <v>0.8637252449989319</v>
+        <v>0.8637253046035767</v>
       </c>
     </row>
     <row r="67">
@@ -3494,27 +3494,27 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>渡邉 俊</t>
+          <t>渡邉俊</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>有田 智一</t>
+          <t>有田智一</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>川島宏一</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>0.8704354166984558</v>
+        <v>0.8704356253147125</v>
       </c>
       <c r="I67" t="n">
-        <v>0.8688648343086243</v>
+        <v>0.8688648045063019</v>
       </c>
       <c r="J67" t="n">
-        <v>0.8686460256576538</v>
+        <v>0.8686460554599762</v>
       </c>
     </row>
     <row r="68">
@@ -3540,27 +3540,27 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>秋山 英三</t>
+          <t>秋山英三</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>上市 秀雄</t>
+          <t>上市秀雄</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>澤 亮治</t>
+          <t>讃井知</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>0.851887583732605</v>
+        <v>0.8518876731395721</v>
       </c>
       <c r="I68" t="n">
-        <v>0.8515320420265198</v>
+        <v>0.8515321016311646</v>
       </c>
       <c r="J68" t="n">
-        <v>0.8441035449504852</v>
+        <v>0.8461630642414093</v>
       </c>
     </row>
     <row r="69">
@@ -3586,27 +3586,27 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>牛島光一</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>秋山 英三</t>
+          <t>讃井知</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>堤 盛人</t>
+          <t>秋山英三</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>0.8769174814224243</v>
+        <v>0.8769174218177795</v>
       </c>
       <c r="I69" t="n">
-        <v>0.8631938099861145</v>
+        <v>0.8657227754592896</v>
       </c>
       <c r="J69" t="n">
-        <v>0.8606486916542053</v>
+        <v>0.8631939291954041</v>
       </c>
     </row>
     <row r="70">
@@ -3632,27 +3632,27 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>小西葉子</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>川島宏一</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>堤 盛人</t>
+          <t>牛島光一</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>0.8721948266029358</v>
+        <v>0.8752852082252502</v>
       </c>
       <c r="I70" t="n">
-        <v>0.8721112906932831</v>
+        <v>0.8721947968006134</v>
       </c>
       <c r="J70" t="n">
-        <v>0.8718703389167786</v>
+        <v>0.8721112310886383</v>
       </c>
     </row>
     <row r="71">
@@ -3678,27 +3678,27 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>川島宏一</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>原田 信行</t>
+          <t>原田信行</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>甲斐田 直子</t>
+          <t>甲斐田直子</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>0.8696562647819519</v>
+        <v>0.8696563541889191</v>
       </c>
       <c r="I71" t="n">
         <v>0.8675041198730469</v>
       </c>
       <c r="J71" t="n">
-        <v>0.8670807778835297</v>
+        <v>0.8670808672904968</v>
       </c>
     </row>
     <row r="72">
@@ -3724,27 +3724,27 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>鈴木勉</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>山野博哉</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>太田 充</t>
+          <t>牛島光一</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>0.860741138458252</v>
+        <v>0.8607411682605743</v>
       </c>
       <c r="I72" t="n">
-        <v>0.8596481680870056</v>
+        <v>0.8598228096961975</v>
       </c>
       <c r="J72" t="n">
-        <v>0.859329879283905</v>
+        <v>0.8596481382846832</v>
       </c>
     </row>
     <row r="73">
@@ -3770,17 +3770,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>鈴木勉</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>和田 健太郎</t>
+          <t>和田健太郎</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>岡本 直久</t>
+          <t>岡本直久</t>
         </is>
       </c>
       <c r="H73" t="n">
@@ -3816,27 +3816,27 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>鈴木勉</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>牛島光一</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>川島宏一</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>0.8715938031673431</v>
+        <v>0.8715937733650208</v>
       </c>
       <c r="I74" t="n">
-        <v>0.8709505200386047</v>
+        <v>0.87095046043396</v>
       </c>
       <c r="J74" t="n">
-        <v>0.8709364831447601</v>
+        <v>0.8709364533424377</v>
       </c>
     </row>
     <row r="75">
@@ -3862,27 +3862,27 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>鈴木勉</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Phung-Duc Tuan</t>
+          <t>和田健太郎</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>和田 健太郎</t>
+          <t>長崎滉大</t>
         </is>
       </c>
       <c r="H75" t="n">
         <v>0.8804836571216583</v>
       </c>
       <c r="I75" t="n">
-        <v>0.879767507314682</v>
+        <v>0.8787779808044434</v>
       </c>
       <c r="J75" t="n">
-        <v>0.8787780106067657</v>
+        <v>0.876759946346283</v>
       </c>
     </row>
     <row r="76">
@@ -3908,24 +3908,24 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Phung-Duc Tuan</t>
+          <t>長崎滉大</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>鈴木勉</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>和田 健太郎</t>
+          <t>和田健太郎</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>0.8646460771560669</v>
+        <v>0.8642684817314148</v>
       </c>
       <c r="I76" t="n">
-        <v>0.8588454723358154</v>
+        <v>0.858845442533493</v>
       </c>
       <c r="J76" t="n">
         <v>0.8584803938865662</v>
@@ -3954,27 +3954,27 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>鈴木勉</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Phung-Duc Tuan</t>
+          <t>長崎滉大</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>八森 正泰</t>
+          <t>八森正泰</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>0.8770517706871033</v>
+        <v>0.8770516812801361</v>
       </c>
       <c r="I77" t="n">
-        <v>0.8737709820270538</v>
+        <v>0.8761831521987915</v>
       </c>
       <c r="J77" t="n">
-        <v>0.8715194463729858</v>
+        <v>0.8715193271636963</v>
       </c>
     </row>
     <row r="78">
@@ -4000,27 +4000,27 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>太田 充</t>
+          <t>太田充</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>牛島光一</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>堤 盛人</t>
+          <t>堤盛人</t>
         </is>
       </c>
       <c r="H78" t="n">
         <v>0.880396842956543</v>
       </c>
       <c r="I78" t="n">
-        <v>0.8773620128631592</v>
+        <v>0.8773620426654816</v>
       </c>
       <c r="J78" t="n">
-        <v>0.8741997182369232</v>
+        <v>0.8741994500160217</v>
       </c>
     </row>
     <row r="79">
@@ -4046,27 +4046,27 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>牛島光一</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>岡本翔平</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>甲斐田 直子</t>
+          <t>讃井知</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>0.8768567442893982</v>
+        <v>0.8768567144870758</v>
       </c>
       <c r="I79" t="n">
-        <v>0.8671047687530518</v>
+        <v>0.8733054995536804</v>
       </c>
       <c r="J79" t="n">
-        <v>0.8661922812461853</v>
+        <v>0.867338240146637</v>
       </c>
     </row>
     <row r="80">
@@ -4092,27 +4092,27 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>牛島光一</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>太田 充</t>
+          <t>太田充</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>堤 盛人</t>
+          <t>堤盛人</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>0.8574394285678864</v>
+        <v>0.8574393689632416</v>
       </c>
       <c r="I80" t="n">
-        <v>0.8544398546218872</v>
+        <v>0.8544398844242096</v>
       </c>
       <c r="J80" t="n">
-        <v>0.8538867235183716</v>
+        <v>0.853886753320694</v>
       </c>
     </row>
     <row r="81">
@@ -4138,27 +4138,27 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
+          <t>小西葉子</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>讃井知</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
           <t>浦田淳司</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>岡本 直久</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>佐野 幸恵</t>
-        </is>
-      </c>
       <c r="H81" t="n">
-        <v>0.8557762801647186</v>
+        <v>0.8598234951496124</v>
       </c>
       <c r="I81" t="n">
-        <v>0.8549925088882446</v>
+        <v>0.8560390472412109</v>
       </c>
       <c r="J81" t="n">
-        <v>0.8544768095016479</v>
+        <v>0.8557764291763306</v>
       </c>
     </row>
     <row r="82">
@@ -4184,27 +4184,27 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
+          <t>小西葉子</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>佐野幸恵</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>上市 秀雄</t>
+          <t>牛島光一</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>0.8526224195957184</v>
+        <v>0.853056937456131</v>
       </c>
       <c r="I82" t="n">
-        <v>0.8521038889884949</v>
+        <v>0.852622389793396</v>
       </c>
       <c r="J82" t="n">
-        <v>0.8483676016330719</v>
+        <v>0.8521038293838501</v>
       </c>
     </row>
     <row r="83">
@@ -4230,27 +4230,27 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>小西葉子</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>原田 信行</t>
+          <t>牛島光一</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>上市 秀雄</t>
+          <t>原田信行</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>0.8530831038951874</v>
+        <v>0.85500568151474</v>
       </c>
       <c r="I83" t="n">
+        <v>0.853083074092865</v>
+      </c>
+      <c r="J83" t="n">
         <v>0.8515084087848663</v>
-      </c>
-      <c r="J83" t="n">
-        <v>0.8503592908382416</v>
       </c>
     </row>
     <row r="84">
@@ -4276,27 +4276,27 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>山野博哉</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>牛島光一</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>イリチュ 美佳</t>
+          <t>川島宏一</t>
         </is>
       </c>
       <c r="H84" t="n">
+        <v>0.856723815202713</v>
+      </c>
+      <c r="I84" t="n">
         <v>0.8473110795021057</v>
       </c>
-      <c r="I84" t="n">
+      <c r="J84" t="n">
         <v>0.8449655175209045</v>
-      </c>
-      <c r="J84" t="n">
-        <v>0.8399158716201782</v>
       </c>
     </row>
   </sheetData>
@@ -4384,27 +4384,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>イリチュ 美佳</t>
+          <t>イリチュ美佳</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>高野 祐一</t>
+          <t>高野祐一</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>上市 秀雄</t>
+          <t>上市秀雄</t>
         </is>
       </c>
       <c r="H2" t="n">
         <v>0.8635274171829224</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8589865863323212</v>
+        <v>0.8589867353439331</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8573169112205505</v>
+        <v>0.857316792011261</v>
       </c>
     </row>
     <row r="3">
@@ -4426,27 +4426,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>吉瀬 章子</t>
+          <t>吉瀬章子</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>八森 正泰</t>
+          <t>八森正泰</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phung-Duc Tuan</t>
+          <t>張勇兵</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.8609103560447693</v>
+        <v>0.8609104454517365</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8542723953723907</v>
+        <v>0.8542724251747131</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8513311147689819</v>
+        <v>0.8489381372928619</v>
       </c>
     </row>
     <row r="4">
@@ -4468,27 +4468,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>吉瀬 章子</t>
+          <t>吉瀬章子</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>八森 正泰</t>
+          <t>八森正泰</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phung-Duc Tuan</t>
+          <t>繁野麻衣子</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.8563421070575714</v>
+        <v>0.8563420474529266</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8483154773712158</v>
+        <v>0.848315566778183</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8472438752651215</v>
+        <v>0.8436665534973145</v>
       </c>
     </row>
     <row r="5">
@@ -4510,27 +4510,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>吉瀬 章子</t>
+          <t>吉瀬章子</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>繁野麻衣子</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phung-Duc Tuan</t>
+          <t>有馬澄佳</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.8748292922973633</v>
+        <v>0.8748291730880737</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8652165830135345</v>
+        <v>0.865216463804245</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8607003390789032</v>
+        <v>0.8598293960094452</v>
       </c>
     </row>
     <row r="6">
@@ -4552,24 +4552,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>讃井知</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>上市 秀雄</t>
+          <t>上市秀雄</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>イリチュ 美佳</t>
+          <t>イリチュ美佳</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.8752143979072571</v>
+        <v>0.873845100402832</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8730535209178925</v>
+        <v>0.8730534017086029</v>
       </c>
       <c r="J6" t="n">
         <v>0.8719890415668488</v>
@@ -4594,27 +4594,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
+          <t>佐野幸恵</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>上市 秀雄</t>
+          <t>上市秀雄</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>張勇兵</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.8805915415287018</v>
+        <v>0.8805915117263794</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8642038404941559</v>
+        <v>0.8642037510871887</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8563596606254578</v>
+        <v>0.8553867936134338</v>
       </c>
     </row>
     <row r="8">
@@ -4636,24 +4636,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>吉瀬 章子</t>
+          <t>吉瀬章子</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>高野 祐一</t>
+          <t>高野祐一</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>八森 正泰</t>
+          <t>八森正泰</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.8712441325187683</v>
+        <v>0.8712440133094788</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8685609400272369</v>
+        <v>0.8685610890388489</v>
       </c>
       <c r="J8" t="n">
         <v>0.8668279051780701</v>
@@ -4678,27 +4678,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>岡田幸彦</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>岡田 幸彦</t>
+          <t>イリチュ美佳</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>イリチュ 美佳</t>
+          <t>大西正輝</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.8722025752067566</v>
+        <v>0.8625462651252747</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8625463545322418</v>
+        <v>0.8624857664108276</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8624857068061829</v>
+        <v>0.8615334928035736</v>
       </c>
     </row>
     <row r="10">
@@ -4720,24 +4720,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>吉瀬 章子</t>
+          <t>吉瀬章子</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>有馬 澄佳</t>
+          <t>有馬澄佳</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>繁野麻衣子</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.8638104796409607</v>
+        <v>0.8638104498386383</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8515419661998749</v>
+        <v>0.8515419065952301</v>
       </c>
       <c r="J10" t="n">
         <v>0.8515247106552124</v>
@@ -4762,27 +4762,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>イリチュ 美佳</t>
+          <t>イリチュ美佳</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
+          <t>佐野幸恵</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>岡田 幸彦</t>
+          <t>大西正輝</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.8766615092754364</v>
+        <v>0.8766615390777588</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8584881722927094</v>
+        <v>0.8584880828857422</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8555068969726562</v>
+        <v>0.8581428825855255</v>
       </c>
     </row>
     <row r="12">
@@ -4804,27 +4804,27 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Phung-Duc Tuan</t>
+          <t>高野祐一</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>高野 祐一</t>
+          <t>黒瀬雄大</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>黒瀬 雄大</t>
+          <t>吉瀬章子</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.8860654234886169</v>
+        <v>0.8564328551292419</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8564328849315643</v>
+        <v>0.8518258035182953</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8518258035182953</v>
+        <v>0.8504331409931183</v>
       </c>
     </row>
     <row r="13">
@@ -4846,27 +4846,27 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
+          <t>佐野幸恵</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>上市 秀雄</t>
+          <t>上市秀雄</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>イリチュ 美佳</t>
+          <t>讃井知</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.8769748210906982</v>
+        <v>0.8769749402999878</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8706704080104828</v>
+        <v>0.8706701397895813</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8549315929412842</v>
+        <v>0.8587096333503723</v>
       </c>
     </row>
     <row r="14">
@@ -4888,27 +4888,27 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>高野 祐一</t>
+          <t>高野祐一</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>黒瀬 雄大</t>
+          <t>黒瀬雄大</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>岡田 幸彦</t>
+          <t>小西葉子</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.8499734103679657</v>
+        <v>0.8499733805656433</v>
       </c>
       <c r="I14" t="n">
         <v>0.8485821783542633</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8465899229049683</v>
+        <v>0.847388744354248</v>
       </c>
     </row>
     <row r="15">
@@ -4930,24 +4930,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>岡田 幸彦</t>
+          <t>岡田幸彦</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>小西葉子</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
+          <t>佐野幸恵</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0.8566752672195435</v>
+        <v>0.8566752374172211</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8429910242557526</v>
+        <v>0.8434323072433472</v>
       </c>
       <c r="J15" t="n">
         <v>0.8424454629421234</v>
@@ -4972,27 +4972,27 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>八森 正泰</t>
+          <t>八森正泰</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Phung-Duc Tuan</t>
+          <t>吉瀬章子</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>吉瀬 章子</t>
+          <t>繁野麻衣子</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0.8690818846225739</v>
+        <v>0.8690817356109619</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8608503043651581</v>
+        <v>0.8606576025485992</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8606576025485992</v>
+        <v>0.856191098690033</v>
       </c>
     </row>
     <row r="17">
@@ -5014,27 +5014,27 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>高野 祐一</t>
+          <t>高野祐一</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>小西葉子</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>繁野麻衣子</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.8639224171638489</v>
+        <v>0.8639225661754608</v>
       </c>
       <c r="I17" t="n">
+        <v>0.8517236709594727</v>
+      </c>
+      <c r="J17" t="n">
         <v>0.8516285419464111</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.851314902305603</v>
       </c>
     </row>
     <row r="18">
@@ -5056,27 +5056,27 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>岡本 直久</t>
+          <t>岡本直久</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>浦田淳司</t>
+          <t>小西葉子</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>繁野麻衣子</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0.8556589782238007</v>
+        <v>0.8556587994098663</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8523485958576202</v>
+        <v>0.8488175570964813</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8456804156303406</v>
+        <v>0.8456803560256958</v>
       </c>
     </row>
     <row r="19">
@@ -5098,27 +5098,27 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>吉瀬 章子</t>
+          <t>吉瀬章子</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Phung-Duc Tuan</t>
+          <t>八森正泰</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>八森 正泰</t>
+          <t>繁野麻衣子</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0.8692283034324646</v>
+        <v>0.8692283630371094</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8579657673835754</v>
+        <v>0.8555294871330261</v>
       </c>
       <c r="J19" t="n">
-        <v>0.855529397726059</v>
+        <v>0.8545259237289429</v>
       </c>
     </row>
     <row r="20">
@@ -5140,27 +5140,27 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>上市 秀雄</t>
+          <t>上市秀雄</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>秋山 英三</t>
+          <t>讃井知</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
+          <t>秋山英三</t>
         </is>
       </c>
       <c r="H20" t="n">
         <v>0.8734315931797028</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8657550811767578</v>
+        <v>0.8669519126415253</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8657165765762329</v>
+        <v>0.8657552003860474</v>
       </c>
     </row>
     <row r="21">
@@ -5182,27 +5182,27 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Phung-Duc Tuan</t>
+          <t>吉瀬章子</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>八森正泰</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>吉瀬 章子</t>
+          <t>高野祐一</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.8677213788032532</v>
+        <v>0.8634407520294189</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8647889792919159</v>
+        <v>0.8590059578418732</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8634408414363861</v>
+        <v>0.857612669467926</v>
       </c>
     </row>
     <row r="22">
@@ -5224,27 +5224,27 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>岡田幸彦</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>岡田 幸彦</t>
+          <t>黒瀬雄大</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>黒瀬 雄大</t>
+          <t>原田信行</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0.8656386137008667</v>
+        <v>0.8638789355754852</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8638789355754852</v>
+        <v>0.8628188967704773</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8628188967704773</v>
+        <v>0.8613706529140472</v>
       </c>
     </row>
   </sheetData>

--- a/generated/committee_recommendations.xlsx
+++ b/generated/committee_recommendations.xlsx
@@ -504,17 +504,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>上市秀雄</t>
+          <t>上市 秀雄</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>小西葉子</t>
+          <t>小西 葉子</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>張勇兵</t>
+          <t>張 勇兵</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -524,7 +524,7 @@
         <v>0.8566808700561523</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8556444644927979</v>
+        <v>0.8556444942951202</v>
       </c>
     </row>
     <row r="3">
@@ -550,17 +550,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>牛島光一</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>岡本翔平</t>
+          <t>岡本 翔平</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>小西葉子</t>
+          <t>小西 葉子</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -596,17 +596,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>上市秀雄</t>
+          <t>上市 秀雄</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>張勇兵</t>
+          <t>張 勇兵</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>牛島光一</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -642,27 +642,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>高野祐一</t>
+          <t>高野 祐一</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>吉瀬章子</t>
+          <t>吉瀬 章子</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>澤亮治</t>
+          <t>Liu Tianxiang</t>
         </is>
       </c>
       <c r="H5" t="n">
         <v>0.8717089295387268</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8693714737892151</v>
+        <v>0.8693714141845703</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8665045499801636</v>
+        <v>0.8665716648101807</v>
       </c>
     </row>
     <row r="6">
@@ -688,17 +688,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>三崎広海</t>
+          <t>三崎 広海</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>牛島光一</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>秋山英三</t>
+          <t>岡田 幸彦</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -708,7 +708,7 @@
         <v>0.8621913194656372</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8593439757823944</v>
+        <v>0.860032320022583</v>
       </c>
     </row>
     <row r="7">
@@ -734,27 +734,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>上市秀雄</t>
+          <t>上市 秀雄</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>讃井知</t>
+          <t>讃井 知</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>甲斐田直子</t>
+          <t>甲斐田 直子</t>
         </is>
       </c>
       <c r="H7" t="n">
         <v>0.8779138922691345</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8748931884765625</v>
+        <v>0.8748932182788849</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8710569143295288</v>
+        <v>0.8710567057132721</v>
       </c>
     </row>
     <row r="8">
@@ -780,17 +780,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>阿武秀和</t>
+          <t>阿武 秀和</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>澤亮治</t>
+          <t>澤 亮治</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>張勇兵</t>
+          <t>張 勇兵</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -826,17 +826,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>阿武秀和</t>
+          <t>阿武 秀和</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>澤亮治</t>
+          <t>澤 亮治</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>八森正泰</t>
+          <t>Liu Tianxiang</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -846,7 +846,7 @@
         <v>0.8741540014743805</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8632311224937439</v>
+        <v>0.8681204319000244</v>
       </c>
     </row>
     <row r="10">
@@ -872,27 +872,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>鈴木勉</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>谷口守</t>
+          <t>太田 充</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>太田充</t>
+          <t>堤 盛人</t>
         </is>
       </c>
       <c r="H10" t="n">
         <v>0.8737158477306366</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8720432817935944</v>
+        <v>0.8714621961116791</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8714621961116791</v>
+        <v>0.8690856099128723</v>
       </c>
     </row>
     <row r="11">
@@ -918,17 +918,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>吉瀬章子</t>
+          <t>吉瀬 章子</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>八森正泰</t>
+          <t>八森 正泰</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>有馬澄佳</t>
+          <t>有馬 澄佳</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -964,17 +964,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>澤亮治</t>
+          <t>澤 亮治</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>川島宏一</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>秋山英三</t>
+          <t>秋山 英三</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -1010,24 +1010,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>八森正泰</t>
+          <t>八森 正泰</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>繁野麻衣子</t>
+          <t>繁野 麻衣子</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>阿武秀和</t>
+          <t>阿武 秀和</t>
         </is>
       </c>
       <c r="H13" t="n">
         <v>0.8598324656486511</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8468530178070068</v>
+        <v>0.8446328341960907</v>
       </c>
       <c r="J13" t="n">
         <v>0.840150386095047</v>
@@ -1056,27 +1056,27 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>鈴木勉</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>八森正泰</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>和田健太郎</t>
+          <t>八森 正泰</t>
         </is>
       </c>
       <c r="H14" t="n">
         <v>0.8803897500038147</v>
       </c>
       <c r="I14" t="n">
+        <v>0.8714250326156616</v>
+      </c>
+      <c r="J14" t="n">
         <v>0.8703752756118774</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.8675501644611359</v>
       </c>
     </row>
     <row r="15">
@@ -1102,27 +1102,27 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>和田健太郎</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>鈴木勉</t>
+          <t>和田 健太郎</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>岡本直久</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="H15" t="n">
+        <v>0.8797307312488556</v>
+      </c>
+      <c r="I15" t="n">
         <v>0.8746518194675446</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>0.8738219439983368</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.8692348003387451</v>
       </c>
     </row>
     <row r="16">
@@ -1148,27 +1148,27 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>有馬澄佳</t>
+          <t>有馬 澄佳</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>吉瀬章子</t>
+          <t>吉瀬 章子</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>繁野麻衣子</t>
+          <t>繁野 麻衣子</t>
         </is>
       </c>
       <c r="H16" t="n">
         <v>0.87470942735672</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8685948252677917</v>
+        <v>0.8685945868492126</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8660972416400909</v>
+        <v>0.8661421239376068</v>
       </c>
     </row>
     <row r="17">
@@ -1194,21 +1194,21 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>讃井知</t>
+          <t>讃井 知</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>秋山英三</t>
+          <t>秋山 英三</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>上市秀雄</t>
+          <t>上市 秀雄</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.8663342595100403</v>
+        <v>0.8663341999053955</v>
       </c>
       <c r="I17" t="n">
         <v>0.856848806142807</v>
@@ -1240,27 +1240,27 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>高野祐一</t>
+          <t>Liu Tianxiang</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>有馬澄佳</t>
+          <t>高野 祐一</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>黒瀬雄大</t>
+          <t>有馬 澄佳</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0.873232513666153</v>
+        <v>0.8786898851394653</v>
       </c>
       <c r="I18" t="n">
+        <v>0.8732324242591858</v>
+      </c>
+      <c r="J18" t="n">
         <v>0.8712161481380463</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.8647022247314453</v>
       </c>
     </row>
     <row r="19">
@@ -1286,17 +1286,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>イリチュ美佳</t>
+          <t>イリチュ 美佳</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>有馬澄佳</t>
+          <t>有馬 澄佳</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>川島宏一</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -1332,17 +1332,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>阿武秀和</t>
+          <t>阿武 秀和</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>澤亮治</t>
+          <t>澤 亮治</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>和田健太郎</t>
+          <t>和田 健太郎</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -1378,27 +1378,27 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>吉瀬章子</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>高野祐一</t>
+          <t>吉瀬 章子</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>有馬澄佳</t>
+          <t>高野 祐一</t>
         </is>
       </c>
       <c r="H21" t="n">
+        <v>0.8639067411422729</v>
+      </c>
+      <c r="I21" t="n">
         <v>0.8556961417198181</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>0.8522175550460815</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.8516494035720825</v>
       </c>
     </row>
     <row r="22">
@@ -1424,27 +1424,27 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>鈴木勉</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>渡邉俊</t>
+          <t>志田 洋平</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>浦田淳司</t>
+          <t>渡邉 俊</t>
         </is>
       </c>
       <c r="H22" t="n">
         <v>0.8829725384712219</v>
       </c>
       <c r="I22" t="n">
+        <v>0.8785969913005829</v>
+      </c>
+      <c r="J22" t="n">
         <v>0.8760957717895508</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.8759441375732422</v>
       </c>
     </row>
     <row r="23">
@@ -1470,17 +1470,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>牛島光一</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>佐野幸恵</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>有馬澄佳</t>
+          <t>有馬 澄佳</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -1516,17 +1516,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>岡本翔平</t>
+          <t>岡本 翔平</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>小西葉子</t>
+          <t>小西 葉子</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>イリチュ美佳</t>
+          <t>イリチュ 美佳</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -1562,17 +1562,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>佐野幸恵</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>上市秀雄</t>
+          <t>上市 秀雄</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>讃井知</t>
+          <t>讃井 知</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -1608,24 +1608,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>秋山英三</t>
+          <t>秋山 英三</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>三崎広海</t>
+          <t>三崎 広海</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>小西葉子</t>
+          <t>小西 葉子</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0.8609838783740997</v>
+        <v>0.8609838485717773</v>
       </c>
       <c r="I26" t="n">
-        <v>0.8606992065906525</v>
+        <v>0.8606991767883301</v>
       </c>
       <c r="J26" t="n">
         <v>0.8603500425815582</v>
@@ -1654,17 +1654,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>上市秀雄</t>
+          <t>上市 秀雄</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>川島宏一</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>岡本翔平</t>
+          <t>岡田 幸彦</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -1674,7 +1674,7 @@
         <v>0.8570155799388885</v>
       </c>
       <c r="J27" t="n">
-        <v>0.8550840020179749</v>
+        <v>0.8559012115001678</v>
       </c>
     </row>
     <row r="28">
@@ -1700,27 +1700,27 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>有馬澄佳</t>
+          <t>有馬 澄佳</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>吉瀬章子</t>
+          <t>吉瀬 章子</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>繁野麻衣子</t>
+          <t>繁野 麻衣子</t>
         </is>
       </c>
       <c r="H28" t="n">
         <v>0.8741349577903748</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8709459602832794</v>
+        <v>0.8709458708763123</v>
       </c>
       <c r="J28" t="n">
-        <v>0.8677204847335815</v>
+        <v>0.8677653074264526</v>
       </c>
     </row>
     <row r="29">
@@ -1746,24 +1746,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>有馬澄佳</t>
+          <t>有馬 澄佳</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>牛島光一</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>高野祐一</t>
+          <t>高野 祐一</t>
         </is>
       </c>
       <c r="H29" t="n">
         <v>0.8854930698871613</v>
       </c>
       <c r="I29" t="n">
-        <v>0.8639018535614014</v>
+        <v>0.8639017939567566</v>
       </c>
       <c r="J29" t="n">
         <v>0.863455206155777</v>
@@ -1792,27 +1792,27 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>川島宏一</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>鈴木勉</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>張勇兵</t>
+          <t>岡田 幸彦</t>
         </is>
       </c>
       <c r="H30" t="n">
+        <v>0.8844201862812042</v>
+      </c>
+      <c r="I30" t="n">
         <v>0.8559956550598145</v>
       </c>
-      <c r="I30" t="n">
-        <v>0.852905809879303</v>
-      </c>
       <c r="J30" t="n">
-        <v>0.8527995347976685</v>
+        <v>0.8549239039421082</v>
       </c>
     </row>
     <row r="31">
@@ -1838,17 +1838,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>黒瀬雄大</t>
+          <t>黒瀬 雄大</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>秋山英三</t>
+          <t>秋山 英三</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>有田智一</t>
+          <t>有田 智一</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -1884,17 +1884,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>梅本通孝</t>
+          <t>梅本 通孝</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>川島宏一</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>讃井知</t>
+          <t>讃井 知</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -1904,7 +1904,7 @@
         <v>0.857513427734375</v>
       </c>
       <c r="J32" t="n">
-        <v>0.8540211617946625</v>
+        <v>0.8540211319923401</v>
       </c>
     </row>
     <row r="33">
@@ -1930,24 +1930,24 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>岡本翔平</t>
+          <t>岡本 翔平</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>讃井知</t>
+          <t>讃井 知</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>佐野幸恵</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="H33" t="n">
         <v>0.8646641969680786</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8642511367797852</v>
+        <v>0.8642510771751404</v>
       </c>
       <c r="J33" t="n">
         <v>0.8624968230724335</v>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>讃井知</t>
+          <t>讃井 知</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>雨宮護</t>
+          <t>雨宮 護</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>川島宏一</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -2022,21 +2022,21 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>山本幸子</t>
+          <t>山本 幸子</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>有田智一</t>
+          <t>有田 智一</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>渡邉俊</t>
+          <t>渡邉 俊</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>0.8801655769348145</v>
+        <v>0.8801654279232025</v>
       </c>
       <c r="I35" t="n">
         <v>0.8784414231777191</v>
@@ -2068,24 +2068,24 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>太田充</t>
+          <t>太田 充</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>牛島光一</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>鈴木勉</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="H36" t="n">
         <v>0.8759267032146454</v>
       </c>
       <c r="I36" t="n">
-        <v>0.8731177449226379</v>
+        <v>0.8731176853179932</v>
       </c>
       <c r="J36" t="n">
         <v>0.8701472282409668</v>
@@ -2114,27 +2114,27 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>川島宏一</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>牛島光一</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>鈴木勉</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="H37" t="n">
         <v>0.8812141716480255</v>
       </c>
       <c r="I37" t="n">
-        <v>0.8785417973995209</v>
+        <v>0.8785416781902313</v>
       </c>
       <c r="J37" t="n">
-        <v>0.8743590414524078</v>
+        <v>0.8743589520454407</v>
       </c>
     </row>
     <row r="38">
@@ -2160,21 +2160,21 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>山本幸子</t>
+          <t>山本 幸子</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>川島宏一</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>讃井知</t>
+          <t>讃井 知</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>0.8687266111373901</v>
+        <v>0.8687264025211334</v>
       </c>
       <c r="I38" t="n">
         <v>0.8683319091796875</v>
@@ -2206,21 +2206,21 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>鈴木勉</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>川島宏一</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>渡邉俊</t>
+          <t>渡邉 俊</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>0.8869521021842957</v>
+        <v>0.886952131986618</v>
       </c>
       <c r="I39" t="n">
         <v>0.8798272311687469</v>
@@ -2252,24 +2252,24 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>鈴木勉</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>堤盛人</t>
+          <t>堤 盛人</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>太田充</t>
+          <t>太田 充</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>0.8817867934703827</v>
+        <v>0.8817868828773499</v>
       </c>
       <c r="I40" t="n">
-        <v>0.8813002407550812</v>
+        <v>0.881300151348114</v>
       </c>
       <c r="J40" t="n">
         <v>0.8805911839008331</v>
@@ -2298,21 +2298,21 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>堤盛人</t>
+          <t>堤 盛人</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>梅本通孝</t>
+          <t>梅本 通孝</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>川島宏一</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>0.8820194005966187</v>
+        <v>0.8820194602012634</v>
       </c>
       <c r="I41" t="n">
         <v>0.8765389025211334</v>
@@ -2344,24 +2344,24 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>讃井知</t>
+          <t>讃井 知</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>雨宮護</t>
+          <t>雨宮 護</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>川島宏一</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>0.8671787083148956</v>
+        <v>0.8671787977218628</v>
       </c>
       <c r="I42" t="n">
-        <v>0.8621289134025574</v>
+        <v>0.8621288537979126</v>
       </c>
       <c r="J42" t="n">
         <v>0.8617662489414215</v>
@@ -2390,17 +2390,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>渡邉俊</t>
+          <t>渡邉 俊</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>讃井知</t>
+          <t>讃井 知</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>鈴木勉</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -2436,24 +2436,24 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>川島宏一</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>讃井知</t>
+          <t>讃井 知</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>藤川昌樹</t>
+          <t>藤川 昌樹</t>
         </is>
       </c>
       <c r="H44" t="n">
         <v>0.8610954582691193</v>
       </c>
       <c r="I44" t="n">
-        <v>0.8604769706726074</v>
+        <v>0.8604768514633179</v>
       </c>
       <c r="J44" t="n">
         <v>0.8600713014602661</v>
@@ -2482,21 +2482,21 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>渡邉俊</t>
+          <t>渡邉 俊</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>藤川昌樹</t>
+          <t>藤川 昌樹</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>松原康介</t>
+          <t>松原 康介</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0.8848141133785248</v>
+        <v>0.8848141729831696</v>
       </c>
       <c r="I45" t="n">
         <v>0.884340912103653</v>
@@ -2528,27 +2528,27 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>張勇兵</t>
+          <t>Tran Lam Anh Duong</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>鈴木勉</t>
+          <t>張 勇兵</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>八森正泰</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>0.8679175674915314</v>
+        <v>0.8686491549015045</v>
       </c>
       <c r="I46" t="n">
+        <v>0.8679175078868866</v>
+      </c>
+      <c r="J46" t="n">
         <v>0.8637300729751587</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0.8612132370471954</v>
       </c>
     </row>
     <row r="47">
@@ -2574,17 +2574,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>川島宏一</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>太田充</t>
+          <t>太田 充</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>牛島光一</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="H47" t="n">
@@ -2620,17 +2620,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>岡本直久</t>
+          <t>岡本 直久</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>牛島光一</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>梅本通孝</t>
+          <t>梅本 通孝</t>
         </is>
       </c>
       <c r="H48" t="n">
@@ -2640,7 +2640,7 @@
         <v>0.8687419593334198</v>
       </c>
       <c r="J48" t="n">
-        <v>0.8667345643043518</v>
+        <v>0.8667344450950623</v>
       </c>
     </row>
     <row r="49">
@@ -2666,17 +2666,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>岡本直久</t>
+          <t>岡本 直久</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>藤川昌樹</t>
+          <t>藤川 昌樹</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>渡邉俊</t>
+          <t>渡邉 俊</t>
         </is>
       </c>
       <c r="H49" t="n">
@@ -2686,7 +2686,7 @@
         <v>0.8646083772182465</v>
       </c>
       <c r="J49" t="n">
-        <v>0.8645975291728973</v>
+        <v>0.8645975589752197</v>
       </c>
     </row>
     <row r="50">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>鈴木勉</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>岡本直久</t>
+          <t>岡本 直久</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>和田健太郎</t>
+          <t>和田 健太郎</t>
         </is>
       </c>
       <c r="H50" t="n">
@@ -2758,17 +2758,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>讃井知</t>
+          <t>讃井 知</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>雨宮護</t>
+          <t>雨宮 護</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>川島宏一</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -2804,17 +2804,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>鈴木勉</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>牛島光一</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>小西葉子</t>
+          <t>小西 葉子</t>
         </is>
       </c>
       <c r="H52" t="n">
@@ -2850,17 +2850,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>岡本翔平</t>
+          <t>岡本 翔平</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>牛島光一</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>太田充</t>
+          <t>太田 充</t>
         </is>
       </c>
       <c r="H53" t="n">
@@ -2896,27 +2896,27 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>鈴木勉</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>谷口守</t>
+          <t>堤 盛人</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>堤盛人</t>
+          <t>讃井 知</t>
         </is>
       </c>
       <c r="H54" t="n">
         <v>0.866838663816452</v>
       </c>
       <c r="I54" t="n">
-        <v>0.8643345534801483</v>
+        <v>0.8634083867073059</v>
       </c>
       <c r="J54" t="n">
-        <v>0.8634083867073059</v>
+        <v>0.8592371940612793</v>
       </c>
     </row>
     <row r="55">
@@ -2942,27 +2942,27 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>牛島光一</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>大久保正勝</t>
+          <t>太田 充</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>太田充</t>
+          <t>甲斐田 直子</t>
         </is>
       </c>
       <c r="H55" t="n">
         <v>0.8447581827640533</v>
       </c>
       <c r="I55" t="n">
-        <v>0.8440878391265869</v>
+        <v>0.8435723781585693</v>
       </c>
       <c r="J55" t="n">
-        <v>0.8435723781585693</v>
+        <v>0.8434951305389404</v>
       </c>
     </row>
     <row r="56">
@@ -2988,17 +2988,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>岡本直久</t>
+          <t>岡本 直久</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>和田健太郎</t>
+          <t>和田 健太郎</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>鈴木勉</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="H56" t="n">
@@ -3034,17 +3034,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>讃井知</t>
+          <t>讃井 知</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>上市秀雄</t>
+          <t>上市 秀雄</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>甲斐田直子</t>
+          <t>甲斐田 直子</t>
         </is>
       </c>
       <c r="H57" t="n">
@@ -3054,7 +3054,7 @@
         <v>0.8431252837181091</v>
       </c>
       <c r="J57" t="n">
-        <v>0.8418351113796234</v>
+        <v>0.8418348729610443</v>
       </c>
     </row>
     <row r="58">
@@ -3080,17 +3080,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>和田健太郎</t>
+          <t>和田 健太郎</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>鈴木勉</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>牛島光一</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="H58" t="n">
@@ -3126,17 +3126,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>長崎滉大</t>
+          <t>長崎 滉大</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>岡本直久</t>
+          <t>岡本 直久</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>和田健太郎</t>
+          <t>和田 健太郎</t>
         </is>
       </c>
       <c r="H59" t="n">
@@ -3172,27 +3172,27 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>鈴木勉</t>
+          <t>志田 洋平</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>黒瀬雄大</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>川島宏一</t>
+          <t>黒瀬 雄大</t>
         </is>
       </c>
       <c r="H60" t="n">
+        <v>0.8772633671760559</v>
+      </c>
+      <c r="I60" t="n">
         <v>0.874665379524231</v>
       </c>
-      <c r="I60" t="n">
+      <c r="J60" t="n">
         <v>0.8743585348129272</v>
-      </c>
-      <c r="J60" t="n">
-        <v>0.8681854605674744</v>
       </c>
     </row>
     <row r="61">
@@ -3218,27 +3218,27 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>甲斐田直子</t>
+          <t>甲斐田 直子</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>川島宏一</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>讃井知</t>
+          <t>讃井 知</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>0.8799073100090027</v>
+        <v>0.8799072504043579</v>
       </c>
       <c r="I61" t="n">
         <v>0.8760300278663635</v>
       </c>
       <c r="J61" t="n">
-        <v>0.874771922826767</v>
+        <v>0.8747718930244446</v>
       </c>
     </row>
     <row r="62">
@@ -3264,17 +3264,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>梅本通孝</t>
+          <t>梅本 通孝</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>鈴木勉</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>讃井知</t>
+          <t>讃井 知</t>
         </is>
       </c>
       <c r="H62" t="n">
@@ -3310,17 +3310,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>讃井知</t>
+          <t>讃井 知</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>川島宏一</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>甲斐田直子</t>
+          <t>甲斐田 直子</t>
         </is>
       </c>
       <c r="H63" t="n">
@@ -3356,17 +3356,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>甲斐田直子</t>
+          <t>甲斐田 直子</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>谷口綾子</t>
+          <t>谷口 綾子</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>澤亮治</t>
+          <t>澤 亮治</t>
         </is>
       </c>
       <c r="H64" t="n">
@@ -3402,17 +3402,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>渡邉俊</t>
+          <t>渡邉 俊</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>川島宏一</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>太田充</t>
+          <t>太田 充</t>
         </is>
       </c>
       <c r="H65" t="n">
@@ -3448,17 +3448,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>鈴木勉</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>川島宏一</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>渡邉俊</t>
+          <t>渡邉 俊</t>
         </is>
       </c>
       <c r="H66" t="n">
@@ -3494,17 +3494,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>渡邉俊</t>
+          <t>渡邉 俊</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>有田智一</t>
+          <t>有田 智一</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>川島宏一</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="H67" t="n">
@@ -3540,17 +3540,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>秋山英三</t>
+          <t>秋山 英三</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>上市秀雄</t>
+          <t>上市 秀雄</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>讃井知</t>
+          <t>讃井 知</t>
         </is>
       </c>
       <c r="H68" t="n">
@@ -3560,7 +3560,7 @@
         <v>0.8515321016311646</v>
       </c>
       <c r="J68" t="n">
-        <v>0.8461630642414093</v>
+        <v>0.8461630940437317</v>
       </c>
     </row>
     <row r="69">
@@ -3586,27 +3586,27 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>牛島光一</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>讃井知</t>
+          <t>讃井 知</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>秋山英三</t>
+          <t>秋山 英三</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>0.8769174218177795</v>
+        <v>0.8769176304340363</v>
       </c>
       <c r="I69" t="n">
-        <v>0.8657227754592896</v>
+        <v>0.8657228648662567</v>
       </c>
       <c r="J69" t="n">
-        <v>0.8631939291954041</v>
+        <v>0.8631937503814697</v>
       </c>
     </row>
     <row r="70">
@@ -3632,17 +3632,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>小西葉子</t>
+          <t>小西 葉子</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>川島宏一</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>牛島光一</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="H70" t="n">
@@ -3652,7 +3652,7 @@
         <v>0.8721947968006134</v>
       </c>
       <c r="J70" t="n">
-        <v>0.8721112310886383</v>
+        <v>0.8721112906932831</v>
       </c>
     </row>
     <row r="71">
@@ -3678,17 +3678,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>川島宏一</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>原田信行</t>
+          <t>原田 信行</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>甲斐田直子</t>
+          <t>甲斐田 直子</t>
         </is>
       </c>
       <c r="H71" t="n">
@@ -3698,7 +3698,7 @@
         <v>0.8675041198730469</v>
       </c>
       <c r="J71" t="n">
-        <v>0.8670808672904968</v>
+        <v>0.8670809268951416</v>
       </c>
     </row>
     <row r="72">
@@ -3724,21 +3724,21 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>鈴木勉</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>山野博哉</t>
+          <t>山野 博哉</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>牛島光一</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>0.8607411682605743</v>
+        <v>0.860741138458252</v>
       </c>
       <c r="I72" t="n">
         <v>0.8598228096961975</v>
@@ -3770,21 +3770,21 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>鈴木勉</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>和田健太郎</t>
+          <t>和田 健太郎</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>岡本直久</t>
+          <t>岡本 直久</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>0.8742718696594238</v>
+        <v>0.8742719292640686</v>
       </c>
       <c r="I73" t="n">
         <v>0.8719367384910583</v>
@@ -3816,24 +3816,24 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>鈴木勉</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>牛島光一</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>川島宏一</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>0.8715937733650208</v>
+        <v>0.8715938329696655</v>
       </c>
       <c r="I74" t="n">
-        <v>0.87095046043396</v>
+        <v>0.8709504008293152</v>
       </c>
       <c r="J74" t="n">
         <v>0.8709364533424377</v>
@@ -3862,27 +3862,27 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>鈴木勉</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>和田健太郎</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>長崎滉大</t>
+          <t>和田 健太郎</t>
         </is>
       </c>
       <c r="H75" t="n">
         <v>0.8804836571216583</v>
       </c>
       <c r="I75" t="n">
+        <v>0.879767507314682</v>
+      </c>
+      <c r="J75" t="n">
         <v>0.8787779808044434</v>
-      </c>
-      <c r="J75" t="n">
-        <v>0.876759946346283</v>
       </c>
     </row>
     <row r="76">
@@ -3908,27 +3908,27 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>長崎滉大</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>鈴木勉</t>
+          <t>長崎 滉大</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>和田健太郎</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="H76" t="n">
+        <v>0.8646461963653564</v>
+      </c>
+      <c r="I76" t="n">
         <v>0.8642684817314148</v>
       </c>
-      <c r="I76" t="n">
+      <c r="J76" t="n">
         <v>0.858845442533493</v>
-      </c>
-      <c r="J76" t="n">
-        <v>0.8584803938865662</v>
       </c>
     </row>
     <row r="77">
@@ -3954,27 +3954,27 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>鈴木勉</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>長崎滉大</t>
+          <t>長崎 滉大</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>八森正泰</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>0.8770516812801361</v>
+        <v>0.8770518004894257</v>
       </c>
       <c r="I77" t="n">
         <v>0.8761831521987915</v>
       </c>
       <c r="J77" t="n">
-        <v>0.8715193271636963</v>
+        <v>0.8737709820270538</v>
       </c>
     </row>
     <row r="78">
@@ -4000,27 +4000,27 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>太田充</t>
+          <t>太田 充</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>牛島光一</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>堤盛人</t>
+          <t>堤 盛人</t>
         </is>
       </c>
       <c r="H78" t="n">
         <v>0.880396842956543</v>
       </c>
       <c r="I78" t="n">
-        <v>0.8773620426654816</v>
+        <v>0.8773619830608368</v>
       </c>
       <c r="J78" t="n">
-        <v>0.8741994500160217</v>
+        <v>0.8741996884346008</v>
       </c>
     </row>
     <row r="79">
@@ -4046,21 +4046,21 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>牛島光一</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>岡本翔平</t>
+          <t>岡本 翔平</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>讃井知</t>
+          <t>讃井 知</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>0.8768567144870758</v>
+        <v>0.876856803894043</v>
       </c>
       <c r="I79" t="n">
         <v>0.8733054995536804</v>
@@ -4092,17 +4092,17 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>牛島光一</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>太田充</t>
+          <t>太田 充</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>堤盛人</t>
+          <t>堤 盛人</t>
         </is>
       </c>
       <c r="H80" t="n">
@@ -4112,7 +4112,7 @@
         <v>0.8544398844242096</v>
       </c>
       <c r="J80" t="n">
-        <v>0.853886753320694</v>
+        <v>0.8538867235183716</v>
       </c>
     </row>
     <row r="81">
@@ -4138,24 +4138,24 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>小西葉子</t>
+          <t>小西 葉子</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>讃井知</t>
+          <t>讃井 知</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>浦田淳司</t>
+          <t>浦田 淳司</t>
         </is>
       </c>
       <c r="H81" t="n">
         <v>0.8598234951496124</v>
       </c>
       <c r="I81" t="n">
-        <v>0.8560390472412109</v>
+        <v>0.8560391366481781</v>
       </c>
       <c r="J81" t="n">
         <v>0.8557764291763306</v>
@@ -4184,17 +4184,17 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>小西葉子</t>
+          <t>小西 葉子</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>佐野幸恵</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>牛島光一</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="H82" t="n">
@@ -4204,7 +4204,7 @@
         <v>0.852622389793396</v>
       </c>
       <c r="J82" t="n">
-        <v>0.8521038293838501</v>
+        <v>0.8521038889884949</v>
       </c>
     </row>
     <row r="83">
@@ -4230,27 +4230,27 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>小西葉子</t>
+          <t>小西 葉子</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>牛島光一</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>原田信行</t>
+          <t>原田 信行</t>
         </is>
       </c>
       <c r="H83" t="n">
         <v>0.85500568151474</v>
       </c>
       <c r="I83" t="n">
-        <v>0.853083074092865</v>
+        <v>0.8530831038951874</v>
       </c>
       <c r="J83" t="n">
-        <v>0.8515084087848663</v>
+        <v>0.8515084981918335</v>
       </c>
     </row>
     <row r="84">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>山野博哉</t>
+          <t>山野 博哉</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>牛島光一</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>川島宏一</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="H84" t="n">
         <v>0.856723815202713</v>
       </c>
       <c r="I84" t="n">
-        <v>0.8473110795021057</v>
+        <v>0.8473109900951385</v>
       </c>
       <c r="J84" t="n">
         <v>0.8449655175209045</v>
@@ -4384,24 +4384,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>イリチュ美佳</t>
+          <t>イリチュ 美佳</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>高野祐一</t>
+          <t>高野 祐一</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>上市秀雄</t>
+          <t>上市 秀雄</t>
         </is>
       </c>
       <c r="H2" t="n">
         <v>0.8635274171829224</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8589867353439331</v>
+        <v>0.8589865863323212</v>
       </c>
       <c r="J2" t="n">
         <v>0.857316792011261</v>
@@ -4426,27 +4426,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>吉瀬章子</t>
+          <t>吉瀬 章子</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>八森正泰</t>
+          <t>Liu Tianxiang</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>張勇兵</t>
+          <t>八森 正泰</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.8609104454517365</v>
+        <v>0.8609103560447693</v>
       </c>
       <c r="I3" t="n">
+        <v>0.8553825318813324</v>
+      </c>
+      <c r="J3" t="n">
         <v>0.8542724251747131</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.8489381372928619</v>
       </c>
     </row>
     <row r="4">
@@ -4468,27 +4468,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>吉瀬章子</t>
+          <t>吉瀬 章子</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>八森正泰</t>
+          <t>Liu Tianxiang</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>繁野麻衣子</t>
+          <t>八森 正泰</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.8563420474529266</v>
+        <v>0.8563421070575714</v>
       </c>
       <c r="I4" t="n">
+        <v>0.8490735590457916</v>
+      </c>
+      <c r="J4" t="n">
         <v>0.848315566778183</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.8436665534973145</v>
       </c>
     </row>
     <row r="5">
@@ -4510,27 +4510,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>吉瀬章子</t>
+          <t>吉瀬 章子</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>繁野麻衣子</t>
+          <t>繁野 麻衣子</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>有馬澄佳</t>
+          <t>Liu Tianxiang</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.8748291730880737</v>
+        <v>0.8748292922973633</v>
       </c>
       <c r="I5" t="n">
-        <v>0.865216463804245</v>
+        <v>0.8648773431777954</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8598293960094452</v>
+        <v>0.8610253930091858</v>
       </c>
     </row>
     <row r="6">
@@ -4552,27 +4552,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>讃井知</t>
+          <t>岡本 翔平</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>上市秀雄</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>イリチュ美佳</t>
+          <t>讃井 知</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.873845100402832</v>
+        <v>0.8810135126113892</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8730534017086029</v>
+        <v>0.8752143383026123</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8719890415668488</v>
+        <v>0.8738452196121216</v>
       </c>
     </row>
     <row r="7">
@@ -4594,17 +4594,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>佐野幸恵</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>上市秀雄</t>
+          <t>上市 秀雄</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>張勇兵</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -4614,7 +4614,7 @@
         <v>0.8642037510871887</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8553867936134338</v>
+        <v>0.8563595116138458</v>
       </c>
     </row>
     <row r="8">
@@ -4636,27 +4636,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>吉瀬章子</t>
+          <t>Liu Tianxiang</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>高野祐一</t>
+          <t>吉瀬 章子</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>八森正泰</t>
+          <t>高野 祐一</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.8712440133094788</v>
+        <v>0.8779240846633911</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8685610890388489</v>
+        <v>0.8712441325187683</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8668279051780701</v>
+        <v>0.8685609400272369</v>
       </c>
     </row>
     <row r="9">
@@ -4678,27 +4678,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>岡田幸彦</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>イリチュ美佳</t>
+          <t>岡田 幸彦</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>大西正輝</t>
+          <t>イリチュ 美佳</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.8625462651252747</v>
+        <v>0.8722024857997894</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8624857664108276</v>
+        <v>0.8625463247299194</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8615334928035736</v>
+        <v>0.8624857068061829</v>
       </c>
     </row>
     <row r="10">
@@ -4720,27 +4720,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>吉瀬章子</t>
+          <t>吉瀬 章子</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>有馬澄佳</t>
+          <t>有馬 澄佳</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>繁野麻衣子</t>
+          <t>繁野 麻衣子</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.8638104498386383</v>
+        <v>0.8638104796409607</v>
       </c>
       <c r="I10" t="n">
         <v>0.8515419065952301</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8515247106552124</v>
+        <v>0.8513235151767731</v>
       </c>
     </row>
     <row r="11">
@@ -4762,24 +4762,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>イリチュ美佳</t>
+          <t>イリチュ 美佳</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>佐野幸恵</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>大西正輝</t>
+          <t>大西 正輝</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.8766615390777588</v>
+        <v>0.8766615092754364</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8584880828857422</v>
+        <v>0.858488142490387</v>
       </c>
       <c r="J11" t="n">
         <v>0.8581428825855255</v>
@@ -4804,27 +4804,27 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>高野祐一</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>黒瀬雄大</t>
+          <t>高野 祐一</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>吉瀬章子</t>
+          <t>黒瀬 雄大</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.8564328551292419</v>
+        <v>0.8860654234886169</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8518258035182953</v>
+        <v>0.8564328849315643</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8504331409931183</v>
+        <v>0.8518258333206177</v>
       </c>
     </row>
     <row r="13">
@@ -4846,27 +4846,27 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>佐野幸恵</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>上市秀雄</t>
+          <t>上市 秀雄</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>讃井知</t>
+          <t>讃井 知</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.8769749402999878</v>
+        <v>0.8769748508930206</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8706701397895813</v>
+        <v>0.8706703186035156</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8587096333503723</v>
+        <v>0.8587097227573395</v>
       </c>
     </row>
     <row r="14">
@@ -4888,27 +4888,27 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>高野祐一</t>
+          <t>三崎 広海</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>黒瀬雄大</t>
+          <t>高野 祐一</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>小西葉子</t>
+          <t>黒瀬 雄大</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.8499733805656433</v>
+        <v>0.8558283150196075</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8485821783542633</v>
+        <v>0.8499734103679657</v>
       </c>
       <c r="J14" t="n">
-        <v>0.847388744354248</v>
+        <v>0.8485821187496185</v>
       </c>
     </row>
     <row r="15">
@@ -4930,27 +4930,27 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>岡田幸彦</t>
+          <t>岡田 幸彦</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>小西葉子</t>
+          <t>三崎 広海</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>佐野幸恵</t>
+          <t>小西 葉子</t>
         </is>
       </c>
       <c r="H15" t="n">
         <v>0.8566752374172211</v>
       </c>
       <c r="I15" t="n">
+        <v>0.8484805524349213</v>
+      </c>
+      <c r="J15" t="n">
         <v>0.8434323072433472</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.8424454629421234</v>
       </c>
     </row>
     <row r="16">
@@ -4972,27 +4972,27 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>八森正泰</t>
+          <t>八森 正泰</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>吉瀬章子</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>繁野麻衣子</t>
+          <t>吉瀬 章子</t>
         </is>
       </c>
       <c r="H16" t="n">
         <v>0.8690817356109619</v>
       </c>
       <c r="I16" t="n">
+        <v>0.8608503043651581</v>
+      </c>
+      <c r="J16" t="n">
         <v>0.8606576025485992</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.856191098690033</v>
       </c>
     </row>
     <row r="17">
@@ -5014,27 +5014,27 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>高野祐一</t>
+          <t>高野 祐一</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>小西葉子</t>
+          <t>小西 葉子</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>繁野麻衣子</t>
+          <t>繁野 麻衣子</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.8639225661754608</v>
+        <v>0.8639224171638489</v>
       </c>
       <c r="I17" t="n">
         <v>0.8517236709594727</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8516285419464111</v>
+        <v>0.8516994714736938</v>
       </c>
     </row>
     <row r="18">
@@ -5056,27 +5056,27 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>岡本直久</t>
+          <t>岡本 直久</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>小西葉子</t>
+          <t>浦田 淳司</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>繁野麻衣子</t>
+          <t>小西 葉子</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0.8556587994098663</v>
+        <v>0.8556589782238007</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8488175570964813</v>
+        <v>0.852348655462265</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8456803560256958</v>
+        <v>0.8488177359104156</v>
       </c>
     </row>
     <row r="19">
@@ -5098,27 +5098,27 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>吉瀬章子</t>
+          <t>吉瀬 章子</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>八森正泰</t>
+          <t>Liu Tianxiang</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>繁野麻衣子</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0.8692283630371094</v>
+        <v>0.8692283034324646</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8555294871330261</v>
+        <v>0.8582851588726044</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8545259237289429</v>
+        <v>0.8579657673835754</v>
       </c>
     </row>
     <row r="20">
@@ -5140,27 +5140,27 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>上市秀雄</t>
+          <t>上市 秀雄</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>讃井知</t>
+          <t>讃井 知</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>秋山英三</t>
+          <t>秋山 英三</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0.8734315931797028</v>
+        <v>0.8734315633773804</v>
       </c>
       <c r="I20" t="n">
         <v>0.8669519126415253</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8657552003860474</v>
+        <v>0.865755021572113</v>
       </c>
     </row>
     <row r="21">
@@ -5182,27 +5182,27 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>吉瀬章子</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>八森正泰</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>高野祐一</t>
+          <t>吉瀬 章子</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.8634407520294189</v>
+        <v>0.8677213788032532</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8590059578418732</v>
+        <v>0.8647889792919159</v>
       </c>
       <c r="J21" t="n">
-        <v>0.857612669467926</v>
+        <v>0.8634408414363861</v>
       </c>
     </row>
     <row r="22">
@@ -5224,27 +5224,27 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>岡田幸彦</t>
+          <t>三崎 広海</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>黒瀬雄大</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>原田信行</t>
+          <t>岡田 幸彦</t>
         </is>
       </c>
       <c r="H22" t="n">
+        <v>0.8706386387348175</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.8656386733055115</v>
+      </c>
+      <c r="J22" t="n">
         <v>0.8638789355754852</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.8628188967704773</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.8613706529140472</v>
       </c>
     </row>
   </sheetData>

--- a/generated/committee_recommendations.xlsx
+++ b/generated/committee_recommendations.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J84"/>
+  <dimension ref="A1:J86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,42 +489,42 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>中島 元毅</t>
+          <t>青山 史秀</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>202420453</t>
+          <t>202520421</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>日本の就活市場における新卒採用に関する研究</t>
+          <t>土地利用規制の緩和が地価に与える影響－京都市の規制緩和を対象として―</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>上市 秀雄</t>
+          <t>太田 充</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>小西 葉子</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>張 勇兵</t>
+          <t>堤 盛人</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.8624107539653778</v>
+        <v>0.8725054264068604</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8566808700561523</v>
+        <v>0.8694877028465271</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8556444942951202</v>
+        <v>0.8679138123989105</v>
       </c>
     </row>
     <row r="3">
@@ -535,17 +535,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>荒金 志紀</t>
+          <t>朝賀 史織</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>202420409</t>
+          <t>202520422</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>結婚の意思決定に対する独身税の効果と税制度の提案</t>
+          <t>離島における官民連携事業の効果と地域への影響－伊豆諸島のスタートアップ事業に着目して－</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -555,22 +555,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>岡本 翔平</t>
+          <t>太田 充</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>小西 葉子</t>
+          <t>山本 幸子</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.872869074344635</v>
+        <v>0.8699927926063538</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8679050207138062</v>
+        <v>0.8690958321094513</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8613480925559998</v>
+        <v>0.8680389225482941</v>
       </c>
     </row>
     <row r="4">
@@ -581,42 +581,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>小峯 拓也</t>
+          <t>家城 悠紀</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>202420429</t>
+          <t>202520423</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>学生の選考情報を利用した就活支援サービスに関する研究</t>
+          <t>プロヴァンス地域における修道院とテリトワールの相互関係</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>上市 秀雄</t>
+          <t>松原 康介</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>張 勇兵</t>
+          <t>山本 幸子</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>有田 智一</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.8692523539066315</v>
+        <v>0.8407678604125977</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8587264716625214</v>
+        <v>0.8383740782737732</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8567101359367371</v>
+        <v>0.8299179673194885</v>
       </c>
     </row>
     <row r="5">
@@ -627,42 +627,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>貫井 虹希</t>
+          <t>五十嵐 則晶</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>202420454</t>
+          <t>202520424</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>最適停止問題を用いた就活市場の分析と改善提案</t>
+          <t>chordal graphにおける(X,Y)-pathのconjectureについての検証</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>高野 祐一</t>
+          <t>秋山 英三</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>吉瀬 章子</t>
+          <t>浦田 淳司</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Liu Tianxiang</t>
+          <t>讃井 知</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.8717089295387268</v>
+        <v>0.8525646924972534</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8693714141845703</v>
+        <v>0.8467219471931458</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8665716648101807</v>
+        <v>0.8441798388957977</v>
       </c>
     </row>
     <row r="6">
@@ -673,42 +673,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>安達 未晴</t>
+          <t>伊澤 直弥</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>202420407</t>
+          <t>202520425</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>視線計測を用いた保険加入行動の分析</t>
+          <t>複数の評価指標を考慮したタブーサーチによる住宅間取り図最適化</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>三崎 広海</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>吉瀬 章子</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>岡田 幸彦</t>
+          <t>山本 幸子</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.8649015724658966</v>
+        <v>0.8804560601711273</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8621913194656372</v>
+        <v>0.8787815570831299</v>
       </c>
       <c r="J6" t="n">
-        <v>0.860032320022583</v>
+        <v>0.8734155297279358</v>
       </c>
     </row>
     <row r="7">
@@ -719,42 +719,42 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>YANG LUXI</t>
+          <t>市川 滉樹</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>202420493</t>
+          <t>202520426</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>価値観が失敗の対処行動に与える影響-失敗体験の重大性と領域を考えて-</t>
+          <t>地籍整備事業の実施状況が相続不動産の所有権移転登記の発生確率に与える影響分析</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>上市 秀雄</t>
+          <t>堤 盛人</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>讃井 知</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>甲斐田 直子</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.8779138922691345</v>
+        <v>0.8718103170394897</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8748932182788849</v>
+        <v>0.8701826930046082</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8710567057132721</v>
+        <v>0.8687415421009064</v>
       </c>
     </row>
     <row r="8">
@@ -765,42 +765,42 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>釆原 周弥</t>
+          <t>市田 佳汰</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>202420416</t>
+          <t>202520427</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Priority-neutral matchingsの集合の格子構造に関する研究</t>
+          <t>高校生の就職市場における学校（仲介者）の推薦・選抜行動がマッチングに与える影響</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>阿武 秀和</t>
+          <t>澤 亮治</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>澤 亮治</t>
+          <t>秋山 英三</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>張 勇兵</t>
+          <t>上市 秀雄</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.8727771043777466</v>
+        <v>0.8684000670909882</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8699049353599548</v>
+        <v>0.8601691126823425</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8581907451152802</v>
+        <v>0.8557591736316681</v>
       </c>
     </row>
     <row r="9">
@@ -811,42 +811,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>金井 公亮</t>
+          <t>伊藤 彩乃</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>202420420</t>
+          <t>202520428</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>不確実性下の同質財割当における randomized uniform rule のパレート効率性について</t>
+          <t>小学校通学路における歩行環境評価に関する研究</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>阿武 秀和</t>
+          <t>山本 幸子</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>澤 亮治</t>
+          <t>渡邉 俊</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Liu Tianxiang</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.8814799785614014</v>
+        <v>0.870919406414032</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8741540014743805</v>
+        <v>0.8701505959033966</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8681204319000244</v>
+        <v>0.8696761429309845</v>
       </c>
     </row>
     <row r="10">
@@ -857,17 +857,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>原 笙太</t>
+          <t>井上 皓介</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>202420460</t>
+          <t>202520429</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>都市特性・社会経済要因が外国人居住パターンに与える影響：東京23区の実証・シミュレーション分析</t>
+          <t>大規模人流データを用いた徒歩圏の再定義：施設差と地域差に着目して</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>太田 充</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -886,13 +886,13 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.8737158477306366</v>
+        <v>0.8743027150630951</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8714621961116791</v>
+        <v>0.8654838502407074</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8690856099128723</v>
+        <v>0.865404337644577</v>
       </c>
     </row>
     <row r="11">
@@ -903,42 +903,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>間嶋 大智</t>
+          <t>井上 陽斗</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>202420467</t>
+          <t>202520430</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>マルチエージェントシミュレーション&amp;最適化による間取り生成</t>
+          <t>AI特許は“いつ”企業価値に織り込まれるのか ― 出願公開・特許登録とニュース露出による投資家注意の役割 ―</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>吉瀬 章子</t>
+          <t>三崎 広海</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>八森 正泰</t>
+          <t>秋山 英三</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>有馬 澄佳</t>
+          <t>小西 葉子</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.8717465400695801</v>
+        <v>0.8726991415023804</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8681822121143341</v>
+        <v>0.8597236573696136</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8677197694778442</v>
+        <v>0.8510848581790924</v>
       </c>
     </row>
     <row r="12">
@@ -949,42 +949,42 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>山田 幹大</t>
+          <t>猪熊 柾人</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>202420484</t>
+          <t>202520431</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>eスポーツにおけるチームのプレイスタイル分析</t>
+          <t>需要の不確実性と参照価格効果を考慮した多期間価格最適化</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>澤 亮治</t>
+          <t>高野 祐一</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>吉瀬 章子</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>秋山 英三</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.8534895181655884</v>
+        <v>0.8739632070064545</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8504402041435242</v>
+        <v>0.8737334609031677</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8496212363243103</v>
+        <v>0.8713179230690002</v>
       </c>
     </row>
     <row r="13">
@@ -995,42 +995,42 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>笹木 重聖</t>
+          <t>岩崎 真由子</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>202420434</t>
+          <t>202520432</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>単位コイングラフにおける部分彩色の拡張</t>
+          <t>大学キャンパスにおける屋外滞在空間創出が学生生活や活動に及ぼす変化 －筑波大学第3エリアスマートキャンパスプロジェクトを対象として－</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>八森 正泰</t>
+          <t>雨宮 護</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>山本 幸子</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>阿武 秀和</t>
+          <t>藤井 さやか</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.8598324656486511</v>
+        <v>0.8786501288414001</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8446328341960907</v>
+        <v>0.8759361505508423</v>
       </c>
       <c r="J13" t="n">
-        <v>0.840150386095047</v>
+        <v>0.8751761913299561</v>
       </c>
     </row>
     <row r="14">
@@ -1041,42 +1041,42 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>井出 裕二</t>
+          <t>岩田 健太朗</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>202420412</t>
+          <t>202520433</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>人口を考慮した均等輸送問題による道路ネットワークの連結性の定量化とその最適補強問題</t>
+          <t>従業員の安全行動変容に関する研究</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>讃井 知</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Phung-Duc Tuan</t>
+          <t>甲斐田 直子</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>八森 正泰</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.8803897500038147</v>
+        <v>0.8674522936344147</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8714250326156616</v>
+        <v>0.8637472689151764</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8703752756118774</v>
+        <v>0.8552792072296143</v>
       </c>
     </row>
     <row r="15">
@@ -1087,42 +1087,42 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>矢中 祥吾</t>
+          <t>宇佐見 光</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>202420478</t>
+          <t>202520434</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>消費電力と所要時間の不確実性を考慮した電動バスの運行計画最適化</t>
+          <t>不確実な情報による参照点操作と購買意思決定</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Phung-Duc Tuan</t>
+          <t>讃井 知</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>和田 健太郎</t>
+          <t>上市 秀雄</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>甲斐田 直子</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0.8797307312488556</v>
+        <v>0.8603215217590332</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8746518194675446</v>
+        <v>0.859508603811264</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8738219439983368</v>
+        <v>0.8559390604496002</v>
       </c>
     </row>
     <row r="16">
@@ -1133,42 +1133,42 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>片岡 弓澄</t>
+          <t>及川 智也</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>202320421</t>
+          <t>202520435</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>品質保証時間と工場間搬送を考慮した多目的マルチファクトリー・スケジューリング</t>
+          <t>地域環境変化の認識が場所愛着・アイデンティティに与える影響</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>有馬 澄佳</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>吉瀬 章子</t>
+          <t>甲斐田 直子</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>太田 充</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0.87470942735672</v>
+        <v>0.8840882480144501</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8685945868492126</v>
+        <v>0.8795138895511627</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8661421239376068</v>
+        <v>0.8777675032615662</v>
       </c>
     </row>
     <row r="17">
@@ -1179,42 +1179,42 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>渡邊 悠義</t>
+          <t>大島 弘也</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>202420485</t>
+          <t>202520436</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>自律性モデルに基づくゲーミフィケーションによる安全行動変容</t>
+          <t>都市の工事現場における仮囲いアートの公共性と社会性に関する研究</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>讃井 知</t>
+          <t>山本 幸子</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>秋山 英三</t>
+          <t>松原 康介</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>上市 秀雄</t>
+          <t>渡邉 俊</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.8663341999053955</v>
+        <v>0.8654569983482361</v>
       </c>
       <c r="I17" t="n">
-        <v>0.856848806142807</v>
+        <v>0.8594346046447754</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8562292158603668</v>
+        <v>0.8577826619148254</v>
       </c>
     </row>
     <row r="18">
@@ -1225,42 +1225,42 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>小澤 陽樹</t>
+          <t>大野 友伽里</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>202420417</t>
+          <t>202520437</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>確率的最適化による高次元交互作用スパースモデリング~Factorization Machines の発展形態</t>
+          <t>自治体保有古民家の利活用におけるサウンディング調査の役割とプロセスの分析</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Liu Tianxiang</t>
+          <t>山本 幸子</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>高野 祐一</t>
+          <t>有田 智一</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>有馬 澄佳</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0.8786898851394653</v>
+        <v>0.8641208410263062</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8732324242591858</v>
+        <v>0.8593732714653015</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8712161481380463</v>
+        <v>0.856412410736084</v>
       </c>
     </row>
     <row r="19">
@@ -1271,42 +1271,42 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>安田 朗</t>
+          <t>小笹 晃生</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>202420477</t>
+          <t>202520438</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>画像と生体計測情報に基づくアクティブラーニングと業務管理</t>
+          <t>二地域居住と幸福感の関係性</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>イリチュ 美佳</t>
+          <t>山本 幸子</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>有馬 澄佳</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>甲斐田 直子</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0.8637226223945618</v>
+        <v>0.8628750443458557</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8616419732570648</v>
+        <v>0.8513096272945404</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8606040179729462</v>
+        <v>0.850258469581604</v>
       </c>
     </row>
     <row r="20">
@@ -1317,42 +1317,42 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>古山 雄晟</t>
+          <t>小野寺 輝</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>202420430</t>
+          <t>202520439</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>単独と集団を区別したライドシェアモデルにおけるゲーム理論的解析</t>
+          <t>消費者のマルチホーミングが存在するVOD市場の研究：垂直統合や独占契約がもたらす市場集中度への影響について</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>阿武 秀和</t>
+          <t>小西 葉子</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>澤 亮治</t>
+          <t>太田 充</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>和田 健太郎</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0.8815976977348328</v>
+        <v>0.8699538707733154</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8796173930168152</v>
+        <v>0.8609905242919922</v>
       </c>
       <c r="J20" t="n">
-        <v>0.877262145280838</v>
+        <v>0.8602003455162048</v>
       </c>
     </row>
     <row r="21">
@@ -1363,22 +1363,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>関田 千隼</t>
+          <t>加藤 啓斗</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>202420441</t>
+          <t>202520440</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>異なる容量を持つ複数システムの負荷分散</t>
+          <t>マッチング市場における異質な売り手へのタイプ別情報設計</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Phung-Duc Tuan</t>
+          <t>澤 亮治</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.8639067411422729</v>
+        <v>0.867156058549881</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8556961417198181</v>
+        <v>0.85415118932724</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8522175550460815</v>
+        <v>0.8522708117961884</v>
       </c>
     </row>
     <row r="22">
@@ -1409,17 +1409,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>位曼曼</t>
+          <t>加藤 麻里絵</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>202420487</t>
+          <t>202520441</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>歩車共存空間における歩行者の移動モデルの構築</t>
+          <t>人流シミュレーションに基づく都市部における避難誘導施策の定量的評価</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1429,22 +1429,22 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>志田 洋平</t>
+          <t>梅本 通孝</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>渡邉 俊</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0.8829725384712219</v>
+        <v>0.8780646622180939</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8785969913005829</v>
+        <v>0.8772540986537933</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8760957717895508</v>
+        <v>0.8761959671974182</v>
       </c>
     </row>
     <row r="23">
@@ -1455,42 +1455,42 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>三輪 珠嶺</t>
+          <t>上山 滉介</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>202420473</t>
+          <t>202520442</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>骨格に基づく行動認識における関節角の導入</t>
+          <t>電力使用状況や気候特性に基づくデマンドレスポンス応答傾向の世帯別分析</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>甲斐田 直子</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
+          <t>奥島 真一郎</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>有馬 澄佳</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0.858246386051178</v>
+        <v>0.8644822537899017</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8524554967880249</v>
+        <v>0.863353967666626</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8519752025604248</v>
+        <v>0.8620575964450836</v>
       </c>
     </row>
     <row r="24">
@@ -1501,42 +1501,42 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>加口 貴美子</t>
+          <t>川北 大洋</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>202420418</t>
+          <t>202520443</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>日本における男女の賃金格差の推移</t>
+          <t>無人型宿泊施設集積地における防災対応の実態と課題に関する研究 －東京都墨田区を対象として－</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>岡本 翔平</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>小西 葉子</t>
+          <t>有田 智一</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>イリチュ 美佳</t>
+          <t>梅本 通孝</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0.8589707612991333</v>
+        <v>0.8778388798236847</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8557016253471375</v>
+        <v>0.8740247189998627</v>
       </c>
       <c r="J24" t="n">
-        <v>0.8524296879768372</v>
+        <v>0.871728777885437</v>
       </c>
     </row>
     <row r="25">
@@ -1547,42 +1547,42 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>田之口 輝毅</t>
+          <t>河嶋 由羽</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>202420447</t>
+          <t>202520444</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SNS上のESGセンチメント</t>
+          <t>自動車社会を前提とした歩きたくなるまちづくりに向けた研究</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
+          <t>讃井 知</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>上市 秀雄</t>
+          <t>雨宮 護</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>讃井 知</t>
+          <t>甲斐田 直子</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0.8711104393005371</v>
+        <v>0.8605781495571136</v>
       </c>
       <c r="I25" t="n">
-        <v>0.8644373416900635</v>
+        <v>0.8576709926128387</v>
       </c>
       <c r="J25" t="n">
-        <v>0.8609387874603271</v>
+        <v>0.8573781847953796</v>
       </c>
     </row>
     <row r="26">
@@ -1593,27 +1593,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>笹井 大</t>
+          <t>北川 悠太</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>202420433</t>
+          <t>202520445</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ESG関連インデックスと株式市場</t>
+          <t>SNS上の分極の生成メカニズムが誤情報対策の有効性に与える影響：同質性モデルと再配線モデルの比較</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>秋山 英三</t>
+          <t>上市 秀雄</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>三崎 広海</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1622,13 +1622,13 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0.8609838485717773</v>
+        <v>0.8725013732910156</v>
       </c>
       <c r="I26" t="n">
-        <v>0.8606991767883301</v>
+        <v>0.8715296983718872</v>
       </c>
       <c r="J26" t="n">
-        <v>0.8603500425815582</v>
+        <v>0.863963395357132</v>
       </c>
     </row>
     <row r="27">
@@ -1639,42 +1639,42 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>水越 知弘</t>
+          <t>久野 竜一朗</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>202420471</t>
+          <t>202520446</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>介護が労働に与える影響</t>
+          <t>容量制約と認知バイアスを考慮した都市鉄道ネットワークのリダンダンシー評価</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>上市 秀雄</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>岡田 幸彦</t>
+          <t>Tran Lam Anh Duong</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0.8587648272514343</v>
+        <v>0.878728061914444</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8570155799388885</v>
+        <v>0.8697108924388885</v>
       </c>
       <c r="J27" t="n">
-        <v>0.8559012115001678</v>
+        <v>0.8690555095672607</v>
       </c>
     </row>
     <row r="28">
@@ -1685,42 +1685,42 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>鈴木 優梨歌</t>
+          <t>黒田 諄人</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>202420439</t>
+          <t>202520448</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>複数工場間の経路最適化を含む多目的マルチファクトリー・スケジューリング</t>
+          <t>日本市場で情報取得コストが高い局面における議決権行使助言会社の議決への影響</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>有馬 澄佳</t>
+          <t>小西 葉子</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>吉瀬 章子</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>原田 信行</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0.8741349577903748</v>
+        <v>0.8659414350986481</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8709458708763123</v>
+        <v>0.8614097535610199</v>
       </c>
       <c r="J28" t="n">
-        <v>0.8677653074264526</v>
+        <v>0.8572182357311249</v>
       </c>
     </row>
     <row r="29">
@@ -1731,42 +1731,42 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>永井 康友</t>
+          <t>高 野</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>202420451</t>
+          <t>202520449</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>品質検査レイヤーを横断した異常原因探索～画像マルチモーダルアプローチ</t>
+          <t>日本と諸外国のインバウンド政策の比較に基づく観光客推移の予測に関する研究</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>有馬 澄佳</t>
+          <t>岡本 直久</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>高野 祐一</t>
+          <t>小西 葉子</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0.8854930698871613</v>
+        <v>0.8861464560031891</v>
       </c>
       <c r="I29" t="n">
-        <v>0.8639017939567566</v>
+        <v>0.8746454119682312</v>
       </c>
       <c r="J29" t="n">
-        <v>0.863455206155777</v>
+        <v>0.8714252412319183</v>
       </c>
     </row>
     <row r="30">
@@ -1777,42 +1777,42 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>戴 家成</t>
+          <t>兒玉 名奈</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>202420442</t>
+          <t>202520450</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>機械サーバと人間サーバが混在するサービスシステムの性能解析</t>
+          <t>地域拠点における対話による市民の潜在的ニーズの発掘と資源化に関する研究 －地域コミュニティ拠点『machimin』を対象として－</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Phung-Duc Tuan</t>
+          <t>山本 幸子</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>讃井 知</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>岡田 幸彦</t>
+          <t>有田 智一</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>0.8844201862812042</v>
+        <v>0.8737453818321228</v>
       </c>
       <c r="I30" t="n">
-        <v>0.8559956550598145</v>
+        <v>0.8686347007751465</v>
       </c>
       <c r="J30" t="n">
-        <v>0.8549239039421082</v>
+        <v>0.8675165772438049</v>
       </c>
     </row>
     <row r="31">
@@ -1823,42 +1823,42 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>神野 大地</t>
+          <t>後藤 優希</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>202420427</t>
+          <t>202520451</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>東京証券取引所によるPBR改善要請の影響は企業特性によって異なるか？</t>
+          <t>バースト到着とウォームアップ時間を考慮した省電力NFVハイブリッドシステムの解析</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>黒瀬 雄大</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>秋山 英三</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>有田 智一</t>
+          <t>讃井 知</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>0.8590705394744873</v>
+        <v>0.8504707515239716</v>
       </c>
       <c r="I31" t="n">
-        <v>0.8586950898170471</v>
+        <v>0.8496311902999878</v>
       </c>
       <c r="J31" t="n">
-        <v>0.8542488515377045</v>
+        <v>0.8495571911334991</v>
       </c>
     </row>
     <row r="32">
@@ -1869,22 +1869,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LU SICHEN</t>
+          <t>櫻井 舜</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>202420494</t>
+          <t>202520452</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>四川大震災についての地元住民の記憶とその変容—汶川県映秀鎮と北川県を比較して—</t>
+          <t>半自動アノテーションに基づく汎用視聴覚音響イベント物体定位・検出</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>梅本 通孝</t>
+          <t>讃井 知</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1894,17 +1894,17 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>讃井 知</t>
+          <t>秋山 英三</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0.8718172013759613</v>
+        <v>0.8459481298923492</v>
       </c>
       <c r="I32" t="n">
-        <v>0.857513427734375</v>
+        <v>0.8438551723957062</v>
       </c>
       <c r="J32" t="n">
-        <v>0.8540211319923401</v>
+        <v>0.8411489725112915</v>
       </c>
     </row>
     <row r="33">
@@ -1915,42 +1915,42 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>石川 夏帆</t>
+          <t>櫻井 俊太郎</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>202420410</t>
+          <t>202520453</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>多様な主体が関わる出産祝いによる産後家庭アウトリーチの実態と課題－横浜市戸塚区の認定NPO法人こまちぷらすのウェルカムベビープロジェクトに着目して－</t>
+          <t>多ノイズ在庫・物流の構造的分析～因果分析と正準相関分析に基づいて</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>岡本 翔平</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>讃井 知</t>
+          <t>八森 正泰</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
+          <t>高野 祐一</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>0.8646641969680786</v>
+        <v>0.8735739290714264</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8642510771751404</v>
+        <v>0.8708217442035675</v>
       </c>
       <c r="J33" t="n">
-        <v>0.8624968230724335</v>
+        <v>0.8674927651882172</v>
       </c>
     </row>
     <row r="34">
@@ -1961,42 +1961,42 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>鳩貝 優太</t>
+          <t>佐藤 日向子</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>202420458</t>
+          <t>202520454</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>カフェ型居場所の開設・運営プロセスにおける障壁と支援に関する研究－認定NPO法人こまちぷらすの講座に着目して－</t>
+          <t>ロードプライシングの段階的料金変更に対する需要の価格弾力性分析： 東京湾アクアラインのケーススタディ</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>讃井 知</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>雨宮 護</t>
+          <t>吉瀬 章子</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>0.8659263253211975</v>
+        <v>0.8794162273406982</v>
       </c>
       <c r="I34" t="n">
-        <v>0.8634572923183441</v>
+        <v>0.8755110502243042</v>
       </c>
       <c r="J34" t="n">
-        <v>0.8626151084899902</v>
+        <v>0.8711532652378082</v>
       </c>
     </row>
     <row r="35">
@@ -2007,42 +2007,42 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>畑 颯汰</t>
+          <t>猿渡 豪</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>202420456</t>
+          <t>202520455</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>斜面住宅地の存続可能性に関する研究 －段差解消のための共有財の維持管理に着目して－</t>
+          <t>公害苦情の感覚・心理的被害の変遷についての研究</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>山本 幸子</t>
+          <t>讃井 知</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>有田 智一</t>
+          <t>上市 秀雄</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>渡邉 俊</t>
+          <t>雨宮 護</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>0.8801654279232025</v>
+        <v>0.8534249365329742</v>
       </c>
       <c r="I35" t="n">
-        <v>0.8784414231777191</v>
+        <v>0.8462549448013306</v>
       </c>
       <c r="J35" t="n">
-        <v>0.8745453953742981</v>
+        <v>0.8445098996162415</v>
       </c>
     </row>
     <row r="36">
@@ -2053,42 +2053,42 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>石田 悠人</t>
+          <t>柴田 龍聖</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>202420411</t>
+          <t>202520456</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>公園の農的利用の効果と課題に関する研究</t>
+          <t>避難シミュレータの汎用化にむけた避難行動への影響要因のメタ分析</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>太田 充</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>梅本 通孝</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>小西 葉子</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>0.8759267032146454</v>
+        <v>0.8738100528717041</v>
       </c>
       <c r="I36" t="n">
-        <v>0.8731176853179932</v>
+        <v>0.8697246611118317</v>
       </c>
       <c r="J36" t="n">
-        <v>0.8701472282409668</v>
+        <v>0.8684316277503967</v>
       </c>
     </row>
     <row r="37">
@@ -2099,42 +2099,42 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>高橋 慧</t>
+          <t>白鳥 春菜</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>202420444</t>
+          <t>202520457</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>地方自治体における統計的因果推論に基づく政策分析の適用方法に関する研究</t>
+          <t>確率制約付き最適化問題に対するペナルティ交互方向法</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>Liu Tianxiang</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>八森 正泰</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>吉瀬 章子</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>0.8812141716480255</v>
+        <v>0.8708596229553223</v>
       </c>
       <c r="I37" t="n">
-        <v>0.8785416781902313</v>
+        <v>0.8647412061691284</v>
       </c>
       <c r="J37" t="n">
-        <v>0.8743589520454407</v>
+        <v>0.8604106307029724</v>
       </c>
     </row>
     <row r="38">
@@ -2145,42 +2145,42 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>酒井 佑</t>
+          <t>助川 雅俊</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>202420431</t>
+          <t>202520458</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>地域外の人材を対象とした逆指名による創業支援制度の運用実態と他地域展開の可能性に関する研究</t>
+          <t>線形相補性問題のBard型アルゴリズムによる超立方体構造に出現するサイクルの考察</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>山本 幸子</t>
+          <t>秋山 英三</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>讃井 知</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>讃井 知</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>0.8687264025211334</v>
+        <v>0.8495572209358215</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8683319091796875</v>
+        <v>0.8459269106388092</v>
       </c>
       <c r="J38" t="n">
-        <v>0.8674037456512451</v>
+        <v>0.8455456793308258</v>
       </c>
     </row>
     <row r="39">
@@ -2191,42 +2191,42 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>佐藤 佳乃</t>
+          <t>鈴木 大志</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>202420437</t>
+          <t>202520459</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>地籍調査の進捗に関する地理空間分析</t>
+          <t>東京都の総量削減義務と排出量取引制度が大規模事業所のCO2削減に及ぼす効果 ～臨海副都心地域を対象として～</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
+          <t>甲斐田 直子</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
           <t>川島 宏一</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>渡邉 俊</t>
-        </is>
-      </c>
       <c r="H39" t="n">
-        <v>0.886952131986618</v>
+        <v>0.8758090436458588</v>
       </c>
       <c r="I39" t="n">
-        <v>0.8798272311687469</v>
+        <v>0.8726612329483032</v>
       </c>
       <c r="J39" t="n">
-        <v>0.8780930638313293</v>
+        <v>0.8673579096794128</v>
       </c>
     </row>
     <row r="40">
@@ -2237,42 +2237,42 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>早坂 遼</t>
+          <t>鈴木 敏博</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>202420547</t>
+          <t>202520460</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>羽田空港新飛行経路の運用開始が東京都心の不動産価値に与えた影響に関する計量分析</t>
+          <t>クラインガルテンを起点とした二地域居住者の地域関与の形成プロセスに関する研究― 笠間市を事例として ―</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>山本 幸子</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>堤 盛人</t>
+          <t>有田 智一</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>太田 充</t>
+          <t>松原 康介</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>0.8817868828773499</v>
+        <v>0.8725372850894928</v>
       </c>
       <c r="I40" t="n">
-        <v>0.881300151348114</v>
+        <v>0.8562148809432983</v>
       </c>
       <c r="J40" t="n">
-        <v>0.8805911839008331</v>
+        <v>0.8561661839485168</v>
       </c>
     </row>
     <row r="41">
@@ -2283,42 +2283,42 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>釜谷 紘生</t>
+          <t>角田 圭梧</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>202420422</t>
+          <t>202520461</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>マニラ都市圏における洪水リスクが不動産価格に与える影響の分析</t>
+          <t>睡眠の質と空間条件および活動内容が認知機能と心理的回復に与える影響に関する研究</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>堤 盛人</t>
+          <t>讃井 知</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>梅本 通孝</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>渡邉 俊</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>0.8820194602012634</v>
+        <v>0.8807381391525269</v>
       </c>
       <c r="I41" t="n">
-        <v>0.8765389025211334</v>
+        <v>0.8756651878356934</v>
       </c>
       <c r="J41" t="n">
-        <v>0.8708105087280273</v>
+        <v>0.8744292557239532</v>
       </c>
     </row>
     <row r="42">
@@ -2329,42 +2329,42 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>市川 はるひ</t>
+          <t>瀨古 希</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>202420455</t>
+          <t>202520462</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>冒険遊び場における犯罪被害と運営者の対応の実態解明</t>
+          <t>ヨジェ・プレチニック(1872年-1957年)の都市計画業績にみるポストモダニズムの萌芽</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>讃井 知</t>
+          <t>松原 康介</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>雨宮 護</t>
+          <t>渡邉 俊</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>有田 智一</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>0.8671787977218628</v>
+        <v>0.8656892478466034</v>
       </c>
       <c r="I42" t="n">
-        <v>0.8621288537979126</v>
+        <v>0.850430428981781</v>
       </c>
       <c r="J42" t="n">
-        <v>0.8617662489414215</v>
+        <v>0.849077045917511</v>
       </c>
     </row>
     <row r="43">
@@ -2375,42 +2375,42 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>舩戸 祐汰</t>
+          <t>高橋 勲平</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>202420466</t>
+          <t>202520463</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>屋外着座空間への評価と独り好き志向性との関係</t>
+          <t>オンライン・マーケットプレイスにおける新規参入に関する分析</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>渡邉 俊</t>
+          <t>上市 秀雄</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>讃井 知</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>髙橋 裕紀</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>0.8732402622699738</v>
+        <v>0.8466545939445496</v>
       </c>
       <c r="I43" t="n">
-        <v>0.8722307682037354</v>
+        <v>0.8459292948246002</v>
       </c>
       <c r="J43" t="n">
-        <v>0.8673423528671265</v>
+        <v>0.8441087305545807</v>
       </c>
     </row>
     <row r="44">
@@ -2421,42 +2421,42 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>廣田 華</t>
+          <t>高橋 南織</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>202420465</t>
+          <t>202520464</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>農村舞台の現状とその保全—ハード・ソフトの両面に着目して—</t>
+          <t>幼少期の過ごし方が地域コミュニティへの関与意向に与える影響</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>讃井 知</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>讃井 知</t>
+          <t>山本 幸子</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>藤川 昌樹</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>0.8610954582691193</v>
+        <v>0.8725491166114807</v>
       </c>
       <c r="I44" t="n">
-        <v>0.8604768514633179</v>
+        <v>0.8676817417144775</v>
       </c>
       <c r="J44" t="n">
-        <v>0.8600713014602661</v>
+        <v>0.8616174459457397</v>
       </c>
     </row>
     <row r="45">
@@ -2467,42 +2467,42 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>陳 泓儒</t>
+          <t>髙村 瑠璃</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>202420492</t>
+          <t>202520465</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ディープラーニングに基づく武漢の都市イメージの空間構造と都市計画実施に関する研究</t>
+          <t>商業機能が衰退した地域における分散型宿泊施設の存立構造ー「まちやど」を対象としてー</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>渡邉 俊</t>
+          <t>山本 幸子</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
+          <t>松原 康介</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
           <t>藤川 昌樹</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>松原 康介</t>
-        </is>
-      </c>
       <c r="H45" t="n">
-        <v>0.8848141729831696</v>
+        <v>0.8705042600631714</v>
       </c>
       <c r="I45" t="n">
-        <v>0.884340912103653</v>
+        <v>0.8618135452270508</v>
       </c>
       <c r="J45" t="n">
-        <v>0.8809525072574615</v>
+        <v>0.8590433597564697</v>
       </c>
     </row>
     <row r="46">
@@ -2513,42 +2513,42 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>坂本 怜奈</t>
+          <t>瀧澤 遥希</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>202420432</t>
+          <t>202520466</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>地域ネットワークにおける中間支援組織の役割とマネジメントシステムの構築に関する考察</t>
+          <t>欠損データを考慮した多次元項目反応理論モデルのベイズ推定</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Tran Lam Anh Duong</t>
+          <t>イリチュ 美佳</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>張 勇兵</t>
+          <t>黒瀬 雄大</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>0.8686491549015045</v>
+        <v>0.8530411720275879</v>
       </c>
       <c r="I46" t="n">
-        <v>0.8679175078868866</v>
+        <v>0.845608651638031</v>
       </c>
       <c r="J46" t="n">
-        <v>0.8637300729751587</v>
+        <v>0.8430800437927246</v>
       </c>
     </row>
     <row r="47">
@@ -2559,42 +2559,42 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>佐々木 智哉</t>
+          <t>田中 大凱</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>202420435</t>
+          <t>202520467</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>都市再生緊急整備地域における都市再生の政策効果の検証ー地方中核都市の事例を対象として</t>
+          <t>ネットワーク上の2×2ゲームにおける学習能力の異質性と協力進化</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>澤 亮治</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>太田 充</t>
+          <t>八森 正泰</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>0.8822457492351532</v>
+        <v>0.8600080013275146</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8808684647083282</v>
+        <v>0.8581774532794952</v>
       </c>
       <c r="J47" t="n">
-        <v>0.8796663880348206</v>
+        <v>0.8559065759181976</v>
       </c>
     </row>
     <row r="48">
@@ -2605,42 +2605,42 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>髙野 駿</t>
+          <t>為沢 雄太</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>202420443</t>
+          <t>202520468</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>観光都市におけるオーバーツーリズムの対策やそれに伴う効果と課題について</t>
+          <t>バス運転手の仕業作成問題における混合整数計画モデルの拡張と計算時間短縮手法の検討</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>岡本 直久</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>髙橋 裕紀</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>梅本 通孝</t>
+          <t>浦田 淳司</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>0.8762216567993164</v>
+        <v>0.8463076949119568</v>
       </c>
       <c r="I48" t="n">
-        <v>0.8687419593334198</v>
+        <v>0.8454867601394653</v>
       </c>
       <c r="J48" t="n">
-        <v>0.8667344450950623</v>
+        <v>0.8453716337680817</v>
       </c>
     </row>
     <row r="49">
@@ -2651,42 +2651,42 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>高橋 梨沙子</t>
+          <t>塚本 瑞貴</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>202420445</t>
+          <t>202520469</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>観光地における駅舎建築に関する研究</t>
+          <t>Transformer型Pointer Networkを用いた飲食店における調理順序スケジューリング</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>岡本 直久</t>
+          <t>繁野 麻衣子</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>藤川 昌樹</t>
+          <t>吉瀬 章子</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>渡邉 俊</t>
+          <t>八森 正泰</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0.8662877678871155</v>
+        <v>0.870422899723053</v>
       </c>
       <c r="I49" t="n">
-        <v>0.8646083772182465</v>
+        <v>0.869493305683136</v>
       </c>
       <c r="J49" t="n">
-        <v>0.8645975589752197</v>
+        <v>0.861149787902832</v>
       </c>
     </row>
     <row r="50">
@@ -2697,42 +2697,42 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>小松 諒治</t>
+          <t>出本 大起</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>202420428</t>
+          <t>202520470</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>地域公共交通サービス変化時の活動機会変化の計測に関する研究</t>
+          <t>幹線・フィーダー型のバスネットワーク最適化手法の構築</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>八森 正泰</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>岡本 直久</t>
+          <t>吉瀬 章子</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>和田 健太郎</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>0.8832989037036896</v>
+        <v>0.8789788782596588</v>
       </c>
       <c r="I50" t="n">
-        <v>0.8805747926235199</v>
+        <v>0.8715095520019531</v>
       </c>
       <c r="J50" t="n">
-        <v>0.878088504076004</v>
+        <v>0.8685348629951477</v>
       </c>
     </row>
     <row r="51">
@@ -2743,42 +2743,42 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>佐光 未帆</t>
+          <t>中澤 瑠河</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>202420438</t>
+          <t>202520472</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>大学敷地内における大学生の犯罪被害の実態と報告行動の解明</t>
+          <t>歩行者・自転車の錯綜評価にむけた相互作用モデルへの個人間異質性と量子計算の導入</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>讃井 知</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>雨宮 護</t>
+          <t>和田 健太郎</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>谷口 綾子</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>0.8624387383460999</v>
+        <v>0.8764743208885193</v>
       </c>
       <c r="I51" t="n">
-        <v>0.862365335226059</v>
+        <v>0.8751050531864166</v>
       </c>
       <c r="J51" t="n">
-        <v>0.8559727668762207</v>
+        <v>0.8731650412082672</v>
       </c>
     </row>
     <row r="52">
@@ -2789,42 +2789,42 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tang Xinyu</t>
+          <t>中嶋 駿</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>202420490</t>
+          <t>202520473</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>職住近接と生活域の拡がりとの関連：GPSデータを用いた検討</t>
+          <t>大規模言語モデルによる半構造化表明選考調査手法の構築</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>上市 秀雄</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>イリチュ 美佳</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>小西 葉子</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>0.8600000739097595</v>
+        <v>0.8628562092781067</v>
       </c>
       <c r="I52" t="n">
-        <v>0.8592597246170044</v>
+        <v>0.8604255318641663</v>
       </c>
       <c r="J52" t="n">
-        <v>0.8584930300712585</v>
+        <v>0.8562762439250946</v>
       </c>
     </row>
     <row r="53">
@@ -2835,42 +2835,42 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>田上 朋樹</t>
+          <t>中山 晴斗</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>202420446</t>
+          <t>202520474</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>人口再配分による食料需給バランス改善への試案 ー「地域で食料が自給できる国土」への視座－</t>
+          <t>大規模イベント開催時の会場周辺における映像解析に基づく混雑状況の定量分析</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>岡本 翔平</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>太田 充</t>
+          <t>浦田 淳司</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>0.8763241469860077</v>
+        <v>0.8492535650730133</v>
       </c>
       <c r="I53" t="n">
-        <v>0.8757403492927551</v>
+        <v>0.8484686315059662</v>
       </c>
       <c r="J53" t="n">
-        <v>0.8713475465774536</v>
+        <v>0.8479881286621094</v>
       </c>
     </row>
     <row r="54">
@@ -2881,42 +2881,42 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>矢橋 敦之</t>
+          <t>中山 凜空</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>202420480</t>
+          <t>202520475</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>都市サービスの長期的な入れ替わりの実態 －2002年と2022年の２時点比較－</t>
+          <t>大規模移動軌跡データの品質向上に向けた欠測検知手法の開発</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
+          <t>イリチュ 美佳</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>浦田 淳司</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
           <t>鈴木 勉</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>堤 盛人</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>讃井 知</t>
-        </is>
-      </c>
       <c r="H54" t="n">
-        <v>0.866838663816452</v>
+        <v>0.8539004325866699</v>
       </c>
       <c r="I54" t="n">
-        <v>0.8634083867073059</v>
+        <v>0.8537878096103668</v>
       </c>
       <c r="J54" t="n">
-        <v>0.8592371940612793</v>
+        <v>0.8486493527889252</v>
       </c>
     </row>
     <row r="55">
@@ -2927,42 +2927,42 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>松浦 海斗</t>
+          <t>西澤 尚輝</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>202420468</t>
+          <t>202520476</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>子どもの体験格差の全国横断的把握 ―学校外での生活行動に着目して－</t>
+          <t>集約データに基づく分布推定と距離指標を用いた類似性分析</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>太田 充</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>甲斐田 直子</t>
+          <t>イリチュ 美佳</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0.8447581827640533</v>
+        <v>0.8511146903038025</v>
       </c>
       <c r="I55" t="n">
-        <v>0.8435723781585693</v>
+        <v>0.8506214320659637</v>
       </c>
       <c r="J55" t="n">
-        <v>0.8434951305389404</v>
+        <v>0.8501562178134918</v>
       </c>
     </row>
     <row r="56">
@@ -2973,42 +2973,42 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>稲葉 翔太</t>
+          <t>西原 梨沙子</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>202420413</t>
+          <t>202520477</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>シェアサイクル運営者の機会損失改善に向けた自転車再配置における調整台数の検討-茨城県つくば市を事例として-</t>
+          <t>金融機関店舗跡地の利用実態および変遷に関する実証研究</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>岡本 直久</t>
+          <t>小西 葉子</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>和田 健太郎</t>
+          <t>三崎 広海</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>有田 智一</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>0.8806582093238831</v>
+        <v>0.8653828203678131</v>
       </c>
       <c r="I56" t="n">
-        <v>0.87824946641922</v>
+        <v>0.8632269501686096</v>
       </c>
       <c r="J56" t="n">
-        <v>0.8735235035419464</v>
+        <v>0.8617116212844849</v>
       </c>
     </row>
     <row r="57">
@@ -3019,42 +3019,42 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>三重野 馨</t>
+          <t>根岸 美空</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>202420470</t>
+          <t>202520478</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>アルジェリアにおけるフェルナン・プイヨンのツーリスト・コンプレックスに関する研究</t>
+          <t>復興都市計画において都市アイデンティティはいかに失われたか ーモロッコ・アガディール地震（1960）をめぐる証言と実像ー</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>讃井 知</t>
+          <t>松原 康介</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>上市 秀雄</t>
+          <t>有田 智一</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>甲斐田 直子</t>
+          <t>山本 幸子</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>0.8453637659549713</v>
+        <v>0.860146701335907</v>
       </c>
       <c r="I57" t="n">
-        <v>0.8431252837181091</v>
+        <v>0.8540288209915161</v>
       </c>
       <c r="J57" t="n">
-        <v>0.8418348729610443</v>
+        <v>0.8500931262969971</v>
       </c>
     </row>
     <row r="58">
@@ -3065,42 +3065,42 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>犬竹 智哉</t>
+          <t>橋本 響</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>202420414</t>
+          <t>202520480</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>商用FCVの普及に向けた水素ステーション配置とCO2排出量の予測</t>
+          <t>特殊詐欺を対象とした犯罪予測モデルの構築</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>和田 健太郎</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>三崎 広海</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>浦田 淳司</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>0.8711833655834198</v>
+        <v>0.8541621565818787</v>
       </c>
       <c r="I58" t="n">
-        <v>0.8702840805053711</v>
+        <v>0.8514554500579834</v>
       </c>
       <c r="J58" t="n">
-        <v>0.8700034618377686</v>
+        <v>0.8468368351459503</v>
       </c>
     </row>
     <row r="59">
@@ -3111,42 +3111,42 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>日高 優一</t>
+          <t>服部 文則</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>202420461</t>
+          <t>202520481</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>基幹交通の組み合わせ利用を考慮した将来交通需要予測に関する研究</t>
+          <t>Capacity Drop 現象の発生メカニズム： マクロモデルとミクロモデルの関係性分析</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>長崎 滉大</t>
+          <t>大久保 正勝</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>岡本 直久</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>和田 健太郎</t>
+          <t>イリチュ 美佳</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>0.8824211359024048</v>
+        <v>0.8487860560417175</v>
       </c>
       <c r="I59" t="n">
-        <v>0.8817901909351349</v>
+        <v>0.8485636711120605</v>
       </c>
       <c r="J59" t="n">
-        <v>0.8766686320304871</v>
+        <v>0.8466636836528778</v>
       </c>
     </row>
     <row r="60">
@@ -3157,42 +3157,42 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>鎌田 晴人</t>
+          <t>東浦 大晟</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>202420421</t>
+          <t>202520482</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ETC2.0プローブデータを活用した旅行時間信頼性の時空間的評価</t>
+          <t>弾性光ネットワークにおける周波数利用効率向上のための動的セグメント経路保護</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>志田 洋平</t>
+          <t>八森 正泰</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>黒瀬 雄大</t>
+          <t>繁野 麻衣子</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>0.8772633671760559</v>
+        <v>0.8760022819042206</v>
       </c>
       <c r="I60" t="n">
-        <v>0.874665379524231</v>
+        <v>0.8626532554626465</v>
       </c>
       <c r="J60" t="n">
-        <v>0.8743585348129272</v>
+        <v>0.8607532680034637</v>
       </c>
     </row>
     <row r="61">
@@ -3203,17 +3203,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>畑山 公希</t>
+          <t>飛田 晴哉</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>202420457</t>
+          <t>202520483</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>自治体におけるグリーンインフラの計画的展開を阻害する要因についての研究</t>
+          <t>工場立地法の緑地規制緩和に伴う環境保全及び生活環境配慮に関する研究</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3223,22 +3223,22 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>村上 暁信</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>讃井 知</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>0.8799072504043579</v>
+        <v>0.8657460808753967</v>
       </c>
       <c r="I61" t="n">
-        <v>0.8760300278663635</v>
+        <v>0.8657316863536835</v>
       </c>
       <c r="J61" t="n">
-        <v>0.8747718930244446</v>
+        <v>0.8615502119064331</v>
       </c>
     </row>
     <row r="62">
@@ -3249,42 +3249,42 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>張 宇星</t>
+          <t>舩橋 佑生</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>202420491</t>
+          <t>202520484</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>清代における祭祀行宮の構成と変容—龍王廟を中心に—</t>
+          <t>待ち行列システムにおいてプロスペクト理論を考慮した最適見積もり時間の提示戦略</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>梅本 通孝</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>吉瀬 章子</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>讃井 知</t>
+          <t>高野 祐一</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>0.8310251235961914</v>
+        <v>0.8874904811382294</v>
       </c>
       <c r="I62" t="n">
-        <v>0.8276545107364655</v>
+        <v>0.8681735396385193</v>
       </c>
       <c r="J62" t="n">
-        <v>0.827650785446167</v>
+        <v>0.8610672652721405</v>
       </c>
     </row>
     <row r="63">
@@ -3295,42 +3295,42 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>森下 陽平</t>
+          <t>古谷 莉菜</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>202420474</t>
+          <t>202520485</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>騒音問題と自己観の関係性：日本・カナダ比較研究</t>
+          <t>港湾緑地における官民連携の特性に関する研究―みなと緑地PPP制度を対象として―</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>讃井 知</t>
+          <t>村上 暁信</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>甲斐田 直子</t>
+          <t>太田 充</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>0.8619557023048401</v>
+        <v>0.8482206463813782</v>
       </c>
       <c r="I63" t="n">
-        <v>0.8604455292224884</v>
+        <v>0.8416445255279541</v>
       </c>
       <c r="J63" t="n">
-        <v>0.8598349094390869</v>
+        <v>0.8387836813926697</v>
       </c>
     </row>
     <row r="64">
@@ -3341,42 +3341,42 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>平林 優希</t>
+          <t>松澤 拓也</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>202420463</t>
+          <t>202520486</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>環境配慮意識・行動の自他評価の特性と行動意図の関係</t>
+          <t>半導体リソグラフィーの条件出し最適化 ～量産特徴活かすデータ駆動アプローチ</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>甲斐田 直子</t>
+          <t>八森 正泰</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>谷口 綾子</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>澤 亮治</t>
+          <t>繁野 麻衣子</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>0.8832572996616364</v>
+        <v>0.8797740340232849</v>
       </c>
       <c r="I64" t="n">
-        <v>0.8624671101570129</v>
+        <v>0.8664391338825226</v>
       </c>
       <c r="J64" t="n">
-        <v>0.8614659905433655</v>
+        <v>0.8657128810882568</v>
       </c>
     </row>
     <row r="65">
@@ -3387,42 +3387,42 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>中澤 光希</t>
+          <t>皆川 雄太</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>202420452</t>
+          <t>202520487</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>都市再生特別地区において多様化する域外貢献の実態と課題に関する研究</t>
+          <t>複雑ネットワークにおける意見の分極化のヒステリシスについて</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>渡邉 俊</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>八森 正泰</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>太田 充</t>
+          <t>上市 秀雄</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>0.8763947486877441</v>
+        <v>0.8648021221160889</v>
       </c>
       <c r="I65" t="n">
-        <v>0.8731106221675873</v>
+        <v>0.8587773740291595</v>
       </c>
       <c r="J65" t="n">
-        <v>0.8720408380031586</v>
+        <v>0.8559302091598511</v>
       </c>
     </row>
     <row r="66">
@@ -3433,17 +3433,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>草田 弦喜</t>
+          <t>宮下 和士</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>202420424</t>
+          <t>202520488</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>銀座ルールと比較した『日本橋らしさ』に関する研究-東京都日本橋地区を対象として-</t>
+          <t>買物消費額と交通行動の関係 －都市機能誘導区域と個人属性に着目して－</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3453,22 +3453,22 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>渡邉 俊</t>
+          <t>谷口 綾子</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>0.8690553307533264</v>
+        <v>0.8854454457759857</v>
       </c>
       <c r="I66" t="n">
-        <v>0.865460604429245</v>
+        <v>0.8833464384078979</v>
       </c>
       <c r="J66" t="n">
-        <v>0.8637253046035767</v>
+        <v>0.8789984881877899</v>
       </c>
     </row>
     <row r="67">
@@ -3479,42 +3479,42 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>加藤 優弥</t>
+          <t>森 正晴</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>202420419</t>
+          <t>202520490</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>スタジアム・アリーナの多機能化に伴う公民連携によるエリアマネジメントに関する研究</t>
+          <t>交差確認規準と最小二乗SVMに基づく特徴量選択</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>渡邉 俊</t>
+          <t>秋山 英三</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>有田 智一</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>大久保 正勝</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>0.8704356253147125</v>
+        <v>0.8467667102813721</v>
       </c>
       <c r="I67" t="n">
-        <v>0.8688648045063019</v>
+        <v>0.8456202745437622</v>
       </c>
       <c r="J67" t="n">
-        <v>0.8686460554599762</v>
+        <v>0.8442079126834869</v>
       </c>
     </row>
     <row r="68">
@@ -3525,42 +3525,42 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>水野 瑛介</t>
+          <t>矢口 未於乃</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>202420472</t>
+          <t>202520491</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>メジャーリーグにおける統計的差別と選好的差別</t>
+          <t>ビッグデータを用いた観光地域内周遊行動のモデル化とその応用</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>秋山 英三</t>
+          <t>岡本 直久</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>上市 秀雄</t>
+          <t>志田 洋平</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>讃井 知</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>0.8518876731395721</v>
+        <v>0.8728138208389282</v>
       </c>
       <c r="I68" t="n">
-        <v>0.8515321016311646</v>
+        <v>0.8711625337600708</v>
       </c>
       <c r="J68" t="n">
-        <v>0.8461630940437317</v>
+        <v>0.8694121241569519</v>
       </c>
     </row>
     <row r="69">
@@ -3571,42 +3571,42 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>山縣 力也</t>
+          <t>柳田 周造</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>202420481</t>
+          <t>202520492</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>非罰則規制の犯罪波及効果：渋谷区の路上飲酒禁止条例を事例として</t>
+          <t>地方中小企業における複業人材との互恵的協働モデルに関する研究 －企業の自走化を促す業務設計と仲介機能に着目して－</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>讃井 知</t>
+          <t>岡田 幸彦</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>秋山 英三</t>
+          <t>髙橋 裕紀</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>0.8769176304340363</v>
+        <v>0.8480951189994812</v>
       </c>
       <c r="I69" t="n">
-        <v>0.8657228648662567</v>
+        <v>0.8476590514183044</v>
       </c>
       <c r="J69" t="n">
-        <v>0.8631937503814697</v>
+        <v>0.8476487994194031</v>
       </c>
     </row>
     <row r="70">
@@ -3617,42 +3617,42 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>青木 日花</t>
+          <t>山口 遥大</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>202420406</t>
+          <t>202520493</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>アメニティに着目した価値あるオフィスビルの要因分析と効果検証</t>
+          <t>鉄道延伸事業に対する便益評価方法の比較研究</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>小西 葉子</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>太田 充</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>0.8752852082252502</v>
+        <v>0.8448813855648041</v>
       </c>
       <c r="I70" t="n">
-        <v>0.8721947968006134</v>
+        <v>0.8417623937129974</v>
       </c>
       <c r="J70" t="n">
-        <v>0.8721112906932831</v>
+        <v>0.8410535752773285</v>
       </c>
     </row>
     <row r="71">
@@ -3663,42 +3663,42 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>GAO WENWEN</t>
+          <t>山渕 智也</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>202420488</t>
+          <t>202520494</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>グリーンビルディング認証がJ-REITのパフォーマンスに与える影響の実証分析</t>
+          <t>全国における二地域居住の実施状況 －DaaS(Dual Habitation as a Service)の実現に向けてー</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
+          <t>山本 幸子</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
           <t>川島 宏一</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>原田 信行</t>
-        </is>
-      </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>甲斐田 直子</t>
+          <t>有田 智一</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>0.8696563541889191</v>
+        <v>0.8706452250480652</v>
       </c>
       <c r="I71" t="n">
-        <v>0.8675041198730469</v>
+        <v>0.8576701283454895</v>
       </c>
       <c r="J71" t="n">
-        <v>0.8670809268951416</v>
+        <v>0.8568777441978455</v>
       </c>
     </row>
     <row r="72">
@@ -3709,42 +3709,42 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>平野 晴也</t>
+          <t>山本 紗菜子</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>202420462</t>
+          <t>202520495</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>3次元地図更新のための衛星リモートセンシングによる地形計測手法の開発</t>
+          <t>間接互恵における複数集団への所属が協力の進化と内集団びいきに与える影響</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>秋山 英三</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>山野 博哉</t>
+          <t>讃井 知</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>澤 亮治</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>0.860741138458252</v>
+        <v>0.8674946427345276</v>
       </c>
       <c r="I72" t="n">
-        <v>0.8598228096961975</v>
+        <v>0.865528404712677</v>
       </c>
       <c r="J72" t="n">
-        <v>0.8596481382846832</v>
+        <v>0.8628238141536713</v>
       </c>
     </row>
     <row r="73">
@@ -3755,42 +3755,42 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>WEI MIAOHENG</t>
+          <t>LI JIANGXI</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>202420486</t>
+          <t>202520496</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>往復移動と滞在行動を考慮したバス頻度問題</t>
+          <t>物資の緊急度と避難者属性を考慮した災害時救援物資配送問題の数理モデル</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>和田 健太郎</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>岡本 直久</t>
+          <t>吉瀬 章子</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>0.8742719292640686</v>
+        <v>0.8715511560440063</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8719367384910583</v>
+        <v>0.8690094351768494</v>
       </c>
       <c r="J73" t="n">
-        <v>0.8718547224998474</v>
+        <v>0.868798553943634</v>
       </c>
     </row>
     <row r="74">
@@ -3801,42 +3801,42 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>田村 侑介</t>
+          <t>和田 菜々里</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>202420449</t>
+          <t>202520497</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>共同住宅におけるEV充電器設置の意思決定メカニズムの解析</t>
+          <t>ポートフォリオ最適化に対する最適保証スクリーニング</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>八森 正泰</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>Liu Tianxiang</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>0.8715938329696655</v>
+        <v>0.863420844078064</v>
       </c>
       <c r="I74" t="n">
-        <v>0.8709504008293152</v>
+        <v>0.8619250059127808</v>
       </c>
       <c r="J74" t="n">
-        <v>0.8709364533424377</v>
+        <v>0.859403520822525</v>
       </c>
     </row>
     <row r="75">
@@ -3847,42 +3847,42 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>山田 圭祐</t>
+          <t>渡邉 唯斗</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>202420483</t>
+          <t>202520498</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>ミクロ交通シミュレーション利用における機械学習モデルの有効性検討</t>
+          <t>中世〜近世における境内都市の形成と変容：香取神宮と鹿島神宮を対象として</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>松原 康介</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Phung-Duc Tuan</t>
+          <t>山本 幸子</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>和田 健太郎</t>
+          <t>藤川 昌樹</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>0.8804836571216583</v>
+        <v>0.8413382172584534</v>
       </c>
       <c r="I75" t="n">
-        <v>0.879767507314682</v>
+        <v>0.8388773202896118</v>
       </c>
       <c r="J75" t="n">
-        <v>0.8787779808044434</v>
+        <v>0.8376223742961884</v>
       </c>
     </row>
     <row r="76">
@@ -3893,42 +3893,42 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>平山 裕紀人</t>
+          <t>渡邊 優樹</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>202420464</t>
+          <t>202520499</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>マクロ交通流理論に基づくグリッドロック現象の分析：タイ・バンコクを対象として</t>
+          <t>生きづらさを抱えた子ども・若者の居場所における動物介在の意義に関する研究 －認定NPO法人キドックスを対象として－</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Phung-Duc Tuan</t>
+          <t>讃井 知</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>長崎 滉大</t>
+          <t>山本 幸子</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>雨宮 護</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>0.8646461963653564</v>
+        <v>0.8615443408489227</v>
       </c>
       <c r="I76" t="n">
-        <v>0.8642684817314148</v>
+        <v>0.8565350770950317</v>
       </c>
       <c r="J76" t="n">
-        <v>0.858845442533493</v>
+        <v>0.8549287915229797</v>
       </c>
     </row>
     <row r="77">
@@ -3939,42 +3939,42 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>桑原 慶太</t>
+          <t>YIN MIN</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>202420426</t>
+          <t>202520500</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>データ同化手法を用いたネットワーク交通流モデルの精度改善及びパラメータ推定</t>
+          <t>製造装置の予知保全に関する研究 ―処理系列横断の因果構造分析を中心に ―</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>イリチュ 美佳</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>長崎 滉大</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phung-Duc Tuan</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>0.8770518004894257</v>
+        <v>0.8526158630847931</v>
       </c>
       <c r="I77" t="n">
-        <v>0.8761831521987915</v>
+        <v>0.8472535312175751</v>
       </c>
       <c r="J77" t="n">
-        <v>0.8737709820270538</v>
+        <v>0.8447800874710083</v>
       </c>
     </row>
     <row r="78">
@@ -3985,42 +3985,42 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>徐 摯恒</t>
+          <t>張 家賓</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>202420489</t>
+          <t>202520501</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>高速鉄道の開通が都市経済に与える影響の分析</t>
+          <t>Affine-Independence Approach to a Fingerprinting Code Problem</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>太田 充</t>
+          <t>讃井 知</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>堤 盛人</t>
+          <t>澤 亮治</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>0.880396842956543</v>
+        <v>0.8150631785392761</v>
       </c>
       <c r="I78" t="n">
-        <v>0.8773619830608368</v>
+        <v>0.8095495998859406</v>
       </c>
       <c r="J78" t="n">
-        <v>0.8741996884346008</v>
+        <v>0.8084698915481567</v>
       </c>
     </row>
     <row r="79">
@@ -4031,42 +4031,42 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>松場 拓海</t>
+          <t>陳 怀之</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>202420469</t>
+          <t>202520502</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>「認識人口」概念の提案とその実態―市町村に対するポジティブ／ネガティブイメージの分析から－</t>
+          <t>Transient Analysis of M/M/c/Setup Queues based on Physics-Informed Neural Net...</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>岡本 翔平</t>
+          <t>讃井 知</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>讃井 知</t>
+          <t>浦田 淳司</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>0.876856803894043</v>
+        <v>0.8340822756290436</v>
       </c>
       <c r="I79" t="n">
-        <v>0.8733054995536804</v>
+        <v>0.8291230797767639</v>
       </c>
       <c r="J79" t="n">
-        <v>0.867338240146637</v>
+        <v>0.8263863027095795</v>
       </c>
     </row>
     <row r="80">
@@ -4077,42 +4077,42 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>馬場 理彰</t>
+          <t>CHEN ZHIYAO</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>202420459</t>
+          <t>202520503</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>プロサッカーチームのリーグ昇降格が街並みに与える影響</t>
+          <t>観光化に伴う「人村分離」の空間変容―中国雲南省翁丁集落を事例に</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>藤川 昌樹</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
+          <t>松原 康介</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
           <t>太田 充</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>堤 盛人</t>
-        </is>
-      </c>
       <c r="H80" t="n">
-        <v>0.8574393689632416</v>
+        <v>0.8768689632415771</v>
       </c>
       <c r="I80" t="n">
-        <v>0.8544398844242096</v>
+        <v>0.8746379613876343</v>
       </c>
       <c r="J80" t="n">
-        <v>0.8538867235183716</v>
+        <v>0.8696686923503876</v>
       </c>
     </row>
     <row r="81">
@@ -4123,42 +4123,42 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>佐々木 智哉</t>
+          <t>HU MIMI</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>202420436</t>
+          <t>202520505</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>コロナ禍以降のバイク需要の持続的拡大の要因：経験財理論に基づく考察</t>
+          <t>Heterogeneous impacts of carbon taxes on households in China</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>小西 葉子</t>
+          <t>讃井 知</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>讃井 知</t>
+          <t>作道 真理</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>浦田 淳司</t>
+          <t>甲斐田 直子</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>0.8598234951496124</v>
+        <v>0.8296012878417969</v>
       </c>
       <c r="I81" t="n">
-        <v>0.8560391366481781</v>
+        <v>0.8292419612407684</v>
       </c>
       <c r="J81" t="n">
-        <v>0.8557764291763306</v>
+        <v>0.8284183740615845</v>
       </c>
     </row>
     <row r="82">
@@ -4169,42 +4169,42 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>網野 景介</t>
+          <t>熊 龍天</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>202420408</t>
+          <t>202520506</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>M-1グランプリのシグナリング効果：動画再生数への影響</t>
+          <t>Exploiting Sparsity toTackle High-Dimensionality in Non-Convex-Concave Mim-M...</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>小西 葉子</t>
+          <t>讃井 知</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
+          <t>高野 祐一</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>作道 真理</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>0.853056937456131</v>
+        <v>0.8296072781085968</v>
       </c>
       <c r="I82" t="n">
-        <v>0.852622389793396</v>
+        <v>0.8292145133018494</v>
       </c>
       <c r="J82" t="n">
-        <v>0.8521038889884949</v>
+        <v>0.8283562362194061</v>
       </c>
     </row>
     <row r="83">
@@ -4215,42 +4215,42 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>神尾 瑞貴</t>
+          <t>LIN PENGWEI</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>202420423</t>
+          <t>202520507</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>花粉が経済活動に与える影響</t>
+          <t>Algebraic Manipulation Detection Codes: Refinements and Optimal Constructions</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>小西 葉子</t>
+          <t>イリチュ 美佳</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>Liu Tianxiang</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>原田 信行</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>0.85500568151474</v>
+        <v>0.8149228394031525</v>
       </c>
       <c r="I83" t="n">
-        <v>0.8530831038951874</v>
+        <v>0.8099619150161743</v>
       </c>
       <c r="J83" t="n">
-        <v>0.8515084981918335</v>
+        <v>0.8083364963531494</v>
       </c>
     </row>
     <row r="84">
@@ -4261,42 +4261,134 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>柳 千宙</t>
+          <t>Hongkai Chen</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>202420479</t>
+          <t>202520508</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>分布北限域における南方系海洋生物の北上とその認識</t>
+          <t>Carbon Emission Minimization in an IESS-Based Collaborative Last-Mile Deliver...</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>山野 博哉</t>
+          <t>甲斐田 直子</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>讃井 知</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>作道 真理</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>0.856723815202713</v>
+        <v>0.8309312462806702</v>
       </c>
       <c r="I84" t="n">
-        <v>0.8473109900951385</v>
+        <v>0.8293078541755676</v>
       </c>
       <c r="J84" t="n">
-        <v>0.8449655175209045</v>
+        <v>0.8292732536792755</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>YANG HAOYU</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>202520509</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Understanding and Predicting Electric Vehicle Charging Behavior using Probe c...</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>秋山 英三</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>甲斐田 直子</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>讃井 知</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>0.8385043144226074</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0.8338599503040314</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0.8336627185344696</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>MPPS</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>北條 英次</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>202220454</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>部活動運営主体の地域移行改革とコミュニティ</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>山本 幸子</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>讃井 知</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>有田 智一</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>0.8619189262390137</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0.855473667383194</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0.8548861145973206</v>
       </c>
     </row>
   </sheetData>
@@ -4310,7 +4402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4373,38 +4465,42 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>益子颯太</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>岩本 諒</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>202520510</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>摘要欄情報を用いた仕訳データの異常検知モデルの開発</t>
+          <t>ファミリーレストランの売上予測モデル精度向上に向けた取り組み</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>イリチュ 美佳</t>
+          <t>小西 葉子</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>高野 祐一</t>
+          <t>岡田 幸彦</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>上市 秀雄</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.8635274171829224</v>
+        <v>0.8615496456623077</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8589865863323212</v>
+        <v>0.8529864549636841</v>
       </c>
       <c r="J2" t="n">
-        <v>0.857316792011261</v>
+        <v>0.8524919748306274</v>
       </c>
     </row>
     <row r="3">
@@ -4415,38 +4511,42 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>加田昌杜</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>上島 司</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>202520511</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>筑波大学学年歴の曜日変更最小化</t>
+          <t>新商品のマルチモーダル需要予測</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>吉瀬 章子</t>
+          <t>有馬 澄佳</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Liu Tianxiang</t>
+          <t>小西 葉子</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>八森 正泰</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.8609103560447693</v>
+        <v>0.862902969121933</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8553825318813324</v>
+        <v>0.8564811944961548</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8542724251747131</v>
+        <v>0.8502500951290131</v>
       </c>
     </row>
     <row r="4">
@@ -4457,38 +4557,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>吉田響</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>上野 遥平</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>202520512</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>中規模学会における発表スケジュール作成モデル</t>
+          <t>オーバーツーリズムによる迷惑行為発生環境に関する分析</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>吉瀬 章子</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Liu Tianxiang</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>八森 正泰</t>
+          <t>有馬 澄佳</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.8563421070575714</v>
+        <v>0.8726406395435333</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8490735590457916</v>
+        <v>0.8723745942115784</v>
       </c>
       <c r="J4" t="n">
-        <v>0.848315566778183</v>
+        <v>0.8699900805950165</v>
       </c>
     </row>
     <row r="5">
@@ -4499,38 +4603,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>佐川翼</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>柿本 直勇</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>202520513</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>多段階モデルを用いた修士論文発表会スケジューリングシステムの開発</t>
+          <t>pLSAを用いた孤独・孤立クラスタの構造把握と遷移分析:可変要因および介入効果の検討</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>吉瀬 章子</t>
+          <t>讃井 知</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>上市 秀雄</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Liu Tianxiang</t>
+          <t>秋山 英三</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.8748292922973633</v>
+        <v>0.8725573122501373</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8648773431777954</v>
+        <v>0.868150919675827</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8610253930091858</v>
+        <v>0.8653525114059448</v>
       </c>
     </row>
     <row r="6">
@@ -4541,38 +4649,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>出口達也</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>上條 薫</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>202520514</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>日本の慢性腎臓病進行症例患者における地域のソーシャルキャピタルが腎機能低下に及ぼす影響の分析</t>
+          <t>データコラボレーション解析技術を用いた腎疾患患者の層別化と予後予測の検証</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>岡本 翔平</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>イリチュ 美佳</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>讃井 知</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.8810135126113892</v>
+        <v>0.8685602843761444</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8752143383026123</v>
+        <v>0.8665047883987427</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8738452196121216</v>
+        <v>0.8663018941879272</v>
       </c>
     </row>
     <row r="7">
@@ -4583,38 +4695,42 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>川井貫太朗</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>黒岩 幹太</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>202520515</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SNSデータを用いた日本の空気感と単語ネットワーク</t>
+          <t>地域ソーシャルキャピタルと慢性腎臓病(CKD) 指標との関連:2次医療圏データを用いたパネルデータ分析</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>上市 秀雄</t>
+          <t>イリチュ 美佳</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>岡本 翔平</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.8805915117263794</v>
+        <v>0.8784606158733368</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8642037510871887</v>
+        <v>0.8773766160011292</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8563595116138458</v>
+        <v>0.8744112253189087</v>
       </c>
     </row>
     <row r="8">
@@ -4625,38 +4741,42 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>但木陸</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>小林 遼生</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>202520516</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>大学入試業務の人員配置最適化における暗黙知制約の検知と数理モデルの改良</t>
+          <t>グラフ表現学習による目的別人流ネットワーク構造の推定と特性記述</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Liu Tianxiang</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>吉瀬 章子</t>
+          <t>志田 洋平</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>高野 祐一</t>
+          <t>堤 盛人</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.8779240846633911</v>
+        <v>0.8793413639068604</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8712441325187683</v>
+        <v>0.8671495318412781</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8685609400272369</v>
+        <v>0.8640706539154053</v>
       </c>
     </row>
     <row r="9">
@@ -4667,38 +4787,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>中山友琉</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>齋藤 郁馬</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>202520517</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>データ分散状況を想定したプライバシー保護ハザード比推定手法の提案</t>
+          <t>需要不確実性を考慮した定期配送化における店舗補充頻度・在庫設計の最適化</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>岡田 幸彦</t>
+          <t>吉瀬 章子</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>イリチュ 美佳</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.8722024857997894</v>
+        <v>0.8687701225280762</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8625463247299194</v>
+        <v>0.8564662933349609</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8624857068061829</v>
+        <v>0.8544216752052307</v>
       </c>
     </row>
     <row r="10">
@@ -4709,38 +4833,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>中本武志</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>佐久間 貴彦</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>202520518</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>パートタイム労働者を主力とするサービス業におけるシフトスケジューリング</t>
+          <t>日常移動パターンに着目したPOIネットワーク</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>吉瀬 章子</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>有馬 澄佳</t>
+          <t>和田 健太郎</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.8638104796409607</v>
+        <v>0.878412127494812</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8515419065952301</v>
+        <v>0.8746395409107208</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8513235151767731</v>
+        <v>0.8692611157894135</v>
       </c>
     </row>
     <row r="11">
@@ -4751,38 +4879,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>長谷川弘貴</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>迫屋 景亮</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>202520519</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>生体データにもとづくサービスデータ解析手法の提案</t>
+          <t>自治体条例に基づく公共広場の制度設計と運用実態に関する研究</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>イリチュ 美佳</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
+          <t>太田 充</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>大西 正輝</t>
+          <t>渡邉 俊</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.8766615092754364</v>
+        <v>0.8776608407497406</v>
       </c>
       <c r="I11" t="n">
-        <v>0.858488142490387</v>
+        <v>0.8772943019866943</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8581428825855255</v>
+        <v>0.87617427110672</v>
       </c>
     </row>
     <row r="12">
@@ -4793,38 +4925,42 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>堤敬信</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>塩田 智也</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>202520520</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>待ち行列モデルを用いた機械学習システムの性能分析</t>
+          <t>孤独予防に向けたソーシャルキャピタルに基づく住民の類型化</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Phung-Duc Tuan</t>
+          <t>讃井 知</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>高野 祐一</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>黒瀬 雄大</t>
+          <t>雨宮 護</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.8860654234886169</v>
+        <v>0.8686253428459167</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8564328849315643</v>
+        <v>0.8617160618305206</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8518258333206177</v>
+        <v>0.857864648103714</v>
       </c>
     </row>
     <row r="13">
@@ -4835,13 +4971,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>飯田真実</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>鮏川 未来</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>202520521</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HPVワクチン接種に対する意見の変遷とその要因</t>
+          <t>Wikipediaデータによる集合的記憶の再想起分析</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -4856,17 +4996,17 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>讃井 知</t>
+          <t>イリチュ 美佳</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.8769748508930206</v>
+        <v>0.881976842880249</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8706703186035156</v>
+        <v>0.8667441010475159</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8587097227573395</v>
+        <v>0.8615249991416931</v>
       </c>
     </row>
     <row r="14">
@@ -4877,38 +5017,42 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>冨樫歩大</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>関河 悠磨</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>202520522</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>大規模言語モデルを用いた事業性評価シートのテキスト分析</t>
+          <t>マルチサーバー待ち行列システムにおける強化学習を用いたジョブスケジューリング</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>三崎 広海</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>高野 祐一</t>
+          <t>有馬 澄佳</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>黒瀬 雄大</t>
+          <t>繁野 麻衣子</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.8558283150196075</v>
+        <v>0.8876061737537384</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8499734103679657</v>
+        <v>0.8659283518791199</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8485821187496185</v>
+        <v>0.8646425902843475</v>
       </c>
     </row>
     <row r="15">
@@ -4919,38 +5063,42 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>平井佑樹</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>武田 侃人</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>202520523</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>仕訳データにもとづく利速測定の研究</t>
+          <t>倉庫の出荷物量フォーキャストの精度向上に向けた店舗ごと需要データの利活用によるモデル開発</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>岡田 幸彦</t>
+          <t>小西 葉子</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>三崎 広海</t>
+          <t>黒瀬 雄大</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>小西 葉子</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0.8566752374172211</v>
+        <v>0.8653980195522308</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8484805524349213</v>
+        <v>0.8549571931362152</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8434323072433472</v>
+        <v>0.8538030087947845</v>
       </c>
     </row>
     <row r="16">
@@ -4961,38 +5109,42 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>李宗晟</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>田村 青葉</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>202520524</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>光ネットワークにおける予約のある資源割り当ての提案</t>
+          <t>職場におけるストレス要因の再概念化:ソフトな要因とハードな要因の機能的差異</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>八森 正泰</t>
+          <t>上市 秀雄</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Phung-Duc Tuan</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>吉瀬 章子</t>
+          <t>讃井 知</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0.8690817356109619</v>
+        <v>0.8583924770355225</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8608503043651581</v>
+        <v>0.8568210601806641</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8606576025485992</v>
+        <v>0.8549480438232422</v>
       </c>
     </row>
     <row r="17">
@@ -5003,18 +5155,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>鈴木颯斗</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>檜山 恵梨香</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>202520525</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>クーポン配布における分類モデルの負例抽出</t>
+          <t>Transformerを用いた疑似仕訳データ生成</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>高野 祐一</t>
+          <t>三崎 広海</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -5024,17 +5180,17 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>黒瀬 雄大</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.8639224171638489</v>
+        <v>0.8657762110233307</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8517236709594727</v>
+        <v>0.8645855784416199</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8516994714736938</v>
+        <v>0.8605440855026245</v>
       </c>
     </row>
     <row r="18">
@@ -5045,38 +5201,42 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>崔涵喬</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
+          <t>水沼 健</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>202520526</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>クラスター分析を用いた観光客のセグメンテーションとマーケティングへの応用可能性に関する研究</t>
+          <t>Mask2Formerを用いた住宅間取り図に対するセマンティックセグメンテーション</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>岡本 直久</t>
+          <t>有馬 澄佳</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>浦田 淳司</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>小西 葉子</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0.8556589782238007</v>
+        <v>0.8643296360969543</v>
       </c>
       <c r="I18" t="n">
-        <v>0.852348655462265</v>
+        <v>0.8624945878982544</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8488177359104156</v>
+        <v>0.862152636051178</v>
       </c>
     </row>
     <row r="19">
@@ -5087,38 +5247,42 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>澤口瑛都</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>最上 慎太郎</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>202520527</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>列生成法を軸としたバス運行業務の仕業編成</t>
+          <t>状態依存到着率を考慮した閉鎖型待ち行列モデルによるシェアサイクルの運用分析</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>吉瀬 章子</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liu Tianxiang</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phung-Duc Tuan</t>
+          <t>和田 健太郎</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0.8692283034324646</v>
+        <v>0.8965592980384827</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8582851588726044</v>
+        <v>0.8704787790775299</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8579657673835754</v>
+        <v>0.8676624000072479</v>
       </c>
     </row>
     <row r="20">
@@ -5129,38 +5293,42 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>齋藤彩</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>八木 絢子</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>202520528</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>pLSAによる潜在クラス間の遷移予想と効果検証</t>
+          <t>非線形移動抵抗導入による人流ポテンシャルモデルの拡張</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>上市 秀雄</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>讃井 知</t>
+          <t>志田 洋平</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>秋山 英三</t>
+          <t>渡邉 俊</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0.8734315633773804</v>
+        <v>0.887686014175415</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8669519126415253</v>
+        <v>0.8774204552173615</v>
       </c>
       <c r="J20" t="n">
-        <v>0.865755021572113</v>
+        <v>0.8773219287395477</v>
       </c>
     </row>
     <row r="21">
@@ -5171,38 +5339,42 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>髙橋優介</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+          <t>山下 穂乃果</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>202520529</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>実データを用いた平常時の収益性と災害時の孤立リスクを考慮したドローン配送基地の施設立地最適化</t>
+          <t>二層加法リスクモデルを用いた営業架電の成約率予測</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Phung-Duc Tuan</t>
+          <t>小西 葉子</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>高野 祐一</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
           <t>鈴木 勉</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>吉瀬 章子</t>
-        </is>
-      </c>
       <c r="H21" t="n">
-        <v>0.8677213788032532</v>
+        <v>0.8698301017284393</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8647889792919159</v>
+        <v>0.8667502701282501</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8634408414363861</v>
+        <v>0.8629519045352936</v>
       </c>
     </row>
     <row r="22">
@@ -5213,38 +5385,88 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>寺田海渡</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>吉岡 聖</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>202520530</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>地域金融機関の預貸金データを用いた中小企業会計品質指標の提案</t>
+          <t>需要変動下での安定的かつ再現可能な納品回数設定の最適化</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>三崎 広海</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>八森 正泰</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>吉瀬 章子</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>0.8635926842689514</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.8507093787193298</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.8474651873111725</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>MSE</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>吉村 龍</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>202520531</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>優先権付き待ち行列モデルを用いたサポートデスク業務の性能評価</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Phung-Duc Tuan</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>佐野 幸恵</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
           <t>川島 宏一</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>岡田 幸彦</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>0.8706386387348175</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.8656386733055115</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.8638789355754852</v>
+      <c r="H23" t="n">
+        <v>0.873361200094223</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.8450472950935364</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.8445885479450226</v>
       </c>
     </row>
   </sheetData>

--- a/generated/committee_recommendations.xlsx
+++ b/generated/committee_recommendations.xlsx
@@ -504,27 +504,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>太田 充</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>堤 盛人</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>堤 盛人</t>
+          <t>有田 智一</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.8725054264068604</v>
+        <v>0.8694877028465271</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8694877028465271</v>
+        <v>0.8679137825965881</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8679138123989105</v>
+        <v>0.859418511390686</v>
       </c>
     </row>
     <row r="3">
@@ -555,22 +555,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>太田 充</t>
+          <t>堤 盛人</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>山本 幸子</t>
+          <t>渡邉 俊</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.8699927926063538</v>
+        <v>0.8699927628040314</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8690958321094513</v>
+        <v>0.8664485514163971</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8680389225482941</v>
+        <v>0.8623868525028229</v>
       </c>
     </row>
     <row r="4">
@@ -601,22 +601,22 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>山本 幸子</t>
+          <t>有田 智一</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>有田 智一</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.8407678604125977</v>
+        <v>0.8407678008079529</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8383740782737732</v>
+        <v>0.8299179673194885</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8299179673194885</v>
+        <v>0.8276243209838867</v>
       </c>
     </row>
     <row r="5">
@@ -652,17 +652,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>讃井 知</t>
+          <t>村上 暁信</t>
         </is>
       </c>
       <c r="H5" t="n">
         <v>0.8525646924972534</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8467219471931458</v>
+        <v>0.8467218577861786</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8441798388957977</v>
+        <v>0.8440098166465759</v>
       </c>
     </row>
     <row r="6">
@@ -688,27 +688,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>吉瀬 章子</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>吉瀬 章子</t>
+          <t>有馬 澄佳</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>山本 幸子</t>
+          <t>渡邉 俊</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.8804560601711273</v>
+        <v>0.8787815570831299</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8787815570831299</v>
+        <v>0.870666116476059</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8734155297279358</v>
+        <v>0.8701993227005005</v>
       </c>
     </row>
     <row r="7">
@@ -739,22 +739,22 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>有田 智一</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.8718103170394897</v>
+        <v>0.8718103468418121</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8701826930046082</v>
+        <v>0.8672458827495575</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8687415421009064</v>
+        <v>0.8657021820545197</v>
       </c>
     </row>
     <row r="8">
@@ -790,17 +790,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>上市 秀雄</t>
+          <t>吉瀬 章子</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.8684000670909882</v>
+        <v>0.8684000968933105</v>
       </c>
       <c r="I8" t="n">
         <v>0.8601691126823425</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8557591736316681</v>
+        <v>0.8557119965553284</v>
       </c>
     </row>
     <row r="9">
@@ -826,27 +826,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>山本 幸子</t>
+          <t>渡邉 俊</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>渡邉 俊</t>
+          <t>甲斐田 直子</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>村上 暁信</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.870919406414032</v>
+        <v>0.8701505959033966</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8701505959033966</v>
+        <v>0.8692824840545654</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8696761429309845</v>
+        <v>0.8664173483848572</v>
       </c>
     </row>
     <row r="10">
@@ -872,27 +872,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>堤 盛人</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>堤 盛人</t>
+          <t>渡邉 俊</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.8743027150630951</v>
+        <v>0.8654041886329651</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8654838502407074</v>
+        <v>0.8622785210609436</v>
       </c>
       <c r="J10" t="n">
-        <v>0.865404337644577</v>
+        <v>0.8618445992469788</v>
       </c>
     </row>
     <row r="11">
@@ -918,27 +918,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>三崎 広海</t>
+          <t>秋山 英三</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>秋山 英三</t>
+          <t>黒瀬 雄大</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>小西 葉子</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.8726991415023804</v>
+        <v>0.859723687171936</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8597236573696136</v>
+        <v>0.8509807288646698</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8510848581790924</v>
+        <v>0.8484225869178772</v>
       </c>
     </row>
     <row r="12">
@@ -1015,22 +1015,22 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>山本 幸子</t>
+          <t>藤井 さやか</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>藤井 さやか</t>
+          <t>渡邉 俊</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.8786501288414001</v>
+        <v>0.8786501884460449</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8759361505508423</v>
+        <v>0.8751763701438904</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8751761913299561</v>
+        <v>0.8725005686283112</v>
       </c>
     </row>
     <row r="14">
@@ -1056,27 +1056,27 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>讃井 知</t>
+          <t>甲斐田 直子</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>甲斐田 直子</t>
+          <t>雨宮 護</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>澤 亮治</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.8674522936344147</v>
+        <v>0.8637474477291107</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8637472689151764</v>
+        <v>0.8538913130760193</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8552792072296143</v>
+        <v>0.8533703684806824</v>
       </c>
     </row>
     <row r="15">
@@ -1102,27 +1102,27 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>讃井 知</t>
+          <t>甲斐田 直子</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>上市 秀雄</t>
+          <t>秋山 英三</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>甲斐田 直子</t>
+          <t>雨宮 護</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0.8603215217590332</v>
+        <v>0.8559390306472778</v>
       </c>
       <c r="I15" t="n">
-        <v>0.859508603811264</v>
+        <v>0.8508188724517822</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8559390604496002</v>
+        <v>0.8468877077102661</v>
       </c>
     </row>
     <row r="16">
@@ -1158,17 +1158,17 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>太田 充</t>
+          <t>村上 暁信</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0.8840882480144501</v>
+        <v>0.8840882182121277</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8795138895511627</v>
+        <v>0.8795138299465179</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8777675032615662</v>
+        <v>0.8731004893779755</v>
       </c>
     </row>
     <row r="17">
@@ -1194,27 +1194,27 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>山本 幸子</t>
+          <t>松原 康介</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>松原 康介</t>
+          <t>渡邉 俊</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>渡邉 俊</t>
+          <t>藤井 さやか</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.8654569983482361</v>
+        <v>0.8594345450401306</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8594346046447754</v>
+        <v>0.8577826619148254</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8577826619148254</v>
+        <v>0.8537378907203674</v>
       </c>
     </row>
     <row r="18">
@@ -1240,27 +1240,27 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>山本 幸子</t>
+          <t>有田 智一</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>有田 智一</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>藤井 さやか</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0.8641208410263062</v>
+        <v>0.8593732714653015</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8593732714653015</v>
+        <v>0.854110985994339</v>
       </c>
       <c r="J18" t="n">
-        <v>0.856412410736084</v>
+        <v>0.8515381217002869</v>
       </c>
     </row>
     <row r="19">
@@ -1286,27 +1286,27 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>山本 幸子</t>
+          <t>甲斐田 直子</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>松原 康介</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>甲斐田 直子</t>
+          <t>藤井 さやか</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0.8628750443458557</v>
+        <v>0.8502585589885712</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8513096272945404</v>
+        <v>0.8502442538738251</v>
       </c>
       <c r="J19" t="n">
-        <v>0.850258469581604</v>
+        <v>0.8497434854507446</v>
       </c>
     </row>
     <row r="20">
@@ -1332,27 +1332,27 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>小西 葉子</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>太田 充</t>
+          <t>秋山 英三</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>澤 亮治</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0.8699538707733154</v>
+        <v>0.860200434923172</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8609905242919922</v>
+        <v>0.8571360409259796</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8602003455162048</v>
+        <v>0.8559625148773193</v>
       </c>
     </row>
     <row r="21">
@@ -1424,27 +1424,27 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>有田 智一</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>梅本 通孝</t>
+          <t>堤 盛人</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>渡邉 俊</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0.8780646622180939</v>
+        <v>0.8694944977760315</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8772540986537933</v>
+        <v>0.8677712976932526</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8761959671974182</v>
+        <v>0.8667417764663696</v>
       </c>
     </row>
     <row r="23">
@@ -1480,17 +1480,17 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>村上 暁信</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0.8644822537899017</v>
+        <v>0.8644822835922241</v>
       </c>
       <c r="I23" t="n">
-        <v>0.863353967666626</v>
+        <v>0.8633539974689484</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8620575964450836</v>
+        <v>0.8604942560195923</v>
       </c>
     </row>
     <row r="24">
@@ -1516,27 +1516,27 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>有田 智一</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>有田 智一</t>
+          <t>村上 暁信</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>梅本 通孝</t>
+          <t>甲斐田 直子</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0.8778388798236847</v>
+        <v>0.8740248084068298</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8740247189998627</v>
+        <v>0.8682364821434021</v>
       </c>
       <c r="J24" t="n">
-        <v>0.871728777885437</v>
+        <v>0.8672411739826202</v>
       </c>
     </row>
     <row r="25">
@@ -1562,27 +1562,27 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>讃井 知</t>
+          <t>雨宮 護</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>雨宮 護</t>
+          <t>甲斐田 直子</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>甲斐田 直子</t>
+          <t>村上 暁信</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0.8605781495571136</v>
+        <v>0.8576710522174835</v>
       </c>
       <c r="I25" t="n">
-        <v>0.8576709926128387</v>
+        <v>0.8573780655860901</v>
       </c>
       <c r="J25" t="n">
-        <v>0.8573781847953796</v>
+        <v>0.856936514377594</v>
       </c>
     </row>
     <row r="26">
@@ -1608,27 +1608,27 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>上市 秀雄</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
+          <t>イリチュ 美佳</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>小西 葉子</t>
+          <t>黒瀬 雄大</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0.8725013732910156</v>
+        <v>0.8625889718532562</v>
       </c>
       <c r="I26" t="n">
-        <v>0.8715296983718872</v>
+        <v>0.861405223608017</v>
       </c>
       <c r="J26" t="n">
-        <v>0.863963395357132</v>
+        <v>0.8584799766540527</v>
       </c>
     </row>
     <row r="27">
@@ -1654,27 +1654,27 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>和田 健太郎</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tran Lam Anh Duong</t>
+          <t>渡邉 俊</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0.878728061914444</v>
+        <v>0.8697108030319214</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8697108924388885</v>
+        <v>0.8689082562923431</v>
       </c>
       <c r="J27" t="n">
-        <v>0.8690555095672607</v>
+        <v>0.8632592856884003</v>
       </c>
     </row>
     <row r="28">
@@ -1700,27 +1700,27 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>小西 葉子</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>秋山 英三</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>原田 信行</t>
+          <t>堤 盛人</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0.8659414350986481</v>
+        <v>0.8614097535610199</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8614097535610199</v>
+        <v>0.8560521602630615</v>
       </c>
       <c r="J28" t="n">
-        <v>0.8572182357311249</v>
+        <v>0.8548654913902283</v>
       </c>
     </row>
     <row r="29">
@@ -1751,22 +1751,22 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>小西 葉子</t>
+          <t>堤 盛人</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0.8861464560031891</v>
+        <v>0.8861463367938995</v>
       </c>
       <c r="I29" t="n">
-        <v>0.8746454119682312</v>
+        <v>0.8699300587177277</v>
       </c>
       <c r="J29" t="n">
-        <v>0.8714252412319183</v>
+        <v>0.8695700168609619</v>
       </c>
     </row>
     <row r="30">
@@ -1792,27 +1792,27 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>山本 幸子</t>
+          <t>有田 智一</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>讃井 知</t>
+          <t>藤井 さやか</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>有田 智一</t>
+          <t>渡邉 俊</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>0.8737453818321228</v>
+        <v>0.8675165772438049</v>
       </c>
       <c r="I30" t="n">
-        <v>0.8686347007751465</v>
+        <v>0.8674237728118896</v>
       </c>
       <c r="J30" t="n">
-        <v>0.8675165772438049</v>
+        <v>0.8648247718811035</v>
       </c>
     </row>
     <row r="31">
@@ -1838,27 +1838,27 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Phung-Duc Tuan</t>
+          <t>秋山 英三</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>讃井 知</t>
+          <t>浦田 淳司</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>0.8504707515239716</v>
+        <v>0.8496311902999878</v>
       </c>
       <c r="I31" t="n">
-        <v>0.8496311902999878</v>
+        <v>0.8476453721523285</v>
       </c>
       <c r="J31" t="n">
-        <v>0.8495571911334991</v>
+        <v>0.8473740816116333</v>
       </c>
     </row>
     <row r="32">
@@ -1884,27 +1884,27 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>讃井 知</t>
+          <t>大西 正輝</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>秋山 英三</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>秋山 英三</t>
+          <t>雨宮 護</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0.8459481298923492</v>
+        <v>0.8455413579940796</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8438551723957062</v>
+        <v>0.8411490023136139</v>
       </c>
       <c r="J32" t="n">
-        <v>0.8411489725112915</v>
+        <v>0.8403199911117554</v>
       </c>
     </row>
     <row r="33">
@@ -1947,7 +1947,7 @@
         <v>0.8735739290714264</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8708217442035675</v>
+        <v>0.8708216845989227</v>
       </c>
       <c r="J33" t="n">
         <v>0.8674927651882172</v>
@@ -1976,27 +1976,27 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>吉瀬 章子</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>吉瀬 章子</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phung-Duc Tuan</t>
+          <t>岡本 直久</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>0.8794162273406982</v>
+        <v>0.8755110502243042</v>
       </c>
       <c r="I34" t="n">
-        <v>0.8755110502243042</v>
+        <v>0.8711532652378082</v>
       </c>
       <c r="J34" t="n">
-        <v>0.8711532652378082</v>
+        <v>0.8682165145874023</v>
       </c>
     </row>
     <row r="35">
@@ -2022,27 +2022,27 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>讃井 知</t>
+          <t>雨宮 護</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>上市 秀雄</t>
+          <t>甲斐田 直子</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>雨宮 護</t>
+          <t>村上 暁信</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>0.8534249365329742</v>
+        <v>0.8445099592208862</v>
       </c>
       <c r="I35" t="n">
-        <v>0.8462549448013306</v>
+        <v>0.8385109901428223</v>
       </c>
       <c r="J35" t="n">
-        <v>0.8445098996162415</v>
+        <v>0.837116003036499</v>
       </c>
     </row>
     <row r="36">
@@ -2068,27 +2068,27 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>梅本 通孝</t>
+          <t>黒瀬 雄大</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>小西 葉子</t>
+          <t>イリチュ 美佳</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>0.8738100528717041</v>
+        <v>0.8662265539169312</v>
       </c>
       <c r="I36" t="n">
-        <v>0.8697246611118317</v>
+        <v>0.8639206290245056</v>
       </c>
       <c r="J36" t="n">
-        <v>0.8684316277503967</v>
+        <v>0.8605668544769287</v>
       </c>
     </row>
     <row r="37">
@@ -2114,27 +2114,27 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Liu Tianxiang</t>
+          <t>八森 正泰</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>八森 正泰</t>
+          <t>吉瀬 章子</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>吉瀬 章子</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>0.8708596229553223</v>
+        <v>0.8647412657737732</v>
       </c>
       <c r="I37" t="n">
-        <v>0.8647412061691284</v>
+        <v>0.860410749912262</v>
       </c>
       <c r="J37" t="n">
-        <v>0.8604106307029724</v>
+        <v>0.8583733439445496</v>
       </c>
     </row>
     <row r="38">
@@ -2165,22 +2165,22 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>讃井 知</t>
+          <t>浦田 淳司</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>雨宮 護</t>
         </is>
       </c>
       <c r="H38" t="n">
         <v>0.8495572209358215</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8459269106388092</v>
+        <v>0.843469649553299</v>
       </c>
       <c r="J38" t="n">
-        <v>0.8455456793308258</v>
+        <v>0.8432528376579285</v>
       </c>
     </row>
     <row r="39">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>堤 盛人</t>
         </is>
       </c>
       <c r="H39" t="n">
         <v>0.8758090436458588</v>
       </c>
       <c r="I39" t="n">
-        <v>0.8726612329483032</v>
+        <v>0.8726611733436584</v>
       </c>
       <c r="J39" t="n">
-        <v>0.8673579096794128</v>
+        <v>0.8652368485927582</v>
       </c>
     </row>
     <row r="40">
@@ -2252,27 +2252,27 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>山本 幸子</t>
+          <t>有田 智一</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>有田 智一</t>
+          <t>松原 康介</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>松原 康介</t>
+          <t>藤井 さやか</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>0.8725372850894928</v>
+        <v>0.8562148213386536</v>
       </c>
       <c r="I40" t="n">
-        <v>0.8562148809432983</v>
+        <v>0.8561661243438721</v>
       </c>
       <c r="J40" t="n">
-        <v>0.8561661839485168</v>
+        <v>0.8556602001190186</v>
       </c>
     </row>
     <row r="41">
@@ -2298,27 +2298,27 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>讃井 知</t>
+          <t>渡邉 俊</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>雨宮 護</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>渡邉 俊</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>0.8807381391525269</v>
+        <v>0.8744291663169861</v>
       </c>
       <c r="I41" t="n">
-        <v>0.8756651878356934</v>
+        <v>0.8729338943958282</v>
       </c>
       <c r="J41" t="n">
-        <v>0.8744292557239532</v>
+        <v>0.8692703545093536</v>
       </c>
     </row>
     <row r="42">
@@ -2358,13 +2358,13 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>0.8656892478466034</v>
+        <v>0.8656891882419586</v>
       </c>
       <c r="I42" t="n">
-        <v>0.850430428981781</v>
+        <v>0.8504304587841034</v>
       </c>
       <c r="J42" t="n">
-        <v>0.849077045917511</v>
+        <v>0.8490769863128662</v>
       </c>
     </row>
     <row r="43">
@@ -2390,27 +2390,27 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>上市 秀雄</t>
+          <t>繁野 麻衣子</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
+          <t>秋山 英三</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>髙橋 裕紀</t>
+          <t>作道 真理</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>0.8466545939445496</v>
+        <v>0.8414866030216217</v>
       </c>
       <c r="I43" t="n">
-        <v>0.8459292948246002</v>
+        <v>0.8378401696681976</v>
       </c>
       <c r="J43" t="n">
-        <v>0.8441087305545807</v>
+        <v>0.8372129499912262</v>
       </c>
     </row>
     <row r="44">
@@ -2436,27 +2436,27 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>讃井 知</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>山本 幸子</t>
+          <t>甲斐田 直子</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>堤 盛人</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>0.8725491166114807</v>
+        <v>0.8616174161434174</v>
       </c>
       <c r="I44" t="n">
-        <v>0.8676817417144775</v>
+        <v>0.860570102930069</v>
       </c>
       <c r="J44" t="n">
-        <v>0.8616174459457397</v>
+        <v>0.858036994934082</v>
       </c>
     </row>
     <row r="45">
@@ -2482,27 +2482,27 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>山本 幸子</t>
+          <t>松原 康介</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>松原 康介</t>
+          <t>藤川 昌樹</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>藤川 昌樹</t>
+          <t>有田 智一</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>0.8705042600631714</v>
+        <v>0.861813485622406</v>
       </c>
       <c r="I45" t="n">
-        <v>0.8618135452270508</v>
+        <v>0.8590433597564697</v>
       </c>
       <c r="J45" t="n">
-        <v>0.8590433597564697</v>
+        <v>0.8576594591140747</v>
       </c>
     </row>
     <row r="46">
@@ -2538,17 +2538,17 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
+          <t>浦田 淳司</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>0.8530411720275879</v>
+        <v>0.8530412614345551</v>
       </c>
       <c r="I46" t="n">
-        <v>0.845608651638031</v>
+        <v>0.8456086218357086</v>
       </c>
       <c r="J46" t="n">
-        <v>0.8430800437927246</v>
+        <v>0.8429499566555023</v>
       </c>
     </row>
     <row r="47">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
+          <t>秋山 英三</t>
         </is>
       </c>
       <c r="H47" t="n">
         <v>0.8600080013275146</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8581774532794952</v>
+        <v>0.8581773638725281</v>
       </c>
       <c r="J47" t="n">
-        <v>0.8559065759181976</v>
+        <v>0.8540851473808289</v>
       </c>
     </row>
     <row r="48">
@@ -2620,27 +2620,27 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>浦田 淳司</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>髙橋 裕紀</t>
+          <t>繁野 麻衣子</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>浦田 淳司</t>
+          <t>イリチュ 美佳</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>0.8463076949119568</v>
+        <v>0.8453716635704041</v>
       </c>
       <c r="I48" t="n">
-        <v>0.8454867601394653</v>
+        <v>0.8445407748222351</v>
       </c>
       <c r="J48" t="n">
-        <v>0.8453716337680817</v>
+        <v>0.844357967376709</v>
       </c>
     </row>
     <row r="49">
@@ -2680,13 +2680,13 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0.870422899723053</v>
+        <v>0.8699431717395782</v>
       </c>
       <c r="I49" t="n">
-        <v>0.869493305683136</v>
+        <v>0.8694933354854584</v>
       </c>
       <c r="J49" t="n">
-        <v>0.861149787902832</v>
+        <v>0.8611498475074768</v>
       </c>
     </row>
     <row r="50">
@@ -2726,10 +2726,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>0.8789788782596588</v>
+        <v>0.878978818655014</v>
       </c>
       <c r="I50" t="n">
-        <v>0.8715095520019531</v>
+        <v>0.8715093731880188</v>
       </c>
       <c r="J50" t="n">
         <v>0.8685348629951477</v>
@@ -2758,27 +2758,27 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>和田 健太郎</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>和田 健太郎</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>谷口 綾子</t>
+          <t>浦田 淳司</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>0.8764743208885193</v>
+        <v>0.8751050531864166</v>
       </c>
       <c r="I51" t="n">
-        <v>0.8751050531864166</v>
+        <v>0.8725587427616119</v>
       </c>
       <c r="J51" t="n">
-        <v>0.8731650412082672</v>
+        <v>0.8720654249191284</v>
       </c>
     </row>
     <row r="52">
@@ -2804,27 +2804,27 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>上市 秀雄</t>
+          <t>イリチュ 美佳</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>イリチュ 美佳</t>
+          <t>高野 祐一</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
+          <t>澤 亮治</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>0.8628562092781067</v>
+        <v>0.8604255318641663</v>
       </c>
       <c r="I52" t="n">
-        <v>0.8604255318641663</v>
+        <v>0.8557384312152863</v>
       </c>
       <c r="J52" t="n">
-        <v>0.8562762439250946</v>
+        <v>0.854552298784256</v>
       </c>
     </row>
     <row r="53">
@@ -2850,27 +2850,27 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
+          <t>浦田 淳司</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>イリチュ 美佳</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>浦田 淳司</t>
+          <t>大西 正輝</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>0.8492535650730133</v>
+        <v>0.847988098859787</v>
       </c>
       <c r="I53" t="n">
-        <v>0.8484686315059662</v>
+        <v>0.8451839983463287</v>
       </c>
       <c r="J53" t="n">
-        <v>0.8479881286621094</v>
+        <v>0.8436055183410645</v>
       </c>
     </row>
     <row r="54">
@@ -2906,17 +2906,17 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>繁野 麻衣子</t>
         </is>
       </c>
       <c r="H54" t="n">
         <v>0.8539004325866699</v>
       </c>
       <c r="I54" t="n">
-        <v>0.8537878096103668</v>
+        <v>0.8537877798080444</v>
       </c>
       <c r="J54" t="n">
-        <v>0.8486493527889252</v>
+        <v>0.8420813381671906</v>
       </c>
     </row>
     <row r="55">
@@ -2942,27 +2942,27 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>イリチュ 美佳</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>黒瀬 雄大</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>イリチュ 美佳</t>
+          <t>浦田 淳司</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>0.8511146903038025</v>
+        <v>0.8501562178134918</v>
       </c>
       <c r="I55" t="n">
-        <v>0.8506214320659637</v>
+        <v>0.8440068364143372</v>
       </c>
       <c r="J55" t="n">
-        <v>0.8501562178134918</v>
+        <v>0.8433963358402252</v>
       </c>
     </row>
     <row r="56">
@@ -2988,27 +2988,27 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>小西 葉子</t>
+          <t>有田 智一</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>三崎 広海</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>有田 智一</t>
+          <t>堤 盛人</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>0.8653828203678131</v>
+        <v>0.8617116212844849</v>
       </c>
       <c r="I56" t="n">
-        <v>0.8632269501686096</v>
+        <v>0.8599629104137421</v>
       </c>
       <c r="J56" t="n">
-        <v>0.8617116212844849</v>
+        <v>0.8598028123378754</v>
       </c>
     </row>
     <row r="57">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>山本 幸子</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>0.860146701335907</v>
+        <v>0.8601466417312622</v>
       </c>
       <c r="I57" t="n">
         <v>0.8540288209915161</v>
       </c>
       <c r="J57" t="n">
-        <v>0.8500931262969971</v>
+        <v>0.8462729454040527</v>
       </c>
     </row>
     <row r="58">
@@ -3080,27 +3080,27 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>浦田 淳司</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>三崎 広海</t>
+          <t>黒瀬 雄大</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>浦田 淳司</t>
+          <t>繁野 麻衣子</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>0.8541621565818787</v>
+        <v>0.8468367457389832</v>
       </c>
       <c r="I58" t="n">
-        <v>0.8514554500579834</v>
+        <v>0.8459519445896149</v>
       </c>
       <c r="J58" t="n">
-        <v>0.8468368351459503</v>
+        <v>0.8456976413726807</v>
       </c>
     </row>
     <row r="59">
@@ -3126,27 +3126,27 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>大久保 正勝</t>
+          <t>イリチュ 美佳</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
+          <t>作道 真理</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>イリチュ 美佳</t>
+          <t>村上 暁信</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>0.8487860560417175</v>
+        <v>0.8466636836528778</v>
       </c>
       <c r="I59" t="n">
-        <v>0.8485636711120605</v>
+        <v>0.8414956629276276</v>
       </c>
       <c r="J59" t="n">
-        <v>0.8466636836528778</v>
+        <v>0.8412843644618988</v>
       </c>
     </row>
     <row r="60">
@@ -3186,13 +3186,13 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>0.8760022819042206</v>
+        <v>0.8760022222995758</v>
       </c>
       <c r="I60" t="n">
         <v>0.8626532554626465</v>
       </c>
       <c r="J60" t="n">
-        <v>0.8607532680034637</v>
+        <v>0.8603174686431885</v>
       </c>
     </row>
     <row r="61">
@@ -3218,27 +3218,27 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
+          <t>村上 暁信</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
           <t>甲斐田 直子</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>村上 暁信</t>
-        </is>
-      </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>0.8657460808753967</v>
+        <v>0.8658595085144043</v>
       </c>
       <c r="I61" t="n">
-        <v>0.8657316863536835</v>
+        <v>0.8657461404800415</v>
       </c>
       <c r="J61" t="n">
-        <v>0.8615502119064331</v>
+        <v>0.8604395687580109</v>
       </c>
     </row>
     <row r="62">
@@ -3281,7 +3281,7 @@
         <v>0.8874904811382294</v>
       </c>
       <c r="I62" t="n">
-        <v>0.8681735396385193</v>
+        <v>0.8681735992431641</v>
       </c>
       <c r="J62" t="n">
         <v>0.8610672652721405</v>
@@ -3320,17 +3320,17 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>太田 充</t>
+          <t>甲斐田 直子</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>0.8482206463813782</v>
+        <v>0.8477002382278442</v>
       </c>
       <c r="I63" t="n">
-        <v>0.8416445255279541</v>
+        <v>0.8416444659233093</v>
       </c>
       <c r="J63" t="n">
-        <v>0.8387836813926697</v>
+        <v>0.8346581757068634</v>
       </c>
     </row>
     <row r="64">
@@ -3370,13 +3370,13 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>0.8797740340232849</v>
+        <v>0.8797739744186401</v>
       </c>
       <c r="I64" t="n">
         <v>0.8664391338825226</v>
       </c>
       <c r="J64" t="n">
-        <v>0.8657128810882568</v>
+        <v>0.8655925691127777</v>
       </c>
     </row>
     <row r="65">
@@ -3402,27 +3402,27 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
+          <t>八森 正泰</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>八森 正泰</t>
+          <t>高野 祐一</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>上市 秀雄</t>
+          <t>秋山 英三</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>0.8648021221160889</v>
+        <v>0.8587773442268372</v>
       </c>
       <c r="I65" t="n">
-        <v>0.8587773740291595</v>
+        <v>0.8530013859272003</v>
       </c>
       <c r="J65" t="n">
-        <v>0.8559302091598511</v>
+        <v>0.852728933095932</v>
       </c>
     </row>
     <row r="66">
@@ -3448,27 +3448,27 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>堤 盛人</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>谷口 綾子</t>
+          <t>和田 健太郎</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>0.8854454457759857</v>
+        <v>0.8833464980125427</v>
       </c>
       <c r="I66" t="n">
-        <v>0.8833464384078979</v>
+        <v>0.8777274489402771</v>
       </c>
       <c r="J66" t="n">
-        <v>0.8789984881877899</v>
+        <v>0.8760351538658142</v>
       </c>
     </row>
     <row r="67">
@@ -3499,22 +3499,22 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>甲斐田 直子</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>大久保 正勝</t>
+          <t>高野 祐一</t>
         </is>
       </c>
       <c r="H67" t="n">
         <v>0.8467667102813721</v>
       </c>
       <c r="I67" t="n">
-        <v>0.8456202745437622</v>
+        <v>0.8428299427032471</v>
       </c>
       <c r="J67" t="n">
-        <v>0.8442079126834869</v>
+        <v>0.8421742618083954</v>
       </c>
     </row>
     <row r="68">
@@ -3545,22 +3545,22 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>志田 洋平</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>雨宮 護</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>0.8728138208389282</v>
+        <v>0.8728137910366058</v>
       </c>
       <c r="I68" t="n">
-        <v>0.8711625337600708</v>
+        <v>0.8687836229801178</v>
       </c>
       <c r="J68" t="n">
-        <v>0.8694121241569519</v>
+        <v>0.865785539150238</v>
       </c>
     </row>
     <row r="69">
@@ -3586,27 +3586,27 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>浦田 淳司</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>岡田 幸彦</t>
+          <t>繁野 麻衣子</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>髙橋 裕紀</t>
+          <t>イリチュ 美佳</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>0.8480951189994812</v>
+        <v>0.843207448720932</v>
       </c>
       <c r="I69" t="n">
-        <v>0.8476590514183044</v>
+        <v>0.8409813344478607</v>
       </c>
       <c r="J69" t="n">
-        <v>0.8476487994194031</v>
+        <v>0.8402246534824371</v>
       </c>
     </row>
     <row r="70">
@@ -3637,22 +3637,22 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>太田 充</t>
+          <t>岡本 直久</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>村上 暁信</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>0.8448813855648041</v>
+        <v>0.8448812961578369</v>
       </c>
       <c r="I70" t="n">
-        <v>0.8417623937129974</v>
+        <v>0.8380181491374969</v>
       </c>
       <c r="J70" t="n">
-        <v>0.8410535752773285</v>
+        <v>0.8377423882484436</v>
       </c>
     </row>
     <row r="71">
@@ -3678,27 +3678,27 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>山本 幸子</t>
+          <t>有田 智一</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>松原 康介</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>有田 智一</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>0.8706452250480652</v>
+        <v>0.8568777740001678</v>
       </c>
       <c r="I71" t="n">
-        <v>0.8576701283454895</v>
+        <v>0.8562575578689575</v>
       </c>
       <c r="J71" t="n">
-        <v>0.8568777441978455</v>
+        <v>0.8555001616477966</v>
       </c>
     </row>
     <row r="72">
@@ -3729,22 +3729,22 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>讃井 知</t>
+          <t>澤 亮治</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>澤 亮治</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>0.8674946427345276</v>
+        <v>0.8674947023391724</v>
       </c>
       <c r="I72" t="n">
-        <v>0.865528404712677</v>
+        <v>0.8628239333629608</v>
       </c>
       <c r="J72" t="n">
-        <v>0.8628238141536713</v>
+        <v>0.8551492691040039</v>
       </c>
     </row>
     <row r="73">
@@ -3770,27 +3770,27 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Phung-Duc Tuan</t>
+          <t>吉瀬 章子</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>吉瀬 章子</t>
+          <t>澤 亮治</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>0.8715511560440063</v>
+        <v>0.8690094351768494</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8690094351768494</v>
+        <v>0.8687985241413116</v>
       </c>
       <c r="J73" t="n">
-        <v>0.868798553943634</v>
+        <v>0.862273633480072</v>
       </c>
     </row>
     <row r="74">
@@ -3821,22 +3821,22 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Liu Tianxiang</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phung-Duc Tuan</t>
+          <t>吉瀬 章子</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>0.863420844078064</v>
+        <v>0.8634209930896759</v>
       </c>
       <c r="I74" t="n">
-        <v>0.8619250059127808</v>
+        <v>0.8594034314155579</v>
       </c>
       <c r="J74" t="n">
-        <v>0.859403520822525</v>
+        <v>0.8593776822090149</v>
       </c>
     </row>
     <row r="75">
@@ -3867,22 +3867,22 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>山本 幸子</t>
+          <t>藤川 昌樹</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>藤川 昌樹</t>
+          <t>有田 智一</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>0.8413382172584534</v>
+        <v>0.8413383066654205</v>
       </c>
       <c r="I75" t="n">
-        <v>0.8388773202896118</v>
+        <v>0.8376224637031555</v>
       </c>
       <c r="J75" t="n">
-        <v>0.8376223742961884</v>
+        <v>0.8287526071071625</v>
       </c>
     </row>
     <row r="76">
@@ -3908,27 +3908,27 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>讃井 知</t>
+          <t>雨宮 護</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>山本 幸子</t>
+          <t>甲斐田 直子</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>雨宮 護</t>
+          <t>村上 暁信</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>0.8615443408489227</v>
+        <v>0.8549287021160126</v>
       </c>
       <c r="I76" t="n">
-        <v>0.8565350770950317</v>
+        <v>0.851565808057785</v>
       </c>
       <c r="J76" t="n">
-        <v>0.8549287915229797</v>
+        <v>0.8490276336669922</v>
       </c>
     </row>
     <row r="77">
@@ -3959,22 +3959,22 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
+          <t>繁野 麻衣子</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>浦田 淳司</t>
         </is>
       </c>
       <c r="H77" t="n">
         <v>0.8526158630847931</v>
       </c>
       <c r="I77" t="n">
-        <v>0.8472535312175751</v>
+        <v>0.8439355790615082</v>
       </c>
       <c r="J77" t="n">
-        <v>0.8447800874710083</v>
+        <v>0.8418673872947693</v>
       </c>
     </row>
     <row r="78">
@@ -4000,27 +4000,27 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>讃井 知</t>
+          <t>石井 儀光</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
+          <t>澤 亮治</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>澤 亮治</t>
+          <t>雨宮 護</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>0.8150631785392761</v>
+        <v>0.8125244677066803</v>
       </c>
       <c r="I78" t="n">
-        <v>0.8095495998859406</v>
+        <v>0.8084699511528015</v>
       </c>
       <c r="J78" t="n">
-        <v>0.8084698915481567</v>
+        <v>0.8075909912586212</v>
       </c>
     </row>
     <row r="79">
@@ -4051,22 +4051,22 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>讃井 知</t>
+          <t>浦田 淳司</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>浦田 淳司</t>
+          <t>村上 暁信</t>
         </is>
       </c>
       <c r="H79" t="n">
         <v>0.8340822756290436</v>
       </c>
       <c r="I79" t="n">
-        <v>0.8291230797767639</v>
+        <v>0.8263863027095795</v>
       </c>
       <c r="J79" t="n">
-        <v>0.8263863027095795</v>
+        <v>0.8239715397357941</v>
       </c>
     </row>
     <row r="80">
@@ -4102,17 +4102,17 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>太田 充</t>
+          <t>渡邉 俊</t>
         </is>
       </c>
       <c r="H80" t="n">
         <v>0.8768689632415771</v>
       </c>
       <c r="I80" t="n">
-        <v>0.8746379613876343</v>
+        <v>0.8746379911899567</v>
       </c>
       <c r="J80" t="n">
-        <v>0.8696686923503876</v>
+        <v>0.8685058951377869</v>
       </c>
     </row>
     <row r="81">
@@ -4138,27 +4138,27 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>讃井 知</t>
+          <t>作道 真理</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>作道 真理</t>
+          <t>甲斐田 直子</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>甲斐田 直子</t>
+          <t>奥島 真一郎</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>0.8296012878417969</v>
+        <v>0.8292419016361237</v>
       </c>
       <c r="I81" t="n">
-        <v>0.8292419612407684</v>
+        <v>0.8284184038639069</v>
       </c>
       <c r="J81" t="n">
-        <v>0.8284183740615845</v>
+        <v>0.8275057971477509</v>
       </c>
     </row>
     <row r="82">
@@ -4184,27 +4184,27 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>讃井 知</t>
+          <t>高野 祐一</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>高野 祐一</t>
+          <t>作道 真理</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>作道 真理</t>
+          <t>秋山 英三</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>0.8296072781085968</v>
+        <v>0.8292145431041718</v>
       </c>
       <c r="I82" t="n">
-        <v>0.8292145133018494</v>
+        <v>0.8283562064170837</v>
       </c>
       <c r="J82" t="n">
-        <v>0.8283562362194061</v>
+        <v>0.828016072511673</v>
       </c>
     </row>
     <row r="83">
@@ -4235,22 +4235,22 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Liu Tianxiang</t>
+          <t>石井 儀光</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
+          <t>大西 正輝</t>
         </is>
       </c>
       <c r="H83" t="n">
         <v>0.8149228394031525</v>
       </c>
       <c r="I83" t="n">
-        <v>0.8099619150161743</v>
+        <v>0.8128287494182587</v>
       </c>
       <c r="J83" t="n">
-        <v>0.8083364963531494</v>
+        <v>0.807068407535553</v>
       </c>
     </row>
     <row r="84">
@@ -4281,22 +4281,22 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>讃井 知</t>
+          <t>作道 真理</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>作道 真理</t>
+          <t>秋山 英三</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>0.8309312462806702</v>
+        <v>0.8309313058853149</v>
       </c>
       <c r="I84" t="n">
-        <v>0.8293078541755676</v>
+        <v>0.829272985458374</v>
       </c>
       <c r="J84" t="n">
-        <v>0.8292732536792755</v>
+        <v>0.8282457590103149</v>
       </c>
     </row>
     <row r="85">
@@ -4332,17 +4332,17 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>讃井 知</t>
+          <t>村上 暁信</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>0.8385043144226074</v>
+        <v>0.8385042548179626</v>
       </c>
       <c r="I85" t="n">
-        <v>0.8338599503040314</v>
+        <v>0.833859920501709</v>
       </c>
       <c r="J85" t="n">
-        <v>0.8336627185344696</v>
+        <v>0.8319239020347595</v>
       </c>
     </row>
     <row r="86">
@@ -4368,27 +4368,27 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>山本 幸子</t>
+          <t>有田 智一</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>讃井 知</t>
+          <t>藤井 さやか</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>有田 智一</t>
+          <t>堤 盛人</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>0.8619189262390137</v>
+        <v>0.8548861145973206</v>
       </c>
       <c r="I86" t="n">
-        <v>0.855473667383194</v>
+        <v>0.8524208664894104</v>
       </c>
       <c r="J86" t="n">
-        <v>0.8548861145973206</v>
+        <v>0.8500982522964478</v>
       </c>
     </row>
   </sheetData>
@@ -4480,27 +4480,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>小西 葉子</t>
+          <t>岡田 幸彦</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>岡田 幸彦</t>
+          <t>岡本 直久</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.8615496456623077</v>
+        <v>0.8529865443706512</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8529864549636841</v>
+        <v>0.8522876501083374</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8524919748306274</v>
+        <v>0.8513901829719543</v>
       </c>
     </row>
     <row r="3">
@@ -4526,27 +4526,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>有馬 澄佳</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>小西 葉子</t>
+          <t>高野 祐一</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
+          <t>志田 洋平</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.862902969121933</v>
+        <v>0.8502500951290131</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8564811944961548</v>
+        <v>0.8491443991661072</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8502500951290131</v>
+        <v>0.8473080396652222</v>
       </c>
     </row>
     <row r="4">
@@ -4572,27 +4572,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>岡本 直久</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>志田 洋平</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>有馬 澄佳</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.8726406395435333</v>
+        <v>0.8634753227233887</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8723745942115784</v>
+        <v>0.8584830462932587</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8699900805950165</v>
+        <v>0.8570760786533356</v>
       </c>
     </row>
     <row r="5">
@@ -4618,27 +4618,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>讃井 知</t>
+          <t>岡田 幸彦</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>上市 秀雄</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>秋山 英三</t>
+          <t>志田 洋平</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.8725573122501373</v>
+        <v>0.8646489381790161</v>
       </c>
       <c r="I5" t="n">
-        <v>0.868150919675827</v>
+        <v>0.8614354729652405</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8653525114059448</v>
+        <v>0.8505673408508301</v>
       </c>
     </row>
     <row r="6">
@@ -4664,27 +4664,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>イリチュ 美佳</t>
+          <t>岡田 幸彦</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
+          <t>高野 祐一</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.8685602843761444</v>
+        <v>0.8663020431995392</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8665047883987427</v>
+        <v>0.8624062240123749</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8663018941879272</v>
+        <v>0.859586626291275</v>
       </c>
     </row>
     <row r="7">
@@ -4710,27 +4710,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>岡田 幸彦</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>イリチュ 美佳</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>岡本 翔平</t>
+          <t>吉瀬 章子</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.8784606158733368</v>
+        <v>0.8727982044219971</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8773766160011292</v>
+        <v>0.8707009255886078</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8744112253189087</v>
+        <v>0.8608711659908295</v>
       </c>
     </row>
     <row r="8">
@@ -4756,27 +4756,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>志田 洋平</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>志田 洋平</t>
+          <t>繁野 麻衣子</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>堤 盛人</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.8793413639068604</v>
+        <v>0.8671495914459229</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8671495318412781</v>
+        <v>0.8573973178863525</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8640706539154053</v>
+        <v>0.8571834564208984</v>
       </c>
     </row>
     <row r="9">
@@ -4812,17 +4812,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>高野 祐一</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.8687701225280762</v>
+        <v>0.8687700629234314</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8564662933349609</v>
+        <v>0.8564662337303162</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8544216752052307</v>
+        <v>0.8542343080043793</v>
       </c>
     </row>
     <row r="10">
@@ -4848,27 +4848,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>岡本 直久</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>和田 健太郎</t>
+          <t>志田 洋平</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.878412127494812</v>
+        <v>0.8673241138458252</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8746395409107208</v>
+        <v>0.8617254197597504</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8692611157894135</v>
+        <v>0.8601478338241577</v>
       </c>
     </row>
     <row r="11">
@@ -4894,27 +4894,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>有田 智一</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>太田 充</t>
+          <t>岡本 直久</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>渡邉 俊</t>
+          <t>志田 洋平</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.8776608407497406</v>
+        <v>0.8733630180358887</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8772943019866943</v>
+        <v>0.8574979305267334</v>
       </c>
       <c r="J11" t="n">
-        <v>0.87617427110672</v>
+        <v>0.8510553240776062</v>
       </c>
     </row>
     <row r="12">
@@ -4940,27 +4940,27 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>讃井 知</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>岡田 幸彦</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>雨宮 護</t>
+          <t>有田 智一</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.8686253428459167</v>
+        <v>0.8568483889102936</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8617160618305206</v>
+        <v>0.8547086715698242</v>
       </c>
       <c r="J12" t="n">
-        <v>0.857864648103714</v>
+        <v>0.8487116694450378</v>
       </c>
     </row>
     <row r="13">
@@ -4991,22 +4991,22 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>上市 秀雄</t>
+          <t>岡田 幸彦</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>イリチュ 美佳</t>
+          <t>志田 洋平</t>
         </is>
       </c>
       <c r="H13" t="n">
         <v>0.881976842880249</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8667441010475159</v>
+        <v>0.8592317700386047</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8615249991416931</v>
+        <v>0.8585523664951324</v>
       </c>
     </row>
     <row r="14">
@@ -5037,22 +5037,22 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>有馬 澄佳</t>
+          <t>繁野 麻衣子</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>吉瀬 章子</t>
         </is>
       </c>
       <c r="H14" t="n">
         <v>0.8876061737537384</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8659283518791199</v>
+        <v>0.8648438453674316</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8646425902843475</v>
+        <v>0.8630379140377045</v>
       </c>
     </row>
     <row r="15">
@@ -5078,27 +5078,27 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>小西 葉子</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>黒瀬 雄大</t>
+          <t>高野 祐一</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phung-Duc Tuan</t>
+          <t>志田 洋平</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0.8653980195522308</v>
+        <v>0.8538029789924622</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8549571931362152</v>
+        <v>0.8517937362194061</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8538030087947845</v>
+        <v>0.8510238230228424</v>
       </c>
     </row>
     <row r="16">
@@ -5124,27 +5124,27 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>上市 秀雄</t>
+          <t>岡田 幸彦</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>讃井 知</t>
+          <t>高野 祐一</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0.8583924770355225</v>
+        <v>0.8545618057250977</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8568210601806641</v>
+        <v>0.8458708822727203</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8549480438232422</v>
+        <v>0.8376062512397766</v>
       </c>
     </row>
     <row r="17">
@@ -5170,27 +5170,27 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>三崎 広海</t>
+          <t>高野 祐一</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>小西 葉子</t>
+          <t>岡田 幸彦</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>黒瀬 雄大</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.8657762110233307</v>
+        <v>0.8589096665382385</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8645855784416199</v>
+        <v>0.8580231368541718</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8605440855026245</v>
+        <v>0.8544259071350098</v>
       </c>
     </row>
     <row r="18">
@@ -5216,27 +5216,27 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>有馬 澄佳</t>
+          <t>志田 洋平</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>岡本 直久</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>有田 智一</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0.8643296360969543</v>
+        <v>0.855168342590332</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8624945878982544</v>
+        <v>0.8508627712726593</v>
       </c>
       <c r="J18" t="n">
-        <v>0.862152636051178</v>
+        <v>0.8499838709831238</v>
       </c>
     </row>
     <row r="19">
@@ -5267,22 +5267,22 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>岡本 直久</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>和田 健太郎</t>
+          <t>吉瀬 章子</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0.8965592980384827</v>
+        <v>0.8965593874454498</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8704787790775299</v>
+        <v>0.8609089851379395</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8676624000072479</v>
+        <v>0.8589943647384644</v>
       </c>
     </row>
     <row r="20">
@@ -5308,27 +5308,27 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>志田 洋平</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>志田 洋平</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>渡邉 俊</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0.887686014175415</v>
+        <v>0.8774204552173615</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8774204552173615</v>
+        <v>0.8656096756458282</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8773219287395477</v>
+        <v>0.8639147281646729</v>
       </c>
     </row>
     <row r="21">
@@ -5354,27 +5354,27 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>小西 葉子</t>
+          <t>高野 祐一</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>高野 祐一</t>
+          <t>志田 洋平</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>鈴木 勉</t>
+          <t>Phung-Duc Tuan</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.8698301017284393</v>
+        <v>0.8667503893375397</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8667502701282501</v>
+        <v>0.8609132766723633</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8629519045352936</v>
+        <v>0.8602559268474579</v>
       </c>
     </row>
     <row r="22">
@@ -5405,22 +5405,22 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>八森 正泰</t>
+          <t>吉瀬 章子</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>吉瀬 章子</t>
+          <t>繁野 麻衣子</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0.8635926842689514</v>
+        <v>0.8635925948619843</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8507093787193298</v>
+        <v>0.8474651873111725</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8474651873111725</v>
+        <v>0.8455659449100494</v>
       </c>
     </row>
     <row r="23">
@@ -5456,17 +5456,17 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>川島 宏一</t>
+          <t>岡田 幸彦</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0.873361200094223</v>
+        <v>0.8733612298965454</v>
       </c>
       <c r="I23" t="n">
         <v>0.8450472950935364</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8445885479450226</v>
+        <v>0.8442730307579041</v>
       </c>
     </row>
   </sheetData>

--- a/generated/committee_recommendations.xlsx
+++ b/generated/committee_recommendations.xlsx
@@ -662,7 +662,7 @@
         <v>0.8467218577861786</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8440098166465759</v>
+        <v>0.8435449302196503</v>
       </c>
     </row>
     <row r="6">
@@ -846,7 +846,7 @@
         <v>0.8692824840545654</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8664173483848572</v>
+        <v>0.8661611378192902</v>
       </c>
     </row>
     <row r="10">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>雨宮 護</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -1122,7 +1122,7 @@
         <v>0.8508188724517822</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8468877077102661</v>
+        <v>0.8489751815795898</v>
       </c>
     </row>
     <row r="16">
@@ -1168,7 +1168,7 @@
         <v>0.8795138299465179</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8731004893779755</v>
+        <v>0.8724113404750824</v>
       </c>
     </row>
     <row r="17">
@@ -1490,7 +1490,7 @@
         <v>0.8633539974689484</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8604942560195923</v>
+        <v>0.8604661822319031</v>
       </c>
     </row>
     <row r="24">
@@ -1533,7 +1533,7 @@
         <v>0.8740248084068298</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8682364821434021</v>
+        <v>0.8680716753005981</v>
       </c>
       <c r="J24" t="n">
         <v>0.8672411739826202</v>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>村上 暁信</t>
+          <t>浦田 淳司</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -1582,7 +1582,7 @@
         <v>0.8573780655860901</v>
       </c>
       <c r="J25" t="n">
-        <v>0.856936514377594</v>
+        <v>0.8569363653659821</v>
       </c>
     </row>
     <row r="26">
@@ -1608,27 +1608,27 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>佐野 幸恵</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t>牛島 光一</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>イリチュ 美佳</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>黒瀬 雄大</t>
-        </is>
-      </c>
       <c r="H26" t="n">
+        <v>0.8715297877788544</v>
+      </c>
+      <c r="I26" t="n">
         <v>0.8625889718532562</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>0.861405223608017</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.8584799766540527</v>
       </c>
     </row>
     <row r="27">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>渡邉 俊</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -1674,7 +1674,7 @@
         <v>0.8689082562923431</v>
       </c>
       <c r="J27" t="n">
-        <v>0.8632592856884003</v>
+        <v>0.867827296257019</v>
       </c>
     </row>
     <row r="28">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>雨宮 護</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -1904,7 +1904,7 @@
         <v>0.8411490023136139</v>
       </c>
       <c r="J32" t="n">
-        <v>0.8403199911117554</v>
+        <v>0.8407794237136841</v>
       </c>
     </row>
     <row r="33">
@@ -2027,22 +2027,22 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
+          <t>佐野 幸恵</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
           <t>甲斐田 直子</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>村上 暁信</t>
         </is>
       </c>
       <c r="H35" t="n">
         <v>0.8445099592208862</v>
       </c>
       <c r="I35" t="n">
+        <v>0.8402862548828125</v>
+      </c>
+      <c r="J35" t="n">
         <v>0.8385109901428223</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0.837116003036499</v>
       </c>
     </row>
     <row r="36">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>イリチュ 美佳</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -2088,7 +2088,7 @@
         <v>0.8639206290245056</v>
       </c>
       <c r="J36" t="n">
-        <v>0.8605668544769287</v>
+        <v>0.8613840043544769</v>
       </c>
     </row>
     <row r="37">
@@ -2390,27 +2390,27 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
+          <t>佐野 幸恵</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t>繁野 麻衣子</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>秋山 英三</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>作道 真理</t>
-        </is>
-      </c>
       <c r="H43" t="n">
-        <v>0.8414866030216217</v>
+        <v>0.8459293246269226</v>
       </c>
       <c r="I43" t="n">
+        <v>0.8408311605453491</v>
+      </c>
+      <c r="J43" t="n">
         <v>0.8378401696681976</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0.8372129499912262</v>
       </c>
     </row>
     <row r="44">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>浦田 淳司</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="H46" t="n">
@@ -2548,7 +2548,7 @@
         <v>0.8456086218357086</v>
       </c>
       <c r="J46" t="n">
-        <v>0.8429499566555023</v>
+        <v>0.843080073595047</v>
       </c>
     </row>
     <row r="47">
@@ -2584,7 +2584,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>秋山 英三</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="H47" t="n">
@@ -2594,7 +2594,7 @@
         <v>0.8581773638725281</v>
       </c>
       <c r="J47" t="n">
-        <v>0.8540851473808289</v>
+        <v>0.8559066355228424</v>
       </c>
     </row>
     <row r="48">
@@ -2625,22 +2625,22 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>イリチュ 美佳</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>イリチュ 美佳</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="H48" t="n">
         <v>0.8453716635704041</v>
       </c>
       <c r="I48" t="n">
-        <v>0.8445407748222351</v>
+        <v>0.844357967376709</v>
       </c>
       <c r="J48" t="n">
-        <v>0.844357967376709</v>
+        <v>0.8441737592220306</v>
       </c>
     </row>
     <row r="49">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
+          <t>吉瀬 章子</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
           <t>繁野 麻衣子</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>吉瀬 章子</t>
-        </is>
-      </c>
       <c r="G49" t="inlineStr">
         <is>
           <t>八森 正泰</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0.8699431717395782</v>
+        <v>0.8694933354854584</v>
       </c>
       <c r="I49" t="n">
-        <v>0.8694933354854584</v>
+        <v>0.8682685494422913</v>
       </c>
       <c r="J49" t="n">
         <v>0.8611498475074768</v>
@@ -2809,22 +2809,22 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
+          <t>佐野 幸恵</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
           <t>高野 祐一</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>澤 亮治</t>
         </is>
       </c>
       <c r="H52" t="n">
         <v>0.8604255318641663</v>
       </c>
       <c r="I52" t="n">
+        <v>0.8562762141227722</v>
+      </c>
+      <c r="J52" t="n">
         <v>0.8557384312152863</v>
-      </c>
-      <c r="J52" t="n">
-        <v>0.854552298784256</v>
       </c>
     </row>
     <row r="53">
@@ -2850,27 +2850,27 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
+          <t>佐野 幸恵</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
           <t>浦田 淳司</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>イリチュ 美佳</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>大西 正輝</t>
-        </is>
-      </c>
       <c r="H53" t="n">
+        <v>0.8492535948753357</v>
+      </c>
+      <c r="I53" t="n">
         <v>0.847988098859787</v>
       </c>
-      <c r="I53" t="n">
+      <c r="J53" t="n">
         <v>0.8451839983463287</v>
-      </c>
-      <c r="J53" t="n">
-        <v>0.8436055183410645</v>
       </c>
     </row>
     <row r="54">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="H54" t="n">
@@ -2916,7 +2916,7 @@
         <v>0.8537877798080444</v>
       </c>
       <c r="J54" t="n">
-        <v>0.8420813381671906</v>
+        <v>0.8456676602363586</v>
       </c>
     </row>
     <row r="55">
@@ -2947,22 +2947,22 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
+          <t>佐野 幸恵</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
           <t>黒瀬 雄大</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>浦田 淳司</t>
         </is>
       </c>
       <c r="H55" t="n">
         <v>0.8501562178134918</v>
       </c>
       <c r="I55" t="n">
+        <v>0.8466014564037323</v>
+      </c>
+      <c r="J55" t="n">
         <v>0.8440068364143372</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0.8433963358402252</v>
       </c>
     </row>
     <row r="56">
@@ -2993,22 +2993,22 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
+          <t>岡田 幸彦</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
           <t>牛島 光一</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>堤 盛人</t>
         </is>
       </c>
       <c r="H56" t="n">
         <v>0.8617116212844849</v>
       </c>
       <c r="I56" t="n">
+        <v>0.8601812720298767</v>
+      </c>
+      <c r="J56" t="n">
         <v>0.8599629104137421</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0.8598028123378754</v>
       </c>
     </row>
     <row r="57">
@@ -3100,7 +3100,7 @@
         <v>0.8459519445896149</v>
       </c>
       <c r="J58" t="n">
-        <v>0.8456976413726807</v>
+        <v>0.8450420796871185</v>
       </c>
     </row>
     <row r="59">
@@ -3126,27 +3126,27 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
+          <t>佐野 幸恵</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
           <t>イリチュ 美佳</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>作道 真理</t>
-        </is>
-      </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>村上 暁信</t>
+          <t>岡田 幸彦</t>
         </is>
       </c>
       <c r="H59" t="n">
+        <v>0.8485637009143829</v>
+      </c>
+      <c r="I59" t="n">
         <v>0.8466636836528778</v>
       </c>
-      <c r="I59" t="n">
-        <v>0.8414956629276276</v>
-      </c>
       <c r="J59" t="n">
-        <v>0.8412843644618988</v>
+        <v>0.8420409262180328</v>
       </c>
     </row>
     <row r="60">
@@ -3192,7 +3192,7 @@
         <v>0.8626532554626465</v>
       </c>
       <c r="J60" t="n">
-        <v>0.8603174686431885</v>
+        <v>0.8584358096122742</v>
       </c>
     </row>
     <row r="61">
@@ -3218,24 +3218,24 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
+          <t>甲斐田 直子</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
           <t>村上 暁信</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>甲斐田 直子</t>
-        </is>
-      </c>
       <c r="G61" t="inlineStr">
         <is>
           <t>牛島 光一</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>0.8658595085144043</v>
+        <v>0.8657461404800415</v>
       </c>
       <c r="I61" t="n">
-        <v>0.8657461404800415</v>
+        <v>0.8657316565513611</v>
       </c>
       <c r="J61" t="n">
         <v>0.8604395687580109</v>
@@ -3324,7 +3324,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>0.8477002382278442</v>
+        <v>0.8482207059860229</v>
       </c>
       <c r="I63" t="n">
         <v>0.8416444659233093</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>吉瀬 章子</t>
         </is>
       </c>
       <c r="H64" t="n">
@@ -3376,7 +3376,7 @@
         <v>0.8664391338825226</v>
       </c>
       <c r="J64" t="n">
-        <v>0.8655925691127777</v>
+        <v>0.86557537317276</v>
       </c>
     </row>
     <row r="65">
@@ -3402,27 +3402,27 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
+          <t>佐野 幸恵</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
           <t>八森 正泰</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>高野 祐一</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>秋山 英三</t>
-        </is>
-      </c>
       <c r="H65" t="n">
+        <v>0.8648021817207336</v>
+      </c>
+      <c r="I65" t="n">
         <v>0.8587773442268372</v>
       </c>
-      <c r="I65" t="n">
+      <c r="J65" t="n">
         <v>0.8530013859272003</v>
-      </c>
-      <c r="J65" t="n">
-        <v>0.852728933095932</v>
       </c>
     </row>
     <row r="66">
@@ -3504,7 +3504,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>高野 祐一</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="H67" t="n">
@@ -3514,7 +3514,7 @@
         <v>0.8428299427032471</v>
       </c>
       <c r="J67" t="n">
-        <v>0.8421742618083954</v>
+        <v>0.842542827129364</v>
       </c>
     </row>
     <row r="68">
@@ -3545,22 +3545,22 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
+          <t>志田 洋平</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
           <t>牛島 光一</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>雨宮 護</t>
         </is>
       </c>
       <c r="H68" t="n">
         <v>0.8728137910366058</v>
       </c>
       <c r="I68" t="n">
+        <v>0.8711625635623932</v>
+      </c>
+      <c r="J68" t="n">
         <v>0.8687836229801178</v>
-      </c>
-      <c r="J68" t="n">
-        <v>0.865785539150238</v>
       </c>
     </row>
     <row r="69">
@@ -3586,27 +3586,27 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
+          <t>岡田 幸彦</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
           <t>浦田 淳司</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>繁野 麻衣子</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>イリチュ 美佳</t>
-        </is>
-      </c>
       <c r="H69" t="n">
+        <v>0.8476590812206268</v>
+      </c>
+      <c r="I69" t="n">
         <v>0.843207448720932</v>
       </c>
-      <c r="I69" t="n">
-        <v>0.8409813344478607</v>
-      </c>
       <c r="J69" t="n">
-        <v>0.8402246534824371</v>
+        <v>0.8403257727622986</v>
       </c>
     </row>
     <row r="70">
@@ -3637,22 +3637,22 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
+          <t>村上 暁信</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
           <t>岡本 直久</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>村上 暁信</t>
         </is>
       </c>
       <c r="H70" t="n">
         <v>0.8448812961578369</v>
       </c>
       <c r="I70" t="n">
+        <v>0.8382628560066223</v>
+      </c>
+      <c r="J70" t="n">
         <v>0.8380181491374969</v>
-      </c>
-      <c r="J70" t="n">
-        <v>0.8377423882484436</v>
       </c>
     </row>
     <row r="71">
@@ -3734,7 +3734,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>岡田 幸彦</t>
         </is>
       </c>
       <c r="H72" t="n">
@@ -3744,7 +3744,7 @@
         <v>0.8628239333629608</v>
       </c>
       <c r="J72" t="n">
-        <v>0.8551492691040039</v>
+        <v>0.8584659695625305</v>
       </c>
     </row>
     <row r="73">
@@ -3913,22 +3913,22 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
+          <t>佐野 幸恵</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
           <t>甲斐田 直子</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>村上 暁信</t>
         </is>
       </c>
       <c r="H76" t="n">
         <v>0.8549287021160126</v>
       </c>
       <c r="I76" t="n">
+        <v>0.8530536293983459</v>
+      </c>
+      <c r="J76" t="n">
         <v>0.851565808057785</v>
-      </c>
-      <c r="J76" t="n">
-        <v>0.8490276336669922</v>
       </c>
     </row>
     <row r="77">
@@ -3959,22 +3959,22 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
+          <t>佐野 幸恵</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
           <t>繁野 麻衣子</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>浦田 淳司</t>
         </is>
       </c>
       <c r="H77" t="n">
         <v>0.8526158630847931</v>
       </c>
       <c r="I77" t="n">
-        <v>0.8439355790615082</v>
+        <v>0.8472535610198975</v>
       </c>
       <c r="J77" t="n">
-        <v>0.8418673872947693</v>
+        <v>0.843280017375946</v>
       </c>
     </row>
     <row r="78">
@@ -4005,22 +4005,22 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
+          <t>佐野 幸恵</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
           <t>澤 亮治</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>雨宮 護</t>
         </is>
       </c>
       <c r="H78" t="n">
         <v>0.8125244677066803</v>
       </c>
       <c r="I78" t="n">
+        <v>0.8095496296882629</v>
+      </c>
+      <c r="J78" t="n">
         <v>0.8084699511528015</v>
-      </c>
-      <c r="J78" t="n">
-        <v>0.8075909912586212</v>
       </c>
     </row>
     <row r="79">
@@ -4066,7 +4066,7 @@
         <v>0.8263863027095795</v>
       </c>
       <c r="J79" t="n">
-        <v>0.8239715397357941</v>
+        <v>0.8235066533088684</v>
       </c>
     </row>
     <row r="80">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>大西 正輝</t>
+          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="H83" t="n">
@@ -4250,7 +4250,7 @@
         <v>0.8128287494182587</v>
       </c>
       <c r="J83" t="n">
-        <v>0.807068407535553</v>
+        <v>0.8083365261554718</v>
       </c>
     </row>
     <row r="84">
@@ -4342,7 +4342,7 @@
         <v>0.833859920501709</v>
       </c>
       <c r="J85" t="n">
-        <v>0.8319239020347595</v>
+        <v>0.8314589262008667</v>
       </c>
     </row>
     <row r="86">
@@ -4485,22 +4485,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>牛島 光一</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>岡本 直久</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>佐野 幸恵</t>
         </is>
       </c>
       <c r="H2" t="n">
         <v>0.8529865443706512</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8522876501083374</v>
+        <v>0.8524920046329498</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8513901829719543</v>
+        <v>0.8522875905036926</v>
       </c>
     </row>
     <row r="3">
@@ -4526,27 +4526,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>有馬 澄佳</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>佐野 幸恵</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>高野 祐一</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>志田 洋平</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.8502500951290131</v>
+        <v>0.862902969121933</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8491443991661072</v>
+        <v>0.8502500653266907</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8473080396652222</v>
+        <v>0.8499161899089813</v>
       </c>
     </row>
     <row r="4">
@@ -4572,27 +4572,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>岡本 直久</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>志田 洋平</t>
+          <t>有馬 澄佳</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phung-Duc Tuan</t>
+          <t>雨宮 護</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.8634753227233887</v>
+        <v>0.8726406097412109</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8584830462932587</v>
+        <v>0.8699901401996613</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8570760786533356</v>
+        <v>0.8658290803432465</v>
       </c>
     </row>
     <row r="5">
@@ -4618,27 +4618,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>秋山 英三</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>岡田 幸彦</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>佐野 幸恵</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>志田 洋平</t>
-        </is>
-      </c>
       <c r="H5" t="n">
-        <v>0.8646489381790161</v>
+        <v>0.8653525710105896</v>
       </c>
       <c r="I5" t="n">
+        <v>0.8646489977836609</v>
+      </c>
+      <c r="J5" t="n">
         <v>0.8614354729652405</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.8505673408508301</v>
       </c>
     </row>
     <row r="6">
@@ -4664,27 +4664,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>イリチュ 美佳</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>佐野 幸恵</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>岡田 幸彦</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>高野 祐一</t>
-        </is>
-      </c>
       <c r="H6" t="n">
-        <v>0.8663020431995392</v>
+        <v>0.8665047883987427</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8624062240123749</v>
+        <v>0.866301953792572</v>
       </c>
       <c r="J6" t="n">
-        <v>0.859586626291275</v>
+        <v>0.8624062538146973</v>
       </c>
     </row>
     <row r="7">
@@ -4710,27 +4710,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>イリチュ 美佳</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>牛島 光一</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>岡田 幸彦</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>佐野 幸恵</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>吉瀬 章子</t>
-        </is>
-      </c>
       <c r="H7" t="n">
+        <v>0.8773767352104187</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.8732210099697113</v>
+      </c>
+      <c r="J7" t="n">
         <v>0.8727982044219971</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.8707009255886078</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.8608711659908295</v>
       </c>
     </row>
     <row r="8">
@@ -4761,22 +4761,22 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>堤 盛人</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phung-Duc Tuan</t>
+          <t>雨宮 護</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.8671495914459229</v>
+        <v>0.8671495318412781</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8573973178863525</v>
+        <v>0.8640704452991486</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8571834564208984</v>
+        <v>0.86296147108078</v>
       </c>
     </row>
     <row r="9">
@@ -4816,13 +4816,13 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.8687700629234314</v>
+        <v>0.8687701225280762</v>
       </c>
       <c r="I9" t="n">
         <v>0.8564662337303162</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8542343080043793</v>
+        <v>0.8542343378067017</v>
       </c>
     </row>
     <row r="10">
@@ -4848,27 +4848,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>和田 健太郎</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>岡本 直久</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>志田 洋平</t>
-        </is>
-      </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phung-Duc Tuan</t>
+          <t>有馬 澄佳</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.8673241138458252</v>
+        <v>0.8746394515037537</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8617254197597504</v>
+        <v>0.86732417345047</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8601478338241577</v>
+        <v>0.8670890927314758</v>
       </c>
     </row>
     <row r="11">
@@ -4894,27 +4894,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>渡邉 俊</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>有田 智一</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>岡本 直久</t>
-        </is>
-      </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>志田 洋平</t>
+          <t>堤 盛人</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.8733630180358887</v>
+        <v>0.8761743009090424</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8574979305267334</v>
+        <v>0.8733631372451782</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8510553240776062</v>
+        <v>0.8709878623485565</v>
       </c>
     </row>
     <row r="12">
@@ -4940,27 +4940,27 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>雨宮 護</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>佐野 幸恵</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>岡田 幸彦</t>
-        </is>
-      </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>有田 智一</t>
+          <t>甲斐田 直子</t>
         </is>
       </c>
       <c r="H12" t="n">
+        <v>0.857864648103714</v>
+      </c>
+      <c r="I12" t="n">
         <v>0.8568483889102936</v>
       </c>
-      <c r="I12" t="n">
-        <v>0.8547086715698242</v>
-      </c>
       <c r="J12" t="n">
-        <v>0.8487116694450378</v>
+        <v>0.855992317199707</v>
       </c>
     </row>
     <row r="13">
@@ -4991,22 +4991,22 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>イリチュ 美佳</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>岡田 幸彦</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>志田 洋平</t>
         </is>
       </c>
       <c r="H13" t="n">
         <v>0.881976842880249</v>
       </c>
       <c r="I13" t="n">
+        <v>0.8615249693393707</v>
+      </c>
+      <c r="J13" t="n">
         <v>0.8592317700386047</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.8585523664951324</v>
       </c>
     </row>
     <row r="14">
@@ -5037,7 +5037,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>有馬 澄佳</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -5049,10 +5049,10 @@
         <v>0.8876061737537384</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8648438453674316</v>
+        <v>0.8659283518791199</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8630379140377045</v>
+        <v>0.8630378246307373</v>
       </c>
     </row>
     <row r="15">
@@ -5078,27 +5078,27 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>黒瀬 雄大</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>Phung-Duc Tuan</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>高野 祐一</t>
-        </is>
-      </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>志田 洋平</t>
+          <t>有馬 澄佳</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0.8538029789924622</v>
+        <v>0.8549571931362152</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8517937362194061</v>
+        <v>0.8538030087947845</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8510238230228424</v>
+        <v>0.8522914052009583</v>
       </c>
     </row>
     <row r="16">
@@ -5129,22 +5129,22 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
+          <t>甲斐田 直子</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>高野 祐一</t>
+          <t>澤 亮治</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0.8545618057250977</v>
+        <v>0.8545616865158081</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8458708822727203</v>
+        <v>0.8534988462924957</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8376062512397766</v>
+        <v>0.8495171368122101</v>
       </c>
     </row>
     <row r="17">
@@ -5170,27 +5170,27 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>黒瀬 雄大</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>高野 祐一</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>岡田 幸彦</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>佐野 幸恵</t>
-        </is>
-      </c>
       <c r="H17" t="n">
-        <v>0.8589096665382385</v>
+        <v>0.8605440855026245</v>
       </c>
       <c r="I17" t="n">
+        <v>0.8589096367359161</v>
+      </c>
+      <c r="J17" t="n">
         <v>0.8580231368541718</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.8544259071350098</v>
       </c>
     </row>
     <row r="18">
@@ -5216,27 +5216,27 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>志田 洋平</t>
+          <t>有馬 澄佳</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>岡本 直久</t>
+          <t>牛島 光一</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>有田 智一</t>
+          <t>黒瀬 雄大</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0.855168342590332</v>
+        <v>0.8643297851085663</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8508627712726593</v>
+        <v>0.8594227731227875</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8499838709831238</v>
+        <v>0.8584847748279572</v>
       </c>
     </row>
     <row r="19">
@@ -5267,22 +5267,22 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>和田 健太郎</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
           <t>岡本 直久</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>吉瀬 章子</t>
-        </is>
-      </c>
       <c r="H19" t="n">
-        <v>0.8965593874454498</v>
+        <v>0.8965594172477722</v>
       </c>
       <c r="I19" t="n">
+        <v>0.8676624298095703</v>
+      </c>
+      <c r="J19" t="n">
         <v>0.8609089851379395</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.8589943647384644</v>
       </c>
     </row>
     <row r="20">
@@ -5313,22 +5313,22 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Phung-Duc Tuan</t>
+          <t>渡邉 俊</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
+          <t>黒瀬 雄大</t>
         </is>
       </c>
       <c r="H20" t="n">
         <v>0.8774204552173615</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8656096756458282</v>
+        <v>0.8773219287395477</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8639147281646729</v>
+        <v>0.8723052740097046</v>
       </c>
     </row>
     <row r="21">
@@ -5364,17 +5364,17 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phung-Duc Tuan</t>
+          <t>有馬 澄佳</t>
         </is>
       </c>
       <c r="H21" t="n">
         <v>0.8667503893375397</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8609132766723633</v>
+        <v>0.8609131574630737</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8602559268474579</v>
+        <v>0.8609002530574799</v>
       </c>
     </row>
     <row r="22">
@@ -5405,22 +5405,22 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>八森 正泰</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
           <t>吉瀬 章子</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>繁野 麻衣子</t>
-        </is>
-      </c>
       <c r="H22" t="n">
-        <v>0.8635925948619843</v>
+        <v>0.8635926842689514</v>
       </c>
       <c r="I22" t="n">
+        <v>0.8507093191146851</v>
+      </c>
+      <c r="J22" t="n">
         <v>0.8474651873111725</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.8455659449100494</v>
       </c>
     </row>
     <row r="23">
@@ -5460,13 +5460,13 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0.8733612298965454</v>
+        <v>0.873361200094223</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8450472950935364</v>
+        <v>0.845047265291214</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8442730307579041</v>
+        <v>0.8442730903625488</v>
       </c>
     </row>
   </sheetData>

--- a/generated/committee_recommendations.xlsx
+++ b/generated/committee_recommendations.xlsx
@@ -504,27 +504,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>太田 充</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>牛島 光一</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>堤 盛人</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>有田 智一</t>
-        </is>
-      </c>
       <c r="H2" t="n">
+        <v>0.8725054264068604</v>
+      </c>
+      <c r="I2" t="n">
         <v>0.8694877028465271</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>0.8679137825965881</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.859418511390686</v>
       </c>
     </row>
     <row r="3">
@@ -555,22 +555,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>堤 盛人</t>
+          <t>太田 充</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>渡邉 俊</t>
+          <t>山本 幸子</t>
         </is>
       </c>
       <c r="H3" t="n">
         <v>0.8699927628040314</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8664485514163971</v>
+        <v>0.8690957725048065</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8623868525028229</v>
+        <v>0.8680389225482941</v>
       </c>
     </row>
     <row r="4">
@@ -601,22 +601,22 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>山本 幸子</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>有田 智一</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>牛島 光一</t>
         </is>
       </c>
       <c r="H4" t="n">
         <v>0.8407678008079529</v>
       </c>
       <c r="I4" t="n">
+        <v>0.8383740782737732</v>
+      </c>
+      <c r="J4" t="n">
         <v>0.8299179673194885</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.8276243209838867</v>
       </c>
     </row>
     <row r="5">
@@ -659,10 +659,10 @@
         <v>0.8525646924972534</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8467218577861786</v>
+        <v>0.8467219173908234</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8435449302196503</v>
+        <v>0.8445650339126587</v>
       </c>
     </row>
     <row r="6">
@@ -688,27 +688,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>鈴木 勉</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>吉瀬 章子</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>有馬 澄佳</t>
-        </is>
-      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>渡邉 俊</t>
+          <t>山本 幸子</t>
         </is>
       </c>
       <c r="H6" t="n">
+        <v>0.8804560899734497</v>
+      </c>
+      <c r="I6" t="n">
         <v>0.8787815570831299</v>
       </c>
-      <c r="I6" t="n">
-        <v>0.870666116476059</v>
-      </c>
       <c r="J6" t="n">
-        <v>0.8701993227005005</v>
+        <v>0.8734155297279358</v>
       </c>
     </row>
     <row r="7">
@@ -739,22 +739,22 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>有田 智一</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="H7" t="n">
         <v>0.8718103468418121</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8672458827495575</v>
+        <v>0.8701827228069305</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8657021820545197</v>
+        <v>0.8687415421009064</v>
       </c>
     </row>
     <row r="8">
@@ -790,17 +790,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>吉瀬 章子</t>
+          <t>上市 秀雄</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.8684000968933105</v>
+        <v>0.8684000670909882</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8601691126823425</v>
+        <v>0.8601690530776978</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8557119965553284</v>
+        <v>0.8557591140270233</v>
       </c>
     </row>
     <row r="9">
@@ -826,27 +826,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>山本 幸子</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>渡邉 俊</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>甲斐田 直子</t>
-        </is>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>村上 暁信</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.8701505959033966</v>
+        <v>0.870919406414032</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8692824840545654</v>
+        <v>0.870150625705719</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8661611378192902</v>
+        <v>0.8696761429309845</v>
       </c>
     </row>
     <row r="10">
@@ -872,27 +872,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>鈴木 勉</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>川島 宏一</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
           <t>堤 盛人</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>牛島 光一</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>渡邉 俊</t>
-        </is>
-      </c>
       <c r="H10" t="n">
+        <v>0.8743027448654175</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.8654838800430298</v>
+      </c>
+      <c r="J10" t="n">
         <v>0.8654041886329651</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.8622785210609436</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.8618445992469788</v>
       </c>
     </row>
     <row r="11">
@@ -918,27 +918,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>三崎 広海</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>秋山 英三</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>黒瀬 雄大</t>
-        </is>
-      </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>小西 葉子</t>
         </is>
       </c>
       <c r="H11" t="n">
+        <v>0.8726991415023804</v>
+      </c>
+      <c r="I11" t="n">
         <v>0.859723687171936</v>
       </c>
-      <c r="I11" t="n">
-        <v>0.8509807288646698</v>
-      </c>
       <c r="J11" t="n">
-        <v>0.8484225869178772</v>
+        <v>0.8510848581790924</v>
       </c>
     </row>
     <row r="12">
@@ -1015,22 +1015,22 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>山本 幸子</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>藤井 さやか</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>渡邉 俊</t>
-        </is>
-      </c>
       <c r="H13" t="n">
-        <v>0.8786501884460449</v>
+        <v>0.8786501586437225</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8751763701438904</v>
+        <v>0.8759361505508423</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8725005686283112</v>
+        <v>0.8751762509346008</v>
       </c>
     </row>
     <row r="14">
@@ -1056,27 +1056,27 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
+          <t>讃井 知</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>甲斐田 直子</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>雨宮 護</t>
-        </is>
-      </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>澤 亮治</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.8637474477291107</v>
+        <v>0.8674522936344147</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8538913130760193</v>
+        <v>0.8637473881244659</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8533703684806824</v>
+        <v>0.8552792370319366</v>
       </c>
     </row>
     <row r="15">
@@ -1102,27 +1102,27 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>讃井 知</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>上市 秀雄</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
           <t>甲斐田 直子</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>秋山 英三</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>佐野 幸恵</t>
-        </is>
-      </c>
       <c r="H15" t="n">
-        <v>0.8559390306472778</v>
+        <v>0.860321581363678</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8508188724517822</v>
+        <v>0.8595085144042969</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8489751815795898</v>
+        <v>0.8559391796588898</v>
       </c>
     </row>
     <row r="16">
@@ -1158,17 +1158,17 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>村上 暁信</t>
+          <t>太田 充</t>
         </is>
       </c>
       <c r="H16" t="n">
         <v>0.8840882182121277</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8795138299465179</v>
+        <v>0.8795139193534851</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8724113404750824</v>
+        <v>0.8777674734592438</v>
       </c>
     </row>
     <row r="17">
@@ -1194,27 +1194,27 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>山本 幸子</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>松原 康介</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>渡邉 俊</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>藤井 さやか</t>
-        </is>
-      </c>
       <c r="H17" t="n">
+        <v>0.8654569983482361</v>
+      </c>
+      <c r="I17" t="n">
         <v>0.8594345450401306</v>
       </c>
-      <c r="I17" t="n">
-        <v>0.8577826619148254</v>
-      </c>
       <c r="J17" t="n">
-        <v>0.8537378907203674</v>
+        <v>0.8577827215194702</v>
       </c>
     </row>
     <row r="18">
@@ -1240,27 +1240,27 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>山本 幸子</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>有田 智一</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>牛島 光一</t>
-        </is>
-      </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>藤井 さやか</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="H18" t="n">
+        <v>0.8641208410263062</v>
+      </c>
+      <c r="I18" t="n">
         <v>0.8593732714653015</v>
       </c>
-      <c r="I18" t="n">
-        <v>0.854110985994339</v>
-      </c>
       <c r="J18" t="n">
-        <v>0.8515381217002869</v>
+        <v>0.8564125001430511</v>
       </c>
     </row>
     <row r="19">
@@ -1286,27 +1286,27 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t>山本 幸子</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>鈴木 勉</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
           <t>甲斐田 直子</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>松原 康介</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>藤井 さやか</t>
-        </is>
-      </c>
       <c r="H19" t="n">
-        <v>0.8502585589885712</v>
+        <v>0.8628750443458557</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8502442538738251</v>
+        <v>0.851309597492218</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8497434854507446</v>
+        <v>0.8502584993839264</v>
       </c>
     </row>
     <row r="20">
@@ -1332,27 +1332,27 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>小西 葉子</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>太田 充</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
           <t>牛島 光一</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>秋山 英三</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>澤 亮治</t>
-        </is>
-      </c>
       <c r="H20" t="n">
-        <v>0.860200434923172</v>
+        <v>0.8699538707733154</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8571360409259796</v>
+        <v>0.860990583896637</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8559625148773193</v>
+        <v>0.8602003753185272</v>
       </c>
     </row>
     <row r="21">
@@ -1424,27 +1424,27 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>有田 智一</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>堤 盛人</t>
+          <t>梅本 通孝</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>渡邉 俊</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0.8694944977760315</v>
+        <v>0.8780647218227386</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8677712976932526</v>
+        <v>0.8772540986537933</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8667417764663696</v>
+        <v>0.8761960864067078</v>
       </c>
     </row>
     <row r="23">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>村上 暁信</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -1490,7 +1490,7 @@
         <v>0.8633539974689484</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8604661822319031</v>
+        <v>0.862057626247406</v>
       </c>
     </row>
     <row r="24">
@@ -1516,27 +1516,27 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>川島 宏一</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t>有田 智一</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>村上 暁信</t>
-        </is>
-      </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>甲斐田 直子</t>
+          <t>梅本 通孝</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0.8740248084068298</v>
+        <v>0.8778388798236847</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8680716753005981</v>
+        <v>0.8740247189998627</v>
       </c>
       <c r="J24" t="n">
-        <v>0.8672411739826202</v>
+        <v>0.871728777885437</v>
       </c>
     </row>
     <row r="25">
@@ -1562,27 +1562,27 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>讃井 知</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>雨宮 護</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>甲斐田 直子</t>
-        </is>
-      </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>浦田 淳司</t>
+          <t>村上 暁信</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0.8576710522174835</v>
+        <v>0.8605780899524689</v>
       </c>
       <c r="I25" t="n">
-        <v>0.8573780655860901</v>
+        <v>0.8576710224151611</v>
       </c>
       <c r="J25" t="n">
-        <v>0.8569363653659821</v>
+        <v>0.8574916422367096</v>
       </c>
     </row>
     <row r="26">
@@ -1608,27 +1608,27 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>上市 秀雄</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t>佐野 幸恵</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>牛島 光一</t>
-        </is>
-      </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>イリチュ 美佳</t>
+          <t>小西 葉子</t>
         </is>
       </c>
       <c r="H26" t="n">
+        <v>0.8725011646747589</v>
+      </c>
+      <c r="I26" t="n">
         <v>0.8715297877788544</v>
       </c>
-      <c r="I26" t="n">
-        <v>0.8625889718532562</v>
-      </c>
       <c r="J26" t="n">
-        <v>0.861405223608017</v>
+        <v>0.863963395357132</v>
       </c>
     </row>
     <row r="27">
@@ -1654,27 +1654,27 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>鈴木 勉</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t>牛島 光一</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>和田 健太郎</t>
-        </is>
-      </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
+          <t>Tran Lam Anh Duong</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0.8697108030319214</v>
+        <v>0.878728061914444</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8689082562923431</v>
+        <v>0.8697109222412109</v>
       </c>
       <c r="J27" t="n">
-        <v>0.867827296257019</v>
+        <v>0.8690558075904846</v>
       </c>
     </row>
     <row r="28">
@@ -1700,27 +1700,27 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
+          <t>小西 葉子</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t>牛島 光一</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>秋山 英三</t>
-        </is>
-      </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>堤 盛人</t>
+          <t>原田 信行</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0.8614097535610199</v>
+        <v>0.8659414350986481</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8560521602630615</v>
+        <v>0.8614097833633423</v>
       </c>
       <c r="J28" t="n">
-        <v>0.8548654913902283</v>
+        <v>0.8572182357311249</v>
       </c>
     </row>
     <row r="29">
@@ -1751,22 +1751,22 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>堤 盛人</t>
+          <t>小西 葉子</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0.8861463367938995</v>
+        <v>0.8861464560031891</v>
       </c>
       <c r="I29" t="n">
-        <v>0.8699300587177277</v>
+        <v>0.8746454119682312</v>
       </c>
       <c r="J29" t="n">
-        <v>0.8695700168609619</v>
+        <v>0.8714252412319183</v>
       </c>
     </row>
     <row r="30">
@@ -1792,27 +1792,27 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
+          <t>山本 幸子</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>讃井 知</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
           <t>有田 智一</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>藤井 さやか</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>渡邉 俊</t>
-        </is>
-      </c>
       <c r="H30" t="n">
+        <v>0.8737453818321228</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.8686347007751465</v>
+      </c>
+      <c r="J30" t="n">
         <v>0.8675165772438049</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.8674237728118896</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.8648247718811035</v>
       </c>
     </row>
     <row r="31">
@@ -1838,27 +1838,27 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
+          <t>川島 宏一</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t>Phung-Duc Tuan</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>秋山 英三</t>
-        </is>
-      </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>浦田 淳司</t>
+          <t>讃井 知</t>
         </is>
       </c>
       <c r="H31" t="n">
+        <v>0.8504707813262939</v>
+      </c>
+      <c r="I31" t="n">
         <v>0.8496311902999878</v>
       </c>
-      <c r="I31" t="n">
-        <v>0.8476453721523285</v>
-      </c>
       <c r="J31" t="n">
-        <v>0.8473740816116333</v>
+        <v>0.8495571315288544</v>
       </c>
     </row>
     <row r="32">
@@ -1884,27 +1884,27 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
+          <t>讃井 知</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t>大西 正輝</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>秋山 英三</t>
-        </is>
-      </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="H32" t="n">
+        <v>0.8459480702877045</v>
+      </c>
+      <c r="I32" t="n">
         <v>0.8455413579940796</v>
       </c>
-      <c r="I32" t="n">
-        <v>0.8411490023136139</v>
-      </c>
       <c r="J32" t="n">
-        <v>0.8407794237136841</v>
+        <v>0.8438552021980286</v>
       </c>
     </row>
     <row r="33">
@@ -1947,7 +1947,7 @@
         <v>0.8735739290714264</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8708216845989227</v>
+        <v>0.8708217442035675</v>
       </c>
       <c r="J33" t="n">
         <v>0.8674927651882172</v>
@@ -1976,27 +1976,27 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
+          <t>鈴木 勉</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t>吉瀬 章子</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>Phung-Duc Tuan</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>岡本 直久</t>
-        </is>
-      </c>
       <c r="H34" t="n">
+        <v>0.8794162273406982</v>
+      </c>
+      <c r="I34" t="n">
         <v>0.8755110502243042</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>0.8711532652378082</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0.8682165145874023</v>
       </c>
     </row>
     <row r="35">
@@ -2022,27 +2022,27 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
+          <t>讃井 知</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>上市 秀雄</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
           <t>雨宮 護</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>佐野 幸恵</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>甲斐田 直子</t>
-        </is>
-      </c>
       <c r="H35" t="n">
-        <v>0.8445099592208862</v>
+        <v>0.8534248769283295</v>
       </c>
       <c r="I35" t="n">
-        <v>0.8402862548828125</v>
+        <v>0.8462548553943634</v>
       </c>
       <c r="J35" t="n">
-        <v>0.8385109901428223</v>
+        <v>0.8445098996162415</v>
       </c>
     </row>
     <row r="36">
@@ -2068,27 +2068,27 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>黒瀬 雄大</t>
+          <t>梅本 通孝</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
+          <t>小西 葉子</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>0.8662265539169312</v>
+        <v>0.8738100826740265</v>
       </c>
       <c r="I36" t="n">
-        <v>0.8639206290245056</v>
+        <v>0.8697247207164764</v>
       </c>
       <c r="J36" t="n">
-        <v>0.8613840043544769</v>
+        <v>0.8684316277503967</v>
       </c>
     </row>
     <row r="37">
@@ -2114,27 +2114,27 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
+          <t>Liu Tianxiang</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t>八森 正泰</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>吉瀬 章子</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Phung-Duc Tuan</t>
-        </is>
-      </c>
       <c r="H37" t="n">
+        <v>0.8708595633506775</v>
+      </c>
+      <c r="I37" t="n">
         <v>0.8647412657737732</v>
       </c>
-      <c r="I37" t="n">
-        <v>0.860410749912262</v>
-      </c>
       <c r="J37" t="n">
-        <v>0.8583733439445496</v>
+        <v>0.8604106307029724</v>
       </c>
     </row>
     <row r="38">
@@ -2165,22 +2165,22 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>浦田 淳司</t>
+          <t>讃井 知</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>雨宮 護</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>0.8495572209358215</v>
+        <v>0.8495572507381439</v>
       </c>
       <c r="I38" t="n">
-        <v>0.843469649553299</v>
+        <v>0.8459268510341644</v>
       </c>
       <c r="J38" t="n">
-        <v>0.8432528376579285</v>
+        <v>0.8455456495285034</v>
       </c>
     </row>
     <row r="39">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>堤 盛人</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>0.8758090436458588</v>
+        <v>0.8758089542388916</v>
       </c>
       <c r="I39" t="n">
-        <v>0.8726611733436584</v>
+        <v>0.8726612329483032</v>
       </c>
       <c r="J39" t="n">
-        <v>0.8652368485927582</v>
+        <v>0.8673579692840576</v>
       </c>
     </row>
     <row r="40">
@@ -2252,27 +2252,27 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
+          <t>山本 幸子</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t>有田 智一</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>松原 康介</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>藤井 さやか</t>
-        </is>
-      </c>
       <c r="H40" t="n">
-        <v>0.8562148213386536</v>
+        <v>0.8725372850894928</v>
       </c>
       <c r="I40" t="n">
+        <v>0.8562148809432983</v>
+      </c>
+      <c r="J40" t="n">
         <v>0.8561661243438721</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0.8556602001190186</v>
       </c>
     </row>
     <row r="41">
@@ -2298,27 +2298,27 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
+          <t>讃井 知</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>鈴木 勉</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
           <t>渡邉 俊</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>雨宮 護</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>牛島 光一</t>
-        </is>
-      </c>
       <c r="H41" t="n">
-        <v>0.8744291663169861</v>
+        <v>0.8807381987571716</v>
       </c>
       <c r="I41" t="n">
-        <v>0.8729338943958282</v>
+        <v>0.8756650686264038</v>
       </c>
       <c r="J41" t="n">
-        <v>0.8692703545093536</v>
+        <v>0.8744292855262756</v>
       </c>
     </row>
     <row r="42">
@@ -2361,10 +2361,10 @@
         <v>0.8656891882419586</v>
       </c>
       <c r="I42" t="n">
-        <v>0.8504304587841034</v>
+        <v>0.8504304885864258</v>
       </c>
       <c r="J42" t="n">
-        <v>0.8490769863128662</v>
+        <v>0.849077045917511</v>
       </c>
     </row>
     <row r="43">
@@ -2390,27 +2390,27 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
+          <t>上市 秀雄</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t>佐野 幸恵</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>繁野 麻衣子</t>
-        </is>
-      </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>秋山 英三</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="H43" t="n">
+        <v>0.8466545641422272</v>
+      </c>
+      <c r="I43" t="n">
         <v>0.8459293246269226</v>
       </c>
-      <c r="I43" t="n">
-        <v>0.8408311605453491</v>
-      </c>
       <c r="J43" t="n">
-        <v>0.8378401696681976</v>
+        <v>0.844031423330307</v>
       </c>
     </row>
     <row r="44">
@@ -2436,27 +2436,27 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
+          <t>讃井 知</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>山本 幸子</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
           <t>牛島 光一</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>甲斐田 直子</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>堤 盛人</t>
-        </is>
-      </c>
       <c r="H44" t="n">
+        <v>0.8725491166114807</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.8676817417144775</v>
+      </c>
+      <c r="J44" t="n">
         <v>0.8616174161434174</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0.860570102930069</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0.858036994934082</v>
       </c>
     </row>
     <row r="45">
@@ -2482,27 +2482,27 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
+          <t>山本 幸子</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t>松原 康介</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>藤川 昌樹</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>有田 智一</t>
-        </is>
-      </c>
       <c r="H45" t="n">
+        <v>0.8705042600631714</v>
+      </c>
+      <c r="I45" t="n">
         <v>0.861813485622406</v>
       </c>
-      <c r="I45" t="n">
+      <c r="J45" t="n">
         <v>0.8590433597564697</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0.8576594591140747</v>
       </c>
     </row>
     <row r="46">
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>0.8530412614345551</v>
+        <v>0.8530411720275879</v>
       </c>
       <c r="I46" t="n">
-        <v>0.8456086218357086</v>
+        <v>0.845608651638031</v>
       </c>
       <c r="J46" t="n">
         <v>0.843080073595047</v>
@@ -2620,27 +2620,27 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
+          <t>川島 宏一</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
           <t>浦田 淳司</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>イリチュ 美佳</t>
-        </is>
-      </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
+          <t>髙橋 裕紀</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>0.8453716635704041</v>
+        <v>0.8463076949119568</v>
       </c>
       <c r="I48" t="n">
-        <v>0.844357967376709</v>
+        <v>0.8453716039657593</v>
       </c>
       <c r="J48" t="n">
-        <v>0.8441737592220306</v>
+        <v>0.8443977832794189</v>
       </c>
     </row>
     <row r="49">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
+          <t>繁野 麻衣子</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
           <t>吉瀬 章子</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>繁野 麻衣子</t>
-        </is>
-      </c>
       <c r="G49" t="inlineStr">
         <is>
           <t>八森 正泰</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0.8694933354854584</v>
+        <v>0.8708295226097107</v>
       </c>
       <c r="I49" t="n">
-        <v>0.8682685494422913</v>
+        <v>0.869493305683136</v>
       </c>
       <c r="J49" t="n">
         <v>0.8611498475074768</v>
@@ -2729,7 +2729,7 @@
         <v>0.878978818655014</v>
       </c>
       <c r="I50" t="n">
-        <v>0.8715093731880188</v>
+        <v>0.8715095520019531</v>
       </c>
       <c r="J50" t="n">
         <v>0.8685348629951477</v>
@@ -2758,27 +2758,27 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
+          <t>鈴木 勉</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
           <t>和田 健太郎</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>牛島 光一</t>
-        </is>
-      </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>浦田 淳司</t>
+          <t>谷口 綾子</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>0.8751050531864166</v>
+        <v>0.8764742910861969</v>
       </c>
       <c r="I51" t="n">
-        <v>0.8725587427616119</v>
+        <v>0.875105082988739</v>
       </c>
       <c r="J51" t="n">
-        <v>0.8720654249191284</v>
+        <v>0.8731650710105896</v>
       </c>
     </row>
     <row r="52">
@@ -2804,27 +2804,27 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
+          <t>上市 秀雄</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
           <t>イリチュ 美佳</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>佐野 幸恵</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>高野 祐一</t>
-        </is>
-      </c>
       <c r="H52" t="n">
+        <v>0.8628562092781067</v>
+      </c>
+      <c r="I52" t="n">
         <v>0.8604255318641663</v>
       </c>
-      <c r="I52" t="n">
+      <c r="J52" t="n">
         <v>0.8562762141227722</v>
-      </c>
-      <c r="J52" t="n">
-        <v>0.8557384312152863</v>
       </c>
     </row>
     <row r="53">
@@ -2855,22 +2855,22 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
+          <t>川島 宏一</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
           <t>浦田 淳司</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>イリチュ 美佳</t>
         </is>
       </c>
       <c r="H53" t="n">
         <v>0.8492535948753357</v>
       </c>
       <c r="I53" t="n">
+        <v>0.8484686315059662</v>
+      </c>
+      <c r="J53" t="n">
         <v>0.847988098859787</v>
-      </c>
-      <c r="J53" t="n">
-        <v>0.8451839983463287</v>
       </c>
     </row>
     <row r="54">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="H54" t="n">
@@ -2916,7 +2916,7 @@
         <v>0.8537877798080444</v>
       </c>
       <c r="J54" t="n">
-        <v>0.8456676602363586</v>
+        <v>0.8486493527889252</v>
       </c>
     </row>
     <row r="55">
@@ -2942,27 +2942,27 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
+          <t>川島 宏一</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>鈴木 勉</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
           <t>イリチュ 美佳</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>佐野 幸恵</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>黒瀬 雄大</t>
-        </is>
-      </c>
       <c r="H55" t="n">
+        <v>0.8511146903038025</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.8506214320659637</v>
+      </c>
+      <c r="J55" t="n">
         <v>0.8501562178134918</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0.8466014564037323</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0.8440068364143372</v>
       </c>
     </row>
     <row r="56">
@@ -2988,27 +2988,27 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
+          <t>小西 葉子</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>三崎 広海</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
           <t>有田 智一</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>岡田 幸彦</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>牛島 光一</t>
-        </is>
-      </c>
       <c r="H56" t="n">
+        <v>0.8653828203678131</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.8632269501686096</v>
+      </c>
+      <c r="J56" t="n">
         <v>0.8617116212844849</v>
-      </c>
-      <c r="I56" t="n">
-        <v>0.8601812720298767</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0.8599629104137421</v>
       </c>
     </row>
     <row r="57">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>山本 幸子</t>
         </is>
       </c>
       <c r="H57" t="n">
@@ -3054,7 +3054,7 @@
         <v>0.8540288209915161</v>
       </c>
       <c r="J57" t="n">
-        <v>0.8462729454040527</v>
+        <v>0.8500931262969971</v>
       </c>
     </row>
     <row r="58">
@@ -3080,27 +3080,27 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
+          <t>川島 宏一</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>三崎 広海</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
           <t>浦田 淳司</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>黒瀬 雄大</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>繁野 麻衣子</t>
-        </is>
-      </c>
       <c r="H58" t="n">
-        <v>0.8468367457389832</v>
+        <v>0.8541621565818787</v>
       </c>
       <c r="I58" t="n">
-        <v>0.8459519445896149</v>
+        <v>0.8514554500579834</v>
       </c>
       <c r="J58" t="n">
-        <v>0.8450420796871185</v>
+        <v>0.8468368053436279</v>
       </c>
     </row>
     <row r="59">
@@ -3126,27 +3126,27 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
+          <t>大久保 正勝</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
           <t>佐野 幸恵</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>イリチュ 美佳</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>岡田 幸彦</t>
-        </is>
-      </c>
       <c r="H59" t="n">
+        <v>0.8487860858440399</v>
+      </c>
+      <c r="I59" t="n">
         <v>0.8485637009143829</v>
       </c>
-      <c r="I59" t="n">
+      <c r="J59" t="n">
         <v>0.8466636836528778</v>
-      </c>
-      <c r="J59" t="n">
-        <v>0.8420409262180328</v>
       </c>
     </row>
     <row r="60">
@@ -3192,7 +3192,7 @@
         <v>0.8626532554626465</v>
       </c>
       <c r="J60" t="n">
-        <v>0.8584358096122742</v>
+        <v>0.8617680072784424</v>
       </c>
     </row>
     <row r="61">
@@ -3218,27 +3218,27 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
+          <t>村上 暁信</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
           <t>甲斐田 直子</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>村上 暁信</t>
-        </is>
-      </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>0.8657461404800415</v>
+        <v>0.8661297261714935</v>
       </c>
       <c r="I61" t="n">
-        <v>0.8657316565513611</v>
+        <v>0.8657460808753967</v>
       </c>
       <c r="J61" t="n">
-        <v>0.8604395687580109</v>
+        <v>0.8615502119064331</v>
       </c>
     </row>
     <row r="62">
@@ -3281,7 +3281,7 @@
         <v>0.8874904811382294</v>
       </c>
       <c r="I62" t="n">
-        <v>0.8681735992431641</v>
+        <v>0.8681735396385193</v>
       </c>
       <c r="J62" t="n">
         <v>0.8610672652721405</v>
@@ -3320,17 +3320,17 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>甲斐田 直子</t>
+          <t>太田 充</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>0.8482207059860229</v>
+        <v>0.8481179475784302</v>
       </c>
       <c r="I63" t="n">
         <v>0.8416444659233093</v>
       </c>
       <c r="J63" t="n">
-        <v>0.8346581757068634</v>
+        <v>0.8387836515903473</v>
       </c>
     </row>
     <row r="64">
@@ -3361,22 +3361,22 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
+          <t>繁野 麻衣子</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
           <t>Phung-Duc Tuan</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>吉瀬 章子</t>
         </is>
       </c>
       <c r="H64" t="n">
         <v>0.8797739744186401</v>
       </c>
       <c r="I64" t="n">
+        <v>0.8668175041675568</v>
+      </c>
+      <c r="J64" t="n">
         <v>0.8664391338825226</v>
-      </c>
-      <c r="J64" t="n">
-        <v>0.86557537317276</v>
       </c>
     </row>
     <row r="65">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>高野 祐一</t>
+          <t>上市 秀雄</t>
         </is>
       </c>
       <c r="H65" t="n">
@@ -3422,7 +3422,7 @@
         <v>0.8587773442268372</v>
       </c>
       <c r="J65" t="n">
-        <v>0.8530013859272003</v>
+        <v>0.8559300303459167</v>
       </c>
     </row>
     <row r="66">
@@ -3448,27 +3448,27 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
+          <t>鈴木 勉</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
           <t>牛島 光一</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>堤 盛人</t>
-        </is>
-      </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>和田 健太郎</t>
+          <t>谷口 綾子</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>0.8833464980125427</v>
+        <v>0.8854454457759857</v>
       </c>
       <c r="I66" t="n">
-        <v>0.8777274489402771</v>
+        <v>0.8833464384078979</v>
       </c>
       <c r="J66" t="n">
-        <v>0.8760351538658142</v>
+        <v>0.8789985179901123</v>
       </c>
     </row>
     <row r="67">
@@ -3499,22 +3499,22 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>甲斐田 直子</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
+          <t>大久保 正勝</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>0.8467667102813721</v>
+        <v>0.8467666506767273</v>
       </c>
       <c r="I67" t="n">
-        <v>0.8428299427032471</v>
+        <v>0.8456202745437622</v>
       </c>
       <c r="J67" t="n">
-        <v>0.842542827129364</v>
+        <v>0.8442078828811646</v>
       </c>
     </row>
     <row r="68">
@@ -3550,17 +3550,17 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>0.8728137910366058</v>
+        <v>0.8728138208389282</v>
       </c>
       <c r="I68" t="n">
         <v>0.8711625635623932</v>
       </c>
       <c r="J68" t="n">
-        <v>0.8687836229801178</v>
+        <v>0.8694121241569519</v>
       </c>
     </row>
     <row r="69">
@@ -3586,27 +3586,27 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
+          <t>川島 宏一</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
           <t>岡田 幸彦</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>浦田 淳司</t>
-        </is>
-      </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>髙橋 裕紀</t>
         </is>
       </c>
       <c r="H69" t="n">
+        <v>0.8480951189994812</v>
+      </c>
+      <c r="I69" t="n">
         <v>0.8476590812206268</v>
       </c>
-      <c r="I69" t="n">
-        <v>0.843207448720932</v>
-      </c>
       <c r="J69" t="n">
-        <v>0.8403257727622986</v>
+        <v>0.8465596437454224</v>
       </c>
     </row>
     <row r="70">
@@ -3637,22 +3637,22 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>村上 暁信</t>
+          <t>太田 充</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>岡本 直久</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>0.8448812961578369</v>
+        <v>0.8448813259601593</v>
       </c>
       <c r="I70" t="n">
-        <v>0.8382628560066223</v>
+        <v>0.841762363910675</v>
       </c>
       <c r="J70" t="n">
-        <v>0.8380181491374969</v>
+        <v>0.8410535156726837</v>
       </c>
     </row>
     <row r="71">
@@ -3678,27 +3678,27 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
+          <t>山本 幸子</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>川島 宏一</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
           <t>有田 智一</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>松原 康介</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>牛島 光一</t>
-        </is>
-      </c>
       <c r="H71" t="n">
-        <v>0.8568777740001678</v>
+        <v>0.8706452250480652</v>
       </c>
       <c r="I71" t="n">
-        <v>0.8562575578689575</v>
+        <v>0.8576701581478119</v>
       </c>
       <c r="J71" t="n">
-        <v>0.8555001616477966</v>
+        <v>0.8568777441978455</v>
       </c>
     </row>
     <row r="72">
@@ -3729,22 +3729,22 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
+          <t>讃井 知</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
           <t>澤 亮治</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>岡田 幸彦</t>
-        </is>
-      </c>
       <c r="H72" t="n">
-        <v>0.8674947023391724</v>
+        <v>0.8674946129322052</v>
       </c>
       <c r="I72" t="n">
-        <v>0.8628239333629608</v>
+        <v>0.865528404712677</v>
       </c>
       <c r="J72" t="n">
-        <v>0.8584659695625305</v>
+        <v>0.8628238141536713</v>
       </c>
     </row>
     <row r="73">
@@ -3770,27 +3770,27 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
+          <t>川島 宏一</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
           <t>Phung-Duc Tuan</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>吉瀬 章子</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>澤 亮治</t>
-        </is>
-      </c>
       <c r="H73" t="n">
+        <v>0.8715511560440063</v>
+      </c>
+      <c r="I73" t="n">
         <v>0.8690094351768494</v>
       </c>
-      <c r="I73" t="n">
-        <v>0.8687985241413116</v>
-      </c>
       <c r="J73" t="n">
-        <v>0.862273633480072</v>
+        <v>0.868798553943634</v>
       </c>
     </row>
     <row r="74">
@@ -3821,22 +3821,22 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
+          <t>Liu Tianxiang</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
           <t>Phung-Duc Tuan</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>吉瀬 章子</t>
-        </is>
-      </c>
       <c r="H74" t="n">
-        <v>0.8634209930896759</v>
+        <v>0.8634209036827087</v>
       </c>
       <c r="I74" t="n">
-        <v>0.8594034314155579</v>
+        <v>0.8619250357151031</v>
       </c>
       <c r="J74" t="n">
-        <v>0.8593776822090149</v>
+        <v>0.859403520822525</v>
       </c>
     </row>
     <row r="75">
@@ -3867,22 +3867,22 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
+          <t>山本 幸子</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
           <t>藤川 昌樹</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>有田 智一</t>
-        </is>
-      </c>
       <c r="H75" t="n">
-        <v>0.8413383066654205</v>
+        <v>0.8413381576538086</v>
       </c>
       <c r="I75" t="n">
-        <v>0.8376224637031555</v>
+        <v>0.8388773202896118</v>
       </c>
       <c r="J75" t="n">
-        <v>0.8287526071071625</v>
+        <v>0.8376223742961884</v>
       </c>
     </row>
     <row r="76">
@@ -3908,27 +3908,27 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
+          <t>讃井 知</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>山本 幸子</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
           <t>雨宮 護</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>佐野 幸恵</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>甲斐田 直子</t>
-        </is>
-      </c>
       <c r="H76" t="n">
+        <v>0.8615443408489227</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.8565350770950317</v>
+      </c>
+      <c r="J76" t="n">
         <v>0.8549287021160126</v>
-      </c>
-      <c r="I76" t="n">
-        <v>0.8530536293983459</v>
-      </c>
-      <c r="J76" t="n">
-        <v>0.851565808057785</v>
       </c>
     </row>
     <row r="77">
@@ -3964,7 +3964,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>繁野 麻衣子</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="H77" t="n">
@@ -3974,7 +3974,7 @@
         <v>0.8472535610198975</v>
       </c>
       <c r="J77" t="n">
-        <v>0.843280017375946</v>
+        <v>0.8447800874710083</v>
       </c>
     </row>
     <row r="78">
@@ -4000,27 +4000,27 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
+          <t>讃井 知</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
           <t>石井 儀光</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>佐野 幸恵</t>
-        </is>
-      </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>澤 亮治</t>
+          <t>中川 敏正</t>
         </is>
       </c>
       <c r="H78" t="n">
+        <v>0.8150632083415985</v>
+      </c>
+      <c r="I78" t="n">
         <v>0.8125244677066803</v>
       </c>
-      <c r="I78" t="n">
-        <v>0.8095496296882629</v>
-      </c>
       <c r="J78" t="n">
-        <v>0.8084699511528015</v>
+        <v>0.8125244677066803</v>
       </c>
     </row>
     <row r="79">
@@ -4051,22 +4051,22 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
+          <t>讃井 知</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
           <t>浦田 淳司</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>村上 暁信</t>
         </is>
       </c>
       <c r="H79" t="n">
         <v>0.8340822756290436</v>
       </c>
       <c r="I79" t="n">
-        <v>0.8263863027095795</v>
+        <v>0.8291231095790863</v>
       </c>
       <c r="J79" t="n">
-        <v>0.8235066533088684</v>
+        <v>0.8263862431049347</v>
       </c>
     </row>
     <row r="80">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>渡邉 俊</t>
+          <t>太田 充</t>
         </is>
       </c>
       <c r="H80" t="n">
@@ -4112,7 +4112,7 @@
         <v>0.8746379911899567</v>
       </c>
       <c r="J80" t="n">
-        <v>0.8685058951377869</v>
+        <v>0.8696686625480652</v>
       </c>
     </row>
     <row r="81">
@@ -4138,27 +4138,27 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
+          <t>讃井 知</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
           <t>作道 真理</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>甲斐田 直子</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>奥島 真一郎</t>
-        </is>
-      </c>
       <c r="H81" t="n">
-        <v>0.8292419016361237</v>
+        <v>0.8296013176441193</v>
       </c>
       <c r="I81" t="n">
-        <v>0.8284184038639069</v>
+        <v>0.8292419612407684</v>
       </c>
       <c r="J81" t="n">
-        <v>0.8275057971477509</v>
+        <v>0.8284183442592621</v>
       </c>
     </row>
     <row r="82">
@@ -4184,27 +4184,27 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
+          <t>讃井 知</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
           <t>高野 祐一</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>作道 真理</t>
-        </is>
-      </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>秋山 英三</t>
+          <t>村上 暁信</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>0.8292145431041718</v>
+        <v>0.8296073079109192</v>
       </c>
       <c r="I82" t="n">
-        <v>0.8283562064170837</v>
+        <v>0.8292145133018494</v>
       </c>
       <c r="J82" t="n">
-        <v>0.828016072511673</v>
+        <v>0.8284111022949219</v>
       </c>
     </row>
     <row r="83">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>佐野 幸恵</t>
+          <t>中川 敏正</t>
         </is>
       </c>
       <c r="H83" t="n">
@@ -4250,7 +4250,7 @@
         <v>0.8128287494182587</v>
       </c>
       <c r="J83" t="n">
-        <v>0.8083365261554718</v>
+        <v>0.8128287494182587</v>
       </c>
     </row>
     <row r="84">
@@ -4281,22 +4281,22 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
+          <t>讃井 知</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
           <t>作道 真理</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>秋山 英三</t>
-        </is>
-      </c>
       <c r="H84" t="n">
-        <v>0.8309313058853149</v>
+        <v>0.8309312164783478</v>
       </c>
       <c r="I84" t="n">
-        <v>0.829272985458374</v>
+        <v>0.82930788397789</v>
       </c>
       <c r="J84" t="n">
-        <v>0.8282457590103149</v>
+        <v>0.8292732536792755</v>
       </c>
     </row>
     <row r="85">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>村上 暁信</t>
+          <t>讃井 知</t>
         </is>
       </c>
       <c r="H85" t="n">
@@ -4342,7 +4342,7 @@
         <v>0.833859920501709</v>
       </c>
       <c r="J85" t="n">
-        <v>0.8314589262008667</v>
+        <v>0.833662748336792</v>
       </c>
     </row>
     <row r="86">
@@ -4368,27 +4368,27 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
+          <t>山本 幸子</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>讃井 知</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
           <t>有田 智一</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>藤井 さやか</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>堤 盛人</t>
-        </is>
-      </c>
       <c r="H86" t="n">
+        <v>0.8619189262390137</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0.8554736375808716</v>
+      </c>
+      <c r="J86" t="n">
         <v>0.8548861145973206</v>
-      </c>
-      <c r="I86" t="n">
-        <v>0.8524208664894104</v>
-      </c>
-      <c r="J86" t="n">
-        <v>0.8500982522964478</v>
       </c>
     </row>
   </sheetData>
@@ -4480,27 +4480,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>小西 葉子</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>岡田 幸彦</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>牛島 光一</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>岡本 直久</t>
-        </is>
-      </c>
       <c r="H2" t="n">
-        <v>0.8529865443706512</v>
+        <v>0.8615496456623077</v>
       </c>
       <c r="I2" t="n">
+        <v>0.8529865145683289</v>
+      </c>
+      <c r="J2" t="n">
         <v>0.8524920046329498</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.8522875905036926</v>
       </c>
     </row>
     <row r="3">
@@ -4531,22 +4531,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>小西 葉子</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>佐野 幸恵</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>牛島 光一</t>
         </is>
       </c>
       <c r="H3" t="n">
         <v>0.862902969121933</v>
       </c>
       <c r="I3" t="n">
+        <v>0.8564811944961548</v>
+      </c>
+      <c r="J3" t="n">
         <v>0.8502500653266907</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.8499161899089813</v>
       </c>
     </row>
     <row r="4">
@@ -4577,22 +4577,22 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>鈴木 勉</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>有馬 澄佳</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>雨宮 護</t>
         </is>
       </c>
       <c r="H4" t="n">
         <v>0.8726406097412109</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8699901401996613</v>
+        <v>0.8723746240139008</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8658290803432465</v>
+        <v>0.8699900805950165</v>
       </c>
     </row>
     <row r="5">
@@ -4618,27 +4618,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>讃井 知</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>上市 秀雄</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>秋山 英三</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>岡田 幸彦</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>佐野 幸恵</t>
-        </is>
-      </c>
       <c r="H5" t="n">
-        <v>0.8653525710105896</v>
+        <v>0.8725572526454926</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8646489977836609</v>
+        <v>0.8681508600711823</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8614354729652405</v>
+        <v>0.8653525114059448</v>
       </c>
     </row>
     <row r="6">
@@ -4664,27 +4664,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>川島 宏一</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>イリチュ 美佳</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>佐野 幸恵</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>岡田 幸彦</t>
-        </is>
-      </c>
       <c r="H6" t="n">
+        <v>0.8685602843761444</v>
+      </c>
+      <c r="I6" t="n">
         <v>0.8665047883987427</v>
       </c>
-      <c r="I6" t="n">
-        <v>0.866301953792572</v>
-      </c>
       <c r="J6" t="n">
-        <v>0.8624062538146973</v>
+        <v>0.8663018941879272</v>
       </c>
     </row>
     <row r="7">
@@ -4710,27 +4710,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>川島 宏一</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>イリチュ 美佳</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>牛島 光一</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>岡田 幸彦</t>
+          <t>岡本 翔平</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.8773767352104187</v>
+        <v>0.8784606456756592</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8732210099697113</v>
+        <v>0.8773766160011292</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8727982044219971</v>
+        <v>0.8744111955165863</v>
       </c>
     </row>
     <row r="8">
@@ -4756,27 +4756,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>鈴木 勉</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>志田 洋平</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>堤 盛人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>雨宮 護</t>
-        </is>
-      </c>
       <c r="H8" t="n">
+        <v>0.8793413043022156</v>
+      </c>
+      <c r="I8" t="n">
         <v>0.8671495318412781</v>
       </c>
-      <c r="I8" t="n">
-        <v>0.8640704452991486</v>
-      </c>
       <c r="J8" t="n">
-        <v>0.86296147108078</v>
+        <v>0.8640706837177277</v>
       </c>
     </row>
     <row r="9">
@@ -4812,17 +4812,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>高野 祐一</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="H9" t="n">
         <v>0.8687701225280762</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8564662337303162</v>
+        <v>0.8564662933349609</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8542343378067017</v>
+        <v>0.8544216752052307</v>
       </c>
     </row>
     <row r="10">
@@ -4848,27 +4848,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>鈴木 勉</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>和田 健太郎</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>岡本 直久</t>
-        </is>
-      </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>有馬 澄佳</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="H10" t="n">
+        <v>0.8784121572971344</v>
+      </c>
+      <c r="I10" t="n">
         <v>0.8746394515037537</v>
       </c>
-      <c r="I10" t="n">
-        <v>0.86732417345047</v>
-      </c>
       <c r="J10" t="n">
-        <v>0.8670890927314758</v>
+        <v>0.8692610859870911</v>
       </c>
     </row>
     <row r="11">
@@ -4894,27 +4894,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>鈴木 勉</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>太田 充</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>渡邉 俊</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>有田 智一</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>堤 盛人</t>
-        </is>
-      </c>
       <c r="H11" t="n">
+        <v>0.8776608407497406</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.8772943019866943</v>
+      </c>
+      <c r="J11" t="n">
         <v>0.8761743009090424</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.8733631372451782</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.8709878623485565</v>
       </c>
     </row>
     <row r="12">
@@ -4940,27 +4940,27 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>讃井 知</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>鈴木 勉</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>雨宮 護</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>佐野 幸恵</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>甲斐田 直子</t>
-        </is>
-      </c>
       <c r="H12" t="n">
-        <v>0.857864648103714</v>
+        <v>0.8686253428459167</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8568483889102936</v>
+        <v>0.8617160320281982</v>
       </c>
       <c r="J12" t="n">
-        <v>0.855992317199707</v>
+        <v>0.8578645884990692</v>
       </c>
     </row>
     <row r="13">
@@ -4991,22 +4991,22 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>上市 秀雄</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>イリチュ 美佳</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>岡田 幸彦</t>
         </is>
       </c>
       <c r="H13" t="n">
         <v>0.881976842880249</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8615249693393707</v>
+        <v>0.8667441010475159</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8592317700386047</v>
+        <v>0.8615249991416931</v>
       </c>
     </row>
     <row r="14">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>吉瀬 章子</t>
+          <t>繁野 麻衣子</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -5052,7 +5052,7 @@
         <v>0.8659283518791199</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8630378246307373</v>
+        <v>0.8646276593208313</v>
       </c>
     </row>
     <row r="15">
@@ -5078,27 +5078,27 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>小西 葉子</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>黒瀬 雄大</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Phung-Duc Tuan</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>有馬 澄佳</t>
-        </is>
-      </c>
       <c r="H15" t="n">
+        <v>0.8653980195522308</v>
+      </c>
+      <c r="I15" t="n">
         <v>0.8549571931362152</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>0.8538030087947845</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.8522914052009583</v>
       </c>
     </row>
     <row r="16">
@@ -5124,27 +5124,27 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>岡田 幸彦</t>
+          <t>上市 秀雄</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>甲斐田 直子</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>澤 亮治</t>
+          <t>讃井 知</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0.8545616865158081</v>
+        <v>0.8583923876285553</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8534988462924957</v>
+        <v>0.8568210899829865</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8495171368122101</v>
+        <v>0.8549480438232422</v>
       </c>
     </row>
     <row r="17">
@@ -5170,27 +5170,27 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>三崎 広海</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>小西 葉子</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
           <t>黒瀬 雄大</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>高野 祐一</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>岡田 幸彦</t>
-        </is>
-      </c>
       <c r="H17" t="n">
+        <v>0.8657762110233307</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.8645855784416199</v>
+      </c>
+      <c r="J17" t="n">
         <v>0.8605440855026245</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.8589096367359161</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.8580231368541718</v>
       </c>
     </row>
     <row r="18">
@@ -5221,22 +5221,22 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>牛島 光一</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>黒瀬 雄大</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0.8643297851085663</v>
+        <v>0.8643296360969543</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8594227731227875</v>
+        <v>0.862494558095932</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8584847748279572</v>
+        <v>0.8621526956558228</v>
       </c>
     </row>
     <row r="19">
@@ -5267,22 +5267,22 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>鈴木 勉</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
           <t>和田 健太郎</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>岡本 直久</t>
-        </is>
-      </c>
       <c r="H19" t="n">
-        <v>0.8965594172477722</v>
+        <v>0.8965592980384827</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8676624298095703</v>
+        <v>0.8704787790775299</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8609089851379395</v>
+        <v>0.8676625490188599</v>
       </c>
     </row>
     <row r="20">
@@ -5308,27 +5308,27 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>鈴木 勉</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>志田 洋平</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>渡邉 俊</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>黒瀬 雄大</t>
-        </is>
-      </c>
       <c r="H20" t="n">
+        <v>0.8876860439777374</v>
+      </c>
+      <c r="I20" t="n">
         <v>0.8774204552173615</v>
       </c>
-      <c r="I20" t="n">
-        <v>0.8773219287395477</v>
-      </c>
       <c r="J20" t="n">
-        <v>0.8723052740097046</v>
+        <v>0.8773219585418701</v>
       </c>
     </row>
     <row r="21">
@@ -5354,27 +5354,27 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>小西 葉子</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>高野 祐一</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>志田 洋平</t>
-        </is>
-      </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>有馬 澄佳</t>
+          <t>鈴木 勉</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.8667503893375397</v>
+        <v>0.8698301017284393</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8609131574630737</v>
+        <v>0.8667502701282501</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8609002530574799</v>
+        <v>0.862951934337616</v>
       </c>
     </row>
     <row r="22">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>岡田 幸彦</t>
+          <t>川島 宏一</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -5466,7 +5466,7 @@
         <v>0.845047265291214</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8442730903625488</v>
+        <v>0.8445885181427002</v>
       </c>
     </row>
   </sheetData>
